--- a/data/common_project_data/indicators-master.xlsx
+++ b/data/common_project_data/indicators-master.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steve.crawshaw\projects\weca_regional_indicators\data\common_project_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{37258450-FA34-4C70-9C3A-AAC96A6AD7C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{ADA1BA97-1CA3-4E67-A8A5-B4476BB5E3AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="16440" windowHeight="29040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="10690" windowWidth="19420" windowHeight="11020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="fact_indicator_observation" sheetId="3" r:id="rId1"/>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1603" uniqueCount="838">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1622" uniqueCount="852">
   <si>
     <t>Unique ID</t>
   </si>
@@ -393,9 +393,6 @@
   </si>
   <si>
     <t>Real GDP growth rate</t>
-  </si>
-  <si>
-    <t>Percentage</t>
   </si>
   <si>
     <t>ONS GDP</t>
@@ -480,9 +477,6 @@
     <t>1.D.1</t>
   </si>
   <si>
-    <t>Mbps coverage in the region</t>
-  </si>
-  <si>
     <t>Total premises</t>
   </si>
   <si>
@@ -636,16 +630,7 @@
     <t>Bus and rail trips</t>
   </si>
   <si>
-    <t>Trips and trips per head</t>
-  </si>
-  <si>
     <t>Total trips</t>
-  </si>
-  <si>
-    <t>Population</t>
-  </si>
-  <si>
-    <t>WECA (bus), ORR (rail)</t>
   </si>
   <si>
     <t>Quarterly</t>
@@ -731,9 +716,6 @@
     <t>E-bike hire and E-scooter hire usage</t>
   </si>
   <si>
-    <t>Trips, Trips per head</t>
-  </si>
-  <si>
     <t>Total hire trips</t>
   </si>
   <si>
@@ -779,15 +761,6 @@
     <t>2.C.1</t>
   </si>
   <si>
-    <t>Public transport connectivity score to key services (to be defined)</t>
-  </si>
-  <si>
-    <t>Percentile/score</t>
-  </si>
-  <si>
-    <t>DfT / WECA Connectivity Model</t>
-  </si>
-  <si>
     <t>Line chart of score/percentile over time. Benchmark against national percentile. Choropleth map if spatial variation relevant.</t>
   </si>
   <si>
@@ -801,9 +774,6 @@
   </si>
   <si>
     <t>Proportion of population within (30) minutes of core employment zone by public transport or active travel</t>
-  </si>
-  <si>
-    <t>Population within 30 min</t>
   </si>
   <si>
     <t>WECA Connectivity Model</t>
@@ -972,12 +942,6 @@
     <t>3.A.3</t>
   </si>
   <si>
-    <t>Number and rate of non-decent homes</t>
-  </si>
-  <si>
-    <t>No. of dwellings and % of dwellings</t>
-  </si>
-  <si>
     <t>Non-decent homes</t>
   </si>
   <si>
@@ -1041,12 +1005,6 @@
     <t>3.C.1</t>
   </si>
   <si>
-    <t>[1] Net additional dwellings and [2] total new homes delivered … [1][2] as a % of existing total area stock</t>
-  </si>
-  <si>
-    <t>Dwellings and percentage</t>
-  </si>
-  <si>
     <t>Net additional dwellings</t>
   </si>
   <si>
@@ -1251,9 +1209,6 @@
     <t>4.A.2</t>
   </si>
   <si>
-    <t>Proportion of residents (aged 16-64) with Level 4 or above qualifications</t>
-  </si>
-  <si>
     <t>Residents with Level 4+</t>
   </si>
   <si>
@@ -1288,12 +1243,6 @@
   </si>
   <si>
     <t>4.A.4</t>
-  </si>
-  <si>
-    <t>Key Stage 4 attainment 8 data for all state funded schools, local authority maintained schools and academies</t>
-  </si>
-  <si>
-    <t>Score out of 100 (no unit)</t>
   </si>
   <si>
     <t>By FSM Eligible, Disadvantage Status</t>
@@ -1393,9 +1342,6 @@
     <t>4.B.5</t>
   </si>
   <si>
-    <t>Proportion of residents earning less than the Real Living Wage (as defined by the Living Wage Foundation)</t>
-  </si>
-  <si>
     <t>Residents earning &lt; Real Living Wage</t>
   </si>
   <si>
@@ -1457,9 +1403,6 @@
   </si>
   <si>
     <t>Making the West of England the home for green jobs and green growth</t>
-  </si>
-  <si>
-    <t>Regional GHG emissions from transport, domestic, commercial, industrial and public sectors</t>
   </si>
   <si>
     <t>Sum of regional greenhouse gas emissions (territorial) from transport, domestic, commercial, industrial and public sectors. The data are for a calendar year, normally released in July. Do not use quarterly updates.</t>
@@ -1499,9 +1442,6 @@
     <t>5.A.1</t>
   </si>
   <si>
-    <t>Renewable energy capacity per km sq</t>
-  </si>
-  <si>
     <t>the sum of total MW of installed capacity for each UA divided by the area of the MCA (LEP) in square Km using the boundary polygon lep_bdy_diss_poly on the corporate POSTGIS database.</t>
   </si>
   <si>
@@ -1532,15 +1472,9 @@
     <t>5.A.2</t>
   </si>
   <si>
-    <t>Domestically generated renewable energy</t>
-  </si>
-  <si>
     <t>The sum of the number of PV sites for WECA LEP Uas divided by the sum of households in the same Uas. Both values are in the spreadsheet data source.</t>
   </si>
   <si>
-    <t>Number of sites per household for photovoltaics</t>
-  </si>
-  <si>
     <t>PV sites</t>
   </si>
   <si>
@@ -1646,9 +1580,6 @@
     <t>5.E.2</t>
   </si>
   <si>
-    <t>Flood Warnings Intensity Indicator</t>
-  </si>
-  <si>
     <t>Run the pipeline in the github repo https://github.com/stevecrawshaw/fwii/blob/main/SUMMARY.md to generate the composite indicator. This is a weighted indicator of fluvial and coastal flood warning data relative to 2020. So if the indicator was 100 it would be the same as 2020. Full description is given in the repo.</t>
   </si>
   <si>
@@ -1754,9 +1685,6 @@
     <t>5.F.4</t>
   </si>
   <si>
-    <t>Health of water catchments</t>
-  </si>
-  <si>
     <t>The percentage of watercourses in good ecological health category for the Bristol Avon and North Somerset Streams catchment. It will be necessary to look at the historic classifications spreadsheet as the most recent data is not always available on the website.</t>
   </si>
   <si>
@@ -1805,9 +1733,6 @@
     <t>6.A.1</t>
   </si>
   <si>
-    <t>Child poverty – relative income after housing costs / Children in low income families</t>
-  </si>
-  <si>
     <t>Children in low income families (AHC)</t>
   </si>
   <si>
@@ -2004,9 +1929,6 @@
   </si>
   <si>
     <t>6.D.4</t>
-  </si>
-  <si>
-    <t>Child health: Percentage achieving good level of development at 2-2.5 year review</t>
   </si>
   <si>
     <t>Children achieving good development at 2-2.5yr review</t>
@@ -2576,12 +2498,6 @@
     <t>% of trips per person per year travelled by active travel and public transport</t>
   </si>
   <si>
-    <t>Average trips per person per year travelled by active travel and public transport</t>
-  </si>
-  <si>
-    <t>Average trips per person per year by all modes</t>
-  </si>
-  <si>
     <t>NTS0303aTrips_CA</t>
   </si>
   <si>
@@ -2591,9 +2507,6 @@
     <t>May to August (tbc)</t>
   </si>
   <si>
-    <t>Previous Years; Other Cas</t>
-  </si>
-  <si>
     <t>less than 45% of commuters travel by 2030 (excluding WfH)</t>
   </si>
   <si>
@@ -2601,6 +2514,135 @@
   </si>
   <si>
     <t>purpose, mode</t>
+  </si>
+  <si>
+    <t>Installed renewable electricity capacity per km square</t>
+  </si>
+  <si>
+    <t>Regional greenhouse gas emissions</t>
+  </si>
+  <si>
+    <t>High speed broadband coverage in the region</t>
+  </si>
+  <si>
+    <t>Children in low income families</t>
+  </si>
+  <si>
+    <t>Educational attainment of children</t>
+  </si>
+  <si>
+    <t>Children achieving good level of development at 2-2.5 year review</t>
+  </si>
+  <si>
+    <t>Proportion of residents (aged 16-64) qualified beyond A level</t>
+  </si>
+  <si>
+    <t>Proportion of residents earning less than the Real Living Wage</t>
+  </si>
+  <si>
+    <t>Proportion of watercourses in good ecological health</t>
+  </si>
+  <si>
+    <t>Frequency and duration of flood warnings relative to 2020</t>
+  </si>
+  <si>
+    <t>Proportion of working-age residents qualified to Level 4 and above.</t>
+  </si>
+  <si>
+    <t>Domestically generated renewable electricity</t>
+  </si>
+  <si>
+    <t>Sites per household for solar PV</t>
+  </si>
+  <si>
+    <t>Score</t>
+  </si>
+  <si>
+    <t>Order within Priority</t>
+  </si>
+  <si>
+    <t>order_within_priority</t>
+  </si>
+  <si>
+    <t>Annual net increase in the number of dwellings</t>
+  </si>
+  <si>
+    <t>Proportion of non - decent homes</t>
+  </si>
+  <si>
+    <t>Number of dwellings</t>
+  </si>
+  <si>
+    <t>Number of public transport (bus and rail) trips per person</t>
+  </si>
+  <si>
+    <t>% satisfied with bus journey</t>
+  </si>
+  <si>
+    <t>% of adults or walk/cycle for travel purposes at least twice in the past 28 days</t>
+  </si>
+  <si>
+    <t>Number of ebike and e-scooter trips per year</t>
+  </si>
+  <si>
+    <t>Connectivity score by public transport to reach all amenities</t>
+  </si>
+  <si>
+    <t>% of population within 30 minutes of employment zone (5000+) by public transport or active travel</t>
+  </si>
+  <si>
+    <t>% of bus passengers satisfied with value for money for their journey</t>
+  </si>
+  <si>
+    <t>Public transport connectivity score to key services (education, employment, health, retail)</t>
+  </si>
+  <si>
+    <t>Average % of survey respondents satisfied with walking and cycling provision</t>
+  </si>
+  <si>
+    <t>Trips</t>
+  </si>
+  <si>
+    <t>Average trips per person travelled by active travel and public transport</t>
+  </si>
+  <si>
+    <t>Average trips per person by all modes</t>
+  </si>
+  <si>
+    <t>Satisfied people</t>
+  </si>
+  <si>
+    <t>Score based on journey times to amenities</t>
+  </si>
+  <si>
+    <t>Population within 30 minutes</t>
+  </si>
+  <si>
+    <t>All bus passengers</t>
+  </si>
+  <si>
+    <t>All people (all survey respondents)</t>
+  </si>
+  <si>
+    <t>DfT (bus), ORR (rail)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://assets.publishing.service.gov.uk/media/69c11f97cfa346b9d4704a50/bus01.ods;  https://dataportal.orr.gov.uk/media/1908/table-1415-time-series-of-passenger-entries-and-exits-and-interchanges-by-station.ods </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bus01e; Table 1415</t>
+  </si>
+  <si>
+    <t>2024/5</t>
+  </si>
+  <si>
+    <t>Nov/Dec</t>
+  </si>
+  <si>
+    <t>Previous Years</t>
+  </si>
+  <si>
+    <t>Trips per person</t>
   </si>
 </sst>
 </file>
@@ -2820,7 +2862,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2885,6 +2927,13 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="12" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Bad" xfId="3" builtinId="27"/>
@@ -2893,7 +2942,7 @@
     <cellStyle name="Neutral" xfId="4" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="19">
+  <dxfs count="22">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -3056,6 +3105,39 @@
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
           <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3449,42 +3531,42 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>647</v>
+        <v>621</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>648</v>
+        <v>622</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>649</v>
+        <v>623</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>650</v>
+        <v>624</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>651</v>
+        <v>625</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>652</v>
+        <v>626</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
-        <v>653</v>
+        <v>627</v>
       </c>
       <c r="B2" s="16" t="s">
         <v>39</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>654</v>
+        <v>628</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>655</v>
+        <v>629</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>656</v>
+        <v>630</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>657</v>
+        <v>631</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -9497,50 +9579,51 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AP70"/>
+  <dimension ref="A1:AQ70"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="38" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38" style="1" customWidth="1"/>
     <col min="4" max="4" width="38.140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="31.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="38" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="26.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="31.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="32.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="29.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="106.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="21.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="26.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="23" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="29.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="16.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15" style="1" customWidth="1"/>
+    <col min="6" max="6" width="31.42578125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="38" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="26.42578125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="31.5703125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="32.42578125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="29.42578125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="19.42578125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="106.85546875" style="1" customWidth="1"/>
+    <col min="16" max="16" width="21.140625" style="1" customWidth="1"/>
+    <col min="17" max="17" width="26.140625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="10.5703125" style="1" customWidth="1"/>
+    <col min="19" max="20" width="23" style="1" customWidth="1"/>
+    <col min="21" max="21" width="12.42578125" style="1" customWidth="1"/>
+    <col min="22" max="22" width="29.85546875" style="1" customWidth="1"/>
+    <col min="23" max="23" width="15.140625" style="1" customWidth="1"/>
+    <col min="24" max="24" width="16.5703125" style="1" customWidth="1"/>
     <col min="25" max="25" width="35.42578125" style="1" customWidth="1"/>
-    <col min="26" max="27" width="23" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="33.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="16.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="23" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="28.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="20.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="16.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="26.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="27.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="23" style="1" customWidth="1"/>
+    <col min="28" max="28" width="33.85546875" style="1" customWidth="1"/>
+    <col min="29" max="29" width="16.5703125" style="1" customWidth="1"/>
+    <col min="30" max="30" width="23" style="1" customWidth="1"/>
+    <col min="31" max="31" width="28.42578125" style="1" customWidth="1"/>
+    <col min="32" max="32" width="8.5703125" style="1" customWidth="1"/>
+    <col min="33" max="33" width="20.85546875" style="1" customWidth="1"/>
+    <col min="34" max="34" width="16.5703125" style="1" customWidth="1"/>
+    <col min="35" max="35" width="26.140625" style="1" customWidth="1"/>
+    <col min="36" max="36" width="27.5703125" style="1" customWidth="1"/>
     <col min="37" max="37" width="22.85546875" style="1" customWidth="1"/>
     <col min="38" max="38" width="38.140625" style="1" customWidth="1"/>
-    <col min="39" max="39" width="18.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="16384" width="9.140625" style="1"/>
+    <col min="39" max="39" width="38.140625" style="7" customWidth="1"/>
+    <col min="40" max="40" width="18.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:43" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -9655,14 +9738,17 @@
       <c r="AL1" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="5" t="s">
+      <c r="AM1" s="28" t="s">
+        <v>823</v>
+      </c>
+      <c r="AN1" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="2"/>
-      <c r="AO1" s="3"/>
-      <c r="AP1" s="4"/>
-    </row>
-    <row r="2" spans="1:42" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO1" s="2"/>
+      <c r="AP1" s="3"/>
+      <c r="AQ1" s="4"/>
+    </row>
+    <row r="2" spans="1:43" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>39</v>
       </c>
@@ -9777,14 +9863,17 @@
       <c r="AL2" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="AM2" s="14" t="s">
+      <c r="AM2" s="29" t="s">
+        <v>824</v>
+      </c>
+      <c r="AN2" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="AN2" s="2"/>
-      <c r="AO2" s="3"/>
-      <c r="AP2" s="4"/>
-    </row>
-    <row r="3" spans="1:42" ht="105" x14ac:dyDescent="0.25">
+      <c r="AO2" s="2"/>
+      <c r="AP2" s="3"/>
+      <c r="AQ2" s="4"/>
+    </row>
+    <row r="3" spans="1:43" ht="105" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>78</v>
       </c>
@@ -9804,13 +9893,13 @@
         <v>83</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>793</v>
+        <v>767</v>
       </c>
       <c r="H3" s="1">
         <v>1</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>765</v>
+        <v>739</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>85</v>
@@ -9820,25 +9909,25 @@
       </c>
       <c r="L3" s="7"/>
       <c r="M3" s="1" t="s">
-        <v>766</v>
+        <v>740</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>767</v>
+        <v>741</v>
       </c>
       <c r="O3" s="13" t="s">
-        <v>768</v>
+        <v>742</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>770</v>
+        <v>744</v>
       </c>
       <c r="T3" s="25">
         <v>46133</v>
@@ -9847,19 +9936,19 @@
         <v>4</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>771</v>
+        <v>745</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>772</v>
+        <v>746</v>
       </c>
       <c r="Z3" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AA3" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="AB3" s="1" t="s">
-        <v>773</v>
+        <v>747</v>
       </c>
       <c r="AC3" s="1" t="s">
         <v>90</v>
@@ -9872,10 +9961,13 @@
         <v>92</v>
       </c>
       <c r="AL3" s="1" t="s">
-        <v>774</v>
-      </c>
-    </row>
-    <row r="4" spans="1:42" ht="60" x14ac:dyDescent="0.25">
+        <v>748</v>
+      </c>
+      <c r="AM3" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:43" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>93</v>
       </c>
@@ -9895,13 +9987,13 @@
         <v>95</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>792</v>
+        <v>766</v>
       </c>
       <c r="H4" s="1">
         <v>1</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>775</v>
+        <v>749</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>96</v>
@@ -9911,16 +10003,16 @@
         <v>87</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>777</v>
+        <v>751</v>
       </c>
       <c r="O4" s="13" t="s">
-        <v>776</v>
+        <v>750</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>778</v>
+        <v>752</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>488</v>
+        <v>466</v>
       </c>
       <c r="R4" s="1" t="s">
         <v>97</v>
@@ -9938,22 +10030,22 @@
         <v>99</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>779</v>
+        <v>753</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>786</v>
+        <v>760</v>
       </c>
       <c r="Y4" s="1" t="s">
-        <v>780</v>
+        <v>754</v>
       </c>
       <c r="Z4" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AA4" s="1" t="s">
-        <v>541</v>
+        <v>518</v>
       </c>
       <c r="AB4" s="1" t="s">
-        <v>781</v>
+        <v>755</v>
       </c>
       <c r="AC4" s="1" t="s">
         <v>90</v>
@@ -9965,8 +10057,11 @@
       <c r="AL4" s="1" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="5" spans="1:42" ht="105" x14ac:dyDescent="0.25">
+      <c r="AM4" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:43" ht="105" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>101</v>
       </c>
@@ -9986,34 +10081,34 @@
         <v>104</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>791</v>
+        <v>765</v>
       </c>
       <c r="H5" s="1">
         <v>1</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>782</v>
+        <v>756</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>783</v>
+        <v>757</v>
       </c>
       <c r="L5" s="7">
         <v>2020</v>
       </c>
       <c r="M5" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="O5" s="13" t="s">
+        <v>759</v>
+      </c>
+      <c r="P5" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="N5" s="1" t="s">
-        <v>784</v>
-      </c>
-      <c r="O5" s="13" t="s">
-        <v>785</v>
-      </c>
-      <c r="P5" s="1" t="s">
-        <v>107</v>
-      </c>
       <c r="Q5" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="R5" s="1" t="s">
         <v>97</v>
@@ -10022,28 +10117,28 @@
         <v>2023</v>
       </c>
       <c r="T5" s="26" t="s">
-        <v>799</v>
+        <v>773</v>
       </c>
       <c r="U5" s="1">
         <v>16</v>
       </c>
       <c r="W5" s="1" t="s">
-        <v>779</v>
+        <v>753</v>
       </c>
       <c r="X5" s="1" t="s">
-        <v>787</v>
+        <v>761</v>
       </c>
       <c r="Y5" s="1" t="s">
-        <v>788</v>
+        <v>762</v>
       </c>
       <c r="Z5" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AA5" s="1" t="s">
-        <v>541</v>
+        <v>518</v>
       </c>
       <c r="AB5" s="1" t="s">
-        <v>789</v>
+        <v>763</v>
       </c>
       <c r="AC5" s="1" t="s">
         <v>90</v>
@@ -10053,12 +10148,15 @@
       </c>
       <c r="AG5" s="8"/>
       <c r="AL5" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="AM5" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:43" ht="75" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
         <v>109</v>
-      </c>
-    </row>
-    <row r="6" spans="1:42" ht="75" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>110</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>79</v>
@@ -10070,41 +10168,41 @@
         <v>102</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>112</v>
-      </c>
       <c r="G6" s="1" t="s">
-        <v>790</v>
+        <v>764</v>
       </c>
       <c r="H6" s="1">
         <v>1</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>794</v>
+        <v>768</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>795</v>
+        <v>769</v>
       </c>
       <c r="L6" s="7"/>
       <c r="M6" s="1" t="s">
-        <v>796</v>
+        <v>770</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>797</v>
+        <v>771</v>
       </c>
       <c r="O6" s="13" t="s">
-        <v>798</v>
+        <v>772</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="R6" s="1" t="s">
         <v>97</v>
@@ -10113,25 +10211,25 @@
         <v>2023</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="U6" s="1">
         <v>18</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>779</v>
+        <v>753</v>
       </c>
       <c r="Y6" s="1" t="s">
-        <v>800</v>
+        <v>774</v>
       </c>
       <c r="Z6" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AA6" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="AB6" s="1" t="s">
-        <v>801</v>
+        <v>775</v>
       </c>
       <c r="AC6" s="1" t="s">
         <v>90</v>
@@ -10141,15 +10239,18 @@
       </c>
       <c r="AG6" s="8"/>
       <c r="AI6" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="AL6" s="1" t="s">
+        <v>776</v>
+      </c>
+      <c r="AM6" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:43" ht="90" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
         <v>115</v>
-      </c>
-      <c r="AL6" s="1" t="s">
-        <v>802</v>
-      </c>
-    </row>
-    <row r="7" spans="1:42" ht="90" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
-        <v>116</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>79</v>
@@ -10161,38 +10262,38 @@
         <v>102</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>804</v>
+        <v>778</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>805</v>
+        <v>779</v>
       </c>
       <c r="H7" s="1">
         <v>1</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>804</v>
+        <v>778</v>
       </c>
       <c r="L7" s="7"/>
       <c r="M7" s="1" t="s">
-        <v>806</v>
+        <v>780</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>807</v>
+        <v>781</v>
       </c>
       <c r="O7" s="13" t="s">
-        <v>808</v>
+        <v>782</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>803</v>
+        <v>777</v>
       </c>
       <c r="R7" s="1" t="s">
         <v>88</v>
@@ -10201,25 +10302,25 @@
         <v>46054</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="U7" s="1">
         <v>1</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>779</v>
+        <v>753</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>800</v>
+        <v>774</v>
       </c>
       <c r="Z7" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AA7" s="1" t="s">
-        <v>465</v>
+        <v>446</v>
       </c>
       <c r="AB7" s="1" t="s">
-        <v>809</v>
+        <v>783</v>
       </c>
       <c r="AC7" s="1" t="s">
         <v>90</v>
@@ -10232,12 +10333,15 @@
         <v>92</v>
       </c>
       <c r="AL7" s="1" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="8" spans="1:42" ht="90" x14ac:dyDescent="0.25">
+        <v>784</v>
+      </c>
+      <c r="AM7" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:43" ht="90" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>79</v>
@@ -10246,71 +10350,71 @@
         <v>80</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>123</v>
-      </c>
       <c r="G8" s="1" t="s">
-        <v>811</v>
+        <v>785</v>
       </c>
       <c r="H8" s="1">
         <v>1</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>105</v>
+        <v>739</v>
       </c>
       <c r="J8" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="K8" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>125</v>
       </c>
       <c r="L8" s="7"/>
       <c r="M8" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="O8" s="13" t="s">
-        <v>812</v>
+        <v>786</v>
       </c>
       <c r="P8" s="1" t="s">
         <v>38</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>803</v>
+        <v>777</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S8" s="1">
         <v>2022</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U8" s="1">
         <v>18</v>
       </c>
       <c r="W8" s="1" t="s">
-        <v>779</v>
+        <v>753</v>
       </c>
       <c r="Y8" s="1" t="s">
-        <v>813</v>
+        <v>787</v>
       </c>
       <c r="Z8" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AA8" s="1" t="s">
-        <v>541</v>
+        <v>518</v>
       </c>
       <c r="AB8" s="1" t="s">
-        <v>814</v>
+        <v>788</v>
       </c>
       <c r="AC8" s="1" t="s">
         <v>90</v>
@@ -10320,12 +10424,15 @@
       </c>
       <c r="AG8" s="8"/>
       <c r="AL8" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="AM8" s="7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:43" ht="135" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
         <v>129</v>
-      </c>
-    </row>
-    <row r="9" spans="1:42" ht="135" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
-        <v>130</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>79</v>
@@ -10334,47 +10441,47 @@
         <v>80</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>132</v>
-      </c>
       <c r="F9" s="1" t="s">
-        <v>133</v>
+        <v>811</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>822</v>
+        <v>796</v>
       </c>
       <c r="H9" s="1">
         <v>1</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>105</v>
+        <v>739</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>826</v>
+        <v>800</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L9" s="7"/>
       <c r="M9" s="1" t="s">
-        <v>825</v>
+        <v>799</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="R9" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="T9" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="T9" s="1" t="s">
-        <v>128</v>
       </c>
       <c r="U9" s="1">
         <v>5</v>
       </c>
       <c r="Y9" s="1" t="s">
-        <v>824</v>
+        <v>798</v>
       </c>
       <c r="Z9" s="1" t="s">
         <v>89</v>
@@ -10383,19 +10490,22 @@
         <v>90</v>
       </c>
       <c r="AF9" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AG9" s="8"/>
       <c r="AI9" s="1" t="s">
         <v>92</v>
       </c>
       <c r="AL9" s="1" t="s">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="10" spans="1:42" ht="90" x14ac:dyDescent="0.25">
+        <v>797</v>
+      </c>
+      <c r="AM9" s="7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:43" ht="90" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>79</v>
@@ -10404,62 +10514,62 @@
         <v>80</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>817</v>
+        <v>791</v>
       </c>
       <c r="H10" s="1">
         <v>1</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>775</v>
+        <v>749</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>818</v>
+        <v>792</v>
       </c>
       <c r="L10" s="7"/>
       <c r="M10" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>815</v>
+        <v>789</v>
       </c>
       <c r="O10" s="13" t="s">
-        <v>816</v>
+        <v>790</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>769</v>
+        <v>743</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>538</v>
+        <v>515</v>
       </c>
       <c r="S10" s="26">
         <v>46054</v>
       </c>
       <c r="T10" s="1" t="s">
-        <v>819</v>
+        <v>793</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>820</v>
+        <v>794</v>
       </c>
       <c r="W10" s="1" t="s">
-        <v>821</v>
+        <v>795</v>
       </c>
       <c r="Y10" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="Z10" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="AC10" s="1" t="s">
         <v>90</v>
@@ -10469,12 +10579,15 @@
       </c>
       <c r="AG10" s="8"/>
       <c r="AL10" s="1" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="11" spans="1:42" ht="60" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+      <c r="AM10" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:43" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>79</v>
@@ -10483,26 +10596,26 @@
         <v>80</v>
       </c>
       <c r="D11" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>145</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>147</v>
       </c>
       <c r="H11" s="1">
         <v>1</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="L11" s="7"/>
       <c r="Y11" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="Z11" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="AC11" s="1" t="s">
         <v>90</v>
@@ -10512,12 +10625,15 @@
       </c>
       <c r="AG11" s="8"/>
       <c r="AL11" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="12" spans="1:42" ht="60" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+      <c r="AM11" s="7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:43" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>79</v>
@@ -10526,38 +10642,38 @@
         <v>80</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="H12" s="1">
         <v>1</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>105</v>
+        <v>739</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="L12" s="7"/>
       <c r="M12" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="R12" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="U12" s="1">
         <v>12</v>
       </c>
       <c r="Y12" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="Z12" s="1" t="s">
         <v>89</v>
@@ -10570,12 +10686,15 @@
       </c>
       <c r="AG12" s="8"/>
       <c r="AL12" s="1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="13" spans="1:42" ht="60" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+      <c r="AM12" s="7">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:43" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>79</v>
@@ -10584,41 +10703,41 @@
         <v>80</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H13" s="1">
         <v>1</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>105</v>
+        <v>739</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="L13" s="7"/>
       <c r="M13" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="R13" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="U13" s="1">
         <v>9</v>
       </c>
       <c r="Y13" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="Z13" s="1" t="s">
         <v>89</v>
@@ -10634,163 +10753,185 @@
         <v>92</v>
       </c>
       <c r="AL13" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="AM13" s="7">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:43" ht="90" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="14" spans="1:42" ht="90" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+      <c r="C14" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>170</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>172</v>
       </c>
       <c r="E14" s="27">
         <v>2</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>828</v>
+        <v>802</v>
       </c>
       <c r="H14" s="1">
         <v>1</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>105</v>
+        <v>739</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>829</v>
+        <v>838</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>830</v>
-      </c>
-      <c r="L14" s="7">
-        <v>2002</v>
-      </c>
+        <v>839</v>
+      </c>
+      <c r="L14" s="7"/>
       <c r="M14" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>831</v>
+        <v>803</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>827</v>
+        <v>801</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>778</v>
+        <v>752</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>488</v>
+        <v>466</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S14" s="1" t="s">
-        <v>832</v>
+        <v>804</v>
       </c>
       <c r="T14" s="1" t="s">
-        <v>833</v>
+        <v>805</v>
       </c>
       <c r="U14" s="1">
         <v>8</v>
       </c>
       <c r="V14" s="1" t="s">
-        <v>837</v>
+        <v>808</v>
       </c>
       <c r="W14" s="1" t="s">
-        <v>834</v>
+        <v>850</v>
       </c>
       <c r="X14" s="1" t="s">
-        <v>835</v>
+        <v>806</v>
       </c>
       <c r="Y14" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="Z14" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AA14" s="1" t="s">
-        <v>541</v>
+        <v>518</v>
       </c>
       <c r="AB14" s="1" t="s">
-        <v>836</v>
+        <v>807</v>
       </c>
       <c r="AC14" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AF14" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="AG14" s="8"/>
       <c r="AH14" s="1" t="s">
         <v>92</v>
       </c>
       <c r="AJ14" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="AL14" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="AM14" s="7">
+        <v>10</v>
+      </c>
+      <c r="AN14" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="AL14" s="1" t="s">
+    </row>
+    <row r="15" spans="1:43" ht="120" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="AM14" s="1" t="s">
+      <c r="B15" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="15" spans="1:42" ht="120" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
+      <c r="E15" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="D15" s="1" t="s">
+      <c r="F15" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>184</v>
+      <c r="G15" s="1" t="s">
+        <v>828</v>
       </c>
       <c r="H15" s="1">
         <v>1</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>185</v>
+        <v>851</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="L15" s="7"/>
       <c r="M15" s="1" t="s">
-        <v>188</v>
+        <v>845</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>847</v>
+      </c>
+      <c r="O15" s="13" t="s">
+        <v>846</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>466</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>189</v>
+        <v>97</v>
+      </c>
+      <c r="S15" s="1" t="s">
+        <v>848</v>
+      </c>
+      <c r="T15" s="1" t="s">
+        <v>849</v>
       </c>
       <c r="U15" s="1">
         <v>9</v>
       </c>
       <c r="V15" s="1" t="s">
-        <v>190</v>
+        <v>185</v>
+      </c>
+      <c r="W15" s="1" t="s">
+        <v>850</v>
       </c>
       <c r="Y15" s="1" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="Z15" s="1" t="s">
         <v>89</v>
@@ -10799,71 +10940,80 @@
         <v>90</v>
       </c>
       <c r="AF15" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="AG15" s="8"/>
       <c r="AI15" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="AJ15" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="AL15" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="AM15" s="7">
+        <v>1</v>
+      </c>
+      <c r="AN15" s="1" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="16" spans="1:43" ht="60" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="AJ15" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="AL15" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="AM15" s="1" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="16" spans="1:42" ht="60" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>197</v>
+      <c r="G16" s="1" t="s">
+        <v>829</v>
       </c>
       <c r="H16" s="1">
         <v>1</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>105</v>
+        <v>739</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>164</v>
+        <v>843</v>
       </c>
       <c r="L16" s="7"/>
       <c r="M16" s="1" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="R16" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T16" s="1" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="U16" s="1">
         <v>6</v>
       </c>
       <c r="V16" s="1" t="s">
-        <v>201</v>
+        <v>196</v>
+      </c>
+      <c r="W16" s="1" t="s">
+        <v>850</v>
       </c>
       <c r="Y16" s="1" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="Z16" s="1" t="s">
         <v>89</v>
@@ -10872,65 +11022,71 @@
         <v>90</v>
       </c>
       <c r="AF16" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="AG16" s="8"/>
       <c r="AJ16" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="AL16" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="AM16" s="1" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="17" spans="1:39" ht="75" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+      <c r="AM16" s="7">
+        <v>3</v>
+      </c>
+      <c r="AN16" s="1" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="17" spans="1:40" ht="75" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>207</v>
+        <v>202</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>830</v>
       </c>
       <c r="H17" s="1">
         <v>1</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>105</v>
+        <v>739</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="L17" s="7"/>
       <c r="M17" s="1" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="R17" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T17" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="U17" s="1">
         <v>5</v>
       </c>
       <c r="Y17" s="1" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="Z17" s="1" t="s">
         <v>89</v>
@@ -10939,7 +11095,7 @@
         <v>90</v>
       </c>
       <c r="AF17" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="AG17" s="8"/>
       <c r="AH17" s="1" t="s">
@@ -10949,49 +11105,52 @@
         <v>92</v>
       </c>
       <c r="AJ17" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="AL17" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="AM17" s="1" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="18" spans="1:39" ht="60" x14ac:dyDescent="0.25">
+        <v>207</v>
+      </c>
+      <c r="AM17" s="7">
+        <v>4</v>
+      </c>
+      <c r="AN17" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="18" spans="1:40" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>215</v>
+        <v>210</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>831</v>
       </c>
       <c r="H18" s="1">
         <v>1</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>216</v>
+        <v>837</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>187</v>
+        <v>211</v>
       </c>
       <c r="L18" s="7"/>
       <c r="M18" s="1" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="R18" s="1" t="s">
         <v>88</v>
@@ -11000,7 +11159,7 @@
         <v>1</v>
       </c>
       <c r="Y18" s="1" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="Z18" s="1" t="s">
         <v>89</v>
@@ -11009,41 +11168,53 @@
         <v>90</v>
       </c>
       <c r="AF18" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="AG18" s="8"/>
       <c r="AL18" s="1" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="19" spans="1:39" ht="60" x14ac:dyDescent="0.25">
+        <v>214</v>
+      </c>
+      <c r="AM18" s="7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:40" ht="60" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>223</v>
+        <v>217</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>836</v>
       </c>
       <c r="H19" s="1">
         <v>1</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>105</v>
+        <v>739</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>840</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>844</v>
       </c>
       <c r="L19" s="7"/>
       <c r="M19" s="1" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="R19" s="1" t="s">
         <v>97</v>
@@ -11055,68 +11226,77 @@
         <v>4</v>
       </c>
       <c r="V19" s="1" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="Y19" s="1" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="Z19" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="AB19" s="1" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="AC19" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AF19" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="AG19" s="8"/>
       <c r="AL19" s="1" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="20" spans="1:39" ht="60" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+      <c r="AM19" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:40" ht="60" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>232</v>
+        <v>835</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>832</v>
       </c>
       <c r="H20" s="1">
         <v>1</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>233</v>
+        <v>822</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>841</v>
       </c>
       <c r="L20" s="7"/>
       <c r="M20" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="R20" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U20" s="1">
         <v>1</v>
       </c>
       <c r="Y20" s="1" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="Z20" s="1" t="s">
         <v>89</v>
@@ -11125,68 +11305,74 @@
         <v>90</v>
       </c>
       <c r="AF20" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="AG20" s="8"/>
       <c r="AI20" s="1" t="s">
         <v>92</v>
       </c>
       <c r="AJ20" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="AL20" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="AM20" s="1" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="21" spans="1:39" ht="60" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+      <c r="AM20" s="7">
+        <v>7</v>
+      </c>
+      <c r="AN20" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="21" spans="1:40" ht="60" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D21" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="E21" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>239</v>
+      <c r="G21" s="1" t="s">
+        <v>833</v>
       </c>
       <c r="H21" s="1">
         <v>1</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>105</v>
+        <v>739</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>240</v>
+        <v>842</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="L21" s="7"/>
       <c r="M21" s="1" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="R21" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T21" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U21" s="1">
         <v>1</v>
       </c>
       <c r="Y21" s="1" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="Z21" s="1" t="s">
         <v>89</v>
@@ -11195,93 +11381,102 @@
         <v>90</v>
       </c>
       <c r="AF21" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="AG21" s="8"/>
       <c r="AL21" s="1" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="22" spans="1:39" ht="45" x14ac:dyDescent="0.25">
+        <v>233</v>
+      </c>
+      <c r="AM21" s="7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:40" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="H22" s="1">
         <v>1</v>
       </c>
       <c r="L22" s="7"/>
       <c r="Y22" s="1" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="AF22" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="AG22" s="8"/>
       <c r="AL22" s="1" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="23" spans="1:39" ht="45" x14ac:dyDescent="0.25">
+        <v>239</v>
+      </c>
+      <c r="AM22" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:40" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>252</v>
+        <v>242</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>834</v>
       </c>
       <c r="H23" s="1">
         <v>1</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>105</v>
+        <v>739</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="L23" s="7"/>
       <c r="M23" s="1" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="R23" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T23" s="1" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="U23" s="1">
         <v>6</v>
       </c>
       <c r="Y23" s="1" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="Z23" s="1" t="s">
         <v>89</v>
@@ -11290,31 +11485,34 @@
         <v>90</v>
       </c>
       <c r="AF23" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="AG23" s="8"/>
       <c r="AL23" s="1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="24" spans="1:39" ht="75" x14ac:dyDescent="0.25">
+        <v>246</v>
+      </c>
+      <c r="AM23" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:40" ht="75" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="H24" s="1">
         <v>1</v>
@@ -11323,176 +11521,185 @@
         <v>84</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="L24" s="7"/>
       <c r="M24" s="1" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="V24" s="1" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="Y24" s="1" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="Z24" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="AB24" s="1" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="AC24" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AF24" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="AG24" s="8"/>
       <c r="AL24" s="1" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="25" spans="1:39" ht="45" x14ac:dyDescent="0.25">
+        <v>256</v>
+      </c>
+      <c r="AM24" s="7">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:40" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="H25" s="1">
         <v>-1</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="L25" s="7"/>
       <c r="R25" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T25" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="U25" s="1">
         <v>24</v>
       </c>
       <c r="V25" s="1" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="Y25" s="1" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="AF25" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="AG25" s="8"/>
       <c r="AJ25" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="AL25" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="AM25" s="1" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="26" spans="1:39" ht="45" x14ac:dyDescent="0.25">
+        <v>264</v>
+      </c>
+      <c r="AM25" s="7">
+        <v>11</v>
+      </c>
+      <c r="AN25" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="26" spans="1:40" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="H26" s="1">
         <v>-1</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="L26" s="7"/>
       <c r="R26" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T26" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="U26" s="1">
         <v>24</v>
       </c>
       <c r="V26" s="1" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="Y26" s="1" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="AF26" s="1" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="AG26" s="8"/>
       <c r="AL26" s="1" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="27" spans="1:39" ht="45" x14ac:dyDescent="0.25">
+        <v>264</v>
+      </c>
+      <c r="AM26" s="7">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:40" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="F27" s="1" t="s">
         <v>277</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>287</v>
       </c>
       <c r="H27" s="1">
         <v>1</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>105</v>
+        <v>739</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="L27" s="7"/>
       <c r="M27" s="1" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="R27" s="1" t="s">
         <v>88</v>
@@ -11501,7 +11708,7 @@
         <v>2</v>
       </c>
       <c r="Y27" s="1" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="Z27" s="1" t="s">
         <v>89</v>
@@ -11510,65 +11717,68 @@
         <v>90</v>
       </c>
       <c r="AF27" s="1" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="AG27" s="8"/>
       <c r="AI27" s="1" t="s">
         <v>92</v>
       </c>
       <c r="AL27" s="1" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="28" spans="1:39" ht="45" x14ac:dyDescent="0.25">
+        <v>283</v>
+      </c>
+      <c r="AM27" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:40" ht="45" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>296</v>
+        <v>826</v>
       </c>
       <c r="H28" s="1">
         <v>-1</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>297</v>
+        <v>739</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="L28" s="7"/>
       <c r="M28" s="1" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R28" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T28" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U28" s="1">
         <v>14</v>
       </c>
       <c r="Y28" s="1" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="Z28" s="1" t="s">
         <v>89</v>
@@ -11577,50 +11787,53 @@
         <v>90</v>
       </c>
       <c r="AF28" s="1" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="AG28" s="8"/>
       <c r="AI28" s="1" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="AL28" s="1" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="29" spans="1:39" ht="60" x14ac:dyDescent="0.25">
+        <v>291</v>
+      </c>
+      <c r="AM28" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:40" ht="60" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="H29" s="1">
         <v>-1</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="L29" s="7"/>
       <c r="M29" s="1" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="R29" s="1" t="s">
         <v>88</v>
@@ -11629,77 +11842,80 @@
         <v>1</v>
       </c>
       <c r="Y29" s="1" t="s">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="Z29" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AB29" s="1" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="AC29" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AF29" s="1" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="AG29" s="8"/>
       <c r="AI29" s="1" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="AL29" s="1" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="30" spans="1:39" ht="60" x14ac:dyDescent="0.25">
+        <v>303</v>
+      </c>
+      <c r="AM29" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:40" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>319</v>
+        <v>825</v>
       </c>
       <c r="H30" s="1">
         <v>1</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>320</v>
+        <v>827</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>321</v>
+        <v>307</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="L30" s="7"/>
       <c r="M30" s="1" t="s">
-        <v>323</v>
+        <v>309</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R30" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T30" s="1" t="s">
-        <v>324</v>
+        <v>310</v>
       </c>
       <c r="U30" s="1">
         <v>7</v>
       </c>
       <c r="Y30" s="1" t="s">
-        <v>325</v>
+        <v>311</v>
       </c>
       <c r="Z30" s="1" t="s">
         <v>89</v>
@@ -11708,187 +11924,196 @@
         <v>90</v>
       </c>
       <c r="AF30" s="1" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="AG30" s="8"/>
       <c r="AI30" s="1" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="AL30" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="AM30" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="AM30" s="7">
+        <v>1</v>
+      </c>
+      <c r="AN30" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="31" spans="1:39" ht="45" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:40" ht="45" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>329</v>
+        <v>315</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>330</v>
+        <v>316</v>
       </c>
       <c r="H31" s="1">
         <v>-1</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>331</v>
+        <v>317</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>332</v>
+        <v>318</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>333</v>
+        <v>319</v>
       </c>
       <c r="L31" s="7"/>
       <c r="M31" s="1" t="s">
-        <v>334</v>
+        <v>320</v>
       </c>
       <c r="R31" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T31" s="1" t="s">
-        <v>335</v>
+        <v>321</v>
       </c>
       <c r="U31" s="1">
         <v>6</v>
       </c>
       <c r="Y31" s="1" t="s">
-        <v>336</v>
+        <v>322</v>
       </c>
       <c r="Z31" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="AB31" s="1" t="s">
-        <v>337</v>
+        <v>323</v>
       </c>
       <c r="AC31" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AF31" s="1" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="AG31" s="8"/>
       <c r="AL31" s="1" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="32" spans="1:39" ht="45" x14ac:dyDescent="0.25">
+        <v>324</v>
+      </c>
+      <c r="AM31" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:40" ht="45" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>339</v>
+        <v>325</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>340</v>
+        <v>326</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>341</v>
+        <v>327</v>
       </c>
       <c r="H32" s="1">
         <v>1</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>331</v>
+        <v>317</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>342</v>
+        <v>328</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>343</v>
+        <v>329</v>
       </c>
       <c r="L32" s="7"/>
       <c r="M32" s="1" t="s">
-        <v>334</v>
+        <v>320</v>
       </c>
       <c r="R32" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T32" s="1" t="s">
-        <v>344</v>
+        <v>330</v>
       </c>
       <c r="U32" s="1">
         <v>6</v>
       </c>
       <c r="Y32" s="1" t="s">
-        <v>345</v>
+        <v>331</v>
       </c>
       <c r="Z32" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="AB32" s="1" t="s">
-        <v>337</v>
+        <v>323</v>
       </c>
       <c r="AC32" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AF32" s="1" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="AG32" s="8"/>
       <c r="AL32" s="1" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="33" spans="1:39" ht="60" x14ac:dyDescent="0.25">
+        <v>324</v>
+      </c>
+      <c r="AM32" s="7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:40" ht="60" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>346</v>
+        <v>332</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>347</v>
+        <v>333</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>348</v>
+        <v>334</v>
       </c>
       <c r="H33" s="1">
         <v>-1</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>350</v>
+        <v>336</v>
       </c>
       <c r="L33" s="7"/>
       <c r="M33" s="1" t="s">
-        <v>351</v>
+        <v>337</v>
       </c>
       <c r="R33" s="1" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="U33" s="1">
         <v>6</v>
       </c>
       <c r="Y33" s="1" t="s">
-        <v>352</v>
+        <v>338</v>
       </c>
       <c r="Z33" s="1" t="s">
         <v>89</v>
@@ -11897,59 +12122,62 @@
         <v>90</v>
       </c>
       <c r="AF33" s="1" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="AG33" s="8"/>
       <c r="AI33" s="1" t="s">
-        <v>353</v>
+        <v>339</v>
       </c>
       <c r="AL33" s="1" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="34" spans="1:39" ht="45" x14ac:dyDescent="0.25">
+        <v>340</v>
+      </c>
+      <c r="AM33" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:40" ht="45" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>355</v>
+        <v>341</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>356</v>
+        <v>342</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>357</v>
+        <v>343</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>358</v>
+        <v>344</v>
       </c>
       <c r="H34" s="1">
         <v>1</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>105</v>
+        <v>739</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>359</v>
+        <v>345</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>360</v>
+        <v>346</v>
       </c>
       <c r="L34" s="7"/>
       <c r="M34" s="1" t="s">
-        <v>361</v>
+        <v>347</v>
       </c>
       <c r="R34" s="1" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="U34" s="1">
         <v>6</v>
       </c>
       <c r="Y34" s="1" t="s">
-        <v>362</v>
+        <v>348</v>
       </c>
       <c r="Z34" s="1" t="s">
         <v>89</v>
@@ -11958,151 +12186,160 @@
         <v>90</v>
       </c>
       <c r="AF34" s="1" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="AG34" s="8"/>
       <c r="AL34" s="1" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="35" spans="1:39" ht="45" x14ac:dyDescent="0.25">
+        <v>349</v>
+      </c>
+      <c r="AM34" s="7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:40" ht="45" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>364</v>
+        <v>350</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>356</v>
+        <v>342</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>365</v>
+        <v>351</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>366</v>
+        <v>352</v>
       </c>
       <c r="H35" s="1">
         <v>1</v>
       </c>
       <c r="L35" s="7"/>
       <c r="Y35" s="1" t="s">
-        <v>367</v>
+        <v>353</v>
       </c>
       <c r="Z35" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="AC35" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AF35" s="1" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="AG35" s="8"/>
       <c r="AL35" s="1" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="36" spans="1:39" ht="45" x14ac:dyDescent="0.25">
+        <v>354</v>
+      </c>
+      <c r="AM35" s="7">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:40" ht="45" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>369</v>
+        <v>355</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>370</v>
+        <v>356</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>371</v>
+        <v>357</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H36" s="1">
         <v>1</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>105</v>
+        <v>739</v>
       </c>
       <c r="L36" s="7"/>
       <c r="R36" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T36" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="U36" s="1">
         <v>9</v>
       </c>
       <c r="Y36" s="1" t="s">
-        <v>372</v>
+        <v>358</v>
       </c>
       <c r="AF36" s="1" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="AG36" s="8"/>
       <c r="AI36" s="1" t="s">
         <v>92</v>
       </c>
       <c r="AL36" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="AM36" s="1" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="37" spans="1:39" ht="60" x14ac:dyDescent="0.25">
+        <v>359</v>
+      </c>
+      <c r="AM36" s="7">
+        <v>10</v>
+      </c>
+      <c r="AN36" s="1" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="37" spans="1:40" ht="60" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>375</v>
+        <v>361</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>376</v>
+        <v>362</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>377</v>
+        <v>363</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>378</v>
+        <v>364</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>379</v>
+        <v>365</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>380</v>
+        <v>366</v>
       </c>
       <c r="H37" s="1">
         <v>-1</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>105</v>
+        <v>739</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>381</v>
+        <v>367</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>382</v>
+        <v>368</v>
       </c>
       <c r="L37" s="7"/>
       <c r="M37" s="1" t="s">
-        <v>383</v>
+        <v>369</v>
       </c>
       <c r="R37" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T37" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="U37" s="1">
         <v>4</v>
       </c>
       <c r="Y37" s="1" t="s">
-        <v>384</v>
+        <v>370</v>
       </c>
       <c r="Z37" s="1" t="s">
         <v>89</v>
@@ -12111,59 +12348,62 @@
         <v>90</v>
       </c>
       <c r="AF37" s="1" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="AG37" s="8"/>
       <c r="AL37" s="1" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="38" spans="1:39" ht="60" x14ac:dyDescent="0.25">
+        <v>372</v>
+      </c>
+      <c r="AM37" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:40" ht="60" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>387</v>
+        <v>373</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>376</v>
+        <v>362</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>377</v>
+        <v>363</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>378</v>
+        <v>364</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>388</v>
+        <v>374</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>389</v>
+        <v>815</v>
       </c>
       <c r="H38" s="1">
         <v>1</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>105</v>
+        <v>739</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>390</v>
+        <v>375</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>382</v>
+        <v>368</v>
       </c>
       <c r="L38" s="7"/>
       <c r="M38" s="1" t="s">
-        <v>383</v>
+        <v>369</v>
       </c>
       <c r="R38" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T38" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="U38" s="1">
         <v>4</v>
       </c>
       <c r="Y38" s="1" t="s">
-        <v>391</v>
+        <v>376</v>
       </c>
       <c r="Z38" s="1" t="s">
         <v>89</v>
@@ -12172,62 +12412,65 @@
         <v>90</v>
       </c>
       <c r="AF38" s="1" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="AG38" s="8"/>
       <c r="AI38" s="1" t="s">
         <v>92</v>
       </c>
       <c r="AL38" s="1" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="39" spans="1:39" ht="60" x14ac:dyDescent="0.25">
+        <v>372</v>
+      </c>
+      <c r="AM38" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:40" ht="60" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>392</v>
+        <v>377</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>376</v>
+        <v>362</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>377</v>
+        <v>363</v>
       </c>
       <c r="D39" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="E39" s="1" t="s">
-        <v>393</v>
-      </c>
       <c r="F39" s="1" t="s">
-        <v>394</v>
+        <v>379</v>
       </c>
       <c r="H39" s="1">
         <v>1</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>105</v>
+        <v>739</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>395</v>
+        <v>380</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>396</v>
+        <v>381</v>
       </c>
       <c r="L39" s="7"/>
       <c r="M39" s="1" t="s">
-        <v>397</v>
+        <v>382</v>
       </c>
       <c r="R39" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T39" s="1" t="s">
-        <v>324</v>
+        <v>310</v>
       </c>
       <c r="U39" s="1">
         <v>4</v>
       </c>
       <c r="Y39" s="1" t="s">
-        <v>398</v>
+        <v>383</v>
       </c>
       <c r="Z39" s="1" t="s">
         <v>89</v>
@@ -12236,41 +12479,44 @@
         <v>90</v>
       </c>
       <c r="AF39" s="1" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="AG39" s="8"/>
       <c r="AL39" s="1" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="40" spans="1:39" ht="60" x14ac:dyDescent="0.25">
+        <v>384</v>
+      </c>
+      <c r="AM39" s="7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:40" ht="60" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>400</v>
+        <v>385</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>376</v>
+        <v>362</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>377</v>
+        <v>363</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>378</v>
+        <v>364</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>401</v>
+        <v>386</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>402</v>
+        <v>819</v>
       </c>
       <c r="H40" s="1">
         <v>1</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>403</v>
+        <v>822</v>
       </c>
       <c r="L40" s="7"/>
       <c r="M40" s="1" t="s">
-        <v>397</v>
+        <v>382</v>
       </c>
       <c r="R40" s="1" t="s">
         <v>97</v>
@@ -12282,10 +12528,10 @@
         <v>4</v>
       </c>
       <c r="V40" s="1" t="s">
-        <v>404</v>
+        <v>387</v>
       </c>
       <c r="Y40" s="1" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="Z40" s="1" t="s">
         <v>89</v>
@@ -12294,59 +12540,62 @@
         <v>90</v>
       </c>
       <c r="AF40" s="1" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="AG40" s="8"/>
       <c r="AI40" s="1" t="s">
         <v>92</v>
       </c>
       <c r="AL40" s="1" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="41" spans="1:39" ht="45" x14ac:dyDescent="0.25">
+        <v>389</v>
+      </c>
+      <c r="AM40" s="7">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:40" ht="45" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
-        <v>407</v>
+        <v>390</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>376</v>
+        <v>362</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>377</v>
+        <v>363</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>408</v>
+        <v>391</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>409</v>
+        <v>392</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="H41" s="1">
         <v>1</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>105</v>
+        <v>739</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>411</v>
+        <v>394</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="L41" s="7"/>
       <c r="M41" s="1" t="s">
-        <v>383</v>
+        <v>369</v>
       </c>
       <c r="R41" s="1" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="U41" s="1">
         <v>3</v>
       </c>
       <c r="Y41" s="1" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="Z41" s="1" t="s">
         <v>89</v>
@@ -12355,59 +12604,62 @@
         <v>90</v>
       </c>
       <c r="AF41" s="1" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="AG41" s="8"/>
       <c r="AI41" s="1" t="s">
         <v>92</v>
       </c>
       <c r="AL41" s="1" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="42" spans="1:39" ht="45" x14ac:dyDescent="0.25">
+        <v>369</v>
+      </c>
+      <c r="AM41" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:40" ht="45" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
-        <v>414</v>
+        <v>397</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>376</v>
+        <v>362</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>377</v>
+        <v>363</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>408</v>
+        <v>391</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>415</v>
+        <v>398</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>416</v>
+        <v>399</v>
       </c>
       <c r="H42" s="1">
         <v>-1</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>105</v>
+        <v>739</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>417</v>
+        <v>400</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="L42" s="7"/>
       <c r="M42" s="1" t="s">
-        <v>383</v>
+        <v>369</v>
       </c>
       <c r="R42" s="1" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="U42" s="1">
         <v>3</v>
       </c>
       <c r="Y42" s="1" t="s">
-        <v>418</v>
+        <v>401</v>
       </c>
       <c r="Z42" s="1" t="s">
         <v>89</v>
@@ -12416,62 +12668,65 @@
         <v>90</v>
       </c>
       <c r="AF42" s="1" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="AG42" s="8"/>
       <c r="AL42" s="1" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="43" spans="1:39" ht="45" x14ac:dyDescent="0.25">
+        <v>369</v>
+      </c>
+      <c r="AM42" s="7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:40" ht="45" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
-        <v>419</v>
+        <v>402</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>376</v>
+        <v>362</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>377</v>
+        <v>363</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>408</v>
+        <v>391</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>420</v>
+        <v>403</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>421</v>
+        <v>404</v>
       </c>
       <c r="H43" s="1">
         <v>-1</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>105</v>
+        <v>739</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>423</v>
+        <v>406</v>
       </c>
       <c r="L43" s="7"/>
       <c r="M43" s="1" t="s">
-        <v>397</v>
+        <v>382</v>
       </c>
       <c r="P43" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R43" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>424</v>
+        <v>407</v>
       </c>
       <c r="U43" s="1">
         <v>10</v>
       </c>
       <c r="Y43" s="1" t="s">
-        <v>425</v>
+        <v>408</v>
       </c>
       <c r="Z43" s="1" t="s">
         <v>89</v>
@@ -12480,102 +12735,108 @@
         <v>90</v>
       </c>
       <c r="AF43" s="1" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="AG43" s="8"/>
       <c r="AI43" s="1" t="s">
         <v>92</v>
       </c>
       <c r="AL43" s="1" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="44" spans="1:39" ht="45" x14ac:dyDescent="0.25">
+        <v>409</v>
+      </c>
+      <c r="AM43" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:40" ht="45" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
-        <v>427</v>
+        <v>410</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>376</v>
+        <v>362</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>377</v>
+        <v>363</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>408</v>
+        <v>391</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>428</v>
+        <v>411</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>429</v>
+        <v>412</v>
       </c>
       <c r="H44" s="1">
         <v>-1</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>105</v>
+        <v>739</v>
       </c>
       <c r="L44" s="7"/>
       <c r="Y44" s="1" t="s">
-        <v>430</v>
+        <v>413</v>
       </c>
       <c r="Z44" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="AB44" s="1" t="s">
-        <v>431</v>
+        <v>414</v>
       </c>
       <c r="AC44" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AF44" s="1" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="AG44" s="8"/>
       <c r="AI44" s="1" t="s">
-        <v>432</v>
+        <v>415</v>
       </c>
       <c r="AL44" s="1" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="45" spans="1:39" ht="60" x14ac:dyDescent="0.25">
+        <v>416</v>
+      </c>
+      <c r="AM44" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:40" ht="45" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
-        <v>434</v>
+        <v>417</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>376</v>
+        <v>362</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>377</v>
+        <v>363</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>408</v>
+        <v>391</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>435</v>
+        <v>418</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>436</v>
+        <v>816</v>
       </c>
       <c r="H45" s="1">
         <v>-1</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>105</v>
+        <v>739</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>437</v>
+        <v>419</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>438</v>
+        <v>420</v>
       </c>
       <c r="L45" s="7"/>
       <c r="M45" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="P45" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R45" s="1" t="s">
         <v>97</v>
@@ -12587,7 +12848,7 @@
         <v>6</v>
       </c>
       <c r="Y45" s="1" t="s">
-        <v>425</v>
+        <v>408</v>
       </c>
       <c r="Z45" s="1" t="s">
         <v>89</v>
@@ -12596,44 +12857,47 @@
         <v>90</v>
       </c>
       <c r="AF45" s="1" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="AG45" s="8"/>
       <c r="AL45" s="1" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="46" spans="1:39" ht="60" x14ac:dyDescent="0.25">
+        <v>421</v>
+      </c>
+      <c r="AM45" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:40" ht="60" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>376</v>
+        <v>362</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>377</v>
+        <v>363</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>408</v>
+        <v>391</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>441</v>
+        <v>423</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>442</v>
+        <v>424</v>
       </c>
       <c r="H46" s="1">
         <v>-1</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>443</v>
+        <v>425</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>444</v>
+        <v>426</v>
       </c>
       <c r="L46" s="7"/>
       <c r="M46" s="1" t="s">
-        <v>445</v>
+        <v>427</v>
       </c>
       <c r="R46" s="1" t="s">
         <v>88</v>
@@ -12642,7 +12906,7 @@
         <v>1</v>
       </c>
       <c r="Y46" s="1" t="s">
-        <v>446</v>
+        <v>428</v>
       </c>
       <c r="Z46" s="1" t="s">
         <v>89</v>
@@ -12651,175 +12915,184 @@
         <v>90</v>
       </c>
       <c r="AF46" s="1" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="AG46" s="8"/>
       <c r="AL46" s="1" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="47" spans="1:39" ht="45" x14ac:dyDescent="0.25">
+        <v>429</v>
+      </c>
+      <c r="AM46" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="1:40" ht="45" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>448</v>
+        <v>430</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>376</v>
+        <v>362</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>377</v>
+        <v>363</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>449</v>
+        <v>431</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>450</v>
+        <v>432</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>451</v>
+        <v>433</v>
       </c>
       <c r="H47" s="1">
         <v>-1</v>
       </c>
       <c r="L47" s="7"/>
       <c r="Y47" s="1" t="s">
-        <v>452</v>
+        <v>434</v>
       </c>
       <c r="Z47" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="AB47" s="1" t="s">
-        <v>453</v>
+        <v>435</v>
       </c>
       <c r="AC47" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AF47" s="1" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="AG47" s="8"/>
       <c r="AL47" s="1" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="48" spans="1:39" ht="90" x14ac:dyDescent="0.25">
+        <v>436</v>
+      </c>
+      <c r="AM47" s="7">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" spans="1:40" ht="90" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>455</v>
+        <v>437</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>456</v>
+        <v>438</v>
       </c>
       <c r="C48" s="24" t="s">
-        <v>457</v>
+        <v>439</v>
       </c>
       <c r="D48" s="24" t="s">
-        <v>457</v>
+        <v>439</v>
       </c>
       <c r="E48" s="24">
         <v>5</v>
       </c>
       <c r="F48" s="24" t="s">
-        <v>458</v>
+        <v>810</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>459</v>
+        <v>440</v>
       </c>
       <c r="H48" s="1">
         <v>-1</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="L48" s="7"/>
       <c r="M48" s="1" t="s">
-        <v>460</v>
+        <v>441</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>461</v>
+        <v>442</v>
       </c>
       <c r="P48" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="R48" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T48" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="U48" s="1">
         <v>24</v>
       </c>
       <c r="V48" s="1" t="s">
-        <v>462</v>
+        <v>443</v>
       </c>
       <c r="W48" s="1" t="s">
-        <v>463</v>
+        <v>444</v>
       </c>
       <c r="Y48" s="1" t="s">
-        <v>464</v>
+        <v>445</v>
       </c>
       <c r="Z48" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AA48" s="1" t="s">
-        <v>465</v>
+        <v>446</v>
       </c>
       <c r="AB48" s="1" t="s">
-        <v>466</v>
+        <v>447</v>
       </c>
       <c r="AC48" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AF48" s="1" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="AG48" s="8"/>
       <c r="AL48" s="1" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="49" spans="1:39" ht="75" x14ac:dyDescent="0.25">
+        <v>448</v>
+      </c>
+      <c r="AM48" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:40" ht="75" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
-        <v>468</v>
+        <v>449</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>456</v>
+        <v>438</v>
       </c>
       <c r="C49" s="24" t="s">
-        <v>457</v>
+        <v>439</v>
       </c>
       <c r="D49" s="24" t="s">
-        <v>469</v>
+        <v>450</v>
       </c>
       <c r="E49" s="24" t="s">
-        <v>470</v>
+        <v>451</v>
       </c>
       <c r="F49" s="24" t="s">
-        <v>471</v>
+        <v>809</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>472</v>
+        <v>452</v>
       </c>
       <c r="H49" s="1">
         <v>1</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>473</v>
+        <v>453</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>474</v>
+        <v>454</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>475</v>
+        <v>455</v>
       </c>
       <c r="L49" s="7"/>
       <c r="M49" s="1" t="s">
-        <v>460</v>
+        <v>441</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>476</v>
+        <v>456</v>
       </c>
       <c r="P49" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="R49" s="1" t="s">
         <v>97</v>
@@ -12828,83 +13101,86 @@
         <v>24</v>
       </c>
       <c r="V49" s="1" t="s">
-        <v>477</v>
+        <v>457</v>
       </c>
       <c r="W49" s="1" t="s">
-        <v>463</v>
+        <v>444</v>
       </c>
       <c r="Y49" s="1" t="s">
-        <v>478</v>
+        <v>458</v>
       </c>
       <c r="Z49" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AA49" s="1" t="s">
-        <v>465</v>
+        <v>446</v>
       </c>
       <c r="AB49" s="1" t="s">
-        <v>466</v>
+        <v>447</v>
       </c>
       <c r="AC49" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AF49" s="1" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="AG49" s="8"/>
       <c r="AL49" s="1" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="50" spans="1:39" ht="60" x14ac:dyDescent="0.25">
+        <v>459</v>
+      </c>
+      <c r="AM49" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="1:40" ht="60" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>480</v>
+        <v>460</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>456</v>
+        <v>438</v>
       </c>
       <c r="C50" s="24" t="s">
-        <v>457</v>
+        <v>439</v>
       </c>
       <c r="D50" s="24" t="s">
-        <v>469</v>
+        <v>450</v>
       </c>
       <c r="E50" s="24" t="s">
-        <v>481</v>
+        <v>461</v>
       </c>
       <c r="F50" s="24" t="s">
-        <v>482</v>
+        <v>820</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>483</v>
+        <v>462</v>
       </c>
       <c r="H50" s="1">
         <v>1</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>484</v>
+        <v>821</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>485</v>
+        <v>463</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>486</v>
+        <v>464</v>
       </c>
       <c r="L50" s="7"/>
       <c r="M50" s="1" t="s">
-        <v>460</v>
+        <v>441</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>487</v>
+        <v>465</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>476</v>
+        <v>456</v>
       </c>
       <c r="P50" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="Q50" s="1" t="s">
-        <v>488</v>
+        <v>466</v>
       </c>
       <c r="R50" s="1" t="s">
         <v>97</v>
@@ -12916,77 +13192,80 @@
         <v>12</v>
       </c>
       <c r="V50" s="1" t="s">
-        <v>489</v>
+        <v>467</v>
       </c>
       <c r="W50" s="1" t="s">
-        <v>463</v>
+        <v>444</v>
       </c>
       <c r="Y50" s="1" t="s">
-        <v>490</v>
+        <v>468</v>
       </c>
       <c r="Z50" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AA50" s="1" t="s">
-        <v>465</v>
+        <v>446</v>
       </c>
       <c r="AB50" s="1" t="s">
-        <v>491</v>
+        <v>469</v>
       </c>
       <c r="AC50" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AF50" s="1" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="AG50" s="8"/>
       <c r="AL50" s="1" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="51" spans="1:39" ht="90" x14ac:dyDescent="0.25">
+        <v>459</v>
+      </c>
+      <c r="AM50" s="7">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51" spans="1:40" ht="90" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>492</v>
+        <v>470</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>456</v>
+        <v>438</v>
       </c>
       <c r="C51" s="24" t="s">
-        <v>457</v>
+        <v>439</v>
       </c>
       <c r="D51" s="24" t="s">
-        <v>493</v>
+        <v>471</v>
       </c>
       <c r="E51" s="24" t="s">
-        <v>494</v>
+        <v>472</v>
       </c>
       <c r="F51" s="24" t="s">
-        <v>495</v>
+        <v>473</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>496</v>
+        <v>474</v>
       </c>
       <c r="H51" s="1">
         <v>1</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>105</v>
+        <v>739</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>497</v>
+        <v>475</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>498</v>
+        <v>476</v>
       </c>
       <c r="L51" s="7"/>
       <c r="M51" s="1" t="s">
-        <v>499</v>
+        <v>477</v>
       </c>
       <c r="O51" s="1" t="s">
-        <v>500</v>
+        <v>478</v>
       </c>
       <c r="P51" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="R51" s="1" t="s">
         <v>88</v>
@@ -12995,80 +13274,83 @@
         <v>2</v>
       </c>
       <c r="V51" s="1" t="s">
-        <v>489</v>
+        <v>467</v>
       </c>
       <c r="W51" s="1" t="s">
-        <v>463</v>
+        <v>444</v>
       </c>
       <c r="Y51" s="1" t="s">
-        <v>501</v>
+        <v>479</v>
       </c>
       <c r="Z51" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AA51" s="1" t="s">
-        <v>465</v>
+        <v>446</v>
       </c>
       <c r="AB51" s="1" t="s">
-        <v>502</v>
+        <v>480</v>
       </c>
       <c r="AC51" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AF51" s="1" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="AG51" s="8"/>
       <c r="AK51" s="1" t="s">
-        <v>503</v>
+        <v>481</v>
       </c>
       <c r="AL51" s="1" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="52" spans="1:39" ht="75" x14ac:dyDescent="0.25">
+        <v>482</v>
+      </c>
+      <c r="AM51" s="7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:40" ht="75" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>505</v>
+        <v>483</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>456</v>
+        <v>438</v>
       </c>
       <c r="C52" s="24" t="s">
-        <v>457</v>
+        <v>439</v>
       </c>
       <c r="D52" s="24" t="s">
-        <v>506</v>
+        <v>484</v>
       </c>
       <c r="E52" s="24" t="s">
-        <v>507</v>
+        <v>485</v>
       </c>
       <c r="F52" s="24" t="s">
-        <v>508</v>
+        <v>486</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>509</v>
+        <v>487</v>
       </c>
       <c r="H52" s="1">
         <v>-1</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>510</v>
+        <v>488</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>508</v>
+        <v>486</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>511</v>
+        <v>489</v>
       </c>
       <c r="L52" s="7"/>
       <c r="M52" s="1" t="s">
-        <v>512</v>
+        <v>490</v>
       </c>
       <c r="O52" s="13" t="s">
-        <v>513</v>
+        <v>491</v>
       </c>
       <c r="P52" s="1" t="s">
-        <v>514</v>
+        <v>492</v>
       </c>
       <c r="R52" s="1" t="s">
         <v>97</v>
@@ -13077,67 +13359,70 @@
         <v>24</v>
       </c>
       <c r="V52" s="1" t="s">
-        <v>489</v>
+        <v>467</v>
       </c>
       <c r="W52" s="1" t="s">
-        <v>463</v>
+        <v>444</v>
       </c>
       <c r="Y52" s="1" t="s">
-        <v>515</v>
+        <v>493</v>
       </c>
       <c r="Z52" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AA52" s="1" t="s">
-        <v>465</v>
+        <v>446</v>
       </c>
       <c r="AB52" s="1" t="s">
-        <v>516</v>
+        <v>494</v>
       </c>
       <c r="AC52" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AF52" s="1" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="AG52" s="8"/>
       <c r="AL52" s="1" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="53" spans="1:39" ht="135" x14ac:dyDescent="0.25">
+        <v>495</v>
+      </c>
+      <c r="AM52" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:40" ht="135" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>518</v>
+        <v>496</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>456</v>
+        <v>438</v>
       </c>
       <c r="C53" s="24" t="s">
-        <v>457</v>
+        <v>439</v>
       </c>
       <c r="D53" s="24" t="s">
-        <v>506</v>
+        <v>484</v>
       </c>
       <c r="E53" s="24" t="s">
-        <v>519</v>
+        <v>497</v>
       </c>
       <c r="F53" s="24" t="s">
-        <v>520</v>
+        <v>818</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>521</v>
+        <v>498</v>
       </c>
       <c r="H53" s="1">
         <v>-1</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>522</v>
+        <v>499</v>
       </c>
       <c r="L53" s="7">
         <v>2020</v>
       </c>
       <c r="O53" s="12" t="s">
-        <v>523</v>
+        <v>500</v>
       </c>
       <c r="R53" s="1" t="s">
         <v>97</v>
@@ -13146,242 +13431,254 @@
         <v>13</v>
       </c>
       <c r="V53" s="1" t="s">
-        <v>524</v>
+        <v>501</v>
       </c>
       <c r="W53" s="1" t="s">
-        <v>525</v>
+        <v>502</v>
       </c>
       <c r="Y53" s="1" t="s">
-        <v>526</v>
+        <v>503</v>
       </c>
       <c r="Z53" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AA53" s="1" t="s">
-        <v>465</v>
+        <v>446</v>
       </c>
       <c r="AB53" s="1" t="s">
-        <v>527</v>
+        <v>504</v>
       </c>
       <c r="AC53" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AF53" s="1" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="AG53" s="8"/>
       <c r="AI53" s="1" t="s">
-        <v>528</v>
+        <v>505</v>
       </c>
       <c r="AL53" s="1" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="54" spans="1:39" ht="60" x14ac:dyDescent="0.25">
+        <v>506</v>
+      </c>
+      <c r="AM53" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:40" ht="60" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>530</v>
+        <v>507</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>456</v>
+        <v>438</v>
       </c>
       <c r="C54" s="24" t="s">
-        <v>457</v>
+        <v>439</v>
       </c>
       <c r="D54" s="24" t="s">
-        <v>531</v>
+        <v>508</v>
       </c>
       <c r="E54" s="24" t="s">
-        <v>532</v>
+        <v>509</v>
       </c>
       <c r="F54" s="24" t="s">
-        <v>533</v>
+        <v>510</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>534</v>
+        <v>511</v>
       </c>
       <c r="H54" s="1">
         <v>1</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>535</v>
+        <v>512</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>536</v>
+        <v>513</v>
       </c>
       <c r="L54" s="7"/>
       <c r="M54" s="1" t="s">
-        <v>537</v>
+        <v>514</v>
       </c>
       <c r="R54" s="1" t="s">
-        <v>538</v>
+        <v>515</v>
       </c>
       <c r="U54" s="1">
         <v>24</v>
       </c>
       <c r="V54" s="1" t="s">
-        <v>539</v>
+        <v>516</v>
       </c>
       <c r="W54" s="1" t="s">
-        <v>463</v>
+        <v>444</v>
       </c>
       <c r="Y54" s="1" t="s">
-        <v>540</v>
+        <v>517</v>
       </c>
       <c r="Z54" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AA54" s="1" t="s">
-        <v>541</v>
+        <v>518</v>
       </c>
       <c r="AC54" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AF54" s="1" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="AG54" s="8"/>
       <c r="AK54" s="1" t="s">
-        <v>542</v>
+        <v>519</v>
       </c>
       <c r="AL54" s="1" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="55" spans="1:39" ht="45" x14ac:dyDescent="0.25">
+        <v>520</v>
+      </c>
+      <c r="AM54" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="55" spans="1:40" ht="45" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
-        <v>544</v>
+        <v>521</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>456</v>
+        <v>438</v>
       </c>
       <c r="C55" s="24" t="s">
-        <v>457</v>
+        <v>439</v>
       </c>
       <c r="D55" s="24" t="s">
-        <v>531</v>
+        <v>508</v>
       </c>
       <c r="E55" s="24" t="s">
-        <v>545</v>
+        <v>522</v>
       </c>
       <c r="F55" s="24" t="s">
-        <v>546</v>
+        <v>523</v>
       </c>
       <c r="H55" s="1">
         <v>1</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="L55" s="7"/>
       <c r="Y55" s="1" t="s">
-        <v>547</v>
+        <v>524</v>
       </c>
       <c r="Z55" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="AA55" s="1" t="s">
-        <v>541</v>
+        <v>518</v>
       </c>
       <c r="AC55" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AF55" s="1" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="AG55" s="8"/>
       <c r="AL55" s="1" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="56" spans="1:39" ht="45" x14ac:dyDescent="0.25">
+        <v>525</v>
+      </c>
+      <c r="AM55" s="7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:40" ht="45" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
-        <v>549</v>
+        <v>526</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>456</v>
+        <v>438</v>
       </c>
       <c r="C56" s="24" t="s">
-        <v>457</v>
+        <v>439</v>
       </c>
       <c r="D56" s="24" t="s">
-        <v>531</v>
+        <v>508</v>
       </c>
       <c r="E56" s="24" t="s">
-        <v>550</v>
+        <v>527</v>
       </c>
       <c r="F56" s="24" t="s">
-        <v>551</v>
+        <v>528</v>
       </c>
       <c r="H56" s="1">
         <v>1</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="L56" s="7"/>
       <c r="Y56" s="1" t="s">
-        <v>552</v>
+        <v>529</v>
       </c>
       <c r="Z56" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="AA56" s="1" t="s">
-        <v>541</v>
+        <v>518</v>
       </c>
       <c r="AC56" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AF56" s="1" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="AG56" s="8"/>
       <c r="AL56" s="1" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="57" spans="1:39" ht="105" x14ac:dyDescent="0.25">
+        <v>530</v>
+      </c>
+      <c r="AM56" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:40" ht="105" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
-        <v>554</v>
+        <v>531</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>456</v>
+        <v>438</v>
       </c>
       <c r="C57" s="24" t="s">
-        <v>457</v>
+        <v>439</v>
       </c>
       <c r="D57" s="24" t="s">
-        <v>531</v>
+        <v>508</v>
       </c>
       <c r="E57" s="24" t="s">
-        <v>555</v>
+        <v>532</v>
       </c>
       <c r="F57" s="24" t="s">
-        <v>556</v>
+        <v>817</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>557</v>
+        <v>533</v>
       </c>
       <c r="H57" s="1">
         <v>1</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>105</v>
+        <v>739</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>558</v>
+        <v>534</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>559</v>
+        <v>535</v>
       </c>
       <c r="L57" s="7"/>
       <c r="M57" s="1" t="s">
-        <v>560</v>
+        <v>536</v>
       </c>
       <c r="O57" s="12" t="s">
-        <v>561</v>
+        <v>537</v>
       </c>
       <c r="P57" s="1" t="s">
-        <v>562</v>
+        <v>538</v>
       </c>
       <c r="R57" s="1" t="s">
         <v>97</v>
@@ -13390,80 +13687,83 @@
         <v>15</v>
       </c>
       <c r="V57" s="1" t="s">
-        <v>563</v>
+        <v>539</v>
       </c>
       <c r="W57" s="1" t="s">
-        <v>564</v>
+        <v>540</v>
       </c>
       <c r="Y57" s="1" t="s">
-        <v>565</v>
+        <v>541</v>
       </c>
       <c r="Z57" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AA57" s="1" t="s">
-        <v>541</v>
+        <v>518</v>
       </c>
       <c r="AB57" s="1" t="s">
-        <v>566</v>
+        <v>542</v>
       </c>
       <c r="AC57" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AF57" s="1" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="AG57" s="8"/>
       <c r="AL57" s="1" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="58" spans="1:39" ht="60" x14ac:dyDescent="0.25">
+        <v>543</v>
+      </c>
+      <c r="AM57" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:40" ht="60" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
-        <v>568</v>
+        <v>544</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>569</v>
+        <v>545</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>570</v>
+        <v>546</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>571</v>
+        <v>547</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>572</v>
+        <v>548</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>573</v>
+        <v>812</v>
       </c>
       <c r="H58" s="1">
         <v>-1</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>105</v>
+        <v>739</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>574</v>
+        <v>549</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>575</v>
+        <v>550</v>
       </c>
       <c r="L58" s="7"/>
       <c r="M58" s="1" t="s">
-        <v>576</v>
+        <v>551</v>
       </c>
       <c r="R58" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T58" s="1" t="s">
-        <v>335</v>
+        <v>321</v>
       </c>
       <c r="U58" s="1">
         <v>3</v>
       </c>
       <c r="Y58" s="1" t="s">
-        <v>577</v>
+        <v>552</v>
       </c>
       <c r="Z58" s="1" t="s">
         <v>89</v>
@@ -13472,68 +13772,71 @@
         <v>90</v>
       </c>
       <c r="AF58" s="1" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="AG58" s="8"/>
       <c r="AI58" s="1" t="s">
         <v>92</v>
       </c>
       <c r="AL58" s="1" t="s">
-        <v>578</v>
-      </c>
-      <c r="AM58" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="AM58" s="7">
+        <v>1</v>
+      </c>
+      <c r="AN58" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="59" spans="1:39" ht="45" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:40" ht="45" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
-        <v>579</v>
+        <v>554</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>569</v>
+        <v>545</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>570</v>
+        <v>546</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>571</v>
+        <v>547</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>580</v>
+        <v>555</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>581</v>
+        <v>556</v>
       </c>
       <c r="H59" s="1">
         <v>1</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>105</v>
+        <v>739</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>582</v>
+        <v>557</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>583</v>
+        <v>558</v>
       </c>
       <c r="L59" s="7"/>
       <c r="M59" s="1" t="s">
-        <v>397</v>
+        <v>382</v>
       </c>
       <c r="P59" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R59" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T59" s="1" t="s">
-        <v>324</v>
+        <v>310</v>
       </c>
       <c r="U59" s="1">
         <v>2</v>
       </c>
       <c r="Y59" s="1" t="s">
-        <v>584</v>
+        <v>559</v>
       </c>
       <c r="Z59" s="1" t="s">
         <v>89</v>
@@ -13542,68 +13845,74 @@
         <v>90</v>
       </c>
       <c r="AF59" s="1" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="AG59" s="8"/>
       <c r="AI59" s="1" t="s">
         <v>92</v>
       </c>
       <c r="AL59" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="AM59" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="AM59" s="7">
+        <v>5</v>
+      </c>
+      <c r="AN59" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="60" spans="1:39" ht="90" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:40" ht="60" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
-        <v>586</v>
+        <v>561</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>569</v>
+        <v>545</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>570</v>
+        <v>546</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>571</v>
+        <v>547</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>587</v>
+        <v>562</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>588</v>
+        <v>813</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>563</v>
       </c>
       <c r="H60" s="1">
         <v>1</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>105</v>
+        <v>739</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>589</v>
+        <v>564</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>590</v>
+        <v>565</v>
       </c>
       <c r="L60" s="7"/>
       <c r="M60" s="1" t="s">
-        <v>397</v>
+        <v>382</v>
       </c>
       <c r="P60" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R60" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T60" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="U60" s="1">
         <v>3</v>
       </c>
       <c r="Y60" s="1" t="s">
-        <v>591</v>
+        <v>566</v>
       </c>
       <c r="Z60" s="1" t="s">
         <v>89</v>
@@ -13612,65 +13921,68 @@
         <v>90</v>
       </c>
       <c r="AF60" s="1" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="AG60" s="8"/>
       <c r="AI60" s="1" t="s">
         <v>92</v>
       </c>
       <c r="AL60" s="1" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="61" spans="1:39" ht="45" x14ac:dyDescent="0.25">
+        <v>560</v>
+      </c>
+      <c r="AM60" s="7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:40" ht="45" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
-        <v>592</v>
+        <v>567</v>
       </c>
       <c r="B61" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="F61" s="1" t="s">
         <v>569</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>570</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>571</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>593</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>594</v>
       </c>
       <c r="H61" s="1">
         <v>-1</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>105</v>
+        <v>739</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>595</v>
+        <v>570</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>596</v>
+        <v>571</v>
       </c>
       <c r="L61" s="7"/>
       <c r="M61" s="1" t="s">
-        <v>397</v>
+        <v>382</v>
       </c>
       <c r="P61" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R61" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T61" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="U61" s="1">
         <v>3</v>
       </c>
       <c r="Y61" s="1" t="s">
-        <v>597</v>
+        <v>572</v>
       </c>
       <c r="Z61" s="1" t="s">
         <v>89</v>
@@ -13679,50 +13991,53 @@
         <v>90</v>
       </c>
       <c r="AF61" s="1" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="AG61" s="8"/>
       <c r="AL61" s="1" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="62" spans="1:39" ht="45" x14ac:dyDescent="0.25">
+        <v>560</v>
+      </c>
+      <c r="AM61" s="7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:40" ht="45" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
-        <v>598</v>
+        <v>573</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>569</v>
+        <v>545</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>570</v>
+        <v>546</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>599</v>
+        <v>574</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>600</v>
+        <v>575</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>601</v>
+        <v>576</v>
       </c>
       <c r="H62" s="1">
         <v>1</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>105</v>
+        <v>739</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>602</v>
+        <v>577</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>603</v>
+        <v>578</v>
       </c>
       <c r="L62" s="7"/>
       <c r="M62" s="1" t="s">
-        <v>604</v>
+        <v>579</v>
       </c>
       <c r="P62" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R62" s="1" t="s">
         <v>97</v>
@@ -13731,7 +14046,7 @@
         <v>12</v>
       </c>
       <c r="Y62" s="1" t="s">
-        <v>605</v>
+        <v>580</v>
       </c>
       <c r="Z62" s="1" t="s">
         <v>89</v>
@@ -13740,50 +14055,53 @@
         <v>90</v>
       </c>
       <c r="AF62" s="1" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="AG62" s="8"/>
       <c r="AL62" s="1" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="63" spans="1:39" ht="45" x14ac:dyDescent="0.25">
+        <v>581</v>
+      </c>
+      <c r="AM62" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:40" ht="45" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
-        <v>607</v>
+        <v>582</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>569</v>
+        <v>545</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>570</v>
+        <v>546</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>599</v>
+        <v>574</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>608</v>
+        <v>583</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>609</v>
+        <v>584</v>
       </c>
       <c r="H63" s="1">
         <v>1</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>105</v>
+        <v>739</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>610</v>
+        <v>585</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>611</v>
+        <v>586</v>
       </c>
       <c r="L63" s="7"/>
       <c r="M63" s="1" t="s">
-        <v>612</v>
+        <v>587</v>
       </c>
       <c r="P63" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R63" s="1" t="s">
         <v>97</v>
@@ -13792,7 +14110,7 @@
         <v>12</v>
       </c>
       <c r="Y63" s="1" t="s">
-        <v>613</v>
+        <v>588</v>
       </c>
       <c r="Z63" s="1" t="s">
         <v>89</v>
@@ -13801,139 +14119,148 @@
         <v>90</v>
       </c>
       <c r="AF63" s="1" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="AG63" s="8"/>
       <c r="AL63" s="1" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="64" spans="1:39" ht="45" x14ac:dyDescent="0.25">
+        <v>589</v>
+      </c>
+      <c r="AM63" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:40" ht="45" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
-        <v>615</v>
+        <v>590</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>569</v>
+        <v>545</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>570</v>
+        <v>546</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>616</v>
+        <v>591</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>617</v>
+        <v>592</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>618</v>
+        <v>593</v>
       </c>
       <c r="H64" s="1">
         <v>1</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="L64" s="7"/>
       <c r="R64" s="1" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="U64" s="1">
         <v>3</v>
       </c>
       <c r="Y64" s="1" t="s">
-        <v>619</v>
+        <v>594</v>
       </c>
       <c r="Z64" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="AC64" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AF64" s="1" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="AG64" s="8"/>
       <c r="AL64" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="65" spans="1:39" ht="45" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+      <c r="AM64" s="7">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="65" spans="1:40" ht="45" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
-        <v>620</v>
+        <v>595</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>569</v>
+        <v>545</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>570</v>
+        <v>546</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>621</v>
+        <v>596</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>622</v>
+        <v>597</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>623</v>
+        <v>598</v>
       </c>
       <c r="H65" s="1">
         <v>1</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="L65" s="7"/>
       <c r="Y65" s="1" t="s">
-        <v>624</v>
+        <v>599</v>
       </c>
       <c r="Z65" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="AC65" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AF65" s="1" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="AG65" s="8"/>
       <c r="AL65" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="66" spans="1:39" ht="60" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+      <c r="AM65" s="7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="66" spans="1:40" ht="60" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
-        <v>625</v>
+        <v>600</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>569</v>
+        <v>545</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>570</v>
+        <v>546</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>621</v>
+        <v>596</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>626</v>
+        <v>601</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>627</v>
+        <v>602</v>
       </c>
       <c r="H66" s="1">
         <v>-1</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>628</v>
+        <v>603</v>
       </c>
       <c r="L66" s="7"/>
       <c r="M66" s="1" t="s">
-        <v>629</v>
+        <v>604</v>
       </c>
       <c r="V66" s="1" t="s">
-        <v>630</v>
+        <v>605</v>
       </c>
       <c r="Y66" s="1" t="s">
-        <v>631</v>
+        <v>606</v>
       </c>
       <c r="Z66" s="1" t="s">
         <v>89</v>
@@ -13942,56 +14269,59 @@
         <v>90</v>
       </c>
       <c r="AF66" s="1" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="AG66" s="8"/>
       <c r="AL66" s="1" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="67" spans="1:39" ht="45" x14ac:dyDescent="0.25">
+        <v>607</v>
+      </c>
+      <c r="AM66" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67" spans="1:40" ht="45" x14ac:dyDescent="0.25">
       <c r="A67" s="6" t="s">
-        <v>633</v>
+        <v>608</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>569</v>
+        <v>545</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>570</v>
+        <v>546</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>621</v>
+        <v>596</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>634</v>
+        <v>609</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>635</v>
+        <v>610</v>
       </c>
       <c r="H67" s="1">
         <v>1</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>628</v>
+        <v>603</v>
       </c>
       <c r="L67" s="7"/>
       <c r="M67" s="1" t="s">
-        <v>629</v>
+        <v>604</v>
       </c>
       <c r="P67" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R67" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T67" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="U67" s="1">
         <v>12</v>
       </c>
       <c r="Y67" s="1" t="s">
-        <v>636</v>
+        <v>611</v>
       </c>
       <c r="Z67" s="1" t="s">
         <v>89</v>
@@ -14000,65 +14330,68 @@
         <v>90</v>
       </c>
       <c r="AF67" s="1" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="AG67" s="8"/>
       <c r="AI67" s="1" t="s">
         <v>92</v>
       </c>
       <c r="AL67" s="1" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="68" spans="1:39" ht="45" x14ac:dyDescent="0.25">
+        <v>612</v>
+      </c>
+      <c r="AM67" s="7">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="68" spans="1:40" ht="30" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
-        <v>638</v>
+        <v>613</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>569</v>
+        <v>545</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>570</v>
+        <v>546</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>621</v>
+        <v>596</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>639</v>
+        <v>614</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>640</v>
+        <v>814</v>
       </c>
       <c r="H68" s="1">
         <v>1</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>105</v>
+        <v>739</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>641</v>
+        <v>615</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>642</v>
+        <v>616</v>
       </c>
       <c r="L68" s="7"/>
       <c r="M68" s="1" t="s">
-        <v>629</v>
+        <v>604</v>
       </c>
       <c r="P68" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R68" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T68" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="U68" s="1">
         <v>36</v>
       </c>
       <c r="Y68" s="1" t="s">
-        <v>613</v>
+        <v>588</v>
       </c>
       <c r="Z68" s="1" t="s">
         <v>89</v>
@@ -14067,65 +14400,68 @@
         <v>90</v>
       </c>
       <c r="AF68" s="1" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="AG68" s="8"/>
       <c r="AI68" s="1" t="s">
         <v>92</v>
       </c>
       <c r="AL68" s="1" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="69" spans="1:39" ht="45" x14ac:dyDescent="0.25">
+        <v>612</v>
+      </c>
+      <c r="AM68" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:40" ht="45" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
-        <v>643</v>
+        <v>617</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>569</v>
+        <v>545</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>570</v>
+        <v>546</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>621</v>
+        <v>596</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>644</v>
+        <v>618</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>645</v>
+        <v>619</v>
       </c>
       <c r="H69" s="1">
         <v>-1</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>105</v>
+        <v>739</v>
       </c>
       <c r="J69" s="1" t="s">
-        <v>646</v>
+        <v>620</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>596</v>
+        <v>571</v>
       </c>
       <c r="L69" s="7"/>
       <c r="M69" s="1" t="s">
-        <v>629</v>
+        <v>604</v>
       </c>
       <c r="P69" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R69" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T69" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="U69" s="1">
         <v>12</v>
       </c>
       <c r="Y69" s="1" t="s">
-        <v>597</v>
+        <v>572</v>
       </c>
       <c r="Z69" s="1" t="s">
         <v>89</v>
@@ -14134,14 +14470,17 @@
         <v>90</v>
       </c>
       <c r="AF69" s="1" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="AG69" s="8"/>
       <c r="AL69" s="1" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="70" spans="1:39" x14ac:dyDescent="0.25">
+        <v>612</v>
+      </c>
+      <c r="AM69" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A70"/>
       <c r="B70"/>
       <c r="C70"/>
@@ -14180,101 +14519,117 @@
       <c r="AJ70"/>
       <c r="AK70"/>
       <c r="AL70"/>
-      <c r="AM70"/>
+      <c r="AM70" s="30"/>
+      <c r="AN70"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G3:G69">
-    <cfRule type="expression" dxfId="18" priority="1">
+  <conditionalFormatting sqref="G3:G18">
+    <cfRule type="expression" dxfId="21" priority="4">
       <formula>AND(ISBLANK(G3), NOT(ISBLANK($E3)))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="G19">
+    <cfRule type="expression" dxfId="20" priority="33">
+      <formula>AND(ISBLANK(G19), NOT(ISBLANK($E22)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G20:G59">
+    <cfRule type="expression" dxfId="19" priority="1">
+      <formula>AND(ISBLANK(G20), NOT(ISBLANK($E20)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G61:G69">
+    <cfRule type="expression" dxfId="18" priority="5">
+      <formula>AND(ISBLANK(G61), NOT(ISBLANK($E61)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="I3:I69">
-    <cfRule type="expression" dxfId="17" priority="26">
+    <cfRule type="expression" dxfId="17" priority="30">
       <formula>ISNUMBER(SEARCH(" and ",I3))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="27">
+    <cfRule type="expression" dxfId="16" priority="31">
       <formula>ISNUMBER(SEARCH(",",I3))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="28">
+    <cfRule type="expression" dxfId="15" priority="32">
       <formula>EXACT(I3,"TBC")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I3:K69">
-    <cfRule type="expression" dxfId="14" priority="6">
+    <cfRule type="expression" dxfId="14" priority="10">
       <formula>AND(ISBLANK(I3), NOT(ISBLANK($E3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L3:L69">
-    <cfRule type="expression" dxfId="13" priority="17">
+    <cfRule type="expression" dxfId="13" priority="21">
       <formula>AND(ISBLANK(L3), NOT(ISBLANK($E3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M3:M69">
-    <cfRule type="expression" dxfId="12" priority="2">
+    <cfRule type="expression" dxfId="12" priority="6">
       <formula>AND(ISBLANK(M3), NOT(ISBLANK($E3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N3:N69">
-    <cfRule type="expression" dxfId="11" priority="8">
+    <cfRule type="expression" dxfId="11" priority="12">
       <formula>AND(ISBLANK(N3), NOT(ISBLANK($E3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O3:O52 O54:O56 O58:O69">
-    <cfRule type="expression" dxfId="10" priority="7">
+    <cfRule type="expression" dxfId="10" priority="11">
       <formula>AND(ISBLANK(O3), NOT(ISBLANK($E3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P3:P69">
-    <cfRule type="expression" dxfId="9" priority="3">
+    <cfRule type="expression" dxfId="9" priority="7">
       <formula>AND(ISBLANK(P3), NOT(ISBLANK($E3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q3:Q69">
-    <cfRule type="expression" dxfId="8" priority="9">
+    <cfRule type="expression" dxfId="8" priority="13">
       <formula>AND(ISBLANK(Q3), NOT(ISBLANK($E3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R3:R69">
-    <cfRule type="expression" dxfId="7" priority="4">
+    <cfRule type="expression" dxfId="7" priority="8">
       <formula>AND(ISBLANK(R3), NOT(ISBLANK($E3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S3:S69">
-    <cfRule type="expression" dxfId="6" priority="10">
+    <cfRule type="expression" dxfId="6" priority="14">
       <formula>AND(ISBLANK(S3), NOT(ISBLANK($E3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T3:X69">
-    <cfRule type="expression" dxfId="5" priority="15">
+    <cfRule type="expression" dxfId="5" priority="19">
       <formula>AND(ISBLANK(T3), NOT(ISBLANK($E3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z3:Z69">
-    <cfRule type="expression" dxfId="4" priority="5">
+    <cfRule type="expression" dxfId="4" priority="9">
       <formula>AND(ISBLANK(Z3), NOT(ISBLANK($E3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA3:AB69">
-    <cfRule type="expression" dxfId="3" priority="13">
+    <cfRule type="expression" dxfId="3" priority="17">
       <formula>AND(ISBLANK(AA3), NOT(ISBLANK($E3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC3:AE69">
-    <cfRule type="expression" dxfId="2" priority="21">
+    <cfRule type="expression" dxfId="2" priority="25">
       <formula>AND(ISBLANK(AC3), NOT(ISBLANK($E3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG3:AG69">
-    <cfRule type="expression" dxfId="1" priority="25">
+    <cfRule type="expression" dxfId="1" priority="29">
       <formula>AND(ISBLANK(AG3), NOT(ISBLANK($E3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ3:AJ69">
-    <cfRule type="expression" dxfId="0" priority="24">
+    <cfRule type="expression" dxfId="0" priority="28">
       <formula>AND(ISBLANK(AJ3), NOT(ISBLANK($E3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="10">
+  <dataValidations count="11">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H69" xr:uid="{F3E81D7D-973D-424A-8317-BF708C24C230}">
       <formula1>"1,-1"</formula1>
     </dataValidation>
@@ -14308,6 +14663,10 @@
       <formula1>43831</formula1>
       <formula2>47848</formula2>
     </dataValidation>
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Integers only" promptTitle="Integers only" sqref="AM3:AM69" xr:uid="{5F82191F-5468-40DE-AE34-CD2A4B696998}">
+      <formula1>1</formula1>
+      <formula2>15</formula2>
+    </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="O57" r:id="rId1" display="https://environment.data.gov.uk/catchment-planning/ManagementCatchment/3005/classifications" xr:uid="{D3161A0C-EBAF-4250-B3FF-86792B73D335}"/>
@@ -14320,10 +14679,11 @@
     <hyperlink ref="O7" r:id="rId8" xr:uid="{FACF44FF-2AAA-4BA6-9648-54A7A1044DE3}"/>
     <hyperlink ref="O8" r:id="rId9" xr:uid="{55B796E0-57B6-4245-8E7F-4DC08128D9C8}"/>
     <hyperlink ref="O10" r:id="rId10" xr:uid="{3EF6CD63-BF63-40FC-AF9F-DDFFFDDAFEB3}"/>
+    <hyperlink ref="O15" r:id="rId11" display="https://assets.publishing.service.gov.uk/media/69c11f97cfa346b9d4704a50/bus01.ods; " xr:uid="{47C657F9-13A6-48E9-8F05-FEF33E1708D8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId11"/>
-  <legacyDrawing r:id="rId12"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId12"/>
+  <legacyDrawing r:id="rId13"/>
 </worksheet>
 </file>
 
@@ -14338,47 +14698,47 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
-        <v>658</v>
+        <v>632</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
-        <v>659</v>
+        <v>633</v>
       </c>
       <c r="B2" t="s">
-        <v>660</v>
+        <v>634</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>661</v>
+        <v>635</v>
       </c>
       <c r="B3" t="s">
-        <v>662</v>
+        <v>636</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>663</v>
+        <v>637</v>
       </c>
       <c r="B4" t="s">
-        <v>664</v>
+        <v>638</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>665</v>
+        <v>639</v>
       </c>
       <c r="B6" t="s">
-        <v>666</v>
+        <v>640</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>667</v>
+        <v>641</v>
       </c>
       <c r="B7" t="s">
-        <v>668</v>
+        <v>642</v>
       </c>
     </row>
   </sheetData>
@@ -14400,63 +14760,63 @@
   <sheetData>
     <row r="1" spans="1:5" ht="298.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="19" t="s">
-        <v>669</v>
+        <v>643</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
-        <v>670</v>
+        <v>644</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>671</v>
+        <v>645</v>
       </c>
       <c r="B4" t="s">
-        <v>672</v>
+        <v>646</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>673</v>
+        <v>647</v>
       </c>
       <c r="B5" t="s">
-        <v>674</v>
+        <v>648</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>675</v>
+        <v>649</v>
       </c>
       <c r="B6" t="s">
-        <v>676</v>
+        <v>650</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>677</v>
+        <v>651</v>
       </c>
       <c r="B7" t="s">
-        <v>678</v>
+        <v>652</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="21" t="s">
-        <v>679</v>
+        <v>653</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
-        <v>680</v>
+        <v>654</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>681</v>
+        <v>655</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>682</v>
+        <v>656</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>683</v>
+        <v>657</v>
       </c>
       <c r="E10" s="15" t="s">
         <v>37</v>
@@ -14470,13 +14830,13 @@
         <v>0</v>
       </c>
       <c r="C11" t="s">
-        <v>684</v>
+        <v>658</v>
       </c>
       <c r="D11" t="s">
-        <v>685</v>
+        <v>659</v>
       </c>
       <c r="E11" t="s">
-        <v>686</v>
+        <v>660</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -14487,13 +14847,13 @@
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>687</v>
+        <v>661</v>
       </c>
       <c r="D12" t="s">
-        <v>685</v>
+        <v>659</v>
       </c>
       <c r="E12" t="s">
-        <v>688</v>
+        <v>662</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -14504,13 +14864,13 @@
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>689</v>
+        <v>663</v>
       </c>
       <c r="D13" t="s">
-        <v>685</v>
+        <v>659</v>
       </c>
       <c r="E13" t="s">
-        <v>690</v>
+        <v>664</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -14521,13 +14881,13 @@
         <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>689</v>
+        <v>663</v>
       </c>
       <c r="D14" t="s">
-        <v>685</v>
+        <v>659</v>
       </c>
       <c r="E14" t="s">
-        <v>691</v>
+        <v>665</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -14538,13 +14898,13 @@
         <v>4</v>
       </c>
       <c r="C15" t="s">
-        <v>692</v>
+        <v>666</v>
       </c>
       <c r="D15" t="s">
-        <v>685</v>
+        <v>659</v>
       </c>
       <c r="E15" t="s">
-        <v>693</v>
+        <v>667</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -14555,13 +14915,13 @@
         <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>694</v>
+        <v>668</v>
       </c>
       <c r="D16" t="s">
-        <v>685</v>
+        <v>659</v>
       </c>
       <c r="E16" t="s">
-        <v>695</v>
+        <v>669</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -14572,13 +14932,13 @@
         <v>6</v>
       </c>
       <c r="C17" t="s">
-        <v>689</v>
+        <v>663</v>
       </c>
       <c r="D17" t="s">
-        <v>696</v>
+        <v>670</v>
       </c>
       <c r="E17" t="s">
-        <v>697</v>
+        <v>671</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -14589,13 +14949,13 @@
         <v>7</v>
       </c>
       <c r="C18" t="s">
-        <v>698</v>
+        <v>672</v>
       </c>
       <c r="D18" t="s">
-        <v>696</v>
+        <v>670</v>
       </c>
       <c r="E18" t="s">
-        <v>699</v>
+        <v>673</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -14606,13 +14966,13 @@
         <v>8</v>
       </c>
       <c r="C19" t="s">
-        <v>700</v>
+        <v>674</v>
       </c>
       <c r="D19" t="s">
-        <v>696</v>
+        <v>670</v>
       </c>
       <c r="E19" t="s">
-        <v>701</v>
+        <v>675</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -14623,13 +14983,13 @@
         <v>9</v>
       </c>
       <c r="C20" t="s">
-        <v>689</v>
+        <v>663</v>
       </c>
       <c r="D20" t="s">
-        <v>696</v>
+        <v>670</v>
       </c>
       <c r="E20" t="s">
-        <v>702</v>
+        <v>676</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -14640,13 +15000,13 @@
         <v>10</v>
       </c>
       <c r="C21" t="s">
-        <v>689</v>
+        <v>663</v>
       </c>
       <c r="D21" t="s">
-        <v>696</v>
+        <v>670</v>
       </c>
       <c r="E21" t="s">
-        <v>703</v>
+        <v>677</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -14657,13 +15017,13 @@
         <v>11</v>
       </c>
       <c r="C22" t="s">
-        <v>692</v>
+        <v>666</v>
       </c>
       <c r="D22" t="s">
-        <v>696</v>
+        <v>670</v>
       </c>
       <c r="E22" t="s">
-        <v>704</v>
+        <v>678</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -14674,13 +15034,13 @@
         <v>12</v>
       </c>
       <c r="C23" t="s">
-        <v>694</v>
+        <v>668</v>
       </c>
       <c r="D23" t="s">
-        <v>696</v>
+        <v>670</v>
       </c>
       <c r="E23" t="s">
-        <v>705</v>
+        <v>679</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -14691,13 +15051,13 @@
         <v>13</v>
       </c>
       <c r="C24" t="s">
-        <v>694</v>
+        <v>668</v>
       </c>
       <c r="D24" t="s">
-        <v>696</v>
+        <v>670</v>
       </c>
       <c r="E24" t="s">
-        <v>706</v>
+        <v>680</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -14708,13 +15068,13 @@
         <v>14</v>
       </c>
       <c r="C25" t="s">
-        <v>689</v>
+        <v>663</v>
       </c>
       <c r="D25" t="s">
-        <v>696</v>
+        <v>670</v>
       </c>
       <c r="E25" t="s">
-        <v>707</v>
+        <v>681</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -14725,13 +15085,13 @@
         <v>15</v>
       </c>
       <c r="C26" t="s">
-        <v>684</v>
+        <v>658</v>
       </c>
       <c r="D26" t="s">
-        <v>696</v>
+        <v>670</v>
       </c>
       <c r="E26" t="s">
-        <v>708</v>
+        <v>682</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -14742,13 +15102,13 @@
         <v>16</v>
       </c>
       <c r="C27" t="s">
-        <v>700</v>
+        <v>674</v>
       </c>
       <c r="D27" t="s">
-        <v>696</v>
+        <v>670</v>
       </c>
       <c r="E27" t="s">
-        <v>709</v>
+        <v>683</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -14759,13 +15119,13 @@
         <v>17</v>
       </c>
       <c r="C28" t="s">
-        <v>687</v>
+        <v>661</v>
       </c>
       <c r="D28" t="s">
-        <v>696</v>
+        <v>670</v>
       </c>
       <c r="E28" t="s">
-        <v>710</v>
+        <v>684</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -14776,13 +15136,13 @@
         <v>18</v>
       </c>
       <c r="C29" t="s">
-        <v>684</v>
+        <v>658</v>
       </c>
       <c r="D29" t="s">
-        <v>696</v>
+        <v>670</v>
       </c>
       <c r="E29" t="s">
-        <v>711</v>
+        <v>685</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -14793,13 +15153,13 @@
         <v>19</v>
       </c>
       <c r="C30" t="s">
-        <v>684</v>
+        <v>658</v>
       </c>
       <c r="D30" t="s">
-        <v>696</v>
+        <v>670</v>
       </c>
       <c r="E30" t="s">
-        <v>712</v>
+        <v>686</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -14810,13 +15170,13 @@
         <v>20</v>
       </c>
       <c r="C31" t="s">
-        <v>698</v>
+        <v>672</v>
       </c>
       <c r="D31" t="s">
-        <v>696</v>
+        <v>670</v>
       </c>
       <c r="E31" t="s">
-        <v>713</v>
+        <v>687</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -14827,13 +15187,13 @@
         <v>21</v>
       </c>
       <c r="C32" t="s">
-        <v>689</v>
+        <v>663</v>
       </c>
       <c r="D32" t="s">
-        <v>696</v>
+        <v>670</v>
       </c>
       <c r="E32" t="s">
-        <v>714</v>
+        <v>688</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -14844,13 +15204,13 @@
         <v>22</v>
       </c>
       <c r="C33" t="s">
+        <v>663</v>
+      </c>
+      <c r="D33" t="s">
+        <v>670</v>
+      </c>
+      <c r="E33" t="s">
         <v>689</v>
-      </c>
-      <c r="D33" t="s">
-        <v>696</v>
-      </c>
-      <c r="E33" t="s">
-        <v>715</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -14861,13 +15221,13 @@
         <v>23</v>
       </c>
       <c r="C34" t="s">
-        <v>689</v>
+        <v>663</v>
       </c>
       <c r="D34" t="s">
-        <v>696</v>
+        <v>670</v>
       </c>
       <c r="E34" t="s">
-        <v>716</v>
+        <v>690</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -14878,13 +15238,13 @@
         <v>24</v>
       </c>
       <c r="C35" t="s">
-        <v>689</v>
+        <v>663</v>
       </c>
       <c r="D35" t="s">
-        <v>696</v>
+        <v>670</v>
       </c>
       <c r="E35" t="s">
-        <v>717</v>
+        <v>691</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -14895,13 +15255,13 @@
         <v>25</v>
       </c>
       <c r="C36" t="s">
-        <v>684</v>
+        <v>658</v>
       </c>
       <c r="D36" t="s">
-        <v>696</v>
+        <v>670</v>
       </c>
       <c r="E36" t="s">
-        <v>718</v>
+        <v>692</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -14912,13 +15272,13 @@
         <v>26</v>
       </c>
       <c r="C37" t="s">
-        <v>687</v>
+        <v>661</v>
       </c>
       <c r="D37" t="s">
-        <v>696</v>
+        <v>670</v>
       </c>
       <c r="E37" t="s">
-        <v>719</v>
+        <v>693</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -14929,13 +15289,13 @@
         <v>27</v>
       </c>
       <c r="C38" t="s">
-        <v>689</v>
+        <v>663</v>
       </c>
       <c r="D38" t="s">
-        <v>696</v>
+        <v>670</v>
       </c>
       <c r="E38" t="s">
-        <v>720</v>
+        <v>694</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -14946,13 +15306,13 @@
         <v>28</v>
       </c>
       <c r="C39" t="s">
-        <v>684</v>
+        <v>658</v>
       </c>
       <c r="D39" t="s">
-        <v>696</v>
+        <v>670</v>
       </c>
       <c r="E39" t="s">
-        <v>721</v>
+        <v>695</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -14963,13 +15323,13 @@
         <v>29</v>
       </c>
       <c r="C40" t="s">
-        <v>689</v>
+        <v>663</v>
       </c>
       <c r="D40" t="s">
+        <v>670</v>
+      </c>
+      <c r="E40" t="s">
         <v>696</v>
-      </c>
-      <c r="E40" t="s">
-        <v>722</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -14980,13 +15340,13 @@
         <v>30</v>
       </c>
       <c r="C41" t="s">
-        <v>689</v>
+        <v>663</v>
       </c>
       <c r="D41" t="s">
-        <v>696</v>
+        <v>670</v>
       </c>
       <c r="E41" t="s">
-        <v>723</v>
+        <v>697</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -14997,13 +15357,13 @@
         <v>31</v>
       </c>
       <c r="C42" t="s">
-        <v>692</v>
+        <v>666</v>
       </c>
       <c r="D42" t="s">
-        <v>696</v>
+        <v>670</v>
       </c>
       <c r="E42" t="s">
-        <v>724</v>
+        <v>698</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -15014,13 +15374,13 @@
         <v>32</v>
       </c>
       <c r="C43" t="s">
-        <v>725</v>
+        <v>699</v>
       </c>
       <c r="D43" t="s">
-        <v>696</v>
+        <v>670</v>
       </c>
       <c r="E43" t="s">
-        <v>726</v>
+        <v>700</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -15031,13 +15391,13 @@
         <v>33</v>
       </c>
       <c r="C44" t="s">
-        <v>684</v>
+        <v>658</v>
       </c>
       <c r="D44" t="s">
-        <v>696</v>
+        <v>670</v>
       </c>
       <c r="E44" t="s">
-        <v>727</v>
+        <v>701</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -15048,13 +15408,13 @@
         <v>34</v>
       </c>
       <c r="C45" t="s">
-        <v>684</v>
+        <v>658</v>
       </c>
       <c r="D45" t="s">
-        <v>696</v>
+        <v>670</v>
       </c>
       <c r="E45" t="s">
-        <v>728</v>
+        <v>702</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -15065,13 +15425,13 @@
         <v>35</v>
       </c>
       <c r="C46" t="s">
-        <v>689</v>
+        <v>663</v>
       </c>
       <c r="D46" t="s">
-        <v>696</v>
+        <v>670</v>
       </c>
       <c r="E46" t="s">
-        <v>729</v>
+        <v>703</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -15082,13 +15442,13 @@
         <v>36</v>
       </c>
       <c r="C47" t="s">
-        <v>689</v>
+        <v>663</v>
       </c>
       <c r="D47" t="s">
-        <v>696</v>
+        <v>670</v>
       </c>
       <c r="E47" t="s">
-        <v>730</v>
+        <v>704</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -15099,13 +15459,13 @@
         <v>37</v>
       </c>
       <c r="C48" t="s">
-        <v>689</v>
+        <v>663</v>
       </c>
       <c r="D48" t="s">
-        <v>696</v>
+        <v>670</v>
       </c>
       <c r="E48" t="s">
-        <v>731</v>
+        <v>705</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -15116,69 +15476,69 @@
         <v>38</v>
       </c>
       <c r="C49" t="s">
-        <v>689</v>
+        <v>663</v>
       </c>
       <c r="D49" t="s">
-        <v>696</v>
+        <v>670</v>
       </c>
       <c r="E49" t="s">
-        <v>732</v>
+        <v>706</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A51" s="20" t="s">
-        <v>733</v>
+        <v>707</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="11" t="s">
-        <v>671</v>
+        <v>645</v>
       </c>
       <c r="B52" t="s">
-        <v>734</v>
+        <v>708</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="11" t="s">
-        <v>673</v>
+        <v>647</v>
       </c>
       <c r="B53" t="s">
-        <v>735</v>
+        <v>709</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="11" t="s">
-        <v>675</v>
+        <v>649</v>
       </c>
       <c r="B54" t="s">
-        <v>736</v>
+        <v>710</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="11" t="s">
-        <v>737</v>
+        <v>711</v>
       </c>
       <c r="B55" t="s">
-        <v>738</v>
+        <v>712</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="21" t="s">
-        <v>739</v>
+        <v>713</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="15" t="s">
-        <v>680</v>
+        <v>654</v>
       </c>
       <c r="B58" s="15" t="s">
-        <v>681</v>
+        <v>655</v>
       </c>
       <c r="C58" s="15" t="s">
-        <v>682</v>
+        <v>656</v>
       </c>
       <c r="D58" s="15" t="s">
-        <v>683</v>
+        <v>657</v>
       </c>
       <c r="E58" s="15" t="s">
         <v>37</v>
@@ -15186,19 +15546,19 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>653</v>
+        <v>627</v>
       </c>
       <c r="B59" t="s">
-        <v>647</v>
+        <v>621</v>
       </c>
       <c r="C59" t="s">
-        <v>698</v>
+        <v>672</v>
       </c>
       <c r="D59" t="s">
-        <v>685</v>
+        <v>659</v>
       </c>
       <c r="E59" t="s">
-        <v>740</v>
+        <v>714</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -15206,141 +15566,141 @@
         <v>39</v>
       </c>
       <c r="B60" t="s">
-        <v>648</v>
+        <v>622</v>
       </c>
       <c r="C60" t="s">
-        <v>684</v>
+        <v>658</v>
       </c>
       <c r="D60" t="s">
-        <v>685</v>
+        <v>659</v>
       </c>
       <c r="E60" t="s">
-        <v>741</v>
+        <v>715</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>654</v>
+        <v>628</v>
       </c>
       <c r="B61" t="s">
-        <v>649</v>
+        <v>623</v>
       </c>
       <c r="C61" t="s">
-        <v>725</v>
+        <v>699</v>
       </c>
       <c r="D61" t="s">
-        <v>685</v>
+        <v>659</v>
       </c>
       <c r="E61" t="s">
-        <v>742</v>
+        <v>716</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>655</v>
+        <v>629</v>
       </c>
       <c r="B62" t="s">
-        <v>650</v>
+        <v>624</v>
       </c>
       <c r="C62" t="s">
-        <v>725</v>
+        <v>699</v>
       </c>
       <c r="D62" t="s">
-        <v>685</v>
+        <v>659</v>
       </c>
       <c r="E62" t="s">
-        <v>743</v>
+        <v>717</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>656</v>
+        <v>630</v>
       </c>
       <c r="B63" t="s">
-        <v>651</v>
+        <v>625</v>
       </c>
       <c r="C63" t="s">
-        <v>744</v>
+        <v>718</v>
       </c>
       <c r="D63" t="s">
-        <v>685</v>
+        <v>659</v>
       </c>
       <c r="E63" t="s">
-        <v>745</v>
+        <v>719</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>657</v>
+        <v>631</v>
       </c>
       <c r="B64" t="s">
-        <v>652</v>
+        <v>626</v>
       </c>
       <c r="C64" t="s">
-        <v>725</v>
+        <v>699</v>
       </c>
       <c r="D64" t="s">
-        <v>696</v>
+        <v>670</v>
       </c>
       <c r="E64" t="s">
-        <v>746</v>
+        <v>720</v>
       </c>
     </row>
     <row r="66" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A66" s="20" t="s">
-        <v>747</v>
+        <v>721</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>748</v>
+        <v>722</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>749</v>
+        <v>723</v>
       </c>
     </row>
     <row r="70" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A70" s="20" t="s">
-        <v>750</v>
+        <v>724</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" s="11" t="s">
-        <v>751</v>
+        <v>725</v>
       </c>
       <c r="B71" t="s">
-        <v>752</v>
+        <v>726</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" s="11" t="s">
-        <v>753</v>
+        <v>727</v>
       </c>
       <c r="B72" t="s">
-        <v>754</v>
+        <v>728</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" s="11" t="s">
-        <v>755</v>
+        <v>729</v>
       </c>
       <c r="B73" t="s">
-        <v>756</v>
+        <v>730</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" s="11" t="s">
-        <v>757</v>
+        <v>731</v>
       </c>
       <c r="B74" t="s">
-        <v>758</v>
+        <v>732</v>
       </c>
     </row>
     <row r="76" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A76" s="20" t="s">
-        <v>759</v>
+        <v>733</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -15348,7 +15708,7 @@
         <v>1</v>
       </c>
       <c r="B77" t="s">
-        <v>760</v>
+        <v>734</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -15356,7 +15716,7 @@
         <v>2</v>
       </c>
       <c r="B78" t="s">
-        <v>761</v>
+        <v>735</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -15364,7 +15724,7 @@
         <v>3</v>
       </c>
       <c r="B79" t="s">
-        <v>762</v>
+        <v>736</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -15372,7 +15732,7 @@
         <v>4</v>
       </c>
       <c r="B80" t="s">
-        <v>763</v>
+        <v>737</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
@@ -15380,7 +15740,7 @@
         <v>5</v>
       </c>
       <c r="B81" t="s">
-        <v>764</v>
+        <v>738</v>
       </c>
     </row>
   </sheetData>
@@ -15389,27 +15749,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d56b9130-d22a-480d-bb83-f34040f04d96">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Notes xmlns="d56b9130-d22a-480d-bb83-f34040f04d96" xsi:nil="true"/>
-    <TaxCatchAll xmlns="dd8606a3-d959-45f7-996e-3c98d970357c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010026B67AE13FBD584ABEFCF026840CED6F" ma:contentTypeVersion="21" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="11ebdf7d5c906124ef40ef85c2b08d8b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d56b9130-d22a-480d-bb83-f34040f04d96" xmlns:ns3="dd8606a3-d959-45f7-996e-3c98d970357c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="395e369db30c2620103728840cc29626" ns2:_="" ns3:_="">
     <xsd:import namespace="d56b9130-d22a-480d-bb83-f34040f04d96"/>
@@ -15678,32 +16017,28 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D4B7956-BCA0-46CA-BF6B-C7215DA15D81}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED897AD3-F0B7-437A-A46C-43145E78E644}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="d56b9130-d22a-480d-bb83-f34040f04d96"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="dd8606a3-d959-45f7-996e-3c98d970357c"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d56b9130-d22a-480d-bb83-f34040f04d96">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Notes xmlns="d56b9130-d22a-480d-bb83-f34040f04d96" xsi:nil="true"/>
+    <TaxCatchAll xmlns="dd8606a3-d959-45f7-996e-3c98d970357c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E038410E-E6A9-42FC-B223-5F20C9C2E8EB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -15720,4 +16055,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D4B7956-BCA0-46CA-BF6B-C7215DA15D81}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED897AD3-F0B7-437A-A46C-43145E78E644}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="d56b9130-d22a-480d-bb83-f34040f04d96"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="dd8606a3-d959-45f7-996e-3c98d970357c"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/common_project_data/indicators-master.xlsx
+++ b/data/common_project_data/indicators-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steve.crawshaw\projects\weca_regional_indicators\data\common_project_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EF194CCE-6CAF-4DBB-9727-AB0C6D11AE12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{ED97C362-6935-463D-B7F6-0A254EF57198}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2286,9 +2286,6 @@
     <t>All indicator metadata — units, geography level, data source, definition, polarity — lives exclusively in dim_indicator and is resolved via FK join.</t>
   </si>
   <si>
-    <t>Percent</t>
-  </si>
-  <si>
     <t>ONS Labour Force Survey</t>
   </si>
   <si>
@@ -2680,6 +2677,9 @@
   </si>
   <si>
     <t>include</t>
+  </si>
+  <si>
+    <t>%</t>
   </si>
 </sst>
 </file>
@@ -9748,16 +9748,16 @@
         <v>37</v>
       </c>
       <c r="AM1" s="26" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="AN1" s="3" t="s">
         <v>38</v>
       </c>
       <c r="AO1" s="3" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="AP1" s="3" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="AQ1" s="2"/>
     </row>
@@ -9877,16 +9877,16 @@
         <v>76</v>
       </c>
       <c r="AM2" s="27" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="AN2" s="12" t="s">
         <v>77</v>
       </c>
       <c r="AO2" s="12" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="AP2" s="12" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="AQ2" s="2"/>
     </row>
@@ -9910,13 +9910,13 @@
         <v>83</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H3" s="1">
         <v>1</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>730</v>
+        <v>860</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>84</v>
@@ -9926,13 +9926,13 @@
       </c>
       <c r="L3" s="5"/>
       <c r="M3" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>731</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="O3" s="11" t="s">
         <v>732</v>
-      </c>
-      <c r="O3" s="11" t="s">
-        <v>733</v>
       </c>
       <c r="P3" s="1" t="s">
         <v>117</v>
@@ -9944,7 +9944,7 @@
         <v>183</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="T3" s="23">
         <v>46133</v>
@@ -9953,10 +9953,10 @@
         <v>4</v>
       </c>
       <c r="W3" s="1" t="s">
+        <v>735</v>
+      </c>
+      <c r="Y3" s="1" t="s">
         <v>736</v>
-      </c>
-      <c r="Y3" s="1" t="s">
-        <v>737</v>
       </c>
       <c r="Z3" s="1" t="s">
         <v>88</v>
@@ -9965,7 +9965,7 @@
         <v>173</v>
       </c>
       <c r="AB3" s="1" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="AC3" s="1" t="s">
         <v>89</v>
@@ -9978,13 +9978,13 @@
         <v>91</v>
       </c>
       <c r="AL3" s="1" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="AM3" s="5">
         <v>3</v>
       </c>
       <c r="AO3" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AP3" s="1" t="b">
         <v>1</v>
@@ -10010,13 +10010,13 @@
         <v>94</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H4" s="1">
         <v>1</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>95</v>
@@ -10026,13 +10026,13 @@
         <v>86</v>
       </c>
       <c r="N4" s="1" t="s">
+        <v>741</v>
+      </c>
+      <c r="O4" s="11" t="s">
+        <v>740</v>
+      </c>
+      <c r="P4" s="1" t="s">
         <v>742</v>
-      </c>
-      <c r="O4" s="11" t="s">
-        <v>741</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>743</v>
       </c>
       <c r="Q4" s="1" t="s">
         <v>457</v>
@@ -10053,13 +10053,13 @@
         <v>98</v>
       </c>
       <c r="W4" s="1" t="s">
+        <v>743</v>
+      </c>
+      <c r="X4" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="Y4" s="1" t="s">
         <v>744</v>
-      </c>
-      <c r="X4" s="1" t="s">
-        <v>751</v>
-      </c>
-      <c r="Y4" s="1" t="s">
-        <v>745</v>
       </c>
       <c r="Z4" s="1" t="s">
         <v>88</v>
@@ -10068,7 +10068,7 @@
         <v>509</v>
       </c>
       <c r="AB4" s="1" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="AC4" s="1" t="s">
         <v>89</v>
@@ -10084,7 +10084,7 @@
         <v>4</v>
       </c>
       <c r="AO4" s="1" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="AP4" s="1" t="b">
         <v>1</v>
@@ -10110,16 +10110,16 @@
         <v>103</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H5" s="1">
         <v>1</v>
       </c>
       <c r="I5" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>747</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>748</v>
       </c>
       <c r="L5" s="5">
         <v>2020</v>
@@ -10128,10 +10128,10 @@
         <v>104</v>
       </c>
       <c r="N5" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="O5" s="11" t="s">
         <v>749</v>
-      </c>
-      <c r="O5" s="11" t="s">
-        <v>750</v>
       </c>
       <c r="P5" s="1" t="s">
         <v>105</v>
@@ -10146,19 +10146,19 @@
         <v>2023</v>
       </c>
       <c r="T5" s="24" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="U5" s="1">
         <v>16</v>
       </c>
       <c r="W5" s="1" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="X5" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="Y5" s="1" t="s">
         <v>752</v>
-      </c>
-      <c r="Y5" s="1" t="s">
-        <v>753</v>
       </c>
       <c r="Z5" s="1" t="s">
         <v>88</v>
@@ -10167,7 +10167,7 @@
         <v>509</v>
       </c>
       <c r="AB5" s="1" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="AC5" s="1" t="s">
         <v>89</v>
@@ -10183,7 +10183,7 @@
         <v>1</v>
       </c>
       <c r="AO5" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="AP5" s="1" t="b">
         <v>1</v>
@@ -10209,7 +10209,7 @@
         <v>110</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H6" s="1">
         <v>1</v>
@@ -10218,20 +10218,20 @@
         <v>111</v>
       </c>
       <c r="J6" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>759</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>760</v>
       </c>
       <c r="L6" s="5"/>
       <c r="M6" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="N6" s="1" t="s">
         <v>761</v>
       </c>
-      <c r="N6" s="1" t="s">
+      <c r="O6" s="11" t="s">
         <v>762</v>
-      </c>
-      <c r="O6" s="11" t="s">
-        <v>763</v>
       </c>
       <c r="P6" s="1" t="s">
         <v>105</v>
@@ -10252,10 +10252,10 @@
         <v>18</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="Y6" s="1" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="Z6" s="1" t="s">
         <v>88</v>
@@ -10264,7 +10264,7 @@
         <v>173</v>
       </c>
       <c r="AB6" s="1" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="AC6" s="1" t="s">
         <v>89</v>
@@ -10277,13 +10277,13 @@
         <v>113</v>
       </c>
       <c r="AL6" s="1" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="AM6" s="5">
         <v>2</v>
       </c>
       <c r="AO6" s="1" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="AP6" s="1" t="b">
         <v>1</v>
@@ -10306,10 +10306,10 @@
         <v>115</v>
       </c>
       <c r="F7" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>769</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>770</v>
       </c>
       <c r="H7" s="1">
         <v>1</v>
@@ -10318,23 +10318,23 @@
         <v>116</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="L7" s="5"/>
       <c r="M7" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="N7" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="N7" s="1" t="s">
+      <c r="O7" s="11" t="s">
         <v>772</v>
-      </c>
-      <c r="O7" s="11" t="s">
-        <v>773</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>117</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="R7" s="1" t="s">
         <v>87</v>
@@ -10349,10 +10349,10 @@
         <v>1</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="Z7" s="1" t="s">
         <v>88</v>
@@ -10361,7 +10361,7 @@
         <v>437</v>
       </c>
       <c r="AB7" s="1" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="AC7" s="1" t="s">
         <v>89</v>
@@ -10374,13 +10374,13 @@
         <v>91</v>
       </c>
       <c r="AL7" s="1" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="AM7" s="5">
         <v>5</v>
       </c>
       <c r="AO7" s="1" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="AP7" s="1" t="b">
         <v>1</v>
@@ -10406,13 +10406,13 @@
         <v>121</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="H8" s="1">
         <v>1</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>730</v>
+        <v>860</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>122</v>
@@ -10428,13 +10428,13 @@
         <v>124</v>
       </c>
       <c r="O8" s="11" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="P8" s="1" t="s">
         <v>38</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="R8" s="1" t="s">
         <v>125</v>
@@ -10449,10 +10449,10 @@
         <v>18</v>
       </c>
       <c r="W8" s="1" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="Y8" s="1" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="Z8" s="1" t="s">
         <v>88</v>
@@ -10461,7 +10461,7 @@
         <v>509</v>
       </c>
       <c r="AB8" s="1" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="AC8" s="1" t="s">
         <v>89</v>
@@ -10477,7 +10477,7 @@
         <v>12</v>
       </c>
       <c r="AO8" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AP8" s="1" t="b">
         <v>0</v>
@@ -10500,26 +10500,26 @@
         <v>130</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H9" s="1">
         <v>1</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>730</v>
+        <v>860</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>131</v>
       </c>
       <c r="L9" s="5"/>
       <c r="M9" s="1" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="P9" s="1" t="s">
         <v>132</v>
@@ -10534,7 +10534,7 @@
         <v>5</v>
       </c>
       <c r="Y9" s="1" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="Z9" s="1" t="s">
         <v>88</v>
@@ -10550,13 +10550,13 @@
         <v>91</v>
       </c>
       <c r="AL9" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="AM9" s="5">
         <v>6</v>
       </c>
       <c r="AO9" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AP9" s="1" t="b">
         <v>1</v>
@@ -10582,32 +10582,32 @@
         <v>136</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H10" s="1">
         <v>1</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="L10" s="5"/>
       <c r="M10" s="1" t="s">
         <v>137</v>
       </c>
       <c r="N10" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="O10" s="11" t="s">
         <v>780</v>
-      </c>
-      <c r="O10" s="11" t="s">
-        <v>781</v>
       </c>
       <c r="P10" s="1" t="s">
         <v>117</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="R10" s="1" t="s">
         <v>506</v>
@@ -10616,13 +10616,13 @@
         <v>46054</v>
       </c>
       <c r="T10" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="V10" s="1" t="s">
         <v>784</v>
       </c>
-      <c r="V10" s="1" t="s">
+      <c r="W10" s="1" t="s">
         <v>785</v>
-      </c>
-      <c r="W10" s="1" t="s">
-        <v>786</v>
       </c>
       <c r="Y10" s="1" t="s">
         <v>138</v>
@@ -10644,7 +10644,7 @@
         <v>7</v>
       </c>
       <c r="AO10" s="1" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="AP10" s="1" t="b">
         <v>0</v>
@@ -10722,7 +10722,7 @@
         <v>1</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>730</v>
+        <v>860</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>152</v>
@@ -10760,7 +10760,7 @@
         <v>9</v>
       </c>
       <c r="AO12" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AP12" s="1" t="b">
         <v>1</v>
@@ -10789,7 +10789,7 @@
         <v>1</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>730</v>
+        <v>860</v>
       </c>
       <c r="J13" s="1" t="s">
         <v>160</v>
@@ -10833,7 +10833,7 @@
         <v>11</v>
       </c>
       <c r="AO13" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AP13" s="1" t="b">
         <v>1</v>
@@ -10859,32 +10859,32 @@
         <v>170</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H14" s="1">
         <v>1</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>730</v>
+        <v>860</v>
       </c>
       <c r="J14" s="1" t="s">
+        <v>828</v>
+      </c>
+      <c r="K14" s="1" t="s">
         <v>829</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>830</v>
       </c>
       <c r="L14" s="5"/>
       <c r="M14" s="1" t="s">
         <v>171</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="Q14" s="1" t="s">
         <v>457</v>
@@ -10893,22 +10893,22 @@
         <v>125</v>
       </c>
       <c r="S14" s="1" t="s">
+        <v>794</v>
+      </c>
+      <c r="T14" s="1" t="s">
         <v>795</v>
-      </c>
-      <c r="T14" s="1" t="s">
-        <v>796</v>
       </c>
       <c r="U14" s="1">
         <v>8</v>
       </c>
       <c r="V14" s="1" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="W14" s="1" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="X14" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="Y14" s="1" t="s">
         <v>172</v>
@@ -10920,7 +10920,7 @@
         <v>509</v>
       </c>
       <c r="AB14" s="1" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="AC14" s="1" t="s">
         <v>89</v>
@@ -10945,7 +10945,7 @@
         <v>177</v>
       </c>
       <c r="AO14" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AP14" s="1" t="b">
         <v>1</v>
@@ -10971,26 +10971,26 @@
         <v>181</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H15" s="1">
         <v>1</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="J15" s="1" t="s">
         <v>182</v>
       </c>
       <c r="L15" s="5"/>
       <c r="M15" s="1" t="s">
+        <v>835</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>837</v>
+      </c>
+      <c r="O15" s="11" t="s">
         <v>836</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>838</v>
-      </c>
-      <c r="O15" s="11" t="s">
-        <v>837</v>
       </c>
       <c r="P15" s="1" t="s">
         <v>132</v>
@@ -11002,10 +11002,10 @@
         <v>96</v>
       </c>
       <c r="S15" s="1" t="s">
+        <v>838</v>
+      </c>
+      <c r="T15" s="1" t="s">
         <v>839</v>
-      </c>
-      <c r="T15" s="1" t="s">
-        <v>840</v>
       </c>
       <c r="U15" s="1">
         <v>9</v>
@@ -11014,7 +11014,7 @@
         <v>184</v>
       </c>
       <c r="W15" s="1" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="Y15" s="1" t="s">
         <v>185</v>
@@ -11045,7 +11045,7 @@
         <v>188</v>
       </c>
       <c r="AO15" s="1" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="AP15" s="1" t="b">
         <v>1</v>
@@ -11068,22 +11068,22 @@
         <v>190</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H16" s="1">
         <v>1</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>730</v>
+        <v>860</v>
       </c>
       <c r="J16" s="1" t="s">
         <v>191</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="L16" s="5"/>
       <c r="M16" s="1" t="s">
@@ -11102,7 +11102,7 @@
         <v>194</v>
       </c>
       <c r="W16" s="1" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="Y16" s="1" t="s">
         <v>195</v>
@@ -11130,7 +11130,7 @@
         <v>188</v>
       </c>
       <c r="AO16" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AP16" s="1" t="b">
         <v>1</v>
@@ -11153,16 +11153,16 @@
         <v>199</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H17" s="1">
         <v>1</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>730</v>
+        <v>860</v>
       </c>
       <c r="J17" s="1" t="s">
         <v>200</v>
@@ -11215,7 +11215,7 @@
         <v>175</v>
       </c>
       <c r="AO17" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AP17" s="1" t="b">
         <v>1</v>
@@ -11241,13 +11241,13 @@
         <v>207</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="H18" s="1">
         <v>1</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J18" s="1" t="s">
         <v>208</v>
@@ -11282,7 +11282,7 @@
         <v>6</v>
       </c>
       <c r="AO18" s="1" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="AP18" s="1" t="b">
         <v>1</v>
@@ -11308,19 +11308,19 @@
         <v>214</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="H19" s="1">
         <v>1</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>730</v>
+        <v>860</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="L19" s="5"/>
       <c r="M19" s="1" t="s">
@@ -11361,7 +11361,7 @@
         <v>5</v>
       </c>
       <c r="AO19" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AP19" s="1" t="b">
         <v>1</v>
@@ -11384,19 +11384,19 @@
         <v>222</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="H20" s="1">
         <v>1</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="L20" s="5"/>
       <c r="M20" s="1" t="s">
@@ -11440,7 +11440,7 @@
         <v>175</v>
       </c>
       <c r="AO20" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="AP20" s="1" t="b">
         <v>1</v>
@@ -11463,19 +11463,19 @@
         <v>226</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="H21" s="1">
         <v>1</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>730</v>
+        <v>860</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="K21" s="1" t="s">
         <v>152</v>
@@ -11513,7 +11513,7 @@
         <v>8</v>
       </c>
       <c r="AO21" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AP21" s="1" t="b">
         <v>1</v>
@@ -11576,16 +11576,16 @@
         <v>237</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="H23" s="1">
         <v>1</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>730</v>
+        <v>860</v>
       </c>
       <c r="J23" s="1" t="s">
         <v>238</v>
@@ -11626,7 +11626,7 @@
         <v>3</v>
       </c>
       <c r="AO23" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AP23" s="1" t="b">
         <v>1</v>
@@ -11649,13 +11649,13 @@
         <v>244</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="H24" s="1">
         <v>1</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="J24" s="1" t="s">
         <v>245</v>
@@ -11693,7 +11693,7 @@
         <v>9</v>
       </c>
       <c r="AO24" s="1" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="AP24" s="1" t="b">
         <v>0</v>
@@ -11757,7 +11757,7 @@
         <v>175</v>
       </c>
       <c r="AO25" s="1" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="AP25" s="1" t="b">
         <v>0</v>
@@ -11815,7 +11815,7 @@
         <v>11</v>
       </c>
       <c r="AO26" s="1" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="AP26" s="1" t="b">
         <v>1</v>
@@ -11844,7 +11844,7 @@
         <v>1</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>730</v>
+        <v>860</v>
       </c>
       <c r="J27" s="1" t="s">
         <v>271</v>
@@ -11885,7 +11885,7 @@
         <v>3</v>
       </c>
       <c r="AO27" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AP27" s="1" t="b">
         <v>1</v>
@@ -11908,13 +11908,13 @@
         <v>278</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H28" s="1">
         <v>-1</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>730</v>
+        <v>860</v>
       </c>
       <c r="J28" s="1" t="s">
         <v>279</v>
@@ -11961,7 +11961,7 @@
         <v>2</v>
       </c>
       <c r="AO28" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AP28" s="1" t="b">
         <v>1</v>
@@ -11984,13 +11984,13 @@
         <v>287</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="H29" s="1">
         <v>-1</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="J29" s="1" t="s">
         <v>288</v>
@@ -12034,7 +12034,7 @@
         <v>4</v>
       </c>
       <c r="AO29" s="1" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="AP29" s="1" t="b">
         <v>0</v>
@@ -12057,13 +12057,13 @@
         <v>297</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H30" s="1">
         <v>1</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="J30" s="1" t="s">
         <v>298</v>
@@ -12113,7 +12113,7 @@
         <v>91</v>
       </c>
       <c r="AO30" s="1" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="AP30" s="1" t="b">
         <v>1</v>
@@ -12186,7 +12186,7 @@
         <v>5</v>
       </c>
       <c r="AO31" s="1" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="AP31" s="1" t="b">
         <v>1</v>
@@ -12259,7 +12259,7 @@
         <v>6</v>
       </c>
       <c r="AO32" s="1" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="AP32" s="1" t="b">
         <v>1</v>
@@ -12326,7 +12326,7 @@
         <v>7</v>
       </c>
       <c r="AO33" s="1" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="AP33" s="1" t="b">
         <v>1</v>
@@ -12355,7 +12355,7 @@
         <v>1</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>730</v>
+        <v>860</v>
       </c>
       <c r="J34" s="1" t="s">
         <v>336</v>
@@ -12393,7 +12393,7 @@
         <v>8</v>
       </c>
       <c r="AO34" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AP34" s="1" t="b">
         <v>1</v>
@@ -12468,7 +12468,7 @@
         <v>1</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>730</v>
+        <v>860</v>
       </c>
       <c r="L36" s="5"/>
       <c r="R36" s="1" t="s">
@@ -12500,7 +12500,7 @@
         <v>351</v>
       </c>
       <c r="AO36" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AP36" s="1" t="b">
         <v>1</v>
@@ -12529,7 +12529,7 @@
         <v>-1</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>730</v>
+        <v>860</v>
       </c>
       <c r="J37" s="1" t="s">
         <v>358</v>
@@ -12570,7 +12570,7 @@
         <v>1</v>
       </c>
       <c r="AO37" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AP37" s="1" t="b">
         <v>1</v>
@@ -12593,13 +12593,13 @@
         <v>365</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="H38" s="1">
         <v>1</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>730</v>
+        <v>860</v>
       </c>
       <c r="J38" s="1" t="s">
         <v>366</v>
@@ -12643,7 +12643,7 @@
         <v>2</v>
       </c>
       <c r="AO38" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AP38" s="1" t="b">
         <v>1</v>
@@ -12672,7 +12672,7 @@
         <v>1</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>730</v>
+        <v>860</v>
       </c>
       <c r="J39" s="1" t="s">
         <v>371</v>
@@ -12713,7 +12713,7 @@
         <v>8</v>
       </c>
       <c r="AO39" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AP39" s="1" t="b">
         <v>1</v>
@@ -12736,13 +12736,13 @@
         <v>377</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="H40" s="1">
         <v>1</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="L40" s="5"/>
       <c r="M40" s="1" t="s">
@@ -12783,7 +12783,7 @@
         <v>9</v>
       </c>
       <c r="AO40" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="AP40" s="1" t="b">
         <v>1</v>
@@ -12812,7 +12812,7 @@
         <v>1</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>730</v>
+        <v>860</v>
       </c>
       <c r="J41" s="1" t="s">
         <v>385</v>
@@ -12853,7 +12853,7 @@
         <v>7</v>
       </c>
       <c r="AO41" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AP41" s="1" t="b">
         <v>1</v>
@@ -12882,7 +12882,7 @@
         <v>-1</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>730</v>
+        <v>860</v>
       </c>
       <c r="J42" s="1" t="s">
         <v>391</v>
@@ -12920,7 +12920,7 @@
         <v>6</v>
       </c>
       <c r="AO42" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AP42" s="1" t="b">
         <v>1</v>
@@ -12949,7 +12949,7 @@
         <v>-1</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>730</v>
+        <v>860</v>
       </c>
       <c r="J43" s="1" t="s">
         <v>396</v>
@@ -12996,7 +12996,7 @@
         <v>3</v>
       </c>
       <c r="AO43" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AP43" s="1" t="b">
         <v>1</v>
@@ -13025,7 +13025,7 @@
         <v>-1</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>730</v>
+        <v>860</v>
       </c>
       <c r="L44" s="5"/>
       <c r="Y44" s="1" t="s">
@@ -13054,7 +13054,7 @@
         <v>4</v>
       </c>
       <c r="AO44" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AP44" s="1" t="b">
         <v>1</v>
@@ -13077,13 +13077,13 @@
         <v>409</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="H45" s="1">
         <v>-1</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>730</v>
+        <v>860</v>
       </c>
       <c r="J45" s="1" t="s">
         <v>410</v>
@@ -13127,7 +13127,7 @@
         <v>5</v>
       </c>
       <c r="AO45" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AP45" s="1" t="b">
         <v>1</v>
@@ -13260,7 +13260,7 @@
         <v>5</v>
       </c>
       <c r="F48" s="22" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>431</v>
@@ -13322,7 +13322,7 @@
         <v>1</v>
       </c>
       <c r="AO48" s="1" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="AP48" s="1" t="b">
         <v>1</v>
@@ -13345,7 +13345,7 @@
         <v>442</v>
       </c>
       <c r="F49" s="22" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>443</v>
@@ -13410,7 +13410,7 @@
         <v>10</v>
       </c>
       <c r="AO49" s="1" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="AP49" s="1" t="b">
         <v>1</v>
@@ -13433,7 +13433,7 @@
         <v>452</v>
       </c>
       <c r="F50" s="22" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>453</v>
@@ -13442,7 +13442,7 @@
         <v>1</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="J50" s="1" t="s">
         <v>454</v>
@@ -13507,7 +13507,7 @@
         <v>9</v>
       </c>
       <c r="AO50" s="1" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="AP50" s="1" t="b">
         <v>1</v>
@@ -13539,7 +13539,7 @@
         <v>1</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>730</v>
+        <v>860</v>
       </c>
       <c r="J51" s="1" t="s">
         <v>466</v>
@@ -13598,7 +13598,7 @@
         <v>8</v>
       </c>
       <c r="AO51" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AP51" s="1" t="b">
         <v>1</v>
@@ -13686,7 +13686,7 @@
         <v>2</v>
       </c>
       <c r="AO52" s="1" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="AP52" s="1" t="b">
         <v>1</v>
@@ -13709,7 +13709,7 @@
         <v>488</v>
       </c>
       <c r="F53" s="22" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>489</v>
@@ -13767,7 +13767,7 @@
         <v>3</v>
       </c>
       <c r="AO53" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="AP53" s="1" t="b">
         <v>1</v>
@@ -13846,7 +13846,7 @@
         <v>7</v>
       </c>
       <c r="AO54" s="1" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="AP54" s="1" t="b">
         <v>1</v>
@@ -13973,7 +13973,7 @@
         <v>523</v>
       </c>
       <c r="F57" s="22" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>524</v>
@@ -13982,7 +13982,7 @@
         <v>1</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>730</v>
+        <v>860</v>
       </c>
       <c r="J57" s="1" t="s">
         <v>525</v>
@@ -14038,7 +14038,7 @@
         <v>4</v>
       </c>
       <c r="AO57" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AP57" s="1" t="b">
         <v>1</v>
@@ -14061,13 +14061,13 @@
         <v>539</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H58" s="1">
         <v>-1</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>730</v>
+        <v>860</v>
       </c>
       <c r="J58" s="1" t="s">
         <v>540</v>
@@ -14114,7 +14114,7 @@
         <v>91</v>
       </c>
       <c r="AO58" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AP58" s="1" t="b">
         <v>1</v>
@@ -14143,7 +14143,7 @@
         <v>1</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>730</v>
+        <v>860</v>
       </c>
       <c r="J59" s="1" t="s">
         <v>548</v>
@@ -14193,7 +14193,7 @@
         <v>91</v>
       </c>
       <c r="AO59" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AP59" s="1" t="b">
         <v>1</v>
@@ -14216,7 +14216,7 @@
         <v>553</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>554</v>
@@ -14225,7 +14225,7 @@
         <v>1</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>730</v>
+        <v>860</v>
       </c>
       <c r="J60" s="1" t="s">
         <v>555</v>
@@ -14272,7 +14272,7 @@
         <v>8</v>
       </c>
       <c r="AO60" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AP60" s="1" t="b">
         <v>1</v>
@@ -14301,7 +14301,7 @@
         <v>-1</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>730</v>
+        <v>860</v>
       </c>
       <c r="J61" s="1" t="s">
         <v>561</v>
@@ -14345,7 +14345,7 @@
         <v>6</v>
       </c>
       <c r="AO61" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AP61" s="1" t="b">
         <v>1</v>
@@ -14374,7 +14374,7 @@
         <v>1</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>730</v>
+        <v>860</v>
       </c>
       <c r="J62" s="1" t="s">
         <v>568</v>
@@ -14415,7 +14415,7 @@
         <v>2</v>
       </c>
       <c r="AO62" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AP62" s="1" t="b">
         <v>1</v>
@@ -14444,7 +14444,7 @@
         <v>1</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>730</v>
+        <v>860</v>
       </c>
       <c r="J63" s="1" t="s">
         <v>576</v>
@@ -14485,7 +14485,7 @@
         <v>3</v>
       </c>
       <c r="AO63" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AP63" s="1" t="b">
         <v>1</v>
@@ -14647,7 +14647,7 @@
         <v>10</v>
       </c>
       <c r="AO66" s="1" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="AP66" s="1" t="b">
         <v>1</v>
@@ -14717,7 +14717,7 @@
         <v>11</v>
       </c>
       <c r="AO67" s="1" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="AP67" s="1" t="b">
         <v>1</v>
@@ -14740,13 +14740,13 @@
         <v>605</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="H68" s="1">
         <v>1</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>730</v>
+        <v>860</v>
       </c>
       <c r="J68" s="1" t="s">
         <v>606</v>
@@ -14793,7 +14793,7 @@
         <v>4</v>
       </c>
       <c r="AO68" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AP68" s="1" t="b">
         <v>1</v>
@@ -14822,7 +14822,7 @@
         <v>-1</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>730</v>
+        <v>860</v>
       </c>
       <c r="J69" s="1" t="s">
         <v>611</v>
@@ -14866,7 +14866,7 @@
         <v>7</v>
       </c>
       <c r="AO69" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AP69" s="1" t="b">
         <v>1</v>
@@ -15153,33 +15153,33 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>848</v>
+      </c>
+      <c r="B10" t="s">
         <v>849</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>850</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>851</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>852</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>853</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>854</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>855</v>
-      </c>
-      <c r="H10" t="s">
-        <v>856</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B11" t="b">
         <v>1</v>

--- a/data/common_project_data/indicators-master.xlsx
+++ b/data/common_project_data/indicators-master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steve.crawshaw\projects\weca_regional_indicators\data\common_project_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ED97C362-6935-463D-B7F6-0A254EF57198}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{29DC0B27-D526-4626-A7EF-A7CBC75C7DB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="fact_indicator_observation" sheetId="3" r:id="rId1"/>
@@ -1048,9 +1048,6 @@
     <t>3.C.3</t>
   </si>
   <si>
-    <t>Private rental affordability (ratio of average income to rental price)</t>
-  </si>
-  <si>
     <t>Average income</t>
   </si>
   <si>
@@ -2680,6 +2677,9 @@
   </si>
   <si>
     <t>%</t>
+  </si>
+  <si>
+    <t>Private monthly rental prices</t>
   </si>
 </sst>
 </file>
@@ -3539,42 +3539,42 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="B1" s="13" t="s">
         <v>612</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="C1" s="13" t="s">
         <v>613</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="D1" s="13" t="s">
         <v>614</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="E1" s="13" t="s">
         <v>615</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="F1" s="13" t="s">
         <v>616</v>
-      </c>
-      <c r="F1" s="13" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>39</v>
       </c>
       <c r="C2" s="14" t="s">
+        <v>618</v>
+      </c>
+      <c r="D2" s="14" t="s">
         <v>619</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="E2" s="14" t="s">
         <v>620</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="F2" s="14" t="s">
         <v>621</v>
-      </c>
-      <c r="F2" s="14" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -9748,16 +9748,16 @@
         <v>37</v>
       </c>
       <c r="AM1" s="26" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="AN1" s="3" t="s">
         <v>38</v>
       </c>
       <c r="AO1" s="3" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="AP1" s="3" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="AQ1" s="2"/>
     </row>
@@ -9877,16 +9877,16 @@
         <v>76</v>
       </c>
       <c r="AM2" s="27" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="AN2" s="12" t="s">
         <v>77</v>
       </c>
       <c r="AO2" s="12" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="AP2" s="12" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="AQ2" s="2"/>
     </row>
@@ -9910,13 +9910,13 @@
         <v>83</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H3" s="1">
         <v>1</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>84</v>
@@ -9926,13 +9926,13 @@
       </c>
       <c r="L3" s="5"/>
       <c r="M3" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>730</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="O3" s="11" t="s">
         <v>731</v>
-      </c>
-      <c r="O3" s="11" t="s">
-        <v>732</v>
       </c>
       <c r="P3" s="1" t="s">
         <v>117</v>
@@ -9944,7 +9944,7 @@
         <v>183</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="T3" s="23">
         <v>46133</v>
@@ -9953,10 +9953,10 @@
         <v>4</v>
       </c>
       <c r="W3" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="Y3" s="1" t="s">
         <v>735</v>
-      </c>
-      <c r="Y3" s="1" t="s">
-        <v>736</v>
       </c>
       <c r="Z3" s="1" t="s">
         <v>88</v>
@@ -9965,7 +9965,7 @@
         <v>173</v>
       </c>
       <c r="AB3" s="1" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="AC3" s="1" t="s">
         <v>89</v>
@@ -9978,13 +9978,13 @@
         <v>91</v>
       </c>
       <c r="AL3" s="1" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="AM3" s="5">
         <v>3</v>
       </c>
       <c r="AO3" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="AP3" s="1" t="b">
         <v>1</v>
@@ -10010,13 +10010,13 @@
         <v>94</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H4" s="1">
         <v>1</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>95</v>
@@ -10026,16 +10026,16 @@
         <v>86</v>
       </c>
       <c r="N4" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="O4" s="11" t="s">
+        <v>739</v>
+      </c>
+      <c r="P4" s="1" t="s">
         <v>741</v>
       </c>
-      <c r="O4" s="11" t="s">
-        <v>740</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>742</v>
-      </c>
       <c r="Q4" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="R4" s="1" t="s">
         <v>96</v>
@@ -10053,22 +10053,22 @@
         <v>98</v>
       </c>
       <c r="W4" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="X4" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="Y4" s="1" t="s">
         <v>743</v>
-      </c>
-      <c r="X4" s="1" t="s">
-        <v>750</v>
-      </c>
-      <c r="Y4" s="1" t="s">
-        <v>744</v>
       </c>
       <c r="Z4" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AA4" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AB4" s="1" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="AC4" s="1" t="s">
         <v>89</v>
@@ -10084,7 +10084,7 @@
         <v>4</v>
       </c>
       <c r="AO4" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AP4" s="1" t="b">
         <v>1</v>
@@ -10110,16 +10110,16 @@
         <v>103</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H5" s="1">
         <v>1</v>
       </c>
       <c r="I5" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>746</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>747</v>
       </c>
       <c r="L5" s="5">
         <v>2020</v>
@@ -10128,10 +10128,10 @@
         <v>104</v>
       </c>
       <c r="N5" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="O5" s="11" t="s">
         <v>748</v>
-      </c>
-      <c r="O5" s="11" t="s">
-        <v>749</v>
       </c>
       <c r="P5" s="1" t="s">
         <v>105</v>
@@ -10146,28 +10146,28 @@
         <v>2023</v>
       </c>
       <c r="T5" s="24" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="U5" s="1">
         <v>16</v>
       </c>
       <c r="W5" s="1" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="X5" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="Y5" s="1" t="s">
         <v>751</v>
-      </c>
-      <c r="Y5" s="1" t="s">
-        <v>752</v>
       </c>
       <c r="Z5" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AA5" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AB5" s="1" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="AC5" s="1" t="s">
         <v>89</v>
@@ -10183,7 +10183,7 @@
         <v>1</v>
       </c>
       <c r="AO5" s="1" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="AP5" s="1" t="b">
         <v>1</v>
@@ -10209,7 +10209,7 @@
         <v>110</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H6" s="1">
         <v>1</v>
@@ -10218,20 +10218,20 @@
         <v>111</v>
       </c>
       <c r="J6" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>758</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>759</v>
       </c>
       <c r="L6" s="5"/>
       <c r="M6" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="N6" s="1" t="s">
         <v>760</v>
       </c>
-      <c r="N6" s="1" t="s">
+      <c r="O6" s="11" t="s">
         <v>761</v>
-      </c>
-      <c r="O6" s="11" t="s">
-        <v>762</v>
       </c>
       <c r="P6" s="1" t="s">
         <v>105</v>
@@ -10252,10 +10252,10 @@
         <v>18</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="Y6" s="1" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="Z6" s="1" t="s">
         <v>88</v>
@@ -10264,7 +10264,7 @@
         <v>173</v>
       </c>
       <c r="AB6" s="1" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="AC6" s="1" t="s">
         <v>89</v>
@@ -10277,13 +10277,13 @@
         <v>113</v>
       </c>
       <c r="AL6" s="1" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="AM6" s="5">
         <v>2</v>
       </c>
       <c r="AO6" s="1" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="AP6" s="1" t="b">
         <v>1</v>
@@ -10306,10 +10306,10 @@
         <v>115</v>
       </c>
       <c r="F7" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>768</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>769</v>
       </c>
       <c r="H7" s="1">
         <v>1</v>
@@ -10318,23 +10318,23 @@
         <v>116</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="L7" s="5"/>
       <c r="M7" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="N7" s="1" t="s">
         <v>770</v>
       </c>
-      <c r="N7" s="1" t="s">
+      <c r="O7" s="11" t="s">
         <v>771</v>
-      </c>
-      <c r="O7" s="11" t="s">
-        <v>772</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>117</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="R7" s="1" t="s">
         <v>87</v>
@@ -10349,19 +10349,19 @@
         <v>1</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="Z7" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AA7" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AB7" s="1" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="AC7" s="1" t="s">
         <v>89</v>
@@ -10374,13 +10374,13 @@
         <v>91</v>
       </c>
       <c r="AL7" s="1" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="AM7" s="5">
         <v>5</v>
       </c>
       <c r="AO7" s="1" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="AP7" s="1" t="b">
         <v>1</v>
@@ -10406,13 +10406,13 @@
         <v>121</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H8" s="1">
         <v>1</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>122</v>
@@ -10428,13 +10428,13 @@
         <v>124</v>
       </c>
       <c r="O8" s="11" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="P8" s="1" t="s">
         <v>38</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="R8" s="1" t="s">
         <v>125</v>
@@ -10449,19 +10449,19 @@
         <v>18</v>
       </c>
       <c r="W8" s="1" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="Y8" s="1" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="Z8" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AA8" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AB8" s="1" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="AC8" s="1" t="s">
         <v>89</v>
@@ -10477,7 +10477,7 @@
         <v>12</v>
       </c>
       <c r="AO8" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="AP8" s="1" t="b">
         <v>0</v>
@@ -10500,26 +10500,26 @@
         <v>130</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="H9" s="1">
         <v>1</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>131</v>
       </c>
       <c r="L9" s="5"/>
       <c r="M9" s="1" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="P9" s="1" t="s">
         <v>132</v>
@@ -10534,7 +10534,7 @@
         <v>5</v>
       </c>
       <c r="Y9" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="Z9" s="1" t="s">
         <v>88</v>
@@ -10550,13 +10550,13 @@
         <v>91</v>
       </c>
       <c r="AL9" s="1" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="AM9" s="5">
         <v>6</v>
       </c>
       <c r="AO9" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="AP9" s="1" t="b">
         <v>1</v>
@@ -10582,47 +10582,47 @@
         <v>136</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H10" s="1">
         <v>1</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="L10" s="5"/>
       <c r="M10" s="1" t="s">
         <v>137</v>
       </c>
       <c r="N10" s="1" t="s">
+        <v>778</v>
+      </c>
+      <c r="O10" s="11" t="s">
         <v>779</v>
-      </c>
-      <c r="O10" s="11" t="s">
-        <v>780</v>
       </c>
       <c r="P10" s="1" t="s">
         <v>117</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="S10" s="24">
         <v>46054</v>
       </c>
       <c r="T10" s="1" t="s">
+        <v>782</v>
+      </c>
+      <c r="V10" s="1" t="s">
         <v>783</v>
       </c>
-      <c r="V10" s="1" t="s">
+      <c r="W10" s="1" t="s">
         <v>784</v>
-      </c>
-      <c r="W10" s="1" t="s">
-        <v>785</v>
       </c>
       <c r="Y10" s="1" t="s">
         <v>138</v>
@@ -10644,7 +10644,7 @@
         <v>7</v>
       </c>
       <c r="AO10" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AP10" s="1" t="b">
         <v>0</v>
@@ -10722,7 +10722,7 @@
         <v>1</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>152</v>
@@ -10760,7 +10760,7 @@
         <v>9</v>
       </c>
       <c r="AO12" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="AP12" s="1" t="b">
         <v>1</v>
@@ -10789,7 +10789,7 @@
         <v>1</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="J13" s="1" t="s">
         <v>160</v>
@@ -10833,7 +10833,7 @@
         <v>11</v>
       </c>
       <c r="AO13" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="AP13" s="1" t="b">
         <v>1</v>
@@ -10859,56 +10859,56 @@
         <v>170</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="H14" s="1">
         <v>1</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="J14" s="1" t="s">
+        <v>827</v>
+      </c>
+      <c r="K14" s="1" t="s">
         <v>828</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>829</v>
       </c>
       <c r="L14" s="5"/>
       <c r="M14" s="1" t="s">
         <v>171</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="R14" s="1" t="s">
         <v>125</v>
       </c>
       <c r="S14" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="T14" s="1" t="s">
         <v>794</v>
-      </c>
-      <c r="T14" s="1" t="s">
-        <v>795</v>
       </c>
       <c r="U14" s="1">
         <v>8</v>
       </c>
       <c r="V14" s="1" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="W14" s="1" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="X14" s="1" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="Y14" s="1" t="s">
         <v>172</v>
@@ -10917,10 +10917,10 @@
         <v>88</v>
       </c>
       <c r="AA14" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AB14" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AC14" s="1" t="s">
         <v>89</v>
@@ -10945,7 +10945,7 @@
         <v>177</v>
       </c>
       <c r="AO14" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="AP14" s="1" t="b">
         <v>1</v>
@@ -10971,41 +10971,41 @@
         <v>181</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H15" s="1">
         <v>1</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="J15" s="1" t="s">
         <v>182</v>
       </c>
       <c r="L15" s="5"/>
       <c r="M15" s="1" t="s">
+        <v>834</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>836</v>
+      </c>
+      <c r="O15" s="11" t="s">
         <v>835</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>837</v>
-      </c>
-      <c r="O15" s="11" t="s">
-        <v>836</v>
       </c>
       <c r="P15" s="1" t="s">
         <v>132</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="R15" s="1" t="s">
         <v>96</v>
       </c>
       <c r="S15" s="1" t="s">
+        <v>837</v>
+      </c>
+      <c r="T15" s="1" t="s">
         <v>838</v>
-      </c>
-      <c r="T15" s="1" t="s">
-        <v>839</v>
       </c>
       <c r="U15" s="1">
         <v>9</v>
@@ -11014,7 +11014,7 @@
         <v>184</v>
       </c>
       <c r="W15" s="1" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Y15" s="1" t="s">
         <v>185</v>
@@ -11045,7 +11045,7 @@
         <v>188</v>
       </c>
       <c r="AO15" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AP15" s="1" t="b">
         <v>1</v>
@@ -11068,22 +11068,22 @@
         <v>190</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H16" s="1">
         <v>1</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="J16" s="1" t="s">
         <v>191</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L16" s="5"/>
       <c r="M16" s="1" t="s">
@@ -11102,7 +11102,7 @@
         <v>194</v>
       </c>
       <c r="W16" s="1" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Y16" s="1" t="s">
         <v>195</v>
@@ -11130,7 +11130,7 @@
         <v>188</v>
       </c>
       <c r="AO16" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="AP16" s="1" t="b">
         <v>1</v>
@@ -11153,16 +11153,16 @@
         <v>199</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H17" s="1">
         <v>1</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="J17" s="1" t="s">
         <v>200</v>
@@ -11215,7 +11215,7 @@
         <v>175</v>
       </c>
       <c r="AO17" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="AP17" s="1" t="b">
         <v>1</v>
@@ -11241,13 +11241,13 @@
         <v>207</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H18" s="1">
         <v>1</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="J18" s="1" t="s">
         <v>208</v>
@@ -11282,7 +11282,7 @@
         <v>6</v>
       </c>
       <c r="AO18" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AP18" s="1" t="b">
         <v>1</v>
@@ -11308,19 +11308,19 @@
         <v>214</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H19" s="1">
         <v>1</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="L19" s="5"/>
       <c r="M19" s="1" t="s">
@@ -11361,7 +11361,7 @@
         <v>5</v>
       </c>
       <c r="AO19" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="AP19" s="1" t="b">
         <v>1</v>
@@ -11384,19 +11384,19 @@
         <v>222</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="H20" s="1">
         <v>1</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="L20" s="5"/>
       <c r="M20" s="1" t="s">
@@ -11440,7 +11440,7 @@
         <v>175</v>
       </c>
       <c r="AO20" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="AP20" s="1" t="b">
         <v>1</v>
@@ -11463,19 +11463,19 @@
         <v>226</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="H21" s="1">
         <v>1</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="K21" s="1" t="s">
         <v>152</v>
@@ -11513,7 +11513,7 @@
         <v>8</v>
       </c>
       <c r="AO21" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="AP21" s="1" t="b">
         <v>1</v>
@@ -11576,16 +11576,16 @@
         <v>237</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="H23" s="1">
         <v>1</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="J23" s="1" t="s">
         <v>238</v>
@@ -11626,7 +11626,7 @@
         <v>3</v>
       </c>
       <c r="AO23" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="AP23" s="1" t="b">
         <v>1</v>
@@ -11649,13 +11649,13 @@
         <v>244</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="H24" s="1">
         <v>1</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="J24" s="1" t="s">
         <v>245</v>
@@ -11693,7 +11693,7 @@
         <v>9</v>
       </c>
       <c r="AO24" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AP24" s="1" t="b">
         <v>0</v>
@@ -11757,7 +11757,7 @@
         <v>175</v>
       </c>
       <c r="AO25" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AP25" s="1" t="b">
         <v>0</v>
@@ -11815,7 +11815,7 @@
         <v>11</v>
       </c>
       <c r="AO26" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AP26" s="1" t="b">
         <v>1</v>
@@ -11844,7 +11844,7 @@
         <v>1</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="J27" s="1" t="s">
         <v>271</v>
@@ -11885,7 +11885,7 @@
         <v>3</v>
       </c>
       <c r="AO27" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="AP27" s="1" t="b">
         <v>1</v>
@@ -11908,13 +11908,13 @@
         <v>278</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H28" s="1">
         <v>-1</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="J28" s="1" t="s">
         <v>279</v>
@@ -11961,7 +11961,7 @@
         <v>2</v>
       </c>
       <c r="AO28" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="AP28" s="1" t="b">
         <v>1</v>
@@ -11984,13 +11984,13 @@
         <v>287</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="H29" s="1">
         <v>-1</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="J29" s="1" t="s">
         <v>288</v>
@@ -12034,7 +12034,7 @@
         <v>4</v>
       </c>
       <c r="AO29" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AP29" s="1" t="b">
         <v>0</v>
@@ -12057,13 +12057,13 @@
         <v>297</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H30" s="1">
         <v>1</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="J30" s="1" t="s">
         <v>298</v>
@@ -12113,7 +12113,7 @@
         <v>91</v>
       </c>
       <c r="AO30" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AP30" s="1" t="b">
         <v>1</v>
@@ -12186,7 +12186,7 @@
         <v>5</v>
       </c>
       <c r="AO31" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="AP31" s="1" t="b">
         <v>1</v>
@@ -12209,19 +12209,19 @@
         <v>317</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>318</v>
+        <v>860</v>
       </c>
       <c r="H32" s="1">
         <v>1</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>308</v>
+        <v>116</v>
       </c>
       <c r="J32" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="K32" s="1" t="s">
         <v>319</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>320</v>
       </c>
       <c r="L32" s="5"/>
       <c r="M32" s="1" t="s">
@@ -12231,13 +12231,13 @@
         <v>96</v>
       </c>
       <c r="T32" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="U32" s="1">
         <v>6</v>
       </c>
       <c r="Y32" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="Z32" s="1" t="s">
         <v>139</v>
@@ -12259,7 +12259,7 @@
         <v>6</v>
       </c>
       <c r="AO32" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="AP32" s="1" t="b">
         <v>1</v>
@@ -12267,7 +12267,7 @@
     </row>
     <row r="33" spans="1:42" ht="60" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>260</v>
@@ -12279,23 +12279,23 @@
         <v>296</v>
       </c>
       <c r="E33" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="F33" s="1" t="s">
         <v>324</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>325</v>
       </c>
       <c r="H33" s="1">
         <v>-1</v>
       </c>
       <c r="I33" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="J33" s="1" t="s">
         <v>326</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>327</v>
       </c>
       <c r="L33" s="5"/>
       <c r="M33" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="R33" s="1" t="s">
         <v>183</v>
@@ -12304,7 +12304,7 @@
         <v>6</v>
       </c>
       <c r="Y33" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="Z33" s="1" t="s">
         <v>88</v>
@@ -12317,16 +12317,16 @@
       </c>
       <c r="AG33" s="6"/>
       <c r="AI33" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="AL33" s="1" t="s">
         <v>330</v>
-      </c>
-      <c r="AL33" s="1" t="s">
-        <v>331</v>
       </c>
       <c r="AM33" s="5">
         <v>7</v>
       </c>
       <c r="AO33" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AP33" s="1" t="b">
         <v>1</v>
@@ -12334,7 +12334,7 @@
     </row>
     <row r="34" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>260</v>
@@ -12343,29 +12343,29 @@
         <v>261</v>
       </c>
       <c r="D34" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="F34" s="1" t="s">
         <v>334</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>335</v>
       </c>
       <c r="H34" s="1">
         <v>1</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="J34" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="K34" s="1" t="s">
         <v>336</v>
-      </c>
-      <c r="K34" s="1" t="s">
-        <v>337</v>
       </c>
       <c r="L34" s="5"/>
       <c r="M34" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="R34" s="1" t="s">
         <v>183</v>
@@ -12374,7 +12374,7 @@
         <v>6</v>
       </c>
       <c r="Y34" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="Z34" s="1" t="s">
         <v>88</v>
@@ -12387,13 +12387,13 @@
       </c>
       <c r="AG34" s="6"/>
       <c r="AL34" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AM34" s="5">
         <v>8</v>
       </c>
       <c r="AO34" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="AP34" s="1" t="b">
         <v>1</v>
@@ -12401,7 +12401,7 @@
     </row>
     <row r="35" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>260</v>
@@ -12410,20 +12410,20 @@
         <v>261</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E35" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="F35" s="1" t="s">
         <v>342</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>343</v>
       </c>
       <c r="H35" s="1">
         <v>1</v>
       </c>
       <c r="L35" s="5"/>
       <c r="Y35" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="Z35" s="1" t="s">
         <v>147</v>
@@ -12436,7 +12436,7 @@
       </c>
       <c r="AG35" s="6"/>
       <c r="AL35" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AM35" s="5">
         <v>9</v>
@@ -12447,7 +12447,7 @@
     </row>
     <row r="36" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>260</v>
@@ -12456,10 +12456,10 @@
         <v>261</v>
       </c>
       <c r="D36" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>347</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>348</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>159</v>
@@ -12468,7 +12468,7 @@
         <v>1</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="L36" s="5"/>
       <c r="R36" s="1" t="s">
@@ -12481,7 +12481,7 @@
         <v>9</v>
       </c>
       <c r="Y36" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AF36" s="1" t="s">
         <v>267</v>
@@ -12491,16 +12491,16 @@
         <v>91</v>
       </c>
       <c r="AL36" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AM36" s="5">
         <v>10</v>
       </c>
       <c r="AN36" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AO36" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="AP36" s="1" t="b">
         <v>1</v>
@@ -12508,38 +12508,38 @@
     </row>
     <row r="37" spans="1:42" ht="60" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="C37" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="D37" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="E37" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="F37" s="1" t="s">
         <v>356</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>357</v>
       </c>
       <c r="H37" s="1">
         <v>-1</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="J37" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="K37" s="1" t="s">
         <v>358</v>
-      </c>
-      <c r="K37" s="1" t="s">
-        <v>359</v>
       </c>
       <c r="L37" s="5"/>
       <c r="M37" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="R37" s="1" t="s">
         <v>96</v>
@@ -12551,7 +12551,7 @@
         <v>4</v>
       </c>
       <c r="Y37" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="Z37" s="1" t="s">
         <v>88</v>
@@ -12560,17 +12560,17 @@
         <v>89</v>
       </c>
       <c r="AF37" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG37" s="6"/>
       <c r="AL37" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AM37" s="5">
         <v>1</v>
       </c>
       <c r="AO37" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="AP37" s="1" t="b">
         <v>1</v>
@@ -12578,38 +12578,38 @@
     </row>
     <row r="38" spans="1:42" ht="60" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="E38" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="B38" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>365</v>
-      </c>
       <c r="F38" s="1" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="H38" s="1">
         <v>1</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="L38" s="5"/>
       <c r="M38" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="R38" s="1" t="s">
         <v>96</v>
@@ -12621,7 +12621,7 @@
         <v>4</v>
       </c>
       <c r="Y38" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="Z38" s="1" t="s">
         <v>88</v>
@@ -12630,20 +12630,20 @@
         <v>89</v>
       </c>
       <c r="AF38" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG38" s="6"/>
       <c r="AI38" s="1" t="s">
         <v>91</v>
       </c>
       <c r="AL38" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AM38" s="5">
         <v>2</v>
       </c>
       <c r="AO38" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="AP38" s="1" t="b">
         <v>1</v>
@@ -12651,38 +12651,38 @@
     </row>
     <row r="39" spans="1:42" ht="60" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="E39" s="1" t="s">
+      <c r="F39" s="1" t="s">
         <v>369</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>370</v>
       </c>
       <c r="H39" s="1">
         <v>1</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="J39" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="K39" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="K39" s="1" t="s">
-        <v>372</v>
       </c>
       <c r="L39" s="5"/>
       <c r="M39" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="R39" s="1" t="s">
         <v>96</v>
@@ -12694,7 +12694,7 @@
         <v>4</v>
       </c>
       <c r="Y39" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="Z39" s="1" t="s">
         <v>88</v>
@@ -12703,17 +12703,17 @@
         <v>89</v>
       </c>
       <c r="AF39" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG39" s="6"/>
       <c r="AL39" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AM39" s="5">
         <v>8</v>
       </c>
       <c r="AO39" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="AP39" s="1" t="b">
         <v>1</v>
@@ -12721,32 +12721,32 @@
     </row>
     <row r="40" spans="1:42" ht="60" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="B40" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>377</v>
-      </c>
       <c r="F40" s="1" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="H40" s="1">
         <v>1</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="L40" s="5"/>
       <c r="M40" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="R40" s="1" t="s">
         <v>96</v>
@@ -12758,10 +12758,10 @@
         <v>4</v>
       </c>
       <c r="V40" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="Y40" s="1" t="s">
         <v>378</v>
-      </c>
-      <c r="Y40" s="1" t="s">
-        <v>379</v>
       </c>
       <c r="Z40" s="1" t="s">
         <v>88</v>
@@ -12770,20 +12770,20 @@
         <v>89</v>
       </c>
       <c r="AF40" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG40" s="6"/>
       <c r="AI40" s="1" t="s">
         <v>91</v>
       </c>
       <c r="AL40" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AM40" s="5">
         <v>9</v>
       </c>
       <c r="AO40" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="AP40" s="1" t="b">
         <v>1</v>
@@ -12791,38 +12791,38 @@
     </row>
     <row r="41" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B41" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="D41" s="1" t="s">
+      <c r="E41" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="F41" s="1" t="s">
         <v>383</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>384</v>
       </c>
       <c r="H41" s="1">
         <v>1</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="J41" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="K41" s="1" t="s">
         <v>385</v>
-      </c>
-      <c r="K41" s="1" t="s">
-        <v>386</v>
       </c>
       <c r="L41" s="5"/>
       <c r="M41" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="R41" s="1" t="s">
         <v>183</v>
@@ -12831,7 +12831,7 @@
         <v>3</v>
       </c>
       <c r="Y41" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="Z41" s="1" t="s">
         <v>88</v>
@@ -12840,20 +12840,20 @@
         <v>89</v>
       </c>
       <c r="AF41" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG41" s="6"/>
       <c r="AI41" s="1" t="s">
         <v>91</v>
       </c>
       <c r="AL41" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AM41" s="5">
         <v>7</v>
       </c>
       <c r="AO41" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="AP41" s="1" t="b">
         <v>1</v>
@@ -12861,38 +12861,38 @@
     </row>
     <row r="42" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="E42" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="B42" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="E42" s="1" t="s">
+      <c r="F42" s="1" t="s">
         <v>389</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>390</v>
       </c>
       <c r="H42" s="1">
         <v>-1</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="L42" s="5"/>
       <c r="M42" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="R42" s="1" t="s">
         <v>183</v>
@@ -12901,7 +12901,7 @@
         <v>3</v>
       </c>
       <c r="Y42" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="Z42" s="1" t="s">
         <v>88</v>
@@ -12910,17 +12910,17 @@
         <v>89</v>
       </c>
       <c r="AF42" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG42" s="6"/>
       <c r="AL42" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AM42" s="5">
         <v>6</v>
       </c>
       <c r="AO42" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="AP42" s="1" t="b">
         <v>1</v>
@@ -12928,38 +12928,38 @@
     </row>
     <row r="43" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="E43" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="B43" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="E43" s="1" t="s">
+      <c r="F43" s="1" t="s">
         <v>394</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>395</v>
       </c>
       <c r="H43" s="1">
         <v>-1</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="J43" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="K43" s="1" t="s">
         <v>396</v>
-      </c>
-      <c r="K43" s="1" t="s">
-        <v>397</v>
       </c>
       <c r="L43" s="5"/>
       <c r="M43" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="P43" s="1" t="s">
         <v>117</v>
@@ -12968,13 +12968,13 @@
         <v>96</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="U43" s="1">
         <v>10</v>
       </c>
       <c r="Y43" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="Z43" s="1" t="s">
         <v>88</v>
@@ -12983,20 +12983,20 @@
         <v>89</v>
       </c>
       <c r="AF43" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG43" s="6"/>
       <c r="AI43" s="1" t="s">
         <v>91</v>
       </c>
       <c r="AL43" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AM43" s="5">
         <v>3</v>
       </c>
       <c r="AO43" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="AP43" s="1" t="b">
         <v>1</v>
@@ -13004,57 +13004,57 @@
     </row>
     <row r="44" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="E44" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="E44" s="1" t="s">
+      <c r="F44" s="1" t="s">
         <v>402</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>403</v>
       </c>
       <c r="H44" s="1">
         <v>-1</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="L44" s="5"/>
       <c r="Y44" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Z44" s="1" t="s">
         <v>139</v>
       </c>
       <c r="AB44" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AC44" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AF44" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG44" s="6"/>
       <c r="AI44" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="AL44" s="1" t="s">
         <v>406</v>
-      </c>
-      <c r="AL44" s="1" t="s">
-        <v>407</v>
       </c>
       <c r="AM44" s="5">
         <v>4</v>
       </c>
       <c r="AO44" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="AP44" s="1" t="b">
         <v>1</v>
@@ -13062,34 +13062,34 @@
     </row>
     <row r="45" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="E45" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>409</v>
-      </c>
       <c r="F45" s="1" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="H45" s="1">
         <v>-1</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="J45" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="K45" s="1" t="s">
         <v>410</v>
-      </c>
-      <c r="K45" s="1" t="s">
-        <v>411</v>
       </c>
       <c r="L45" s="5"/>
       <c r="M45" s="1" t="s">
@@ -13108,7 +13108,7 @@
         <v>6</v>
       </c>
       <c r="Y45" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="Z45" s="1" t="s">
         <v>88</v>
@@ -13117,17 +13117,17 @@
         <v>89</v>
       </c>
       <c r="AF45" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG45" s="6"/>
       <c r="AL45" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AM45" s="5">
         <v>5</v>
       </c>
       <c r="AO45" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="AP45" s="1" t="b">
         <v>1</v>
@@ -13135,35 +13135,35 @@
     </row>
     <row r="46" spans="1:42" ht="60" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="E46" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="B46" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="E46" s="1" t="s">
+      <c r="F46" s="1" t="s">
         <v>414</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>415</v>
       </c>
       <c r="H46" s="1">
         <v>-1</v>
       </c>
       <c r="J46" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="K46" s="1" t="s">
         <v>416</v>
-      </c>
-      <c r="K46" s="1" t="s">
-        <v>417</v>
       </c>
       <c r="L46" s="5"/>
       <c r="M46" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="R46" s="1" t="s">
         <v>87</v>
@@ -13172,7 +13172,7 @@
         <v>1</v>
       </c>
       <c r="Y46" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="Z46" s="1" t="s">
         <v>88</v>
@@ -13181,11 +13181,11 @@
         <v>89</v>
       </c>
       <c r="AF46" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG46" s="6"/>
       <c r="AL46" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AM46" s="5">
         <v>10</v>
@@ -13196,45 +13196,45 @@
     </row>
     <row r="47" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="D47" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="B47" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="D47" s="1" t="s">
+      <c r="E47" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="E47" s="1" t="s">
+      <c r="F47" s="1" t="s">
         <v>423</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>424</v>
       </c>
       <c r="H47" s="1">
         <v>-1</v>
       </c>
       <c r="L47" s="5"/>
       <c r="Y47" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="Z47" s="1" t="s">
         <v>147</v>
       </c>
       <c r="AB47" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AC47" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AF47" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG47" s="6"/>
       <c r="AL47" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AM47" s="5">
         <v>11</v>
@@ -13245,25 +13245,25 @@
     </row>
     <row r="48" spans="1:42" ht="90" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="C48" s="22" t="s">
         <v>429</v>
       </c>
-      <c r="C48" s="22" t="s">
-        <v>430</v>
-      </c>
       <c r="D48" s="22" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E48" s="22">
         <v>5</v>
       </c>
       <c r="F48" s="22" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H48" s="1">
         <v>-1</v>
@@ -13273,10 +13273,10 @@
       </c>
       <c r="L48" s="5"/>
       <c r="M48" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="O48" s="1" t="s">
         <v>432</v>
-      </c>
-      <c r="O48" s="1" t="s">
-        <v>433</v>
       </c>
       <c r="P48" s="1" t="s">
         <v>132</v>
@@ -13291,22 +13291,22 @@
         <v>24</v>
       </c>
       <c r="V48" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="W48" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="W48" s="1" t="s">
+      <c r="Y48" s="1" t="s">
         <v>435</v>
-      </c>
-      <c r="Y48" s="1" t="s">
-        <v>436</v>
       </c>
       <c r="Z48" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AA48" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="AB48" s="1" t="s">
         <v>437</v>
-      </c>
-      <c r="AB48" s="1" t="s">
-        <v>438</v>
       </c>
       <c r="AC48" s="1" t="s">
         <v>89</v>
@@ -13316,13 +13316,13 @@
       </c>
       <c r="AG48" s="6"/>
       <c r="AL48" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AM48" s="5">
         <v>1</v>
       </c>
       <c r="AO48" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AP48" s="1" t="b">
         <v>1</v>
@@ -13330,44 +13330,44 @@
     </row>
     <row r="49" spans="1:42" ht="75" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C49" s="22" t="s">
+        <v>429</v>
+      </c>
+      <c r="D49" s="22" t="s">
         <v>440</v>
       </c>
-      <c r="B49" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="C49" s="22" t="s">
-        <v>430</v>
-      </c>
-      <c r="D49" s="22" t="s">
+      <c r="E49" s="22" t="s">
         <v>441</v>
       </c>
-      <c r="E49" s="22" t="s">
+      <c r="F49" s="22" t="s">
+        <v>798</v>
+      </c>
+      <c r="G49" s="1" t="s">
         <v>442</v>
-      </c>
-      <c r="F49" s="22" t="s">
-        <v>799</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>443</v>
       </c>
       <c r="H49" s="1">
         <v>1</v>
       </c>
       <c r="I49" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="J49" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="J49" s="1" t="s">
+      <c r="K49" s="1" t="s">
         <v>445</v>
-      </c>
-      <c r="K49" s="1" t="s">
-        <v>446</v>
       </c>
       <c r="L49" s="5"/>
       <c r="M49" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="P49" s="1" t="s">
         <v>132</v>
@@ -13379,22 +13379,22 @@
         <v>24</v>
       </c>
       <c r="V49" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="W49" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="Y49" s="1" t="s">
         <v>448</v>
-      </c>
-      <c r="W49" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="Y49" s="1" t="s">
-        <v>449</v>
       </c>
       <c r="Z49" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AA49" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="AB49" s="1" t="s">
         <v>437</v>
-      </c>
-      <c r="AB49" s="1" t="s">
-        <v>438</v>
       </c>
       <c r="AC49" s="1" t="s">
         <v>89</v>
@@ -13404,13 +13404,13 @@
       </c>
       <c r="AG49" s="6"/>
       <c r="AL49" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AM49" s="5">
         <v>10</v>
       </c>
       <c r="AO49" s="1" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="AP49" s="1" t="b">
         <v>1</v>
@@ -13418,53 +13418,53 @@
     </row>
     <row r="50" spans="1:42" ht="60" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C50" s="22" t="s">
+        <v>429</v>
+      </c>
+      <c r="D50" s="22" t="s">
+        <v>440</v>
+      </c>
+      <c r="E50" s="22" t="s">
         <v>451</v>
       </c>
-      <c r="B50" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="C50" s="22" t="s">
-        <v>430</v>
-      </c>
-      <c r="D50" s="22" t="s">
-        <v>441</v>
-      </c>
-      <c r="E50" s="22" t="s">
+      <c r="F50" s="22" t="s">
+        <v>809</v>
+      </c>
+      <c r="G50" s="1" t="s">
         <v>452</v>
-      </c>
-      <c r="F50" s="22" t="s">
-        <v>810</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>453</v>
       </c>
       <c r="H50" s="1">
         <v>1</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="J50" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="K50" s="1" t="s">
         <v>454</v>
-      </c>
-      <c r="K50" s="1" t="s">
-        <v>455</v>
       </c>
       <c r="L50" s="5"/>
       <c r="M50" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="P50" s="1" t="s">
         <v>132</v>
       </c>
       <c r="Q50" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="R50" s="1" t="s">
         <v>96</v>
@@ -13476,22 +13476,22 @@
         <v>12</v>
       </c>
       <c r="V50" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="W50" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="Y50" s="1" t="s">
         <v>458</v>
-      </c>
-      <c r="W50" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="Y50" s="1" t="s">
-        <v>459</v>
       </c>
       <c r="Z50" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AA50" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AB50" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AC50" s="1" t="s">
         <v>89</v>
@@ -13501,13 +13501,13 @@
       </c>
       <c r="AG50" s="6"/>
       <c r="AL50" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AM50" s="5">
         <v>9</v>
       </c>
       <c r="AO50" s="1" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="AP50" s="1" t="b">
         <v>1</v>
@@ -13515,44 +13515,44 @@
     </row>
     <row r="51" spans="1:42" ht="90" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C51" s="22" t="s">
+        <v>429</v>
+      </c>
+      <c r="D51" s="22" t="s">
         <v>461</v>
       </c>
-      <c r="B51" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="C51" s="22" t="s">
-        <v>430</v>
-      </c>
-      <c r="D51" s="22" t="s">
+      <c r="E51" s="22" t="s">
         <v>462</v>
       </c>
-      <c r="E51" s="22" t="s">
+      <c r="F51" s="22" t="s">
         <v>463</v>
       </c>
-      <c r="F51" s="22" t="s">
+      <c r="G51" s="1" t="s">
         <v>464</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>465</v>
       </c>
       <c r="H51" s="1">
         <v>1</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="J51" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="K51" s="1" t="s">
         <v>466</v>
-      </c>
-      <c r="K51" s="1" t="s">
-        <v>467</v>
       </c>
       <c r="L51" s="5"/>
       <c r="M51" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="O51" s="1" t="s">
         <v>468</v>
-      </c>
-      <c r="O51" s="1" t="s">
-        <v>469</v>
       </c>
       <c r="P51" s="1" t="s">
         <v>132</v>
@@ -13564,22 +13564,22 @@
         <v>2</v>
       </c>
       <c r="V51" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="W51" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Y51" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="Z51" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AA51" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AB51" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AC51" s="1" t="s">
         <v>89</v>
@@ -13589,16 +13589,16 @@
       </c>
       <c r="AG51" s="6"/>
       <c r="AK51" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="AL51" s="1" t="s">
         <v>472</v>
-      </c>
-      <c r="AL51" s="1" t="s">
-        <v>473</v>
       </c>
       <c r="AM51" s="5">
         <v>8</v>
       </c>
       <c r="AO51" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="AP51" s="1" t="b">
         <v>1</v>
@@ -13606,47 +13606,47 @@
     </row>
     <row r="52" spans="1:42" ht="75" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C52" s="22" t="s">
+        <v>429</v>
+      </c>
+      <c r="D52" s="22" t="s">
         <v>474</v>
       </c>
-      <c r="B52" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="C52" s="22" t="s">
-        <v>430</v>
-      </c>
-      <c r="D52" s="22" t="s">
+      <c r="E52" s="22" t="s">
         <v>475</v>
       </c>
-      <c r="E52" s="22" t="s">
+      <c r="F52" s="22" t="s">
         <v>476</v>
       </c>
-      <c r="F52" s="22" t="s">
+      <c r="G52" s="1" t="s">
         <v>477</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>478</v>
       </c>
       <c r="H52" s="1">
         <v>-1</v>
       </c>
       <c r="I52" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="K52" s="1" t="s">
         <v>479</v>
-      </c>
-      <c r="J52" s="1" t="s">
-        <v>477</v>
-      </c>
-      <c r="K52" s="1" t="s">
-        <v>480</v>
       </c>
       <c r="L52" s="5"/>
       <c r="M52" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="O52" s="11" t="s">
         <v>481</v>
       </c>
-      <c r="O52" s="11" t="s">
+      <c r="P52" s="1" t="s">
         <v>482</v>
-      </c>
-      <c r="P52" s="1" t="s">
-        <v>483</v>
       </c>
       <c r="R52" s="1" t="s">
         <v>96</v>
@@ -13655,22 +13655,22 @@
         <v>24</v>
       </c>
       <c r="V52" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="W52" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Y52" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="Z52" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AA52" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AB52" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="AC52" s="1" t="s">
         <v>89</v>
@@ -13680,13 +13680,13 @@
       </c>
       <c r="AG52" s="6"/>
       <c r="AL52" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AM52" s="5">
         <v>2</v>
       </c>
       <c r="AO52" s="1" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="AP52" s="1" t="b">
         <v>1</v>
@@ -13694,37 +13694,37 @@
     </row>
     <row r="53" spans="1:42" ht="135" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C53" s="22" t="s">
+        <v>429</v>
+      </c>
+      <c r="D53" s="22" t="s">
+        <v>474</v>
+      </c>
+      <c r="E53" s="22" t="s">
         <v>487</v>
       </c>
-      <c r="B53" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="C53" s="22" t="s">
-        <v>430</v>
-      </c>
-      <c r="D53" s="22" t="s">
-        <v>475</v>
-      </c>
-      <c r="E53" s="22" t="s">
+      <c r="F53" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="G53" s="1" t="s">
         <v>488</v>
-      </c>
-      <c r="F53" s="22" t="s">
-        <v>808</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>489</v>
       </c>
       <c r="H53" s="1">
         <v>-1</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="L53" s="5">
         <v>2020</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="R53" s="1" t="s">
         <v>96</v>
@@ -13733,22 +13733,22 @@
         <v>13</v>
       </c>
       <c r="V53" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="W53" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="W53" s="1" t="s">
+      <c r="Y53" s="1" t="s">
         <v>493</v>
-      </c>
-      <c r="Y53" s="1" t="s">
-        <v>494</v>
       </c>
       <c r="Z53" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AA53" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AB53" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="AC53" s="1" t="s">
         <v>89</v>
@@ -13758,16 +13758,16 @@
       </c>
       <c r="AG53" s="6"/>
       <c r="AI53" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="AL53" s="1" t="s">
         <v>496</v>
-      </c>
-      <c r="AL53" s="1" t="s">
-        <v>497</v>
       </c>
       <c r="AM53" s="5">
         <v>3</v>
       </c>
       <c r="AO53" s="1" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="AP53" s="1" t="b">
         <v>1</v>
@@ -13775,59 +13775,59 @@
     </row>
     <row r="54" spans="1:42" ht="60" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
+        <v>497</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C54" s="22" t="s">
+        <v>429</v>
+      </c>
+      <c r="D54" s="22" t="s">
         <v>498</v>
       </c>
-      <c r="B54" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="C54" s="22" t="s">
-        <v>430</v>
-      </c>
-      <c r="D54" s="22" t="s">
+      <c r="E54" s="22" t="s">
         <v>499</v>
       </c>
-      <c r="E54" s="22" t="s">
+      <c r="F54" s="22" t="s">
         <v>500</v>
       </c>
-      <c r="F54" s="22" t="s">
+      <c r="G54" s="1" t="s">
         <v>501</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>502</v>
       </c>
       <c r="H54" s="1">
         <v>1</v>
       </c>
       <c r="I54" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="J54" s="1" t="s">
         <v>503</v>
-      </c>
-      <c r="J54" s="1" t="s">
-        <v>504</v>
       </c>
       <c r="L54" s="5"/>
       <c r="M54" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="R54" s="1" t="s">
         <v>505</v>
-      </c>
-      <c r="R54" s="1" t="s">
-        <v>506</v>
       </c>
       <c r="U54" s="1">
         <v>24</v>
       </c>
       <c r="V54" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="W54" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="Y54" s="1" t="s">
         <v>507</v>
-      </c>
-      <c r="W54" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="Y54" s="1" t="s">
-        <v>508</v>
       </c>
       <c r="Z54" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AA54" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AC54" s="1" t="s">
         <v>89</v>
@@ -13837,16 +13837,16 @@
       </c>
       <c r="AG54" s="6"/>
       <c r="AK54" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="AL54" s="1" t="s">
         <v>510</v>
-      </c>
-      <c r="AL54" s="1" t="s">
-        <v>511</v>
       </c>
       <c r="AM54" s="5">
         <v>7</v>
       </c>
       <c r="AO54" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AP54" s="1" t="b">
         <v>1</v>
@@ -13854,22 +13854,22 @@
     </row>
     <row r="55" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C55" s="22" t="s">
+        <v>429</v>
+      </c>
+      <c r="D55" s="22" t="s">
+        <v>498</v>
+      </c>
+      <c r="E55" s="22" t="s">
         <v>512</v>
       </c>
-      <c r="B55" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="C55" s="22" t="s">
-        <v>430</v>
-      </c>
-      <c r="D55" s="22" t="s">
-        <v>499</v>
-      </c>
-      <c r="E55" s="22" t="s">
+      <c r="F55" s="22" t="s">
         <v>513</v>
-      </c>
-      <c r="F55" s="22" t="s">
-        <v>514</v>
       </c>
       <c r="H55" s="1">
         <v>1</v>
@@ -13879,13 +13879,13 @@
       </c>
       <c r="L55" s="5"/>
       <c r="Y55" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Z55" s="1" t="s">
         <v>139</v>
       </c>
       <c r="AA55" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AC55" s="1" t="s">
         <v>89</v>
@@ -13895,7 +13895,7 @@
       </c>
       <c r="AG55" s="6"/>
       <c r="AL55" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="AM55" s="5">
         <v>6</v>
@@ -13906,22 +13906,22 @@
     </row>
     <row r="56" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C56" s="22" t="s">
+        <v>429</v>
+      </c>
+      <c r="D56" s="22" t="s">
+        <v>498</v>
+      </c>
+      <c r="E56" s="22" t="s">
         <v>517</v>
       </c>
-      <c r="B56" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="C56" s="22" t="s">
-        <v>430</v>
-      </c>
-      <c r="D56" s="22" t="s">
-        <v>499</v>
-      </c>
-      <c r="E56" s="22" t="s">
+      <c r="F56" s="22" t="s">
         <v>518</v>
-      </c>
-      <c r="F56" s="22" t="s">
-        <v>519</v>
       </c>
       <c r="H56" s="1">
         <v>1</v>
@@ -13931,13 +13931,13 @@
       </c>
       <c r="L56" s="5"/>
       <c r="Y56" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="Z56" s="1" t="s">
         <v>139</v>
       </c>
       <c r="AA56" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AC56" s="1" t="s">
         <v>89</v>
@@ -13947,7 +13947,7 @@
       </c>
       <c r="AG56" s="6"/>
       <c r="AL56" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AM56" s="5">
         <v>5</v>
@@ -13958,47 +13958,47 @@
     </row>
     <row r="57" spans="1:42" ht="105" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C57" s="22" t="s">
+        <v>429</v>
+      </c>
+      <c r="D57" s="22" t="s">
+        <v>498</v>
+      </c>
+      <c r="E57" s="22" t="s">
         <v>522</v>
       </c>
-      <c r="B57" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="C57" s="22" t="s">
-        <v>430</v>
-      </c>
-      <c r="D57" s="22" t="s">
-        <v>499</v>
-      </c>
-      <c r="E57" s="22" t="s">
+      <c r="F57" s="22" t="s">
+        <v>806</v>
+      </c>
+      <c r="G57" s="1" t="s">
         <v>523</v>
-      </c>
-      <c r="F57" s="22" t="s">
-        <v>807</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>524</v>
       </c>
       <c r="H57" s="1">
         <v>1</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="J57" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="K57" s="1" t="s">
         <v>525</v>
-      </c>
-      <c r="K57" s="1" t="s">
-        <v>526</v>
       </c>
       <c r="L57" s="5"/>
       <c r="M57" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="O57" s="10" t="s">
         <v>527</v>
       </c>
-      <c r="O57" s="10" t="s">
+      <c r="P57" s="1" t="s">
         <v>528</v>
-      </c>
-      <c r="P57" s="1" t="s">
-        <v>529</v>
       </c>
       <c r="R57" s="1" t="s">
         <v>96</v>
@@ -14007,22 +14007,22 @@
         <v>15</v>
       </c>
       <c r="V57" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="W57" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="W57" s="1" t="s">
+      <c r="Y57" s="1" t="s">
         <v>531</v>
-      </c>
-      <c r="Y57" s="1" t="s">
-        <v>532</v>
       </c>
       <c r="Z57" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AA57" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AB57" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="AC57" s="1" t="s">
         <v>89</v>
@@ -14032,13 +14032,13 @@
       </c>
       <c r="AG57" s="6"/>
       <c r="AL57" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AM57" s="5">
         <v>4</v>
       </c>
       <c r="AO57" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="AP57" s="1" t="b">
         <v>1</v>
@@ -14046,38 +14046,38 @@
     </row>
     <row r="58" spans="1:42" ht="60" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
+        <v>534</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="C58" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="D58" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="D58" s="1" t="s">
+      <c r="E58" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="E58" s="1" t="s">
-        <v>539</v>
-      </c>
       <c r="F58" s="1" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H58" s="1">
         <v>-1</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="J58" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="K58" s="1" t="s">
         <v>540</v>
-      </c>
-      <c r="K58" s="1" t="s">
-        <v>541</v>
       </c>
       <c r="L58" s="5"/>
       <c r="M58" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="R58" s="1" t="s">
         <v>96</v>
@@ -14089,7 +14089,7 @@
         <v>3</v>
       </c>
       <c r="Y58" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="Z58" s="1" t="s">
         <v>88</v>
@@ -14098,14 +14098,14 @@
         <v>89</v>
       </c>
       <c r="AF58" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG58" s="6"/>
       <c r="AI58" s="1" t="s">
         <v>91</v>
       </c>
       <c r="AL58" s="1" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="AM58" s="5">
         <v>1</v>
@@ -14114,7 +14114,7 @@
         <v>91</v>
       </c>
       <c r="AO58" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="AP58" s="1" t="b">
         <v>1</v>
@@ -14122,38 +14122,38 @@
     </row>
     <row r="59" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
+        <v>544</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="E59" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="B59" s="1" t="s">
-        <v>536</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>537</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>538</v>
-      </c>
-      <c r="E59" s="1" t="s">
+      <c r="F59" s="1" t="s">
         <v>546</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>547</v>
       </c>
       <c r="H59" s="1">
         <v>1</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="J59" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="K59" s="1" t="s">
         <v>548</v>
-      </c>
-      <c r="K59" s="1" t="s">
-        <v>549</v>
       </c>
       <c r="L59" s="5"/>
       <c r="M59" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="P59" s="1" t="s">
         <v>117</v>
@@ -14168,7 +14168,7 @@
         <v>2</v>
       </c>
       <c r="Y59" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="Z59" s="1" t="s">
         <v>88</v>
@@ -14177,14 +14177,14 @@
         <v>89</v>
       </c>
       <c r="AF59" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG59" s="6"/>
       <c r="AI59" s="1" t="s">
         <v>91</v>
       </c>
       <c r="AL59" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="AM59" s="5">
         <v>5</v>
@@ -14193,7 +14193,7 @@
         <v>91</v>
       </c>
       <c r="AO59" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="AP59" s="1" t="b">
         <v>1</v>
@@ -14201,41 +14201,41 @@
     </row>
     <row r="60" spans="1:42" ht="60" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="E60" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="B60" s="1" t="s">
-        <v>536</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>537</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>538</v>
-      </c>
-      <c r="E60" s="1" t="s">
+      <c r="F60" s="1" t="s">
+        <v>802</v>
+      </c>
+      <c r="G60" s="1" t="s">
         <v>553</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>803</v>
-      </c>
-      <c r="G60" s="1" t="s">
-        <v>554</v>
       </c>
       <c r="H60" s="1">
         <v>1</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="J60" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="K60" s="1" t="s">
         <v>555</v>
-      </c>
-      <c r="K60" s="1" t="s">
-        <v>556</v>
       </c>
       <c r="L60" s="5"/>
       <c r="M60" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="P60" s="1" t="s">
         <v>117</v>
@@ -14250,7 +14250,7 @@
         <v>3</v>
       </c>
       <c r="Y60" s="1" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="Z60" s="1" t="s">
         <v>88</v>
@@ -14259,20 +14259,20 @@
         <v>89</v>
       </c>
       <c r="AF60" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG60" s="6"/>
       <c r="AI60" s="1" t="s">
         <v>91</v>
       </c>
       <c r="AL60" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="AM60" s="5">
         <v>8</v>
       </c>
       <c r="AO60" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="AP60" s="1" t="b">
         <v>1</v>
@@ -14280,38 +14280,38 @@
     </row>
     <row r="61" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
+        <v>557</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="E61" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="B61" s="1" t="s">
-        <v>536</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>537</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>538</v>
-      </c>
-      <c r="E61" s="1" t="s">
+      <c r="F61" s="1" t="s">
         <v>559</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>560</v>
       </c>
       <c r="H61" s="1">
         <v>-1</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="J61" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="K61" s="1" t="s">
         <v>561</v>
-      </c>
-      <c r="K61" s="1" t="s">
-        <v>562</v>
       </c>
       <c r="L61" s="5"/>
       <c r="M61" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="P61" s="1" t="s">
         <v>117</v>
@@ -14326,7 +14326,7 @@
         <v>3</v>
       </c>
       <c r="Y61" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="Z61" s="1" t="s">
         <v>88</v>
@@ -14335,17 +14335,17 @@
         <v>89</v>
       </c>
       <c r="AF61" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG61" s="6"/>
       <c r="AL61" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="AM61" s="5">
         <v>6</v>
       </c>
       <c r="AO61" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="AP61" s="1" t="b">
         <v>1</v>
@@ -14353,38 +14353,38 @@
     </row>
     <row r="62" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="B62" s="1" t="s">
-        <v>536</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>537</v>
-      </c>
-      <c r="D62" s="1" t="s">
+      <c r="E62" s="1" t="s">
         <v>565</v>
       </c>
-      <c r="E62" s="1" t="s">
+      <c r="F62" s="1" t="s">
         <v>566</v>
-      </c>
-      <c r="F62" s="1" t="s">
-        <v>567</v>
       </c>
       <c r="H62" s="1">
         <v>1</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="J62" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="K62" s="1" t="s">
         <v>568</v>
-      </c>
-      <c r="K62" s="1" t="s">
-        <v>569</v>
       </c>
       <c r="L62" s="5"/>
       <c r="M62" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="P62" s="1" t="s">
         <v>117</v>
@@ -14396,7 +14396,7 @@
         <v>12</v>
       </c>
       <c r="Y62" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="Z62" s="1" t="s">
         <v>88</v>
@@ -14405,17 +14405,17 @@
         <v>89</v>
       </c>
       <c r="AF62" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG62" s="6"/>
       <c r="AL62" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="AM62" s="5">
         <v>2</v>
       </c>
       <c r="AO62" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="AP62" s="1" t="b">
         <v>1</v>
@@ -14423,38 +14423,38 @@
     </row>
     <row r="63" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
+        <v>572</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="E63" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="B63" s="1" t="s">
-        <v>536</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>537</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>565</v>
-      </c>
-      <c r="E63" s="1" t="s">
+      <c r="F63" s="1" t="s">
         <v>574</v>
-      </c>
-      <c r="F63" s="1" t="s">
-        <v>575</v>
       </c>
       <c r="H63" s="1">
         <v>1</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="J63" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="K63" s="1" t="s">
         <v>576</v>
-      </c>
-      <c r="K63" s="1" t="s">
-        <v>577</v>
       </c>
       <c r="L63" s="5"/>
       <c r="M63" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="P63" s="1" t="s">
         <v>117</v>
@@ -14466,7 +14466,7 @@
         <v>12</v>
       </c>
       <c r="Y63" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="Z63" s="1" t="s">
         <v>88</v>
@@ -14475,17 +14475,17 @@
         <v>89</v>
       </c>
       <c r="AF63" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG63" s="6"/>
       <c r="AL63" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="AM63" s="5">
         <v>3</v>
       </c>
       <c r="AO63" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="AP63" s="1" t="b">
         <v>1</v>
@@ -14493,22 +14493,22 @@
     </row>
     <row r="64" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="D64" s="1" t="s">
         <v>581</v>
       </c>
-      <c r="B64" s="1" t="s">
-        <v>536</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>537</v>
-      </c>
-      <c r="D64" s="1" t="s">
+      <c r="E64" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="E64" s="1" t="s">
+      <c r="F64" s="1" t="s">
         <v>583</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>584</v>
       </c>
       <c r="H64" s="1">
         <v>1</v>
@@ -14524,7 +14524,7 @@
         <v>3</v>
       </c>
       <c r="Y64" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="Z64" s="1" t="s">
         <v>147</v>
@@ -14533,7 +14533,7 @@
         <v>89</v>
       </c>
       <c r="AF64" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG64" s="6"/>
       <c r="AL64" s="1" t="s">
@@ -14548,22 +14548,22 @@
     </row>
     <row r="65" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
+        <v>585</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="D65" s="1" t="s">
         <v>586</v>
       </c>
-      <c r="B65" s="1" t="s">
-        <v>536</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>537</v>
-      </c>
-      <c r="D65" s="1" t="s">
+      <c r="E65" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="E65" s="1" t="s">
+      <c r="F65" s="1" t="s">
         <v>588</v>
-      </c>
-      <c r="F65" s="1" t="s">
-        <v>589</v>
       </c>
       <c r="H65" s="1">
         <v>1</v>
@@ -14573,7 +14573,7 @@
       </c>
       <c r="L65" s="5"/>
       <c r="Y65" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="Z65" s="1" t="s">
         <v>147</v>
@@ -14582,7 +14582,7 @@
         <v>89</v>
       </c>
       <c r="AF65" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG65" s="6"/>
       <c r="AL65" s="1" t="s">
@@ -14597,38 +14597,38 @@
     </row>
     <row r="66" spans="1:42" ht="60" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
+        <v>590</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="E66" s="1" t="s">
         <v>591</v>
       </c>
-      <c r="B66" s="1" t="s">
-        <v>536</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>537</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>587</v>
-      </c>
-      <c r="E66" s="1" t="s">
+      <c r="F66" s="1" t="s">
         <v>592</v>
-      </c>
-      <c r="F66" s="1" t="s">
-        <v>593</v>
       </c>
       <c r="H66" s="1">
         <v>-1</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="L66" s="5"/>
       <c r="M66" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="V66" s="1" t="s">
         <v>595</v>
       </c>
-      <c r="V66" s="1" t="s">
+      <c r="Y66" s="1" t="s">
         <v>596</v>
-      </c>
-      <c r="Y66" s="1" t="s">
-        <v>597</v>
       </c>
       <c r="Z66" s="1" t="s">
         <v>88</v>
@@ -14637,17 +14637,17 @@
         <v>89</v>
       </c>
       <c r="AF66" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG66" s="6"/>
       <c r="AL66" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="AM66" s="5">
         <v>10</v>
       </c>
       <c r="AO66" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AP66" s="1" t="b">
         <v>1</v>
@@ -14655,32 +14655,32 @@
     </row>
     <row r="67" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
+        <v>598</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="E67" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="B67" s="1" t="s">
-        <v>536</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>537</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>587</v>
-      </c>
-      <c r="E67" s="1" t="s">
+      <c r="F67" s="1" t="s">
         <v>600</v>
-      </c>
-      <c r="F67" s="1" t="s">
-        <v>601</v>
       </c>
       <c r="H67" s="1">
         <v>1</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="L67" s="5"/>
       <c r="M67" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="P67" s="1" t="s">
         <v>117</v>
@@ -14695,7 +14695,7 @@
         <v>12</v>
       </c>
       <c r="Y67" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="Z67" s="1" t="s">
         <v>88</v>
@@ -14704,20 +14704,20 @@
         <v>89</v>
       </c>
       <c r="AF67" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG67" s="6"/>
       <c r="AI67" s="1" t="s">
         <v>91</v>
       </c>
       <c r="AL67" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AM67" s="5">
         <v>11</v>
       </c>
       <c r="AO67" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AP67" s="1" t="b">
         <v>1</v>
@@ -14725,38 +14725,38 @@
     </row>
     <row r="68" spans="1:42" ht="30" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
+        <v>603</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="E68" s="1" t="s">
         <v>604</v>
       </c>
-      <c r="B68" s="1" t="s">
-        <v>536</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>537</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>587</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>605</v>
-      </c>
       <c r="F68" s="1" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="H68" s="1">
         <v>1</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="J68" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="K68" s="1" t="s">
         <v>606</v>
-      </c>
-      <c r="K68" s="1" t="s">
-        <v>607</v>
       </c>
       <c r="L68" s="5"/>
       <c r="M68" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="P68" s="1" t="s">
         <v>117</v>
@@ -14771,7 +14771,7 @@
         <v>36</v>
       </c>
       <c r="Y68" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="Z68" s="1" t="s">
         <v>88</v>
@@ -14780,20 +14780,20 @@
         <v>89</v>
       </c>
       <c r="AF68" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG68" s="6"/>
       <c r="AI68" s="1" t="s">
         <v>91</v>
       </c>
       <c r="AL68" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AM68" s="5">
         <v>4</v>
       </c>
       <c r="AO68" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="AP68" s="1" t="b">
         <v>1</v>
@@ -14801,38 +14801,38 @@
     </row>
     <row r="69" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
+        <v>607</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="E69" s="1" t="s">
         <v>608</v>
       </c>
-      <c r="B69" s="1" t="s">
-        <v>536</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>537</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>587</v>
-      </c>
-      <c r="E69" s="1" t="s">
+      <c r="F69" s="1" t="s">
         <v>609</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>610</v>
       </c>
       <c r="H69" s="1">
         <v>-1</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="J69" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="L69" s="5"/>
       <c r="M69" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="P69" s="1" t="s">
         <v>117</v>
@@ -14847,7 +14847,7 @@
         <v>12</v>
       </c>
       <c r="Y69" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="Z69" s="1" t="s">
         <v>88</v>
@@ -14856,17 +14856,17 @@
         <v>89</v>
       </c>
       <c r="AF69" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG69" s="6"/>
       <c r="AL69" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AM69" s="5">
         <v>7</v>
       </c>
       <c r="AO69" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="AP69" s="1" t="b">
         <v>1</v>
@@ -15108,78 +15108,78 @@
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="20" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="21" t="s">
+        <v>623</v>
+      </c>
+      <c r="B2" t="s">
         <v>624</v>
-      </c>
-      <c r="B2" t="s">
-        <v>625</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
+        <v>625</v>
+      </c>
+      <c r="B3" t="s">
         <v>626</v>
-      </c>
-      <c r="B3" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
+        <v>627</v>
+      </c>
+      <c r="B4" t="s">
         <v>628</v>
-      </c>
-      <c r="B4" t="s">
-        <v>629</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
+        <v>629</v>
+      </c>
+      <c r="B6" t="s">
         <v>630</v>
-      </c>
-      <c r="B6" t="s">
-        <v>631</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
+        <v>631</v>
+      </c>
+      <c r="B7" t="s">
         <v>632</v>
-      </c>
-      <c r="B7" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>847</v>
+      </c>
+      <c r="B10" t="s">
         <v>848</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>849</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>850</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>851</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>852</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>853</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>854</v>
-      </c>
-      <c r="H10" t="s">
-        <v>855</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="B11" t="b">
         <v>1</v>
@@ -15207,63 +15207,63 @@
   <sheetData>
     <row r="1" spans="1:5" ht="298.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A3" s="18" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="B4" t="s">
         <v>636</v>
-      </c>
-      <c r="B4" t="s">
-        <v>637</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
+        <v>637</v>
+      </c>
+      <c r="B5" t="s">
         <v>638</v>
-      </c>
-      <c r="B5" t="s">
-        <v>639</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="B6" t="s">
         <v>640</v>
-      </c>
-      <c r="B6" t="s">
-        <v>641</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="B7" t="s">
         <v>642</v>
-      </c>
-      <c r="B7" t="s">
-        <v>643</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
+        <v>644</v>
+      </c>
+      <c r="B10" s="13" t="s">
         <v>645</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="C10" s="13" t="s">
         <v>646</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="D10" s="13" t="s">
         <v>647</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>648</v>
       </c>
       <c r="E10" s="13" t="s">
         <v>37</v>
@@ -15277,13 +15277,13 @@
         <v>0</v>
       </c>
       <c r="C11" t="s">
+        <v>648</v>
+      </c>
+      <c r="D11" t="s">
         <v>649</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>650</v>
-      </c>
-      <c r="E11" t="s">
-        <v>651</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -15294,13 +15294,13 @@
         <v>1</v>
       </c>
       <c r="C12" t="s">
+        <v>651</v>
+      </c>
+      <c r="D12" t="s">
+        <v>649</v>
+      </c>
+      <c r="E12" t="s">
         <v>652</v>
-      </c>
-      <c r="D12" t="s">
-        <v>650</v>
-      </c>
-      <c r="E12" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -15311,13 +15311,13 @@
         <v>2</v>
       </c>
       <c r="C13" t="s">
+        <v>653</v>
+      </c>
+      <c r="D13" t="s">
+        <v>649</v>
+      </c>
+      <c r="E13" t="s">
         <v>654</v>
-      </c>
-      <c r="D13" t="s">
-        <v>650</v>
-      </c>
-      <c r="E13" t="s">
-        <v>655</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -15328,13 +15328,13 @@
         <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D14" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E14" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -15345,13 +15345,13 @@
         <v>4</v>
       </c>
       <c r="C15" t="s">
+        <v>656</v>
+      </c>
+      <c r="D15" t="s">
+        <v>649</v>
+      </c>
+      <c r="E15" t="s">
         <v>657</v>
-      </c>
-      <c r="D15" t="s">
-        <v>650</v>
-      </c>
-      <c r="E15" t="s">
-        <v>658</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -15362,13 +15362,13 @@
         <v>5</v>
       </c>
       <c r="C16" t="s">
+        <v>658</v>
+      </c>
+      <c r="D16" t="s">
+        <v>649</v>
+      </c>
+      <c r="E16" t="s">
         <v>659</v>
-      </c>
-      <c r="D16" t="s">
-        <v>650</v>
-      </c>
-      <c r="E16" t="s">
-        <v>660</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -15379,13 +15379,13 @@
         <v>6</v>
       </c>
       <c r="C17" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D17" t="s">
+        <v>660</v>
+      </c>
+      <c r="E17" t="s">
         <v>661</v>
-      </c>
-      <c r="E17" t="s">
-        <v>662</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -15396,13 +15396,13 @@
         <v>7</v>
       </c>
       <c r="C18" t="s">
+        <v>662</v>
+      </c>
+      <c r="D18" t="s">
+        <v>660</v>
+      </c>
+      <c r="E18" t="s">
         <v>663</v>
-      </c>
-      <c r="D18" t="s">
-        <v>661</v>
-      </c>
-      <c r="E18" t="s">
-        <v>664</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -15413,13 +15413,13 @@
         <v>8</v>
       </c>
       <c r="C19" t="s">
+        <v>664</v>
+      </c>
+      <c r="D19" t="s">
+        <v>660</v>
+      </c>
+      <c r="E19" t="s">
         <v>665</v>
-      </c>
-      <c r="D19" t="s">
-        <v>661</v>
-      </c>
-      <c r="E19" t="s">
-        <v>666</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -15430,13 +15430,13 @@
         <v>9</v>
       </c>
       <c r="C20" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D20" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E20" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -15447,13 +15447,13 @@
         <v>10</v>
       </c>
       <c r="C21" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D21" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E21" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -15464,13 +15464,13 @@
         <v>11</v>
       </c>
       <c r="C22" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="D22" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E22" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -15481,13 +15481,13 @@
         <v>12</v>
       </c>
       <c r="C23" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D23" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E23" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -15498,13 +15498,13 @@
         <v>13</v>
       </c>
       <c r="C24" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D24" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E24" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -15515,13 +15515,13 @@
         <v>14</v>
       </c>
       <c r="C25" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D25" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E25" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -15532,13 +15532,13 @@
         <v>15</v>
       </c>
       <c r="C26" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D26" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E26" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -15549,13 +15549,13 @@
         <v>16</v>
       </c>
       <c r="C27" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="D27" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E27" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -15566,13 +15566,13 @@
         <v>17</v>
       </c>
       <c r="C28" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D28" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E28" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -15583,13 +15583,13 @@
         <v>18</v>
       </c>
       <c r="C29" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D29" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E29" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -15600,13 +15600,13 @@
         <v>19</v>
       </c>
       <c r="C30" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D30" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E30" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -15617,13 +15617,13 @@
         <v>20</v>
       </c>
       <c r="C31" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="D31" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E31" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -15634,13 +15634,13 @@
         <v>21</v>
       </c>
       <c r="C32" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D32" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E32" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -15651,13 +15651,13 @@
         <v>22</v>
       </c>
       <c r="C33" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D33" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E33" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -15668,13 +15668,13 @@
         <v>23</v>
       </c>
       <c r="C34" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D34" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E34" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -15685,13 +15685,13 @@
         <v>24</v>
       </c>
       <c r="C35" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D35" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E35" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -15702,13 +15702,13 @@
         <v>25</v>
       </c>
       <c r="C36" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D36" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E36" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -15719,13 +15719,13 @@
         <v>26</v>
       </c>
       <c r="C37" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D37" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E37" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -15736,13 +15736,13 @@
         <v>27</v>
       </c>
       <c r="C38" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D38" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E38" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -15753,13 +15753,13 @@
         <v>28</v>
       </c>
       <c r="C39" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D39" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E39" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -15770,13 +15770,13 @@
         <v>29</v>
       </c>
       <c r="C40" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D40" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E40" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -15787,13 +15787,13 @@
         <v>30</v>
       </c>
       <c r="C41" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D41" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E41" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -15804,13 +15804,13 @@
         <v>31</v>
       </c>
       <c r="C42" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="D42" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E42" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -15821,13 +15821,13 @@
         <v>32</v>
       </c>
       <c r="C43" t="s">
+        <v>689</v>
+      </c>
+      <c r="D43" t="s">
+        <v>660</v>
+      </c>
+      <c r="E43" t="s">
         <v>690</v>
-      </c>
-      <c r="D43" t="s">
-        <v>661</v>
-      </c>
-      <c r="E43" t="s">
-        <v>691</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -15838,13 +15838,13 @@
         <v>33</v>
       </c>
       <c r="C44" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D44" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E44" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -15855,13 +15855,13 @@
         <v>34</v>
       </c>
       <c r="C45" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D45" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E45" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -15872,13 +15872,13 @@
         <v>35</v>
       </c>
       <c r="C46" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D46" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E46" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -15889,13 +15889,13 @@
         <v>36</v>
       </c>
       <c r="C47" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D47" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E47" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -15906,13 +15906,13 @@
         <v>37</v>
       </c>
       <c r="C48" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D48" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E48" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -15923,69 +15923,69 @@
         <v>38</v>
       </c>
       <c r="C49" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D49" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E49" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A51" s="18" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B52" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="9" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B53" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B54" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="9" t="s">
+        <v>701</v>
+      </c>
+      <c r="B55" t="s">
         <v>702</v>
-      </c>
-      <c r="B55" t="s">
-        <v>703</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="19" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="13" t="s">
+        <v>644</v>
+      </c>
+      <c r="B58" s="13" t="s">
         <v>645</v>
       </c>
-      <c r="B58" s="13" t="s">
+      <c r="C58" s="13" t="s">
         <v>646</v>
       </c>
-      <c r="C58" s="13" t="s">
+      <c r="D58" s="13" t="s">
         <v>647</v>
-      </c>
-      <c r="D58" s="13" t="s">
-        <v>648</v>
       </c>
       <c r="E58" s="13" t="s">
         <v>37</v>
@@ -15993,19 +15993,19 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B59" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C59" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="D59" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E59" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -16013,141 +16013,141 @@
         <v>39</v>
       </c>
       <c r="B60" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C60" t="s">
+        <v>648</v>
+      </c>
+      <c r="D60" t="s">
         <v>649</v>
       </c>
-      <c r="D60" t="s">
-        <v>650</v>
-      </c>
       <c r="E60" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B61" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C61" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="D61" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E61" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B62" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C62" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="D62" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E62" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B63" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C63" t="s">
+        <v>708</v>
+      </c>
+      <c r="D63" t="s">
+        <v>649</v>
+      </c>
+      <c r="E63" t="s">
         <v>709</v>
-      </c>
-      <c r="D63" t="s">
-        <v>650</v>
-      </c>
-      <c r="E63" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B64" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C64" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="D64" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E64" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="66" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A66" s="18" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="70" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A70" s="18" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" s="9" t="s">
+        <v>715</v>
+      </c>
+      <c r="B71" t="s">
         <v>716</v>
-      </c>
-      <c r="B71" t="s">
-        <v>717</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" s="9" t="s">
+        <v>717</v>
+      </c>
+      <c r="B72" t="s">
         <v>718</v>
-      </c>
-      <c r="B72" t="s">
-        <v>719</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" s="9" t="s">
+        <v>719</v>
+      </c>
+      <c r="B73" t="s">
         <v>720</v>
-      </c>
-      <c r="B73" t="s">
-        <v>721</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" s="9" t="s">
+        <v>721</v>
+      </c>
+      <c r="B74" t="s">
         <v>722</v>
-      </c>
-      <c r="B74" t="s">
-        <v>723</v>
       </c>
     </row>
     <row r="76" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A76" s="18" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -16155,7 +16155,7 @@
         <v>1</v>
       </c>
       <c r="B77" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -16163,7 +16163,7 @@
         <v>2</v>
       </c>
       <c r="B78" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -16171,7 +16171,7 @@
         <v>3</v>
       </c>
       <c r="B79" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -16179,7 +16179,7 @@
         <v>4</v>
       </c>
       <c r="B80" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
@@ -16187,7 +16187,7 @@
         <v>5</v>
       </c>
       <c r="B81" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
   </sheetData>

--- a/data/common_project_data/indicators-master.xlsx
+++ b/data/common_project_data/indicators-master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steve.crawshaw\projects\weca_regional_indicators\data\common_project_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{29DC0B27-D526-4626-A7EF-A7CBC75C7DB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9540A400-0674-4C41-BF7C-746DDBFEB218}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="fact_indicator_observation" sheetId="3" r:id="rId1"/>
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1693" uniqueCount="861">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1693" uniqueCount="860">
   <si>
     <t>Unique ID</t>
   </si>
@@ -415,25 +415,13 @@
 Can model this to recent periods as the data are not timely.</t>
   </si>
   <si>
-    <t>RI_1B2_gva_per_hour</t>
-  </si>
-  <si>
     <t>1.B.2</t>
   </si>
   <si>
-    <t>GVA per hour</t>
-  </si>
-  <si>
-    <t>£/hour</t>
-  </si>
-  <si>
     <t>June</t>
   </si>
   <si>
     <t>GVA per hour worked</t>
-  </si>
-  <si>
-    <t>RI_1B3_median_weekly_pay</t>
   </si>
   <si>
     <t>1.B.3</t>
@@ -2680,6 +2668,15 @@
   </si>
   <si>
     <t>Private monthly rental prices</t>
+  </si>
+  <si>
+    <t>RI_1B3_median_pay</t>
+  </si>
+  <si>
+    <t>RI_1B2_gva</t>
+  </si>
+  <si>
+    <t>GVA per job</t>
   </si>
 </sst>
 </file>
@@ -3539,42 +3536,42 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
+        <v>607</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>608</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>610</v>
+      </c>
+      <c r="E1" s="13" t="s">
         <v>611</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="F1" s="13" t="s">
         <v>612</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>613</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>614</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>615</v>
-      </c>
-      <c r="F1" s="13" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>39</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -9748,16 +9745,16 @@
         <v>37</v>
       </c>
       <c r="AM1" s="26" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="AN1" s="3" t="s">
         <v>38</v>
       </c>
       <c r="AO1" s="3" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
       <c r="AP1" s="3" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="AQ1" s="2"/>
     </row>
@@ -9877,16 +9874,16 @@
         <v>76</v>
       </c>
       <c r="AM2" s="27" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="AN2" s="12" t="s">
         <v>77</v>
       </c>
       <c r="AO2" s="12" t="s">
-        <v>846</v>
+        <v>842</v>
       </c>
       <c r="AP2" s="12" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
       <c r="AQ2" s="2"/>
     </row>
@@ -9910,13 +9907,13 @@
         <v>83</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="H3" s="1">
         <v>1</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>84</v>
@@ -9926,25 +9923,25 @@
       </c>
       <c r="L3" s="5"/>
       <c r="M3" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="O3" s="11" t="s">
+        <v>727</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="S3" s="1" t="s">
         <v>729</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>730</v>
-      </c>
-      <c r="O3" s="11" t="s">
-        <v>731</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>733</v>
       </c>
       <c r="T3" s="23">
         <v>46133</v>
@@ -9953,19 +9950,19 @@
         <v>4</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="Z3" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AA3" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="AB3" s="1" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="AC3" s="1" t="s">
         <v>89</v>
@@ -9978,13 +9975,13 @@
         <v>91</v>
       </c>
       <c r="AL3" s="1" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="AM3" s="5">
         <v>3</v>
       </c>
       <c r="AO3" s="1" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="AP3" s="1" t="b">
         <v>1</v>
@@ -10010,13 +10007,13 @@
         <v>94</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="H4" s="1">
         <v>1</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>95</v>
@@ -10026,16 +10023,16 @@
         <v>86</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="R4" s="1" t="s">
         <v>96</v>
@@ -10053,22 +10050,22 @@
         <v>98</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="Y4" s="1" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="Z4" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AA4" s="1" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="AB4" s="1" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="AC4" s="1" t="s">
         <v>89</v>
@@ -10084,7 +10081,7 @@
         <v>4</v>
       </c>
       <c r="AO4" s="1" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="AP4" s="1" t="b">
         <v>1</v>
@@ -10110,16 +10107,16 @@
         <v>103</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="H5" s="1">
         <v>1</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="L5" s="5">
         <v>2020</v>
@@ -10128,16 +10125,16 @@
         <v>104</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="P5" s="1" t="s">
         <v>105</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="R5" s="1" t="s">
         <v>96</v>
@@ -10146,28 +10143,28 @@
         <v>2023</v>
       </c>
       <c r="T5" s="24" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="U5" s="1">
         <v>16</v>
       </c>
       <c r="W5" s="1" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="X5" s="1" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="Y5" s="1" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="Z5" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AA5" s="1" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="AB5" s="1" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="AC5" s="1" t="s">
         <v>89</v>
@@ -10183,7 +10180,7 @@
         <v>1</v>
       </c>
       <c r="AO5" s="1" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="AP5" s="1" t="b">
         <v>1</v>
@@ -10191,7 +10188,7 @@
     </row>
     <row r="6" spans="1:43" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>108</v>
+        <v>858</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>79</v>
@@ -10203,41 +10200,41 @@
         <v>101</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>110</v>
+        <v>859</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="H6" s="1">
         <v>1</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="L6" s="5"/>
       <c r="M6" s="1" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="O6" s="11" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="P6" s="1" t="s">
         <v>105</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="R6" s="1" t="s">
         <v>96</v>
@@ -10246,25 +10243,25 @@
         <v>2023</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="U6" s="1">
         <v>18</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="Y6" s="1" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="Z6" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AA6" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="AB6" s="1" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="AC6" s="1" t="s">
         <v>89</v>
@@ -10274,16 +10271,16 @@
       </c>
       <c r="AG6" s="6"/>
       <c r="AI6" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="AL6" s="1" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="AM6" s="5">
         <v>2</v>
       </c>
       <c r="AO6" s="1" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="AP6" s="1" t="b">
         <v>1</v>
@@ -10291,7 +10288,7 @@
     </row>
     <row r="7" spans="1:43" ht="90" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>114</v>
+        <v>857</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>79</v>
@@ -10303,38 +10300,38 @@
         <v>101</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="H7" s="1">
         <v>1</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="L7" s="5"/>
       <c r="M7" s="1" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="O7" s="11" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="R7" s="1" t="s">
         <v>87</v>
@@ -10349,19 +10346,19 @@
         <v>1</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="Z7" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AA7" s="1" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="AB7" s="1" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="AC7" s="1" t="s">
         <v>89</v>
@@ -10374,13 +10371,13 @@
         <v>91</v>
       </c>
       <c r="AL7" s="1" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="AM7" s="5">
         <v>5</v>
       </c>
       <c r="AO7" s="1" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="AP7" s="1" t="b">
         <v>1</v>
@@ -10388,7 +10385,7 @@
     </row>
     <row r="8" spans="1:43" ht="90" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>79</v>
@@ -10397,71 +10394,71 @@
         <v>80</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="H8" s="1">
         <v>1</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="L8" s="5"/>
       <c r="M8" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="O8" s="11" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="P8" s="1" t="s">
         <v>38</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="S8" s="1">
         <v>2022</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="U8" s="1">
         <v>18</v>
       </c>
       <c r="W8" s="1" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="Y8" s="1" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="Z8" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AA8" s="1" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="AB8" s="1" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="AC8" s="1" t="s">
         <v>89</v>
@@ -10471,13 +10468,13 @@
       </c>
       <c r="AG8" s="6"/>
       <c r="AL8" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="AM8" s="5">
         <v>12</v>
       </c>
       <c r="AO8" s="1" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="AP8" s="1" t="b">
         <v>0</v>
@@ -10485,7 +10482,7 @@
     </row>
     <row r="9" spans="1:43" ht="135" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>79</v>
@@ -10494,47 +10491,47 @@
         <v>80</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="H9" s="1">
         <v>1</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="L9" s="5"/>
       <c r="M9" s="1" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="U9" s="1">
         <v>5</v>
       </c>
       <c r="Y9" s="1" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="Z9" s="1" t="s">
         <v>88</v>
@@ -10543,20 +10540,20 @@
         <v>89</v>
       </c>
       <c r="AF9" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="AG9" s="6"/>
       <c r="AI9" s="1" t="s">
         <v>91</v>
       </c>
       <c r="AL9" s="1" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="AM9" s="5">
         <v>6</v>
       </c>
       <c r="AO9" s="1" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="AP9" s="1" t="b">
         <v>1</v>
@@ -10564,7 +10561,7 @@
     </row>
     <row r="10" spans="1:43" ht="90" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>79</v>
@@ -10573,62 +10570,62 @@
         <v>80</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="H10" s="1">
         <v>1</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="L10" s="5"/>
       <c r="M10" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="O10" s="11" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="S10" s="24">
         <v>46054</v>
       </c>
       <c r="T10" s="1" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="W10" s="1" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="Y10" s="1" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="Z10" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="AC10" s="1" t="s">
         <v>89</v>
@@ -10638,13 +10635,13 @@
       </c>
       <c r="AG10" s="6"/>
       <c r="AL10" s="1" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="AM10" s="5">
         <v>7</v>
       </c>
       <c r="AO10" s="1" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="AP10" s="1" t="b">
         <v>0</v>
@@ -10652,7 +10649,7 @@
     </row>
     <row r="11" spans="1:43" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>79</v>
@@ -10661,26 +10658,26 @@
         <v>80</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="H11" s="1">
         <v>1</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="L11" s="5"/>
       <c r="Y11" s="1" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="Z11" s="1" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="AC11" s="1" t="s">
         <v>89</v>
@@ -10690,7 +10687,7 @@
       </c>
       <c r="AG11" s="6"/>
       <c r="AL11" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="AM11" s="5">
         <v>8</v>
@@ -10701,7 +10698,7 @@
     </row>
     <row r="12" spans="1:43" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>79</v>
@@ -10710,38 +10707,38 @@
         <v>80</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="H12" s="1">
         <v>1</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="L12" s="5"/>
       <c r="M12" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="R12" s="1" t="s">
         <v>96</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="U12" s="1">
         <v>12</v>
       </c>
       <c r="Y12" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="Z12" s="1" t="s">
         <v>88</v>
@@ -10754,13 +10751,13 @@
       </c>
       <c r="AG12" s="6"/>
       <c r="AL12" s="1" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="AM12" s="5">
         <v>9</v>
       </c>
       <c r="AO12" s="1" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="AP12" s="1" t="b">
         <v>1</v>
@@ -10768,7 +10765,7 @@
     </row>
     <row r="13" spans="1:43" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>79</v>
@@ -10777,41 +10774,41 @@
         <v>80</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="H13" s="1">
         <v>1</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="L13" s="5"/>
       <c r="M13" s="1" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="R13" s="1" t="s">
         <v>96</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="U13" s="1">
         <v>9</v>
       </c>
       <c r="Y13" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="Z13" s="1" t="s">
         <v>88</v>
@@ -10827,13 +10824,13 @@
         <v>91</v>
       </c>
       <c r="AL13" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="AM13" s="5">
         <v>11</v>
       </c>
       <c r="AO13" s="1" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="AP13" s="1" t="b">
         <v>1</v>
@@ -10841,111 +10838,111 @@
     </row>
     <row r="14" spans="1:43" ht="90" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E14" s="25">
         <v>2</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
       <c r="H14" s="1">
         <v>1</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="L14" s="5"/>
       <c r="M14" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
       <c r="O14" s="1" t="s">
+        <v>786</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="R14" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="S14" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="T14" s="1" t="s">
         <v>790</v>
-      </c>
-      <c r="P14" s="1" t="s">
-        <v>741</v>
-      </c>
-      <c r="Q14" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="R14" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="S14" s="1" t="s">
-        <v>793</v>
-      </c>
-      <c r="T14" s="1" t="s">
-        <v>794</v>
       </c>
       <c r="U14" s="1">
         <v>8</v>
       </c>
       <c r="V14" s="1" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
       <c r="W14" s="1" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="X14" s="1" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="Y14" s="1" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="Z14" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AA14" s="1" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="AB14" s="1" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="AC14" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AF14" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="AG14" s="6"/>
       <c r="AH14" s="1" t="s">
         <v>91</v>
       </c>
       <c r="AJ14" s="1" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="AL14" s="1" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="AM14" s="5">
         <v>10</v>
       </c>
       <c r="AN14" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="AO14" s="1" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="AP14" s="1" t="b">
         <v>1</v>
@@ -10953,71 +10950,71 @@
     </row>
     <row r="15" spans="1:43" ht="120" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="H15" s="1">
         <v>1</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="L15" s="5"/>
       <c r="M15" s="1" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="O15" s="11" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="R15" s="1" t="s">
         <v>96</v>
       </c>
       <c r="S15" s="1" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="U15" s="1">
         <v>9</v>
       </c>
       <c r="V15" s="1" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="W15" s="1" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="Y15" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="Z15" s="1" t="s">
         <v>88</v>
@@ -11026,26 +11023,26 @@
         <v>89</v>
       </c>
       <c r="AF15" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="AG15" s="6"/>
       <c r="AI15" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="AJ15" s="1" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="AL15" s="1" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="AM15" s="5">
         <v>1</v>
       </c>
       <c r="AN15" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="AO15" s="1" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="AP15" s="1" t="b">
         <v>1</v>
@@ -11053,59 +11050,59 @@
     </row>
     <row r="16" spans="1:43" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="H16" s="1">
         <v>1</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="L16" s="5"/>
       <c r="M16" s="1" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="R16" s="1" t="s">
         <v>96</v>
       </c>
       <c r="T16" s="1" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="U16" s="1">
         <v>6</v>
       </c>
       <c r="V16" s="1" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="W16" s="1" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="Y16" s="1" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="Z16" s="1" t="s">
         <v>88</v>
@@ -11114,23 +11111,23 @@
         <v>89</v>
       </c>
       <c r="AF16" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="AG16" s="6"/>
       <c r="AJ16" s="1" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="AL16" s="1" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="AM16" s="5">
         <v>3</v>
       </c>
       <c r="AN16" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="AO16" s="1" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="AP16" s="1" t="b">
         <v>1</v>
@@ -11138,41 +11135,41 @@
     </row>
     <row r="17" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
       <c r="H17" s="1">
         <v>1</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="L17" s="5"/>
       <c r="M17" s="1" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="R17" s="1" t="s">
         <v>96</v>
@@ -11184,7 +11181,7 @@
         <v>5</v>
       </c>
       <c r="Y17" s="1" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="Z17" s="1" t="s">
         <v>88</v>
@@ -11193,7 +11190,7 @@
         <v>89</v>
       </c>
       <c r="AF17" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="AG17" s="6"/>
       <c r="AH17" s="1" t="s">
@@ -11203,19 +11200,19 @@
         <v>91</v>
       </c>
       <c r="AJ17" s="1" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="AL17" s="1" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="AM17" s="5">
         <v>4</v>
       </c>
       <c r="AN17" s="1" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="AO17" s="1" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="AP17" s="1" t="b">
         <v>1</v>
@@ -11223,38 +11220,38 @@
     </row>
     <row r="18" spans="1:42" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="H18" s="1">
         <v>1</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="L18" s="5"/>
       <c r="M18" s="1" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="R18" s="1" t="s">
         <v>87</v>
@@ -11263,7 +11260,7 @@
         <v>1</v>
       </c>
       <c r="Y18" s="1" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="Z18" s="1" t="s">
         <v>88</v>
@@ -11272,17 +11269,17 @@
         <v>89</v>
       </c>
       <c r="AF18" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="AG18" s="6"/>
       <c r="AL18" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="AM18" s="5">
         <v>6</v>
       </c>
       <c r="AO18" s="1" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="AP18" s="1" t="b">
         <v>1</v>
@@ -11290,41 +11287,41 @@
     </row>
     <row r="19" spans="1:42" ht="60" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="H19" s="1">
         <v>1</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="J19" s="1" t="s">
+        <v>825</v>
+      </c>
+      <c r="K19" s="1" t="s">
         <v>829</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>833</v>
       </c>
       <c r="L19" s="5"/>
       <c r="M19" s="1" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="R19" s="1" t="s">
         <v>96</v>
@@ -11336,32 +11333,32 @@
         <v>4</v>
       </c>
       <c r="V19" s="1" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="Y19" s="1" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="Z19" s="1" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="AB19" s="1" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="AC19" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AF19" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="AG19" s="6"/>
       <c r="AL19" s="1" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="AM19" s="5">
         <v>5</v>
       </c>
       <c r="AO19" s="1" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="AP19" s="1" t="b">
         <v>1</v>
@@ -11369,50 +11366,50 @@
     </row>
     <row r="20" spans="1:42" ht="60" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="H20" s="1">
         <v>1</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="L20" s="5"/>
       <c r="M20" s="1" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="R20" s="1" t="s">
         <v>96</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="U20" s="1">
         <v>1</v>
       </c>
       <c r="Y20" s="1" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="Z20" s="1" t="s">
         <v>88</v>
@@ -11421,26 +11418,26 @@
         <v>89</v>
       </c>
       <c r="AF20" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="AG20" s="6"/>
       <c r="AI20" s="1" t="s">
         <v>91</v>
       </c>
       <c r="AJ20" s="1" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="AL20" s="1" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="AM20" s="5">
         <v>7</v>
       </c>
       <c r="AN20" s="1" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="AO20" s="1" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="AP20" s="1" t="b">
         <v>1</v>
@@ -11448,53 +11445,53 @@
     </row>
     <row r="21" spans="1:42" ht="60" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="H21" s="1">
         <v>1</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="L21" s="5"/>
       <c r="M21" s="1" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="R21" s="1" t="s">
         <v>96</v>
       </c>
       <c r="T21" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="U21" s="1">
         <v>1</v>
       </c>
       <c r="Y21" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="Z21" s="1" t="s">
         <v>88</v>
@@ -11503,17 +11500,17 @@
         <v>89</v>
       </c>
       <c r="AF21" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="AG21" s="6"/>
       <c r="AL21" s="1" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="AM21" s="5">
         <v>8</v>
       </c>
       <c r="AO21" s="1" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="AP21" s="1" t="b">
         <v>1</v>
@@ -11521,36 +11518,36 @@
     </row>
     <row r="22" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="H22" s="1">
         <v>1</v>
       </c>
       <c r="L22" s="5"/>
       <c r="Y22" s="1" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="AF22" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="AG22" s="6"/>
       <c r="AL22" s="1" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="AM22" s="5">
         <v>2</v>
@@ -11561,53 +11558,53 @@
     </row>
     <row r="23" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="H23" s="1">
         <v>1</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="L23" s="5"/>
       <c r="M23" s="1" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="R23" s="1" t="s">
         <v>96</v>
       </c>
       <c r="T23" s="1" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="U23" s="1">
         <v>6</v>
       </c>
       <c r="Y23" s="1" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="Z23" s="1" t="s">
         <v>88</v>
@@ -11616,17 +11613,17 @@
         <v>89</v>
       </c>
       <c r="AF23" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="AG23" s="6"/>
       <c r="AL23" s="1" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="AM23" s="5">
         <v>3</v>
       </c>
       <c r="AO23" s="1" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="AP23" s="1" t="b">
         <v>1</v>
@@ -11634,66 +11631,66 @@
     </row>
     <row r="24" spans="1:42" ht="75" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="H24" s="1">
         <v>1</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="L24" s="5"/>
       <c r="M24" s="1" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="V24" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="Y24" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="Z24" s="1" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="AB24" s="1" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="AC24" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AF24" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="AG24" s="6"/>
       <c r="AL24" s="1" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="AM24" s="5">
         <v>9</v>
       </c>
       <c r="AO24" s="1" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="AP24" s="1" t="b">
         <v>0</v>
@@ -11701,63 +11698,63 @@
     </row>
     <row r="25" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="H25" s="1">
         <v>-1</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="L25" s="5"/>
       <c r="R25" s="1" t="s">
         <v>96</v>
       </c>
       <c r="T25" s="1" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="U25" s="1">
         <v>24</v>
       </c>
       <c r="V25" s="1" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="Y25" s="1" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="AF25" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="AG25" s="6"/>
       <c r="AJ25" s="1" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="AL25" s="1" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="AM25" s="5">
         <v>11</v>
       </c>
       <c r="AN25" s="1" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="AO25" s="1" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="AP25" s="1" t="b">
         <v>0</v>
@@ -11765,57 +11762,57 @@
     </row>
     <row r="26" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="F26" s="1" t="s">
         <v>260</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>264</v>
       </c>
       <c r="H26" s="1">
         <v>-1</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="L26" s="5"/>
       <c r="R26" s="1" t="s">
         <v>96</v>
       </c>
       <c r="T26" s="1" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="U26" s="1">
         <v>24</v>
       </c>
       <c r="V26" s="1" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="Y26" s="1" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="AF26" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="AG26" s="6"/>
       <c r="AL26" s="1" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="AM26" s="5">
         <v>11</v>
       </c>
       <c r="AO26" s="1" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="AP26" s="1" t="b">
         <v>1</v>
@@ -11823,38 +11820,38 @@
     </row>
     <row r="27" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="H27" s="1">
         <v>1</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="L27" s="5"/>
       <c r="M27" s="1" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="R27" s="1" t="s">
         <v>87</v>
@@ -11863,7 +11860,7 @@
         <v>2</v>
       </c>
       <c r="Y27" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="Z27" s="1" t="s">
         <v>88</v>
@@ -11872,20 +11869,20 @@
         <v>89</v>
       </c>
       <c r="AF27" s="1" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="AG27" s="6"/>
       <c r="AI27" s="1" t="s">
         <v>91</v>
       </c>
       <c r="AL27" s="1" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="AM27" s="5">
         <v>3</v>
       </c>
       <c r="AO27" s="1" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="AP27" s="1" t="b">
         <v>1</v>
@@ -11893,53 +11890,53 @@
     </row>
     <row r="28" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="H28" s="1">
         <v>-1</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="L28" s="5"/>
       <c r="M28" s="1" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="R28" s="1" t="s">
         <v>96</v>
       </c>
       <c r="T28" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="U28" s="1">
         <v>14</v>
       </c>
       <c r="Y28" s="1" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="Z28" s="1" t="s">
         <v>88</v>
@@ -11948,20 +11945,20 @@
         <v>89</v>
       </c>
       <c r="AF28" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="AG28" s="6"/>
       <c r="AI28" s="1" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="AL28" s="1" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="AM28" s="5">
         <v>2</v>
       </c>
       <c r="AO28" s="1" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="AP28" s="1" t="b">
         <v>1</v>
@@ -11969,38 +11966,38 @@
     </row>
     <row r="29" spans="1:42" ht="60" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
       <c r="H29" s="1">
         <v>-1</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="L29" s="5"/>
       <c r="M29" s="1" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="R29" s="1" t="s">
         <v>87</v>
@@ -12009,32 +12006,32 @@
         <v>1</v>
       </c>
       <c r="Y29" s="1" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="Z29" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AB29" s="1" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="AC29" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AF29" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="AG29" s="6"/>
       <c r="AI29" s="1" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AL29" s="1" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="AM29" s="5">
         <v>4</v>
       </c>
       <c r="AO29" s="1" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="AP29" s="1" t="b">
         <v>0</v>
@@ -12042,53 +12039,53 @@
     </row>
     <row r="30" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="H30" s="1">
         <v>1</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="L30" s="5"/>
       <c r="M30" s="1" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="R30" s="1" t="s">
         <v>96</v>
       </c>
       <c r="T30" s="1" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="U30" s="1">
         <v>7</v>
       </c>
       <c r="Y30" s="1" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="Z30" s="1" t="s">
         <v>88</v>
@@ -12097,14 +12094,14 @@
         <v>89</v>
       </c>
       <c r="AF30" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="AG30" s="6"/>
       <c r="AI30" s="1" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="AL30" s="1" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="AM30" s="5">
         <v>1</v>
@@ -12113,7 +12110,7 @@
         <v>91</v>
       </c>
       <c r="AO30" s="1" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="AP30" s="1" t="b">
         <v>1</v>
@@ -12121,72 +12118,72 @@
     </row>
     <row r="31" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="H31" s="1">
         <v>-1</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="L31" s="5"/>
       <c r="M31" s="1" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="R31" s="1" t="s">
         <v>96</v>
       </c>
       <c r="T31" s="1" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="U31" s="1">
         <v>6</v>
       </c>
       <c r="Y31" s="1" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="Z31" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="AB31" s="1" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="AC31" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AF31" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="AG31" s="6"/>
       <c r="AL31" s="1" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="AM31" s="5">
         <v>5</v>
       </c>
       <c r="AO31" s="1" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="AP31" s="1" t="b">
         <v>1</v>
@@ -12194,72 +12191,72 @@
     </row>
     <row r="32" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="H32" s="1">
         <v>1</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="L32" s="5"/>
       <c r="M32" s="1" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="R32" s="1" t="s">
         <v>96</v>
       </c>
       <c r="T32" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="U32" s="1">
         <v>6</v>
       </c>
       <c r="Y32" s="1" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="Z32" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="AB32" s="1" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="AC32" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AF32" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="AG32" s="6"/>
       <c r="AL32" s="1" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="AM32" s="5">
         <v>6</v>
       </c>
       <c r="AO32" s="1" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="AP32" s="1" t="b">
         <v>1</v>
@@ -12267,44 +12264,44 @@
     </row>
     <row r="33" spans="1:42" ht="60" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="H33" s="1">
         <v>-1</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="L33" s="5"/>
       <c r="M33" s="1" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="R33" s="1" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="U33" s="1">
         <v>6</v>
       </c>
       <c r="Y33" s="1" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="Z33" s="1" t="s">
         <v>88</v>
@@ -12313,20 +12310,20 @@
         <v>89</v>
       </c>
       <c r="AF33" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="AG33" s="6"/>
       <c r="AI33" s="1" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="AL33" s="1" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="AM33" s="5">
         <v>7</v>
       </c>
       <c r="AO33" s="1" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="AP33" s="1" t="b">
         <v>1</v>
@@ -12334,47 +12331,47 @@
     </row>
     <row r="34" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="H34" s="1">
         <v>1</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="L34" s="5"/>
       <c r="M34" s="1" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="R34" s="1" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="U34" s="1">
         <v>6</v>
       </c>
       <c r="Y34" s="1" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="Z34" s="1" t="s">
         <v>88</v>
@@ -12383,17 +12380,17 @@
         <v>89</v>
       </c>
       <c r="AF34" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="AG34" s="6"/>
       <c r="AL34" s="1" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="AM34" s="5">
         <v>8</v>
       </c>
       <c r="AO34" s="1" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="AP34" s="1" t="b">
         <v>1</v>
@@ -12401,42 +12398,42 @@
     </row>
     <row r="35" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="H35" s="1">
         <v>1</v>
       </c>
       <c r="L35" s="5"/>
       <c r="Y35" s="1" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="Z35" s="1" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="AC35" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AF35" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="AG35" s="6"/>
       <c r="AL35" s="1" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="AM35" s="5">
         <v>9</v>
@@ -12447,60 +12444,60 @@
     </row>
     <row r="36" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="H36" s="1">
         <v>1</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="L36" s="5"/>
       <c r="R36" s="1" t="s">
         <v>96</v>
       </c>
       <c r="T36" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="U36" s="1">
         <v>9</v>
       </c>
       <c r="Y36" s="1" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="AF36" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="AG36" s="6"/>
       <c r="AI36" s="1" t="s">
         <v>91</v>
       </c>
       <c r="AL36" s="1" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="AM36" s="5">
         <v>10</v>
       </c>
       <c r="AN36" s="1" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="AO36" s="1" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="AP36" s="1" t="b">
         <v>1</v>
@@ -12508,38 +12505,38 @@
     </row>
     <row r="37" spans="1:42" ht="60" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="E37" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="F37" s="1" t="s">
         <v>352</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>356</v>
       </c>
       <c r="H37" s="1">
         <v>-1</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="L37" s="5"/>
       <c r="M37" s="1" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="R37" s="1" t="s">
         <v>96</v>
@@ -12551,7 +12548,7 @@
         <v>4</v>
       </c>
       <c r="Y37" s="1" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="Z37" s="1" t="s">
         <v>88</v>
@@ -12560,17 +12557,17 @@
         <v>89</v>
       </c>
       <c r="AF37" s="1" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="AG37" s="6"/>
       <c r="AL37" s="1" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="AM37" s="5">
         <v>1</v>
       </c>
       <c r="AO37" s="1" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="AP37" s="1" t="b">
         <v>1</v>
@@ -12578,38 +12575,38 @@
     </row>
     <row r="38" spans="1:42" ht="60" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="H38" s="1">
         <v>1</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="L38" s="5"/>
       <c r="M38" s="1" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="R38" s="1" t="s">
         <v>96</v>
@@ -12621,7 +12618,7 @@
         <v>4</v>
       </c>
       <c r="Y38" s="1" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="Z38" s="1" t="s">
         <v>88</v>
@@ -12630,20 +12627,20 @@
         <v>89</v>
       </c>
       <c r="AF38" s="1" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="AG38" s="6"/>
       <c r="AI38" s="1" t="s">
         <v>91</v>
       </c>
       <c r="AL38" s="1" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="AM38" s="5">
         <v>2</v>
       </c>
       <c r="AO38" s="1" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="AP38" s="1" t="b">
         <v>1</v>
@@ -12651,50 +12648,50 @@
     </row>
     <row r="39" spans="1:42" ht="60" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="H39" s="1">
         <v>1</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="L39" s="5"/>
       <c r="M39" s="1" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="R39" s="1" t="s">
         <v>96</v>
       </c>
       <c r="T39" s="1" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="U39" s="1">
         <v>4</v>
       </c>
       <c r="Y39" s="1" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="Z39" s="1" t="s">
         <v>88</v>
@@ -12703,17 +12700,17 @@
         <v>89</v>
       </c>
       <c r="AF39" s="1" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="AG39" s="6"/>
       <c r="AL39" s="1" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="AM39" s="5">
         <v>8</v>
       </c>
       <c r="AO39" s="1" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="AP39" s="1" t="b">
         <v>1</v>
@@ -12721,32 +12718,32 @@
     </row>
     <row r="40" spans="1:42" ht="60" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="H40" s="1">
         <v>1</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L40" s="5"/>
       <c r="M40" s="1" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="R40" s="1" t="s">
         <v>96</v>
@@ -12758,10 +12755,10 @@
         <v>4</v>
       </c>
       <c r="V40" s="1" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="Y40" s="1" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="Z40" s="1" t="s">
         <v>88</v>
@@ -12770,20 +12767,20 @@
         <v>89</v>
       </c>
       <c r="AF40" s="1" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="AG40" s="6"/>
       <c r="AI40" s="1" t="s">
         <v>91</v>
       </c>
       <c r="AL40" s="1" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="AM40" s="5">
         <v>9</v>
       </c>
       <c r="AO40" s="1" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="AP40" s="1" t="b">
         <v>1</v>
@@ -12791,47 +12788,47 @@
     </row>
     <row r="41" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="H41" s="1">
         <v>1</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="L41" s="5"/>
       <c r="M41" s="1" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="R41" s="1" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="U41" s="1">
         <v>3</v>
       </c>
       <c r="Y41" s="1" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="Z41" s="1" t="s">
         <v>88</v>
@@ -12840,20 +12837,20 @@
         <v>89</v>
       </c>
       <c r="AF41" s="1" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="AG41" s="6"/>
       <c r="AI41" s="1" t="s">
         <v>91</v>
       </c>
       <c r="AL41" s="1" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="AM41" s="5">
         <v>7</v>
       </c>
       <c r="AO41" s="1" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="AP41" s="1" t="b">
         <v>1</v>
@@ -12861,47 +12858,47 @@
     </row>
     <row r="42" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="H42" s="1">
         <v>-1</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="L42" s="5"/>
       <c r="M42" s="1" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="R42" s="1" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="U42" s="1">
         <v>3</v>
       </c>
       <c r="Y42" s="1" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="Z42" s="1" t="s">
         <v>88</v>
@@ -12910,17 +12907,17 @@
         <v>89</v>
       </c>
       <c r="AF42" s="1" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="AG42" s="6"/>
       <c r="AL42" s="1" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="AM42" s="5">
         <v>6</v>
       </c>
       <c r="AO42" s="1" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="AP42" s="1" t="b">
         <v>1</v>
@@ -12928,53 +12925,53 @@
     </row>
     <row r="43" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="H43" s="1">
         <v>-1</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="L43" s="5"/>
       <c r="M43" s="1" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="P43" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="R43" s="1" t="s">
         <v>96</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="U43" s="1">
         <v>10</v>
       </c>
       <c r="Y43" s="1" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="Z43" s="1" t="s">
         <v>88</v>
@@ -12983,20 +12980,20 @@
         <v>89</v>
       </c>
       <c r="AF43" s="1" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="AG43" s="6"/>
       <c r="AI43" s="1" t="s">
         <v>91</v>
       </c>
       <c r="AL43" s="1" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="AM43" s="5">
         <v>3</v>
       </c>
       <c r="AO43" s="1" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="AP43" s="1" t="b">
         <v>1</v>
@@ -13004,57 +13001,57 @@
     </row>
     <row r="44" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="H44" s="1">
         <v>-1</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="L44" s="5"/>
       <c r="Y44" s="1" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="Z44" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="AB44" s="1" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="AC44" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AF44" s="1" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="AG44" s="6"/>
       <c r="AI44" s="1" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="AL44" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="AM44" s="5">
         <v>4</v>
       </c>
       <c r="AO44" s="1" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="AP44" s="1" t="b">
         <v>1</v>
@@ -13062,41 +13059,41 @@
     </row>
     <row r="45" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="H45" s="1">
         <v>-1</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="L45" s="5"/>
       <c r="M45" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="P45" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="R45" s="1" t="s">
         <v>96</v>
@@ -13108,7 +13105,7 @@
         <v>6</v>
       </c>
       <c r="Y45" s="1" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="Z45" s="1" t="s">
         <v>88</v>
@@ -13117,17 +13114,17 @@
         <v>89</v>
       </c>
       <c r="AF45" s="1" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="AG45" s="6"/>
       <c r="AL45" s="1" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="AM45" s="5">
         <v>5</v>
       </c>
       <c r="AO45" s="1" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="AP45" s="1" t="b">
         <v>1</v>
@@ -13135,35 +13132,35 @@
     </row>
     <row r="46" spans="1:42" ht="60" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="H46" s="1">
         <v>-1</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="L46" s="5"/>
       <c r="M46" s="1" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="R46" s="1" t="s">
         <v>87</v>
@@ -13172,7 +13169,7 @@
         <v>1</v>
       </c>
       <c r="Y46" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="Z46" s="1" t="s">
         <v>88</v>
@@ -13181,11 +13178,11 @@
         <v>89</v>
       </c>
       <c r="AF46" s="1" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="AG46" s="6"/>
       <c r="AL46" s="1" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="AM46" s="5">
         <v>10</v>
@@ -13196,45 +13193,45 @@
     </row>
     <row r="47" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="H47" s="1">
         <v>-1</v>
       </c>
       <c r="L47" s="5"/>
       <c r="Y47" s="1" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="Z47" s="1" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="AB47" s="1" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="AC47" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AF47" s="1" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="AG47" s="6"/>
       <c r="AL47" s="1" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="AM47" s="5">
         <v>11</v>
@@ -13245,84 +13242,84 @@
     </row>
     <row r="48" spans="1:42" ht="90" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="C48" s="22" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="D48" s="22" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="E48" s="22">
         <v>5</v>
       </c>
       <c r="F48" s="22" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="H48" s="1">
         <v>-1</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="L48" s="5"/>
       <c r="M48" s="1" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="P48" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="R48" s="1" t="s">
         <v>96</v>
       </c>
       <c r="T48" s="1" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="U48" s="1">
         <v>24</v>
       </c>
       <c r="V48" s="1" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="W48" s="1" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="Y48" s="1" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="Z48" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AA48" s="1" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="AB48" s="1" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="AC48" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AF48" s="1" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="AG48" s="6"/>
       <c r="AL48" s="1" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="AM48" s="5">
         <v>1</v>
       </c>
       <c r="AO48" s="1" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="AP48" s="1" t="b">
         <v>1</v>
@@ -13330,47 +13327,47 @@
     </row>
     <row r="49" spans="1:42" ht="75" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="C49" s="22" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="D49" s="22" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="E49" s="22" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="F49" s="22" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="H49" s="1">
         <v>1</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="L49" s="5"/>
       <c r="M49" s="1" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="P49" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="R49" s="1" t="s">
         <v>96</v>
@@ -13379,38 +13376,38 @@
         <v>24</v>
       </c>
       <c r="V49" s="1" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="W49" s="1" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="Y49" s="1" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="Z49" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AA49" s="1" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="AB49" s="1" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="AC49" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AF49" s="1" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="AG49" s="6"/>
       <c r="AL49" s="1" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="AM49" s="5">
         <v>10</v>
       </c>
       <c r="AO49" s="1" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="AP49" s="1" t="b">
         <v>1</v>
@@ -13418,53 +13415,53 @@
     </row>
     <row r="50" spans="1:42" ht="60" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="C50" s="22" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="D50" s="22" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="E50" s="22" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="F50" s="22" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="H50" s="1">
         <v>1</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="L50" s="5"/>
       <c r="M50" s="1" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="P50" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="Q50" s="1" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="R50" s="1" t="s">
         <v>96</v>
@@ -13476,38 +13473,38 @@
         <v>12</v>
       </c>
       <c r="V50" s="1" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="W50" s="1" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="Y50" s="1" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="Z50" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AA50" s="1" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="AB50" s="1" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="AC50" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AF50" s="1" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="AG50" s="6"/>
       <c r="AL50" s="1" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="AM50" s="5">
         <v>9</v>
       </c>
       <c r="AO50" s="1" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="AP50" s="1" t="b">
         <v>1</v>
@@ -13515,47 +13512,47 @@
     </row>
     <row r="51" spans="1:42" ht="90" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="C51" s="22" t="s">
+        <v>425</v>
+      </c>
+      <c r="D51" s="22" t="s">
+        <v>457</v>
+      </c>
+      <c r="E51" s="22" t="s">
+        <v>458</v>
+      </c>
+      <c r="F51" s="22" t="s">
+        <v>459</v>
+      </c>
+      <c r="G51" s="1" t="s">
         <v>460</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="C51" s="22" t="s">
-        <v>429</v>
-      </c>
-      <c r="D51" s="22" t="s">
-        <v>461</v>
-      </c>
-      <c r="E51" s="22" t="s">
-        <v>462</v>
-      </c>
-      <c r="F51" s="22" t="s">
-        <v>463</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>464</v>
       </c>
       <c r="H51" s="1">
         <v>1</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="L51" s="5"/>
       <c r="M51" s="1" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="O51" s="1" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="P51" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="R51" s="1" t="s">
         <v>87</v>
@@ -13564,41 +13561,41 @@
         <v>2</v>
       </c>
       <c r="V51" s="1" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="W51" s="1" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="Y51" s="1" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="Z51" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AA51" s="1" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="AB51" s="1" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="AC51" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AF51" s="1" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="AG51" s="6"/>
       <c r="AK51" s="1" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="AL51" s="1" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="AM51" s="5">
         <v>8</v>
       </c>
       <c r="AO51" s="1" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="AP51" s="1" t="b">
         <v>1</v>
@@ -13606,47 +13603,47 @@
     </row>
     <row r="52" spans="1:42" ht="75" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="C52" s="22" t="s">
+        <v>425</v>
+      </c>
+      <c r="D52" s="22" t="s">
+        <v>470</v>
+      </c>
+      <c r="E52" s="22" t="s">
+        <v>471</v>
+      </c>
+      <c r="F52" s="22" t="s">
+        <v>472</v>
+      </c>
+      <c r="G52" s="1" t="s">
         <v>473</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="C52" s="22" t="s">
-        <v>429</v>
-      </c>
-      <c r="D52" s="22" t="s">
-        <v>474</v>
-      </c>
-      <c r="E52" s="22" t="s">
-        <v>475</v>
-      </c>
-      <c r="F52" s="22" t="s">
-        <v>476</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>477</v>
       </c>
       <c r="H52" s="1">
         <v>-1</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="L52" s="5"/>
       <c r="M52" s="1" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="O52" s="11" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="P52" s="1" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="R52" s="1" t="s">
         <v>96</v>
@@ -13655,38 +13652,38 @@
         <v>24</v>
       </c>
       <c r="V52" s="1" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="W52" s="1" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="Y52" s="1" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="Z52" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AA52" s="1" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="AB52" s="1" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="AC52" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AF52" s="1" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="AG52" s="6"/>
       <c r="AL52" s="1" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="AM52" s="5">
         <v>2</v>
       </c>
       <c r="AO52" s="1" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="AP52" s="1" t="b">
         <v>1</v>
@@ -13694,37 +13691,37 @@
     </row>
     <row r="53" spans="1:42" ht="135" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="C53" s="22" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="D53" s="22" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="E53" s="22" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="F53" s="22" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="H53" s="1">
         <v>-1</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="L53" s="5">
         <v>2020</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="R53" s="1" t="s">
         <v>96</v>
@@ -13733,41 +13730,41 @@
         <v>13</v>
       </c>
       <c r="V53" s="1" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="W53" s="1" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="Y53" s="1" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="Z53" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AA53" s="1" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="AB53" s="1" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="AC53" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AF53" s="1" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="AG53" s="6"/>
       <c r="AI53" s="1" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="AL53" s="1" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="AM53" s="5">
         <v>3</v>
       </c>
       <c r="AO53" s="1" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="AP53" s="1" t="b">
         <v>1</v>
@@ -13775,78 +13772,78 @@
     </row>
     <row r="54" spans="1:42" ht="60" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="C54" s="22" t="s">
+        <v>425</v>
+      </c>
+      <c r="D54" s="22" t="s">
+        <v>494</v>
+      </c>
+      <c r="E54" s="22" t="s">
+        <v>495</v>
+      </c>
+      <c r="F54" s="22" t="s">
+        <v>496</v>
+      </c>
+      <c r="G54" s="1" t="s">
         <v>497</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="C54" s="22" t="s">
-        <v>429</v>
-      </c>
-      <c r="D54" s="22" t="s">
-        <v>498</v>
-      </c>
-      <c r="E54" s="22" t="s">
-        <v>499</v>
-      </c>
-      <c r="F54" s="22" t="s">
-        <v>500</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>501</v>
       </c>
       <c r="H54" s="1">
         <v>1</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="L54" s="5"/>
       <c r="M54" s="1" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="R54" s="1" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="U54" s="1">
         <v>24</v>
       </c>
       <c r="V54" s="1" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="W54" s="1" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="Y54" s="1" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="Z54" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AA54" s="1" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="AC54" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AF54" s="1" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="AG54" s="6"/>
       <c r="AK54" s="1" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="AL54" s="1" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="AM54" s="5">
         <v>7</v>
       </c>
       <c r="AO54" s="1" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="AP54" s="1" t="b">
         <v>1</v>
@@ -13854,48 +13851,48 @@
     </row>
     <row r="55" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="C55" s="22" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="D55" s="22" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="E55" s="22" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="F55" s="22" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="H55" s="1">
         <v>1</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="L55" s="5"/>
       <c r="Y55" s="1" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="Z55" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="AA55" s="1" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="AC55" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AF55" s="1" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="AG55" s="6"/>
       <c r="AL55" s="1" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="AM55" s="5">
         <v>6</v>
@@ -13906,48 +13903,48 @@
     </row>
     <row r="56" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="C56" s="22" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="D56" s="22" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="E56" s="22" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="F56" s="22" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="H56" s="1">
         <v>1</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="L56" s="5"/>
       <c r="Y56" s="1" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="Z56" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="AA56" s="1" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="AC56" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AF56" s="1" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="AG56" s="6"/>
       <c r="AL56" s="1" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="AM56" s="5">
         <v>5</v>
@@ -13958,47 +13955,47 @@
     </row>
     <row r="57" spans="1:42" ht="105" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="C57" s="22" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="D57" s="22" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="E57" s="22" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="F57" s="22" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="H57" s="1">
         <v>1</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="L57" s="5"/>
       <c r="M57" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="P57" s="1" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="R57" s="1" t="s">
         <v>96</v>
@@ -14007,38 +14004,38 @@
         <v>15</v>
       </c>
       <c r="V57" s="1" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="W57" s="1" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="Y57" s="1" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="Z57" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AA57" s="1" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="AB57" s="1" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="AC57" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AF57" s="1" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="AG57" s="6"/>
       <c r="AL57" s="1" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="AM57" s="5">
         <v>4</v>
       </c>
       <c r="AO57" s="1" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="AP57" s="1" t="b">
         <v>1</v>
@@ -14046,50 +14043,50 @@
     </row>
     <row r="58" spans="1:42" ht="60" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="E58" s="1" t="s">
         <v>534</v>
       </c>
-      <c r="B58" s="1" t="s">
-        <v>535</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>536</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>537</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>538</v>
-      </c>
       <c r="F58" s="1" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="H58" s="1">
         <v>-1</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="L58" s="5"/>
       <c r="M58" s="1" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="R58" s="1" t="s">
         <v>96</v>
       </c>
       <c r="T58" s="1" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="U58" s="1">
         <v>3</v>
       </c>
       <c r="Y58" s="1" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="Z58" s="1" t="s">
         <v>88</v>
@@ -14098,14 +14095,14 @@
         <v>89</v>
       </c>
       <c r="AF58" s="1" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="AG58" s="6"/>
       <c r="AI58" s="1" t="s">
         <v>91</v>
       </c>
       <c r="AL58" s="1" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="AM58" s="5">
         <v>1</v>
@@ -14114,7 +14111,7 @@
         <v>91</v>
       </c>
       <c r="AO58" s="1" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="AP58" s="1" t="b">
         <v>1</v>
@@ -14122,53 +14119,53 @@
     </row>
     <row r="59" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="H59" s="1">
         <v>1</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="L59" s="5"/>
       <c r="M59" s="1" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="P59" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="R59" s="1" t="s">
         <v>96</v>
       </c>
       <c r="T59" s="1" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="U59" s="1">
         <v>2</v>
       </c>
       <c r="Y59" s="1" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="Z59" s="1" t="s">
         <v>88</v>
@@ -14177,14 +14174,14 @@
         <v>89</v>
       </c>
       <c r="AF59" s="1" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="AG59" s="6"/>
       <c r="AI59" s="1" t="s">
         <v>91</v>
       </c>
       <c r="AL59" s="1" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="AM59" s="5">
         <v>5</v>
@@ -14193,7 +14190,7 @@
         <v>91</v>
       </c>
       <c r="AO59" s="1" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="AP59" s="1" t="b">
         <v>1</v>
@@ -14201,56 +14198,56 @@
     </row>
     <row r="60" spans="1:42" ht="60" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="H60" s="1">
         <v>1</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="L60" s="5"/>
       <c r="M60" s="1" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="P60" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="R60" s="1" t="s">
         <v>96</v>
       </c>
       <c r="T60" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="U60" s="1">
         <v>3</v>
       </c>
       <c r="Y60" s="1" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="Z60" s="1" t="s">
         <v>88</v>
@@ -14259,20 +14256,20 @@
         <v>89</v>
       </c>
       <c r="AF60" s="1" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="AG60" s="6"/>
       <c r="AI60" s="1" t="s">
         <v>91</v>
       </c>
       <c r="AL60" s="1" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="AM60" s="5">
         <v>8</v>
       </c>
       <c r="AO60" s="1" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="AP60" s="1" t="b">
         <v>1</v>
@@ -14280,53 +14277,53 @@
     </row>
     <row r="61" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="H61" s="1">
         <v>-1</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="L61" s="5"/>
       <c r="M61" s="1" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="P61" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="R61" s="1" t="s">
         <v>96</v>
       </c>
       <c r="T61" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="U61" s="1">
         <v>3</v>
       </c>
       <c r="Y61" s="1" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="Z61" s="1" t="s">
         <v>88</v>
@@ -14335,17 +14332,17 @@
         <v>89</v>
       </c>
       <c r="AF61" s="1" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="AG61" s="6"/>
       <c r="AL61" s="1" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="AM61" s="5">
         <v>6</v>
       </c>
       <c r="AO61" s="1" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="AP61" s="1" t="b">
         <v>1</v>
@@ -14353,41 +14350,41 @@
     </row>
     <row r="62" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="H62" s="1">
         <v>1</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="L62" s="5"/>
       <c r="M62" s="1" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="P62" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="R62" s="1" t="s">
         <v>96</v>
@@ -14396,7 +14393,7 @@
         <v>12</v>
       </c>
       <c r="Y62" s="1" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="Z62" s="1" t="s">
         <v>88</v>
@@ -14405,17 +14402,17 @@
         <v>89</v>
       </c>
       <c r="AF62" s="1" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="AG62" s="6"/>
       <c r="AL62" s="1" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="AM62" s="5">
         <v>2</v>
       </c>
       <c r="AO62" s="1" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="AP62" s="1" t="b">
         <v>1</v>
@@ -14423,41 +14420,41 @@
     </row>
     <row r="63" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="H63" s="1">
         <v>1</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="L63" s="5"/>
       <c r="M63" s="1" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="P63" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="R63" s="1" t="s">
         <v>96</v>
@@ -14466,7 +14463,7 @@
         <v>12</v>
       </c>
       <c r="Y63" s="1" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="Z63" s="1" t="s">
         <v>88</v>
@@ -14475,17 +14472,17 @@
         <v>89</v>
       </c>
       <c r="AF63" s="1" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="AG63" s="6"/>
       <c r="AL63" s="1" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="AM63" s="5">
         <v>3</v>
       </c>
       <c r="AO63" s="1" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="AP63" s="1" t="b">
         <v>1</v>
@@ -14493,51 +14490,51 @@
     </row>
     <row r="64" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="H64" s="1">
         <v>1</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="L64" s="5"/>
       <c r="R64" s="1" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="U64" s="1">
         <v>3</v>
       </c>
       <c r="Y64" s="1" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="Z64" s="1" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="AC64" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AF64" s="1" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="AG64" s="6"/>
       <c r="AL64" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="AM64" s="5">
         <v>9</v>
@@ -14548,45 +14545,45 @@
     </row>
     <row r="65" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="H65" s="1">
         <v>1</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="L65" s="5"/>
       <c r="Y65" s="1" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="Z65" s="1" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="AC65" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AF65" s="1" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="AG65" s="6"/>
       <c r="AL65" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="AM65" s="5">
         <v>12</v>
@@ -14597,38 +14594,38 @@
     </row>
     <row r="66" spans="1:42" ht="60" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="H66" s="1">
         <v>-1</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="L66" s="5"/>
       <c r="M66" s="1" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="V66" s="1" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="Y66" s="1" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="Z66" s="1" t="s">
         <v>88</v>
@@ -14637,17 +14634,17 @@
         <v>89</v>
       </c>
       <c r="AF66" s="1" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="AG66" s="6"/>
       <c r="AL66" s="1" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="AM66" s="5">
         <v>10</v>
       </c>
       <c r="AO66" s="1" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="AP66" s="1" t="b">
         <v>1</v>
@@ -14655,35 +14652,35 @@
     </row>
     <row r="67" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="H67" s="1">
         <v>1</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="L67" s="5"/>
       <c r="M67" s="1" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="P67" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="R67" s="1" t="s">
         <v>96</v>
@@ -14695,7 +14692,7 @@
         <v>12</v>
       </c>
       <c r="Y67" s="1" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="Z67" s="1" t="s">
         <v>88</v>
@@ -14704,20 +14701,20 @@
         <v>89</v>
       </c>
       <c r="AF67" s="1" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="AG67" s="6"/>
       <c r="AI67" s="1" t="s">
         <v>91</v>
       </c>
       <c r="AL67" s="1" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="AM67" s="5">
         <v>11</v>
       </c>
       <c r="AO67" s="1" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="AP67" s="1" t="b">
         <v>1</v>
@@ -14725,53 +14722,53 @@
     </row>
     <row r="68" spans="1:42" ht="30" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="H68" s="1">
         <v>1</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="L68" s="5"/>
       <c r="M68" s="1" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="P68" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="R68" s="1" t="s">
         <v>96</v>
       </c>
       <c r="T68" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="U68" s="1">
         <v>36</v>
       </c>
       <c r="Y68" s="1" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="Z68" s="1" t="s">
         <v>88</v>
@@ -14780,20 +14777,20 @@
         <v>89</v>
       </c>
       <c r="AF68" s="1" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="AG68" s="6"/>
       <c r="AI68" s="1" t="s">
         <v>91</v>
       </c>
       <c r="AL68" s="1" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="AM68" s="5">
         <v>4</v>
       </c>
       <c r="AO68" s="1" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="AP68" s="1" t="b">
         <v>1</v>
@@ -14801,53 +14798,53 @@
     </row>
     <row r="69" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="H69" s="1">
         <v>-1</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="J69" s="1" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="L69" s="5"/>
       <c r="M69" s="1" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="P69" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="R69" s="1" t="s">
         <v>96</v>
       </c>
       <c r="T69" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="U69" s="1">
         <v>12</v>
       </c>
       <c r="Y69" s="1" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="Z69" s="1" t="s">
         <v>88</v>
@@ -14856,17 +14853,17 @@
         <v>89</v>
       </c>
       <c r="AF69" s="1" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="AG69" s="6"/>
       <c r="AL69" s="1" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="AM69" s="5">
         <v>7</v>
       </c>
       <c r="AO69" s="1" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="AP69" s="1" t="b">
         <v>1</v>
@@ -15108,78 +15105,78 @@
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="20" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="21" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="B2" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="B3" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="B4" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="B6" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="B7" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>843</v>
+      </c>
+      <c r="B10" t="s">
+        <v>844</v>
+      </c>
+      <c r="C10" t="s">
+        <v>845</v>
+      </c>
+      <c r="D10" t="s">
+        <v>846</v>
+      </c>
+      <c r="E10" t="s">
         <v>847</v>
       </c>
-      <c r="B10" t="s">
+      <c r="F10" t="s">
         <v>848</v>
       </c>
-      <c r="C10" t="s">
+      <c r="G10" t="s">
         <v>849</v>
       </c>
-      <c r="D10" t="s">
+      <c r="H10" t="s">
         <v>850</v>
-      </c>
-      <c r="E10" t="s">
-        <v>851</v>
-      </c>
-      <c r="F10" t="s">
-        <v>852</v>
-      </c>
-      <c r="G10" t="s">
-        <v>853</v>
-      </c>
-      <c r="H10" t="s">
-        <v>854</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
       <c r="B11" t="b">
         <v>1</v>
@@ -15207,63 +15204,63 @@
   <sheetData>
     <row r="1" spans="1:5" ht="298.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A3" s="18" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="B4" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="B5" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="B6" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="B7" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="E10" s="13" t="s">
         <v>37</v>
@@ -15277,13 +15274,13 @@
         <v>0</v>
       </c>
       <c r="C11" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="D11" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="E11" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -15294,13 +15291,13 @@
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="D12" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="E12" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -15311,13 +15308,13 @@
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="D13" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="E13" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -15328,13 +15325,13 @@
         <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="D14" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="E14" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -15345,13 +15342,13 @@
         <v>4</v>
       </c>
       <c r="C15" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="D15" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="E15" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -15362,13 +15359,13 @@
         <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="D16" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="E16" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -15379,13 +15376,13 @@
         <v>6</v>
       </c>
       <c r="C17" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="D17" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="E17" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -15396,13 +15393,13 @@
         <v>7</v>
       </c>
       <c r="C18" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="D18" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="E18" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -15413,13 +15410,13 @@
         <v>8</v>
       </c>
       <c r="C19" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="D19" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="E19" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -15430,13 +15427,13 @@
         <v>9</v>
       </c>
       <c r="C20" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="D20" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="E20" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -15447,13 +15444,13 @@
         <v>10</v>
       </c>
       <c r="C21" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="D21" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="E21" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -15464,13 +15461,13 @@
         <v>11</v>
       </c>
       <c r="C22" t="s">
+        <v>652</v>
+      </c>
+      <c r="D22" t="s">
         <v>656</v>
       </c>
-      <c r="D22" t="s">
-        <v>660</v>
-      </c>
       <c r="E22" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -15481,13 +15478,13 @@
         <v>12</v>
       </c>
       <c r="C23" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="D23" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="E23" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -15498,13 +15495,13 @@
         <v>13</v>
       </c>
       <c r="C24" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="D24" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="E24" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -15515,13 +15512,13 @@
         <v>14</v>
       </c>
       <c r="C25" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="D25" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="E25" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -15532,13 +15529,13 @@
         <v>15</v>
       </c>
       <c r="C26" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="D26" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="E26" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -15549,13 +15546,13 @@
         <v>16</v>
       </c>
       <c r="C27" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="D27" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="E27" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -15566,13 +15563,13 @@
         <v>17</v>
       </c>
       <c r="C28" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="D28" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="E28" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -15583,13 +15580,13 @@
         <v>18</v>
       </c>
       <c r="C29" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="D29" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="E29" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -15600,13 +15597,13 @@
         <v>19</v>
       </c>
       <c r="C30" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="D30" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="E30" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -15617,13 +15614,13 @@
         <v>20</v>
       </c>
       <c r="C31" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="D31" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="E31" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -15634,13 +15631,13 @@
         <v>21</v>
       </c>
       <c r="C32" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="D32" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="E32" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -15651,13 +15648,13 @@
         <v>22</v>
       </c>
       <c r="C33" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="D33" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="E33" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -15668,13 +15665,13 @@
         <v>23</v>
       </c>
       <c r="C34" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="D34" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="E34" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -15685,13 +15682,13 @@
         <v>24</v>
       </c>
       <c r="C35" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="D35" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="E35" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -15702,13 +15699,13 @@
         <v>25</v>
       </c>
       <c r="C36" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="D36" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="E36" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -15719,13 +15716,13 @@
         <v>26</v>
       </c>
       <c r="C37" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="D37" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="E37" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -15736,13 +15733,13 @@
         <v>27</v>
       </c>
       <c r="C38" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="D38" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="E38" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -15753,13 +15750,13 @@
         <v>28</v>
       </c>
       <c r="C39" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="D39" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="E39" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -15770,13 +15767,13 @@
         <v>29</v>
       </c>
       <c r="C40" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="D40" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="E40" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -15787,13 +15784,13 @@
         <v>30</v>
       </c>
       <c r="C41" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="D41" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="E41" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -15804,13 +15801,13 @@
         <v>31</v>
       </c>
       <c r="C42" t="s">
+        <v>652</v>
+      </c>
+      <c r="D42" t="s">
         <v>656</v>
       </c>
-      <c r="D42" t="s">
-        <v>660</v>
-      </c>
       <c r="E42" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -15821,13 +15818,13 @@
         <v>32</v>
       </c>
       <c r="C43" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="D43" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="E43" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -15838,13 +15835,13 @@
         <v>33</v>
       </c>
       <c r="C44" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="D44" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="E44" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -15855,13 +15852,13 @@
         <v>34</v>
       </c>
       <c r="C45" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="D45" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="E45" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -15872,13 +15869,13 @@
         <v>35</v>
       </c>
       <c r="C46" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="D46" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="E46" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -15889,13 +15886,13 @@
         <v>36</v>
       </c>
       <c r="C47" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="D47" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="E47" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -15906,13 +15903,13 @@
         <v>37</v>
       </c>
       <c r="C48" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="D48" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="E48" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -15923,69 +15920,69 @@
         <v>38</v>
       </c>
       <c r="C49" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="D49" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="E49" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A51" s="18" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="B52" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="9" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="B53" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="B54" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="9" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="B55" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="19" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="13" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="D58" s="13" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="E58" s="13" t="s">
         <v>37</v>
@@ -15993,19 +15990,19 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="B59" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="C59" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="D59" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="E59" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -16013,141 +16010,141 @@
         <v>39</v>
       </c>
       <c r="B60" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="C60" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="D60" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="E60" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="B61" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="C61" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="D61" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="E61" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="B62" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="C62" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="D62" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="E62" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="B63" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="C63" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="D63" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="E63" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="B64" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="C64" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="D64" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="E64" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
     </row>
     <row r="66" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A66" s="18" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
     </row>
     <row r="70" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A70" s="18" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" s="9" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="B71" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" s="9" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="B72" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" s="9" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="B73" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" s="9" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="B74" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
     </row>
     <row r="76" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A76" s="18" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -16155,7 +16152,7 @@
         <v>1</v>
       </c>
       <c r="B77" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -16163,7 +16160,7 @@
         <v>2</v>
       </c>
       <c r="B78" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -16171,7 +16168,7 @@
         <v>3</v>
       </c>
       <c r="B79" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -16179,7 +16176,7 @@
         <v>4</v>
       </c>
       <c r="B80" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
@@ -16187,7 +16184,7 @@
         <v>5</v>
       </c>
       <c r="B81" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
     </row>
   </sheetData>
@@ -16196,27 +16193,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d56b9130-d22a-480d-bb83-f34040f04d96">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Notes xmlns="d56b9130-d22a-480d-bb83-f34040f04d96" xsi:nil="true"/>
-    <TaxCatchAll xmlns="dd8606a3-d959-45f7-996e-3c98d970357c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010026B67AE13FBD584ABEFCF026840CED6F" ma:contentTypeVersion="21" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="11ebdf7d5c906124ef40ef85c2b08d8b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d56b9130-d22a-480d-bb83-f34040f04d96" xmlns:ns3="dd8606a3-d959-45f7-996e-3c98d970357c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="395e369db30c2620103728840cc29626" ns2:_="" ns3:_="">
     <xsd:import namespace="d56b9130-d22a-480d-bb83-f34040f04d96"/>
@@ -16485,10 +16461,42 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d56b9130-d22a-480d-bb83-f34040f04d96">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Notes xmlns="d56b9130-d22a-480d-bb83-f34040f04d96" xsi:nil="true"/>
+    <TaxCatchAll xmlns="dd8606a3-d959-45f7-996e-3c98d970357c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D4B7956-BCA0-46CA-BF6B-C7215DA15D81}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E038410E-E6A9-42FC-B223-5F20C9C2E8EB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="d56b9130-d22a-480d-bb83-f34040f04d96"/>
+    <ds:schemaRef ds:uri="dd8606a3-d959-45f7-996e-3c98d970357c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -16511,20 +16519,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E038410E-E6A9-42FC-B223-5F20C9C2E8EB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D4B7956-BCA0-46CA-BF6B-C7215DA15D81}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="d56b9130-d22a-480d-bb83-f34040f04d96"/>
-    <ds:schemaRef ds:uri="dd8606a3-d959-45f7-996e-3c98d970357c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data/common_project_data/indicators-master.xlsx
+++ b/data/common_project_data/indicators-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steve.crawshaw\projects\weca_regional_indicators\data\common_project_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9540A400-0674-4C41-BF7C-746DDBFEB218}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5BD7C984-3BAE-465E-B390-E09C55F62ADA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1693" uniqueCount="860">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1693" uniqueCount="859">
   <si>
     <t>Unique ID</t>
   </si>
@@ -2317,9 +2317,6 @@
   </si>
   <si>
     <t>The data for priority sectors goes down to very low SIC (industry) levels where the data are less reliable.</t>
-  </si>
-  <si>
-    <t>Index</t>
   </si>
   <si>
     <t>GDP level indexed to 2020</t>
@@ -9745,16 +9742,16 @@
         <v>37</v>
       </c>
       <c r="AM1" s="26" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="AN1" s="3" t="s">
         <v>38</v>
       </c>
       <c r="AO1" s="3" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="AP1" s="3" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="AQ1" s="2"/>
     </row>
@@ -9874,16 +9871,16 @@
         <v>76</v>
       </c>
       <c r="AM2" s="27" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="AN2" s="12" t="s">
         <v>77</v>
       </c>
       <c r="AO2" s="12" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="AP2" s="12" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="AQ2" s="2"/>
     </row>
@@ -9907,13 +9904,13 @@
         <v>83</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H3" s="1">
         <v>1</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>84</v>
@@ -9981,7 +9978,7 @@
         <v>3</v>
       </c>
       <c r="AO3" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AP3" s="1" t="b">
         <v>1</v>
@@ -10007,7 +10004,7 @@
         <v>94</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="H4" s="1">
         <v>1</v>
@@ -10053,7 +10050,7 @@
         <v>738</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="Y4" s="1" t="s">
         <v>739</v>
@@ -10081,7 +10078,7 @@
         <v>4</v>
       </c>
       <c r="AO4" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="AP4" s="1" t="b">
         <v>1</v>
@@ -10107,16 +10104,16 @@
         <v>103</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H5" s="1">
         <v>1</v>
       </c>
       <c r="I5" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>741</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>742</v>
       </c>
       <c r="L5" s="5">
         <v>2020</v>
@@ -10125,10 +10122,10 @@
         <v>104</v>
       </c>
       <c r="N5" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="O5" s="11" t="s">
         <v>743</v>
-      </c>
-      <c r="O5" s="11" t="s">
-        <v>744</v>
       </c>
       <c r="P5" s="1" t="s">
         <v>105</v>
@@ -10143,7 +10140,7 @@
         <v>2023</v>
       </c>
       <c r="T5" s="24" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="U5" s="1">
         <v>16</v>
@@ -10152,10 +10149,10 @@
         <v>738</v>
       </c>
       <c r="X5" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="Y5" s="1" t="s">
         <v>746</v>
-      </c>
-      <c r="Y5" s="1" t="s">
-        <v>747</v>
       </c>
       <c r="Z5" s="1" t="s">
         <v>88</v>
@@ -10164,7 +10161,7 @@
         <v>504</v>
       </c>
       <c r="AB5" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="AC5" s="1" t="s">
         <v>89</v>
@@ -10180,7 +10177,7 @@
         <v>1</v>
       </c>
       <c r="AO5" s="1" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="AP5" s="1" t="b">
         <v>1</v>
@@ -10188,7 +10185,7 @@
     </row>
     <row r="6" spans="1:43" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>79</v>
@@ -10203,10 +10200,10 @@
         <v>108</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H6" s="1">
         <v>1</v>
@@ -10215,20 +10212,20 @@
         <v>112</v>
       </c>
       <c r="J6" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>753</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>754</v>
       </c>
       <c r="L6" s="5"/>
       <c r="M6" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="N6" s="1" t="s">
         <v>755</v>
       </c>
-      <c r="N6" s="1" t="s">
+      <c r="O6" s="11" t="s">
         <v>756</v>
-      </c>
-      <c r="O6" s="11" t="s">
-        <v>757</v>
       </c>
       <c r="P6" s="1" t="s">
         <v>105</v>
@@ -10252,7 +10249,7 @@
         <v>738</v>
       </c>
       <c r="Y6" s="1" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="Z6" s="1" t="s">
         <v>88</v>
@@ -10261,7 +10258,7 @@
         <v>169</v>
       </c>
       <c r="AB6" s="1" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="AC6" s="1" t="s">
         <v>89</v>
@@ -10274,13 +10271,13 @@
         <v>110</v>
       </c>
       <c r="AL6" s="1" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="AM6" s="5">
         <v>2</v>
       </c>
       <c r="AO6" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="AP6" s="1" t="b">
         <v>1</v>
@@ -10288,7 +10285,7 @@
     </row>
     <row r="7" spans="1:43" ht="90" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>79</v>
@@ -10303,10 +10300,10 @@
         <v>111</v>
       </c>
       <c r="F7" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>763</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>764</v>
       </c>
       <c r="H7" s="1">
         <v>1</v>
@@ -10315,23 +10312,23 @@
         <v>112</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="L7" s="5"/>
       <c r="M7" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="N7" s="1" t="s">
         <v>765</v>
       </c>
-      <c r="N7" s="1" t="s">
+      <c r="O7" s="11" t="s">
         <v>766</v>
-      </c>
-      <c r="O7" s="11" t="s">
-        <v>767</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>113</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="R7" s="1" t="s">
         <v>87</v>
@@ -10349,7 +10346,7 @@
         <v>738</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="Z7" s="1" t="s">
         <v>88</v>
@@ -10358,7 +10355,7 @@
         <v>432</v>
       </c>
       <c r="AB7" s="1" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AC7" s="1" t="s">
         <v>89</v>
@@ -10371,13 +10368,13 @@
         <v>91</v>
       </c>
       <c r="AL7" s="1" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="AM7" s="5">
         <v>5</v>
       </c>
       <c r="AO7" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="AP7" s="1" t="b">
         <v>1</v>
@@ -10403,13 +10400,13 @@
         <v>117</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H8" s="1">
         <v>1</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>118</v>
@@ -10425,13 +10422,13 @@
         <v>120</v>
       </c>
       <c r="O8" s="11" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="P8" s="1" t="s">
         <v>38</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="R8" s="1" t="s">
         <v>121</v>
@@ -10449,7 +10446,7 @@
         <v>738</v>
       </c>
       <c r="Y8" s="1" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="Z8" s="1" t="s">
         <v>88</v>
@@ -10458,7 +10455,7 @@
         <v>504</v>
       </c>
       <c r="AB8" s="1" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="AC8" s="1" t="s">
         <v>89</v>
@@ -10474,7 +10471,7 @@
         <v>12</v>
       </c>
       <c r="AO8" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AP8" s="1" t="b">
         <v>0</v>
@@ -10497,26 +10494,26 @@
         <v>126</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H9" s="1">
         <v>1</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>127</v>
       </c>
       <c r="L9" s="5"/>
       <c r="M9" s="1" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="P9" s="1" t="s">
         <v>128</v>
@@ -10531,7 +10528,7 @@
         <v>5</v>
       </c>
       <c r="Y9" s="1" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="Z9" s="1" t="s">
         <v>88</v>
@@ -10547,13 +10544,13 @@
         <v>91</v>
       </c>
       <c r="AL9" s="1" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="AM9" s="5">
         <v>6</v>
       </c>
       <c r="AO9" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AP9" s="1" t="b">
         <v>1</v>
@@ -10579,7 +10576,7 @@
         <v>132</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="H10" s="1">
         <v>1</v>
@@ -10588,17 +10585,17 @@
         <v>734</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="L10" s="5"/>
       <c r="M10" s="1" t="s">
         <v>133</v>
       </c>
       <c r="N10" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="O10" s="11" t="s">
         <v>774</v>
-      </c>
-      <c r="O10" s="11" t="s">
-        <v>775</v>
       </c>
       <c r="P10" s="1" t="s">
         <v>113</v>
@@ -10613,13 +10610,13 @@
         <v>46054</v>
       </c>
       <c r="T10" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="V10" s="1" t="s">
         <v>778</v>
       </c>
-      <c r="V10" s="1" t="s">
+      <c r="W10" s="1" t="s">
         <v>779</v>
-      </c>
-      <c r="W10" s="1" t="s">
-        <v>780</v>
       </c>
       <c r="Y10" s="1" t="s">
         <v>134</v>
@@ -10641,7 +10638,7 @@
         <v>7</v>
       </c>
       <c r="AO10" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="AP10" s="1" t="b">
         <v>0</v>
@@ -10719,7 +10716,7 @@
         <v>1</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>148</v>
@@ -10757,7 +10754,7 @@
         <v>9</v>
       </c>
       <c r="AO12" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AP12" s="1" t="b">
         <v>1</v>
@@ -10786,7 +10783,7 @@
         <v>1</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="J13" s="1" t="s">
         <v>156</v>
@@ -10830,7 +10827,7 @@
         <v>11</v>
       </c>
       <c r="AO13" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AP13" s="1" t="b">
         <v>1</v>
@@ -10856,29 +10853,29 @@
         <v>166</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H14" s="1">
         <v>1</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="J14" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="K14" s="1" t="s">
         <v>823</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>824</v>
       </c>
       <c r="L14" s="5"/>
       <c r="M14" s="1" t="s">
         <v>167</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="P14" s="1" t="s">
         <v>737</v>
@@ -10890,22 +10887,22 @@
         <v>121</v>
       </c>
       <c r="S14" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="T14" s="1" t="s">
         <v>789</v>
-      </c>
-      <c r="T14" s="1" t="s">
-        <v>790</v>
       </c>
       <c r="U14" s="1">
         <v>8</v>
       </c>
       <c r="V14" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="W14" s="1" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="X14" s="1" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="Y14" s="1" t="s">
         <v>168</v>
@@ -10917,7 +10914,7 @@
         <v>504</v>
       </c>
       <c r="AB14" s="1" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="AC14" s="1" t="s">
         <v>89</v>
@@ -10942,7 +10939,7 @@
         <v>173</v>
       </c>
       <c r="AO14" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AP14" s="1" t="b">
         <v>1</v>
@@ -10968,26 +10965,26 @@
         <v>177</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="H15" s="1">
         <v>1</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="J15" s="1" t="s">
         <v>178</v>
       </c>
       <c r="L15" s="5"/>
       <c r="M15" s="1" t="s">
+        <v>829</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>831</v>
+      </c>
+      <c r="O15" s="11" t="s">
         <v>830</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>832</v>
-      </c>
-      <c r="O15" s="11" t="s">
-        <v>831</v>
       </c>
       <c r="P15" s="1" t="s">
         <v>128</v>
@@ -10999,10 +10996,10 @@
         <v>96</v>
       </c>
       <c r="S15" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="T15" s="1" t="s">
         <v>833</v>
-      </c>
-      <c r="T15" s="1" t="s">
-        <v>834</v>
       </c>
       <c r="U15" s="1">
         <v>9</v>
@@ -11011,7 +11008,7 @@
         <v>180</v>
       </c>
       <c r="W15" s="1" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="Y15" s="1" t="s">
         <v>181</v>
@@ -11042,7 +11039,7 @@
         <v>184</v>
       </c>
       <c r="AO15" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="AP15" s="1" t="b">
         <v>1</v>
@@ -11065,22 +11062,22 @@
         <v>186</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H16" s="1">
         <v>1</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="J16" s="1" t="s">
         <v>187</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="L16" s="5"/>
       <c r="M16" s="1" t="s">
@@ -11099,7 +11096,7 @@
         <v>190</v>
       </c>
       <c r="W16" s="1" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="Y16" s="1" t="s">
         <v>191</v>
@@ -11127,7 +11124,7 @@
         <v>184</v>
       </c>
       <c r="AO16" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AP16" s="1" t="b">
         <v>1</v>
@@ -11150,16 +11147,16 @@
         <v>195</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H17" s="1">
         <v>1</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="J17" s="1" t="s">
         <v>196</v>
@@ -11212,7 +11209,7 @@
         <v>171</v>
       </c>
       <c r="AO17" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AP17" s="1" t="b">
         <v>1</v>
@@ -11238,13 +11235,13 @@
         <v>203</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H18" s="1">
         <v>1</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="J18" s="1" t="s">
         <v>204</v>
@@ -11279,7 +11276,7 @@
         <v>6</v>
       </c>
       <c r="AO18" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="AP18" s="1" t="b">
         <v>1</v>
@@ -11305,19 +11302,19 @@
         <v>210</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H19" s="1">
         <v>1</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="L19" s="5"/>
       <c r="M19" s="1" t="s">
@@ -11358,7 +11355,7 @@
         <v>5</v>
       </c>
       <c r="AO19" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AP19" s="1" t="b">
         <v>1</v>
@@ -11381,19 +11378,19 @@
         <v>218</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H20" s="1">
         <v>1</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="L20" s="5"/>
       <c r="M20" s="1" t="s">
@@ -11437,7 +11434,7 @@
         <v>171</v>
       </c>
       <c r="AO20" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="AP20" s="1" t="b">
         <v>1</v>
@@ -11460,19 +11457,19 @@
         <v>222</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H21" s="1">
         <v>1</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="K21" s="1" t="s">
         <v>148</v>
@@ -11510,7 +11507,7 @@
         <v>8</v>
       </c>
       <c r="AO21" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AP21" s="1" t="b">
         <v>1</v>
@@ -11573,16 +11570,16 @@
         <v>233</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H23" s="1">
         <v>1</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="J23" s="1" t="s">
         <v>234</v>
@@ -11623,7 +11620,7 @@
         <v>3</v>
       </c>
       <c r="AO23" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AP23" s="1" t="b">
         <v>1</v>
@@ -11646,7 +11643,7 @@
         <v>240</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H24" s="1">
         <v>1</v>
@@ -11690,7 +11687,7 @@
         <v>9</v>
       </c>
       <c r="AO24" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="AP24" s="1" t="b">
         <v>0</v>
@@ -11754,7 +11751,7 @@
         <v>171</v>
       </c>
       <c r="AO25" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="AP25" s="1" t="b">
         <v>0</v>
@@ -11812,7 +11809,7 @@
         <v>11</v>
       </c>
       <c r="AO26" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="AP26" s="1" t="b">
         <v>1</v>
@@ -11841,7 +11838,7 @@
         <v>1</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="J27" s="1" t="s">
         <v>267</v>
@@ -11882,7 +11879,7 @@
         <v>3</v>
       </c>
       <c r="AO27" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AP27" s="1" t="b">
         <v>1</v>
@@ -11905,13 +11902,13 @@
         <v>274</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H28" s="1">
         <v>-1</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="J28" s="1" t="s">
         <v>275</v>
@@ -11958,7 +11955,7 @@
         <v>2</v>
       </c>
       <c r="AO28" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AP28" s="1" t="b">
         <v>1</v>
@@ -11981,7 +11978,7 @@
         <v>283</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="H29" s="1">
         <v>-1</v>
@@ -12031,7 +12028,7 @@
         <v>4</v>
       </c>
       <c r="AO29" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="AP29" s="1" t="b">
         <v>0</v>
@@ -12054,13 +12051,13 @@
         <v>293</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="H30" s="1">
         <v>1</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="J30" s="1" t="s">
         <v>294</v>
@@ -12110,7 +12107,7 @@
         <v>91</v>
       </c>
       <c r="AO30" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="AP30" s="1" t="b">
         <v>1</v>
@@ -12183,7 +12180,7 @@
         <v>5</v>
       </c>
       <c r="AO31" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AP31" s="1" t="b">
         <v>1</v>
@@ -12206,7 +12203,7 @@
         <v>313</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="H32" s="1">
         <v>1</v>
@@ -12256,7 +12253,7 @@
         <v>6</v>
       </c>
       <c r="AO32" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AP32" s="1" t="b">
         <v>1</v>
@@ -12323,7 +12320,7 @@
         <v>7</v>
       </c>
       <c r="AO33" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="AP33" s="1" t="b">
         <v>1</v>
@@ -12352,7 +12349,7 @@
         <v>1</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="J34" s="1" t="s">
         <v>331</v>
@@ -12390,7 +12387,7 @@
         <v>8</v>
       </c>
       <c r="AO34" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AP34" s="1" t="b">
         <v>1</v>
@@ -12465,7 +12462,7 @@
         <v>1</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="L36" s="5"/>
       <c r="R36" s="1" t="s">
@@ -12497,7 +12494,7 @@
         <v>346</v>
       </c>
       <c r="AO36" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AP36" s="1" t="b">
         <v>1</v>
@@ -12526,7 +12523,7 @@
         <v>-1</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="J37" s="1" t="s">
         <v>353</v>
@@ -12567,7 +12564,7 @@
         <v>1</v>
       </c>
       <c r="AO37" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AP37" s="1" t="b">
         <v>1</v>
@@ -12590,13 +12587,13 @@
         <v>360</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H38" s="1">
         <v>1</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="J38" s="1" t="s">
         <v>361</v>
@@ -12640,7 +12637,7 @@
         <v>2</v>
       </c>
       <c r="AO38" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AP38" s="1" t="b">
         <v>1</v>
@@ -12669,7 +12666,7 @@
         <v>1</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="J39" s="1" t="s">
         <v>366</v>
@@ -12710,7 +12707,7 @@
         <v>8</v>
       </c>
       <c r="AO39" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AP39" s="1" t="b">
         <v>1</v>
@@ -12733,13 +12730,13 @@
         <v>372</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="H40" s="1">
         <v>1</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="L40" s="5"/>
       <c r="M40" s="1" t="s">
@@ -12780,7 +12777,7 @@
         <v>9</v>
       </c>
       <c r="AO40" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="AP40" s="1" t="b">
         <v>1</v>
@@ -12809,7 +12806,7 @@
         <v>1</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="J41" s="1" t="s">
         <v>380</v>
@@ -12850,7 +12847,7 @@
         <v>7</v>
       </c>
       <c r="AO41" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AP41" s="1" t="b">
         <v>1</v>
@@ -12879,7 +12876,7 @@
         <v>-1</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="J42" s="1" t="s">
         <v>386</v>
@@ -12917,7 +12914,7 @@
         <v>6</v>
       </c>
       <c r="AO42" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AP42" s="1" t="b">
         <v>1</v>
@@ -12946,7 +12943,7 @@
         <v>-1</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="J43" s="1" t="s">
         <v>391</v>
@@ -12993,7 +12990,7 @@
         <v>3</v>
       </c>
       <c r="AO43" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AP43" s="1" t="b">
         <v>1</v>
@@ -13022,7 +13019,7 @@
         <v>-1</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="L44" s="5"/>
       <c r="Y44" s="1" t="s">
@@ -13051,7 +13048,7 @@
         <v>4</v>
       </c>
       <c r="AO44" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AP44" s="1" t="b">
         <v>1</v>
@@ -13074,13 +13071,13 @@
         <v>404</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H45" s="1">
         <v>-1</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="J45" s="1" t="s">
         <v>405</v>
@@ -13124,7 +13121,7 @@
         <v>5</v>
       </c>
       <c r="AO45" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AP45" s="1" t="b">
         <v>1</v>
@@ -13257,7 +13254,7 @@
         <v>5</v>
       </c>
       <c r="F48" s="22" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>426</v>
@@ -13319,7 +13316,7 @@
         <v>1</v>
       </c>
       <c r="AO48" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="AP48" s="1" t="b">
         <v>1</v>
@@ -13342,7 +13339,7 @@
         <v>437</v>
       </c>
       <c r="F49" s="22" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>438</v>
@@ -13407,7 +13404,7 @@
         <v>10</v>
       </c>
       <c r="AO49" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="AP49" s="1" t="b">
         <v>1</v>
@@ -13430,7 +13427,7 @@
         <v>447</v>
       </c>
       <c r="F50" s="22" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>448</v>
@@ -13439,7 +13436,7 @@
         <v>1</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="J50" s="1" t="s">
         <v>449</v>
@@ -13504,7 +13501,7 @@
         <v>9</v>
       </c>
       <c r="AO50" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="AP50" s="1" t="b">
         <v>1</v>
@@ -13536,7 +13533,7 @@
         <v>1</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="J51" s="1" t="s">
         <v>461</v>
@@ -13595,7 +13592,7 @@
         <v>8</v>
       </c>
       <c r="AO51" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AP51" s="1" t="b">
         <v>1</v>
@@ -13683,7 +13680,7 @@
         <v>2</v>
       </c>
       <c r="AO52" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="AP52" s="1" t="b">
         <v>1</v>
@@ -13706,7 +13703,7 @@
         <v>483</v>
       </c>
       <c r="F53" s="22" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>484</v>
@@ -13764,7 +13761,7 @@
         <v>3</v>
       </c>
       <c r="AO53" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="AP53" s="1" t="b">
         <v>1</v>
@@ -13843,7 +13840,7 @@
         <v>7</v>
       </c>
       <c r="AO54" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="AP54" s="1" t="b">
         <v>1</v>
@@ -13970,7 +13967,7 @@
         <v>518</v>
       </c>
       <c r="F57" s="22" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>519</v>
@@ -13979,7 +13976,7 @@
         <v>1</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="J57" s="1" t="s">
         <v>520</v>
@@ -14035,7 +14032,7 @@
         <v>4</v>
       </c>
       <c r="AO57" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AP57" s="1" t="b">
         <v>1</v>
@@ -14058,13 +14055,13 @@
         <v>534</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="H58" s="1">
         <v>-1</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="J58" s="1" t="s">
         <v>535</v>
@@ -14111,7 +14108,7 @@
         <v>91</v>
       </c>
       <c r="AO58" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AP58" s="1" t="b">
         <v>1</v>
@@ -14140,7 +14137,7 @@
         <v>1</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="J59" s="1" t="s">
         <v>543</v>
@@ -14190,7 +14187,7 @@
         <v>91</v>
       </c>
       <c r="AO59" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AP59" s="1" t="b">
         <v>1</v>
@@ -14213,7 +14210,7 @@
         <v>548</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>549</v>
@@ -14222,7 +14219,7 @@
         <v>1</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="J60" s="1" t="s">
         <v>550</v>
@@ -14269,7 +14266,7 @@
         <v>8</v>
       </c>
       <c r="AO60" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AP60" s="1" t="b">
         <v>1</v>
@@ -14298,7 +14295,7 @@
         <v>-1</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="J61" s="1" t="s">
         <v>556</v>
@@ -14342,7 +14339,7 @@
         <v>6</v>
       </c>
       <c r="AO61" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AP61" s="1" t="b">
         <v>1</v>
@@ -14371,7 +14368,7 @@
         <v>1</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="J62" s="1" t="s">
         <v>563</v>
@@ -14412,7 +14409,7 @@
         <v>2</v>
       </c>
       <c r="AO62" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AP62" s="1" t="b">
         <v>1</v>
@@ -14441,7 +14438,7 @@
         <v>1</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="J63" s="1" t="s">
         <v>571</v>
@@ -14482,7 +14479,7 @@
         <v>3</v>
       </c>
       <c r="AO63" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AP63" s="1" t="b">
         <v>1</v>
@@ -14644,7 +14641,7 @@
         <v>10</v>
       </c>
       <c r="AO66" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="AP66" s="1" t="b">
         <v>1</v>
@@ -14714,7 +14711,7 @@
         <v>11</v>
       </c>
       <c r="AO67" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="AP67" s="1" t="b">
         <v>1</v>
@@ -14737,13 +14734,13 @@
         <v>600</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H68" s="1">
         <v>1</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="J68" s="1" t="s">
         <v>601</v>
@@ -14790,7 +14787,7 @@
         <v>4</v>
       </c>
       <c r="AO68" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AP68" s="1" t="b">
         <v>1</v>
@@ -14819,7 +14816,7 @@
         <v>-1</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="J69" s="1" t="s">
         <v>606</v>
@@ -14863,7 +14860,7 @@
         <v>7</v>
       </c>
       <c r="AO69" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AP69" s="1" t="b">
         <v>1</v>
@@ -15150,33 +15147,33 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>842</v>
+      </c>
+      <c r="B10" t="s">
         <v>843</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>844</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>845</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>846</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>847</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>848</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>849</v>
-      </c>
-      <c r="H10" t="s">
-        <v>850</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B11" t="b">
         <v>1</v>
@@ -16193,6 +16190,27 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d56b9130-d22a-480d-bb83-f34040f04d96">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Notes xmlns="d56b9130-d22a-480d-bb83-f34040f04d96" xsi:nil="true"/>
+    <TaxCatchAll xmlns="dd8606a3-d959-45f7-996e-3c98d970357c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010026B67AE13FBD584ABEFCF026840CED6F" ma:contentTypeVersion="21" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="11ebdf7d5c906124ef40ef85c2b08d8b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d56b9130-d22a-480d-bb83-f34040f04d96" xmlns:ns3="dd8606a3-d959-45f7-996e-3c98d970357c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="395e369db30c2620103728840cc29626" ns2:_="" ns3:_="">
     <xsd:import namespace="d56b9130-d22a-480d-bb83-f34040f04d96"/>
@@ -16461,42 +16479,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d56b9130-d22a-480d-bb83-f34040f04d96">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Notes xmlns="d56b9130-d22a-480d-bb83-f34040f04d96" xsi:nil="true"/>
-    <TaxCatchAll xmlns="dd8606a3-d959-45f7-996e-3c98d970357c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E038410E-E6A9-42FC-B223-5F20C9C2E8EB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D4B7956-BCA0-46CA-BF6B-C7215DA15D81}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="d56b9130-d22a-480d-bb83-f34040f04d96"/>
-    <ds:schemaRef ds:uri="dd8606a3-d959-45f7-996e-3c98d970357c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -16519,9 +16505,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D4B7956-BCA0-46CA-BF6B-C7215DA15D81}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E038410E-E6A9-42FC-B223-5F20C9C2E8EB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="d56b9130-d22a-480d-bb83-f34040f04d96"/>
+    <ds:schemaRef ds:uri="dd8606a3-d959-45f7-996e-3c98d970357c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data/common_project_data/indicators-master.xlsx
+++ b/data/common_project_data/indicators-master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steve.crawshaw\projects\weca_regional_indicators\data\common_project_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5BD7C984-3BAE-465E-B390-E09C55F62ADA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{502A94B1-3CA6-4E31-9C5C-C1D04A5174DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="fact_indicator_observation" sheetId="3" r:id="rId1"/>
@@ -3512,26 +3512,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{214232AF-A9B3-43B6-9705-8A3894756A60}">
   <dimension ref="A1:F1000"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.54296875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="13" t="s">
         <v>607</v>
       </c>
@@ -3551,7 +3551,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="14" t="s">
         <v>613</v>
       </c>
@@ -3571,5989 +3571,5989 @@
         <v>617</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C3" s="15"/>
       <c r="D3" s="15"/>
       <c r="E3" s="16"/>
       <c r="F3" s="15"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C4" s="15"/>
       <c r="D4" s="15"/>
       <c r="E4" s="16"/>
       <c r="F4" s="15"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C5" s="15"/>
       <c r="D5" s="15"/>
       <c r="E5" s="16"/>
       <c r="F5" s="15"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C6" s="15"/>
       <c r="D6" s="15"/>
       <c r="E6" s="16"/>
       <c r="F6" s="15"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C7" s="15"/>
       <c r="D7" s="15"/>
       <c r="E7" s="16"/>
       <c r="F7" s="15"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C8" s="15"/>
       <c r="D8" s="15"/>
       <c r="E8" s="16"/>
       <c r="F8" s="15"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C9" s="15"/>
       <c r="D9" s="15"/>
       <c r="E9" s="16"/>
       <c r="F9" s="15"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C10" s="15"/>
       <c r="D10" s="15"/>
       <c r="E10" s="16"/>
       <c r="F10" s="15"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C11" s="15"/>
       <c r="D11" s="15"/>
       <c r="E11" s="16"/>
       <c r="F11" s="15"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C12" s="15"/>
       <c r="D12" s="15"/>
       <c r="E12" s="16"/>
       <c r="F12" s="15"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C13" s="15"/>
       <c r="D13" s="15"/>
       <c r="E13" s="16"/>
       <c r="F13" s="15"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C14" s="15"/>
       <c r="D14" s="15"/>
       <c r="E14" s="16"/>
       <c r="F14" s="15"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C15" s="15"/>
       <c r="D15" s="15"/>
       <c r="E15" s="16"/>
       <c r="F15" s="15"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C16" s="15"/>
       <c r="D16" s="15"/>
       <c r="E16" s="16"/>
       <c r="F16" s="15"/>
     </row>
-    <row r="17" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C17" s="15"/>
       <c r="D17" s="15"/>
       <c r="E17" s="16"/>
       <c r="F17" s="15"/>
     </row>
-    <row r="18" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C18" s="15"/>
       <c r="D18" s="15"/>
       <c r="E18" s="16"/>
       <c r="F18" s="15"/>
     </row>
-    <row r="19" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C19" s="15"/>
       <c r="D19" s="15"/>
       <c r="E19" s="16"/>
       <c r="F19" s="15"/>
     </row>
-    <row r="20" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C20" s="15"/>
       <c r="D20" s="15"/>
       <c r="E20" s="16"/>
       <c r="F20" s="15"/>
     </row>
-    <row r="21" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C21" s="15"/>
       <c r="D21" s="15"/>
       <c r="E21" s="16"/>
       <c r="F21" s="15"/>
     </row>
-    <row r="22" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C22" s="15"/>
       <c r="D22" s="15"/>
       <c r="E22" s="16"/>
       <c r="F22" s="15"/>
     </row>
-    <row r="23" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C23" s="15"/>
       <c r="D23" s="15"/>
       <c r="E23" s="16"/>
       <c r="F23" s="15"/>
     </row>
-    <row r="24" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C24" s="15"/>
       <c r="D24" s="15"/>
       <c r="E24" s="16"/>
       <c r="F24" s="15"/>
     </row>
-    <row r="25" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C25" s="15"/>
       <c r="D25" s="15"/>
       <c r="E25" s="16"/>
       <c r="F25" s="15"/>
     </row>
-    <row r="26" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C26" s="15"/>
       <c r="D26" s="15"/>
       <c r="E26" s="16"/>
       <c r="F26" s="15"/>
     </row>
-    <row r="27" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C27" s="15"/>
       <c r="D27" s="15"/>
       <c r="E27" s="16"/>
       <c r="F27" s="15"/>
     </row>
-    <row r="28" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C28" s="15"/>
       <c r="D28" s="15"/>
       <c r="E28" s="16"/>
       <c r="F28" s="15"/>
     </row>
-    <row r="29" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C29" s="15"/>
       <c r="D29" s="15"/>
       <c r="E29" s="16"/>
       <c r="F29" s="15"/>
     </row>
-    <row r="30" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C30" s="15"/>
       <c r="D30" s="15"/>
       <c r="E30" s="16"/>
       <c r="F30" s="15"/>
     </row>
-    <row r="31" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C31" s="15"/>
       <c r="D31" s="15"/>
       <c r="E31" s="16"/>
       <c r="F31" s="15"/>
     </row>
-    <row r="32" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C32" s="15"/>
       <c r="D32" s="15"/>
       <c r="E32" s="16"/>
       <c r="F32" s="15"/>
     </row>
-    <row r="33" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C33" s="15"/>
       <c r="D33" s="15"/>
       <c r="E33" s="16"/>
       <c r="F33" s="15"/>
     </row>
-    <row r="34" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C34" s="15"/>
       <c r="D34" s="15"/>
       <c r="E34" s="16"/>
       <c r="F34" s="15"/>
     </row>
-    <row r="35" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C35" s="15"/>
       <c r="D35" s="15"/>
       <c r="E35" s="16"/>
       <c r="F35" s="15"/>
     </row>
-    <row r="36" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C36" s="15"/>
       <c r="D36" s="15"/>
       <c r="E36" s="16"/>
       <c r="F36" s="15"/>
     </row>
-    <row r="37" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C37" s="15"/>
       <c r="D37" s="15"/>
       <c r="E37" s="16"/>
       <c r="F37" s="15"/>
     </row>
-    <row r="38" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C38" s="15"/>
       <c r="D38" s="15"/>
       <c r="E38" s="16"/>
       <c r="F38" s="15"/>
     </row>
-    <row r="39" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C39" s="15"/>
       <c r="D39" s="15"/>
       <c r="E39" s="16"/>
       <c r="F39" s="15"/>
     </row>
-    <row r="40" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C40" s="15"/>
       <c r="D40" s="15"/>
       <c r="E40" s="16"/>
       <c r="F40" s="15"/>
     </row>
-    <row r="41" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C41" s="15"/>
       <c r="D41" s="15"/>
       <c r="E41" s="16"/>
       <c r="F41" s="15"/>
     </row>
-    <row r="42" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C42" s="15"/>
       <c r="D42" s="15"/>
       <c r="E42" s="16"/>
       <c r="F42" s="15"/>
     </row>
-    <row r="43" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C43" s="15"/>
       <c r="D43" s="15"/>
       <c r="E43" s="16"/>
       <c r="F43" s="15"/>
     </row>
-    <row r="44" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C44" s="15"/>
       <c r="D44" s="15"/>
       <c r="E44" s="16"/>
       <c r="F44" s="15"/>
     </row>
-    <row r="45" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C45" s="15"/>
       <c r="D45" s="15"/>
       <c r="E45" s="16"/>
       <c r="F45" s="15"/>
     </row>
-    <row r="46" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C46" s="15"/>
       <c r="D46" s="15"/>
       <c r="E46" s="16"/>
       <c r="F46" s="15"/>
     </row>
-    <row r="47" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C47" s="15"/>
       <c r="D47" s="15"/>
       <c r="E47" s="16"/>
       <c r="F47" s="15"/>
     </row>
-    <row r="48" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C48" s="15"/>
       <c r="D48" s="15"/>
       <c r="E48" s="16"/>
       <c r="F48" s="15"/>
     </row>
-    <row r="49" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C49" s="15"/>
       <c r="D49" s="15"/>
       <c r="E49" s="16"/>
       <c r="F49" s="15"/>
     </row>
-    <row r="50" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C50" s="15"/>
       <c r="D50" s="15"/>
       <c r="E50" s="16"/>
       <c r="F50" s="15"/>
     </row>
-    <row r="51" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C51" s="15"/>
       <c r="D51" s="15"/>
       <c r="E51" s="16"/>
       <c r="F51" s="15"/>
     </row>
-    <row r="52" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C52" s="15"/>
       <c r="D52" s="15"/>
       <c r="E52" s="16"/>
       <c r="F52" s="15"/>
     </row>
-    <row r="53" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C53" s="15"/>
       <c r="D53" s="15"/>
       <c r="E53" s="16"/>
       <c r="F53" s="15"/>
     </row>
-    <row r="54" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C54" s="15"/>
       <c r="D54" s="15"/>
       <c r="E54" s="16"/>
       <c r="F54" s="15"/>
     </row>
-    <row r="55" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C55" s="15"/>
       <c r="D55" s="15"/>
       <c r="E55" s="16"/>
       <c r="F55" s="15"/>
     </row>
-    <row r="56" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C56" s="15"/>
       <c r="D56" s="15"/>
       <c r="E56" s="16"/>
       <c r="F56" s="15"/>
     </row>
-    <row r="57" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C57" s="15"/>
       <c r="D57" s="15"/>
       <c r="E57" s="16"/>
       <c r="F57" s="15"/>
     </row>
-    <row r="58" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C58" s="15"/>
       <c r="D58" s="15"/>
       <c r="E58" s="16"/>
       <c r="F58" s="15"/>
     </row>
-    <row r="59" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C59" s="15"/>
       <c r="D59" s="15"/>
       <c r="E59" s="16"/>
       <c r="F59" s="15"/>
     </row>
-    <row r="60" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C60" s="15"/>
       <c r="D60" s="15"/>
       <c r="E60" s="16"/>
       <c r="F60" s="15"/>
     </row>
-    <row r="61" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C61" s="15"/>
       <c r="D61" s="15"/>
       <c r="E61" s="16"/>
       <c r="F61" s="15"/>
     </row>
-    <row r="62" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C62" s="15"/>
       <c r="D62" s="15"/>
       <c r="E62" s="16"/>
       <c r="F62" s="15"/>
     </row>
-    <row r="63" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C63" s="15"/>
       <c r="D63" s="15"/>
       <c r="E63" s="16"/>
       <c r="F63" s="15"/>
     </row>
-    <row r="64" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C64" s="15"/>
       <c r="D64" s="15"/>
       <c r="E64" s="16"/>
       <c r="F64" s="15"/>
     </row>
-    <row r="65" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C65" s="15"/>
       <c r="D65" s="15"/>
       <c r="E65" s="16"/>
       <c r="F65" s="15"/>
     </row>
-    <row r="66" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C66" s="15"/>
       <c r="D66" s="15"/>
       <c r="E66" s="16"/>
       <c r="F66" s="15"/>
     </row>
-    <row r="67" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C67" s="15"/>
       <c r="D67" s="15"/>
       <c r="E67" s="16"/>
       <c r="F67" s="15"/>
     </row>
-    <row r="68" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C68" s="15"/>
       <c r="D68" s="15"/>
       <c r="E68" s="16"/>
       <c r="F68" s="15"/>
     </row>
-    <row r="69" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C69" s="15"/>
       <c r="D69" s="15"/>
       <c r="E69" s="16"/>
       <c r="F69" s="15"/>
     </row>
-    <row r="70" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C70" s="15"/>
       <c r="D70" s="15"/>
       <c r="E70" s="16"/>
       <c r="F70" s="15"/>
     </row>
-    <row r="71" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C71" s="15"/>
       <c r="D71" s="15"/>
       <c r="E71" s="16"/>
       <c r="F71" s="15"/>
     </row>
-    <row r="72" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C72" s="15"/>
       <c r="D72" s="15"/>
       <c r="E72" s="16"/>
       <c r="F72" s="15"/>
     </row>
-    <row r="73" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C73" s="15"/>
       <c r="D73" s="15"/>
       <c r="E73" s="16"/>
       <c r="F73" s="15"/>
     </row>
-    <row r="74" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C74" s="15"/>
       <c r="D74" s="15"/>
       <c r="E74" s="16"/>
       <c r="F74" s="15"/>
     </row>
-    <row r="75" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C75" s="15"/>
       <c r="D75" s="15"/>
       <c r="E75" s="16"/>
       <c r="F75" s="15"/>
     </row>
-    <row r="76" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C76" s="15"/>
       <c r="D76" s="15"/>
       <c r="E76" s="16"/>
       <c r="F76" s="15"/>
     </row>
-    <row r="77" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C77" s="15"/>
       <c r="D77" s="15"/>
       <c r="E77" s="16"/>
       <c r="F77" s="15"/>
     </row>
-    <row r="78" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C78" s="15"/>
       <c r="D78" s="15"/>
       <c r="E78" s="16"/>
       <c r="F78" s="15"/>
     </row>
-    <row r="79" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C79" s="15"/>
       <c r="D79" s="15"/>
       <c r="E79" s="16"/>
       <c r="F79" s="15"/>
     </row>
-    <row r="80" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C80" s="15"/>
       <c r="D80" s="15"/>
       <c r="E80" s="16"/>
       <c r="F80" s="15"/>
     </row>
-    <row r="81" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C81" s="15"/>
       <c r="D81" s="15"/>
       <c r="E81" s="16"/>
       <c r="F81" s="15"/>
     </row>
-    <row r="82" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C82" s="15"/>
       <c r="D82" s="15"/>
       <c r="E82" s="16"/>
       <c r="F82" s="15"/>
     </row>
-    <row r="83" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C83" s="15"/>
       <c r="D83" s="15"/>
       <c r="E83" s="16"/>
       <c r="F83" s="15"/>
     </row>
-    <row r="84" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C84" s="15"/>
       <c r="D84" s="15"/>
       <c r="E84" s="16"/>
       <c r="F84" s="15"/>
     </row>
-    <row r="85" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C85" s="15"/>
       <c r="D85" s="15"/>
       <c r="E85" s="16"/>
       <c r="F85" s="15"/>
     </row>
-    <row r="86" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C86" s="15"/>
       <c r="D86" s="15"/>
       <c r="E86" s="16"/>
       <c r="F86" s="15"/>
     </row>
-    <row r="87" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C87" s="15"/>
       <c r="D87" s="15"/>
       <c r="E87" s="16"/>
       <c r="F87" s="15"/>
     </row>
-    <row r="88" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C88" s="15"/>
       <c r="D88" s="15"/>
       <c r="E88" s="16"/>
       <c r="F88" s="15"/>
     </row>
-    <row r="89" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C89" s="15"/>
       <c r="D89" s="15"/>
       <c r="E89" s="16"/>
       <c r="F89" s="15"/>
     </row>
-    <row r="90" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C90" s="15"/>
       <c r="D90" s="15"/>
       <c r="E90" s="16"/>
       <c r="F90" s="15"/>
     </row>
-    <row r="91" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C91" s="15"/>
       <c r="D91" s="15"/>
       <c r="E91" s="16"/>
       <c r="F91" s="15"/>
     </row>
-    <row r="92" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C92" s="15"/>
       <c r="D92" s="15"/>
       <c r="E92" s="16"/>
       <c r="F92" s="15"/>
     </row>
-    <row r="93" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C93" s="15"/>
       <c r="D93" s="15"/>
       <c r="E93" s="16"/>
       <c r="F93" s="15"/>
     </row>
-    <row r="94" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C94" s="15"/>
       <c r="D94" s="15"/>
       <c r="E94" s="16"/>
       <c r="F94" s="15"/>
     </row>
-    <row r="95" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C95" s="15"/>
       <c r="D95" s="15"/>
       <c r="E95" s="16"/>
       <c r="F95" s="15"/>
     </row>
-    <row r="96" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C96" s="15"/>
       <c r="D96" s="15"/>
       <c r="E96" s="16"/>
       <c r="F96" s="15"/>
     </row>
-    <row r="97" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C97" s="15"/>
       <c r="D97" s="15"/>
       <c r="E97" s="16"/>
       <c r="F97" s="15"/>
     </row>
-    <row r="98" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C98" s="15"/>
       <c r="D98" s="15"/>
       <c r="E98" s="16"/>
       <c r="F98" s="15"/>
     </row>
-    <row r="99" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C99" s="15"/>
       <c r="D99" s="15"/>
       <c r="E99" s="16"/>
       <c r="F99" s="15"/>
     </row>
-    <row r="100" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C100" s="15"/>
       <c r="D100" s="15"/>
       <c r="E100" s="16"/>
       <c r="F100" s="15"/>
     </row>
-    <row r="101" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C101" s="15"/>
       <c r="D101" s="15"/>
       <c r="E101" s="16"/>
       <c r="F101" s="15"/>
     </row>
-    <row r="102" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C102" s="15"/>
       <c r="D102" s="15"/>
       <c r="E102" s="16"/>
       <c r="F102" s="15"/>
     </row>
-    <row r="103" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C103" s="15"/>
       <c r="D103" s="15"/>
       <c r="E103" s="16"/>
       <c r="F103" s="15"/>
     </row>
-    <row r="104" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C104" s="15"/>
       <c r="D104" s="15"/>
       <c r="E104" s="16"/>
       <c r="F104" s="15"/>
     </row>
-    <row r="105" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C105" s="15"/>
       <c r="D105" s="15"/>
       <c r="E105" s="16"/>
       <c r="F105" s="15"/>
     </row>
-    <row r="106" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C106" s="15"/>
       <c r="D106" s="15"/>
       <c r="E106" s="16"/>
       <c r="F106" s="15"/>
     </row>
-    <row r="107" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C107" s="15"/>
       <c r="D107" s="15"/>
       <c r="E107" s="16"/>
       <c r="F107" s="15"/>
     </row>
-    <row r="108" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C108" s="15"/>
       <c r="D108" s="15"/>
       <c r="E108" s="16"/>
       <c r="F108" s="15"/>
     </row>
-    <row r="109" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C109" s="15"/>
       <c r="D109" s="15"/>
       <c r="E109" s="16"/>
       <c r="F109" s="15"/>
     </row>
-    <row r="110" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C110" s="15"/>
       <c r="D110" s="15"/>
       <c r="E110" s="16"/>
       <c r="F110" s="15"/>
     </row>
-    <row r="111" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C111" s="15"/>
       <c r="D111" s="15"/>
       <c r="E111" s="16"/>
       <c r="F111" s="15"/>
     </row>
-    <row r="112" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C112" s="15"/>
       <c r="D112" s="15"/>
       <c r="E112" s="16"/>
       <c r="F112" s="15"/>
     </row>
-    <row r="113" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C113" s="15"/>
       <c r="D113" s="15"/>
       <c r="E113" s="16"/>
       <c r="F113" s="15"/>
     </row>
-    <row r="114" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C114" s="15"/>
       <c r="D114" s="15"/>
       <c r="E114" s="16"/>
       <c r="F114" s="15"/>
     </row>
-    <row r="115" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C115" s="15"/>
       <c r="D115" s="15"/>
       <c r="E115" s="16"/>
       <c r="F115" s="15"/>
     </row>
-    <row r="116" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C116" s="15"/>
       <c r="D116" s="15"/>
       <c r="E116" s="16"/>
       <c r="F116" s="15"/>
     </row>
-    <row r="117" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C117" s="15"/>
       <c r="D117" s="15"/>
       <c r="E117" s="16"/>
       <c r="F117" s="15"/>
     </row>
-    <row r="118" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C118" s="15"/>
       <c r="D118" s="15"/>
       <c r="E118" s="16"/>
       <c r="F118" s="15"/>
     </row>
-    <row r="119" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C119" s="15"/>
       <c r="D119" s="15"/>
       <c r="E119" s="16"/>
       <c r="F119" s="15"/>
     </row>
-    <row r="120" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C120" s="15"/>
       <c r="D120" s="15"/>
       <c r="E120" s="16"/>
       <c r="F120" s="15"/>
     </row>
-    <row r="121" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C121" s="15"/>
       <c r="D121" s="15"/>
       <c r="E121" s="16"/>
       <c r="F121" s="15"/>
     </row>
-    <row r="122" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="122" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C122" s="15"/>
       <c r="D122" s="15"/>
       <c r="E122" s="16"/>
       <c r="F122" s="15"/>
     </row>
-    <row r="123" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C123" s="15"/>
       <c r="D123" s="15"/>
       <c r="E123" s="16"/>
       <c r="F123" s="15"/>
     </row>
-    <row r="124" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C124" s="15"/>
       <c r="D124" s="15"/>
       <c r="E124" s="16"/>
       <c r="F124" s="15"/>
     </row>
-    <row r="125" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="125" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C125" s="15"/>
       <c r="D125" s="15"/>
       <c r="E125" s="16"/>
       <c r="F125" s="15"/>
     </row>
-    <row r="126" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="126" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C126" s="15"/>
       <c r="D126" s="15"/>
       <c r="E126" s="16"/>
       <c r="F126" s="15"/>
     </row>
-    <row r="127" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="127" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C127" s="15"/>
       <c r="D127" s="15"/>
       <c r="E127" s="16"/>
       <c r="F127" s="15"/>
     </row>
-    <row r="128" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="128" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C128" s="15"/>
       <c r="D128" s="15"/>
       <c r="E128" s="16"/>
       <c r="F128" s="15"/>
     </row>
-    <row r="129" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="129" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C129" s="15"/>
       <c r="D129" s="15"/>
       <c r="E129" s="16"/>
       <c r="F129" s="15"/>
     </row>
-    <row r="130" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="130" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C130" s="15"/>
       <c r="D130" s="15"/>
       <c r="E130" s="16"/>
       <c r="F130" s="15"/>
     </row>
-    <row r="131" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="131" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C131" s="15"/>
       <c r="D131" s="15"/>
       <c r="E131" s="16"/>
       <c r="F131" s="15"/>
     </row>
-    <row r="132" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="132" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C132" s="15"/>
       <c r="D132" s="15"/>
       <c r="E132" s="16"/>
       <c r="F132" s="15"/>
     </row>
-    <row r="133" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="133" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C133" s="15"/>
       <c r="D133" s="15"/>
       <c r="E133" s="16"/>
       <c r="F133" s="15"/>
     </row>
-    <row r="134" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="134" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C134" s="15"/>
       <c r="D134" s="15"/>
       <c r="E134" s="16"/>
       <c r="F134" s="15"/>
     </row>
-    <row r="135" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="135" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C135" s="15"/>
       <c r="D135" s="15"/>
       <c r="E135" s="16"/>
       <c r="F135" s="15"/>
     </row>
-    <row r="136" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="136" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C136" s="15"/>
       <c r="D136" s="15"/>
       <c r="E136" s="16"/>
       <c r="F136" s="15"/>
     </row>
-    <row r="137" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="137" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C137" s="15"/>
       <c r="D137" s="15"/>
       <c r="E137" s="16"/>
       <c r="F137" s="15"/>
     </row>
-    <row r="138" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="138" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C138" s="15"/>
       <c r="D138" s="15"/>
       <c r="E138" s="16"/>
       <c r="F138" s="15"/>
     </row>
-    <row r="139" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="139" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C139" s="15"/>
       <c r="D139" s="15"/>
       <c r="E139" s="16"/>
       <c r="F139" s="15"/>
     </row>
-    <row r="140" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="140" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C140" s="15"/>
       <c r="D140" s="15"/>
       <c r="E140" s="16"/>
       <c r="F140" s="15"/>
     </row>
-    <row r="141" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="141" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C141" s="15"/>
       <c r="D141" s="15"/>
       <c r="E141" s="16"/>
       <c r="F141" s="15"/>
     </row>
-    <row r="142" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="142" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C142" s="15"/>
       <c r="D142" s="15"/>
       <c r="E142" s="16"/>
       <c r="F142" s="15"/>
     </row>
-    <row r="143" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="143" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C143" s="15"/>
       <c r="D143" s="15"/>
       <c r="E143" s="16"/>
       <c r="F143" s="15"/>
     </row>
-    <row r="144" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="144" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C144" s="15"/>
       <c r="D144" s="15"/>
       <c r="E144" s="16"/>
       <c r="F144" s="15"/>
     </row>
-    <row r="145" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="145" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C145" s="15"/>
       <c r="D145" s="15"/>
       <c r="E145" s="16"/>
       <c r="F145" s="15"/>
     </row>
-    <row r="146" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="146" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C146" s="15"/>
       <c r="D146" s="15"/>
       <c r="E146" s="16"/>
       <c r="F146" s="15"/>
     </row>
-    <row r="147" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="147" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C147" s="15"/>
       <c r="D147" s="15"/>
       <c r="E147" s="16"/>
       <c r="F147" s="15"/>
     </row>
-    <row r="148" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="148" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C148" s="15"/>
       <c r="D148" s="15"/>
       <c r="E148" s="16"/>
       <c r="F148" s="15"/>
     </row>
-    <row r="149" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="149" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C149" s="15"/>
       <c r="D149" s="15"/>
       <c r="E149" s="16"/>
       <c r="F149" s="15"/>
     </row>
-    <row r="150" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="150" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C150" s="15"/>
       <c r="D150" s="15"/>
       <c r="E150" s="16"/>
       <c r="F150" s="15"/>
     </row>
-    <row r="151" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="151" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C151" s="15"/>
       <c r="D151" s="15"/>
       <c r="E151" s="16"/>
       <c r="F151" s="15"/>
     </row>
-    <row r="152" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="152" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C152" s="15"/>
       <c r="D152" s="15"/>
       <c r="E152" s="16"/>
       <c r="F152" s="15"/>
     </row>
-    <row r="153" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="153" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C153" s="15"/>
       <c r="D153" s="15"/>
       <c r="E153" s="16"/>
       <c r="F153" s="15"/>
     </row>
-    <row r="154" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="154" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C154" s="15"/>
       <c r="D154" s="15"/>
       <c r="E154" s="16"/>
       <c r="F154" s="15"/>
     </row>
-    <row r="155" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="155" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C155" s="15"/>
       <c r="D155" s="15"/>
       <c r="E155" s="16"/>
       <c r="F155" s="15"/>
     </row>
-    <row r="156" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="156" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C156" s="15"/>
       <c r="D156" s="15"/>
       <c r="E156" s="16"/>
       <c r="F156" s="15"/>
     </row>
-    <row r="157" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="157" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C157" s="15"/>
       <c r="D157" s="15"/>
       <c r="E157" s="16"/>
       <c r="F157" s="15"/>
     </row>
-    <row r="158" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="158" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C158" s="15"/>
       <c r="D158" s="15"/>
       <c r="E158" s="16"/>
       <c r="F158" s="15"/>
     </row>
-    <row r="159" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="159" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C159" s="15"/>
       <c r="D159" s="15"/>
       <c r="E159" s="16"/>
       <c r="F159" s="15"/>
     </row>
-    <row r="160" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="160" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C160" s="15"/>
       <c r="D160" s="15"/>
       <c r="E160" s="16"/>
       <c r="F160" s="15"/>
     </row>
-    <row r="161" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="161" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C161" s="15"/>
       <c r="D161" s="15"/>
       <c r="E161" s="16"/>
       <c r="F161" s="15"/>
     </row>
-    <row r="162" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="162" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C162" s="15"/>
       <c r="D162" s="15"/>
       <c r="E162" s="16"/>
       <c r="F162" s="15"/>
     </row>
-    <row r="163" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="163" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C163" s="15"/>
       <c r="D163" s="15"/>
       <c r="E163" s="16"/>
       <c r="F163" s="15"/>
     </row>
-    <row r="164" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="164" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C164" s="15"/>
       <c r="D164" s="15"/>
       <c r="E164" s="16"/>
       <c r="F164" s="15"/>
     </row>
-    <row r="165" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="165" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C165" s="15"/>
       <c r="D165" s="15"/>
       <c r="E165" s="16"/>
       <c r="F165" s="15"/>
     </row>
-    <row r="166" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="166" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C166" s="15"/>
       <c r="D166" s="15"/>
       <c r="E166" s="16"/>
       <c r="F166" s="15"/>
     </row>
-    <row r="167" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="167" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C167" s="15"/>
       <c r="D167" s="15"/>
       <c r="E167" s="16"/>
       <c r="F167" s="15"/>
     </row>
-    <row r="168" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="168" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C168" s="15"/>
       <c r="D168" s="15"/>
       <c r="E168" s="16"/>
       <c r="F168" s="15"/>
     </row>
-    <row r="169" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="169" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C169" s="15"/>
       <c r="D169" s="15"/>
       <c r="E169" s="16"/>
       <c r="F169" s="15"/>
     </row>
-    <row r="170" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="170" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C170" s="15"/>
       <c r="D170" s="15"/>
       <c r="E170" s="16"/>
       <c r="F170" s="15"/>
     </row>
-    <row r="171" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="171" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C171" s="15"/>
       <c r="D171" s="15"/>
       <c r="E171" s="16"/>
       <c r="F171" s="15"/>
     </row>
-    <row r="172" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="172" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C172" s="15"/>
       <c r="D172" s="15"/>
       <c r="E172" s="16"/>
       <c r="F172" s="15"/>
     </row>
-    <row r="173" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="173" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C173" s="15"/>
       <c r="D173" s="15"/>
       <c r="E173" s="16"/>
       <c r="F173" s="15"/>
     </row>
-    <row r="174" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="174" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C174" s="15"/>
       <c r="D174" s="15"/>
       <c r="E174" s="16"/>
       <c r="F174" s="15"/>
     </row>
-    <row r="175" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="175" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C175" s="15"/>
       <c r="D175" s="15"/>
       <c r="E175" s="16"/>
       <c r="F175" s="15"/>
     </row>
-    <row r="176" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="176" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C176" s="15"/>
       <c r="D176" s="15"/>
       <c r="E176" s="16"/>
       <c r="F176" s="15"/>
     </row>
-    <row r="177" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="177" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C177" s="15"/>
       <c r="D177" s="15"/>
       <c r="E177" s="16"/>
       <c r="F177" s="15"/>
     </row>
-    <row r="178" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="178" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C178" s="15"/>
       <c r="D178" s="15"/>
       <c r="E178" s="16"/>
       <c r="F178" s="15"/>
     </row>
-    <row r="179" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="179" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C179" s="15"/>
       <c r="D179" s="15"/>
       <c r="E179" s="16"/>
       <c r="F179" s="15"/>
     </row>
-    <row r="180" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="180" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C180" s="15"/>
       <c r="D180" s="15"/>
       <c r="E180" s="16"/>
       <c r="F180" s="15"/>
     </row>
-    <row r="181" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="181" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C181" s="15"/>
       <c r="D181" s="15"/>
       <c r="E181" s="16"/>
       <c r="F181" s="15"/>
     </row>
-    <row r="182" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="182" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C182" s="15"/>
       <c r="D182" s="15"/>
       <c r="E182" s="16"/>
       <c r="F182" s="15"/>
     </row>
-    <row r="183" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="183" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C183" s="15"/>
       <c r="D183" s="15"/>
       <c r="E183" s="16"/>
       <c r="F183" s="15"/>
     </row>
-    <row r="184" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="184" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C184" s="15"/>
       <c r="D184" s="15"/>
       <c r="E184" s="16"/>
       <c r="F184" s="15"/>
     </row>
-    <row r="185" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="185" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C185" s="15"/>
       <c r="D185" s="15"/>
       <c r="E185" s="16"/>
       <c r="F185" s="15"/>
     </row>
-    <row r="186" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="186" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C186" s="15"/>
       <c r="D186" s="15"/>
       <c r="E186" s="16"/>
       <c r="F186" s="15"/>
     </row>
-    <row r="187" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="187" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C187" s="15"/>
       <c r="D187" s="15"/>
       <c r="E187" s="16"/>
       <c r="F187" s="15"/>
     </row>
-    <row r="188" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="188" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C188" s="15"/>
       <c r="D188" s="15"/>
       <c r="E188" s="16"/>
       <c r="F188" s="15"/>
     </row>
-    <row r="189" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="189" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C189" s="15"/>
       <c r="D189" s="15"/>
       <c r="E189" s="16"/>
       <c r="F189" s="15"/>
     </row>
-    <row r="190" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="190" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C190" s="15"/>
       <c r="D190" s="15"/>
       <c r="E190" s="16"/>
       <c r="F190" s="15"/>
     </row>
-    <row r="191" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="191" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C191" s="15"/>
       <c r="D191" s="15"/>
       <c r="E191" s="16"/>
       <c r="F191" s="15"/>
     </row>
-    <row r="192" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="192" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C192" s="15"/>
       <c r="D192" s="15"/>
       <c r="E192" s="16"/>
       <c r="F192" s="15"/>
     </row>
-    <row r="193" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="193" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C193" s="15"/>
       <c r="D193" s="15"/>
       <c r="E193" s="16"/>
       <c r="F193" s="15"/>
     </row>
-    <row r="194" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="194" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C194" s="15"/>
       <c r="D194" s="15"/>
       <c r="E194" s="16"/>
       <c r="F194" s="15"/>
     </row>
-    <row r="195" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="195" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C195" s="15"/>
       <c r="D195" s="15"/>
       <c r="E195" s="16"/>
       <c r="F195" s="15"/>
     </row>
-    <row r="196" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="196" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C196" s="15"/>
       <c r="D196" s="15"/>
       <c r="E196" s="16"/>
       <c r="F196" s="15"/>
     </row>
-    <row r="197" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="197" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C197" s="15"/>
       <c r="D197" s="15"/>
       <c r="E197" s="16"/>
       <c r="F197" s="15"/>
     </row>
-    <row r="198" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="198" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C198" s="15"/>
       <c r="D198" s="15"/>
       <c r="E198" s="16"/>
       <c r="F198" s="15"/>
     </row>
-    <row r="199" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="199" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C199" s="15"/>
       <c r="D199" s="15"/>
       <c r="E199" s="16"/>
       <c r="F199" s="15"/>
     </row>
-    <row r="200" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="200" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C200" s="15"/>
       <c r="D200" s="15"/>
       <c r="E200" s="16"/>
       <c r="F200" s="15"/>
     </row>
-    <row r="201" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="201" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C201" s="15"/>
       <c r="D201" s="15"/>
       <c r="E201" s="16"/>
       <c r="F201" s="15"/>
     </row>
-    <row r="202" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="202" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C202" s="15"/>
       <c r="D202" s="15"/>
       <c r="E202" s="16"/>
       <c r="F202" s="15"/>
     </row>
-    <row r="203" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="203" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C203" s="15"/>
       <c r="D203" s="15"/>
       <c r="E203" s="16"/>
       <c r="F203" s="15"/>
     </row>
-    <row r="204" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="204" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C204" s="15"/>
       <c r="D204" s="15"/>
       <c r="E204" s="16"/>
       <c r="F204" s="15"/>
     </row>
-    <row r="205" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="205" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C205" s="15"/>
       <c r="D205" s="15"/>
       <c r="E205" s="16"/>
       <c r="F205" s="15"/>
     </row>
-    <row r="206" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="206" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C206" s="15"/>
       <c r="D206" s="15"/>
       <c r="E206" s="16"/>
       <c r="F206" s="15"/>
     </row>
-    <row r="207" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="207" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C207" s="15"/>
       <c r="D207" s="15"/>
       <c r="E207" s="16"/>
       <c r="F207" s="15"/>
     </row>
-    <row r="208" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="208" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C208" s="15"/>
       <c r="D208" s="15"/>
       <c r="E208" s="16"/>
       <c r="F208" s="15"/>
     </row>
-    <row r="209" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="209" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C209" s="15"/>
       <c r="D209" s="15"/>
       <c r="E209" s="16"/>
       <c r="F209" s="15"/>
     </row>
-    <row r="210" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="210" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C210" s="15"/>
       <c r="D210" s="15"/>
       <c r="E210" s="16"/>
       <c r="F210" s="15"/>
     </row>
-    <row r="211" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="211" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C211" s="15"/>
       <c r="D211" s="15"/>
       <c r="E211" s="16"/>
       <c r="F211" s="15"/>
     </row>
-    <row r="212" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="212" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C212" s="15"/>
       <c r="D212" s="15"/>
       <c r="E212" s="16"/>
       <c r="F212" s="15"/>
     </row>
-    <row r="213" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="213" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C213" s="15"/>
       <c r="D213" s="15"/>
       <c r="E213" s="16"/>
       <c r="F213" s="15"/>
     </row>
-    <row r="214" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="214" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C214" s="15"/>
       <c r="D214" s="15"/>
       <c r="E214" s="16"/>
       <c r="F214" s="15"/>
     </row>
-    <row r="215" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="215" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C215" s="15"/>
       <c r="D215" s="15"/>
       <c r="E215" s="16"/>
       <c r="F215" s="15"/>
     </row>
-    <row r="216" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="216" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C216" s="15"/>
       <c r="D216" s="15"/>
       <c r="E216" s="16"/>
       <c r="F216" s="15"/>
     </row>
-    <row r="217" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="217" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C217" s="15"/>
       <c r="D217" s="15"/>
       <c r="E217" s="16"/>
       <c r="F217" s="15"/>
     </row>
-    <row r="218" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="218" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C218" s="15"/>
       <c r="D218" s="15"/>
       <c r="E218" s="16"/>
       <c r="F218" s="15"/>
     </row>
-    <row r="219" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="219" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C219" s="15"/>
       <c r="D219" s="15"/>
       <c r="E219" s="16"/>
       <c r="F219" s="15"/>
     </row>
-    <row r="220" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="220" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C220" s="15"/>
       <c r="D220" s="15"/>
       <c r="E220" s="16"/>
       <c r="F220" s="15"/>
     </row>
-    <row r="221" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="221" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C221" s="15"/>
       <c r="D221" s="15"/>
       <c r="E221" s="16"/>
       <c r="F221" s="15"/>
     </row>
-    <row r="222" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="222" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C222" s="15"/>
       <c r="D222" s="15"/>
       <c r="E222" s="16"/>
       <c r="F222" s="15"/>
     </row>
-    <row r="223" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="223" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C223" s="15"/>
       <c r="D223" s="15"/>
       <c r="E223" s="16"/>
       <c r="F223" s="15"/>
     </row>
-    <row r="224" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="224" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C224" s="15"/>
       <c r="D224" s="15"/>
       <c r="E224" s="16"/>
       <c r="F224" s="15"/>
     </row>
-    <row r="225" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="225" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C225" s="15"/>
       <c r="D225" s="15"/>
       <c r="E225" s="16"/>
       <c r="F225" s="15"/>
     </row>
-    <row r="226" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="226" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C226" s="15"/>
       <c r="D226" s="15"/>
       <c r="E226" s="16"/>
       <c r="F226" s="15"/>
     </row>
-    <row r="227" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="227" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C227" s="15"/>
       <c r="D227" s="15"/>
       <c r="E227" s="16"/>
       <c r="F227" s="15"/>
     </row>
-    <row r="228" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="228" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C228" s="15"/>
       <c r="D228" s="15"/>
       <c r="E228" s="16"/>
       <c r="F228" s="15"/>
     </row>
-    <row r="229" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="229" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C229" s="15"/>
       <c r="D229" s="15"/>
       <c r="E229" s="16"/>
       <c r="F229" s="15"/>
     </row>
-    <row r="230" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="230" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C230" s="15"/>
       <c r="D230" s="15"/>
       <c r="E230" s="16"/>
       <c r="F230" s="15"/>
     </row>
-    <row r="231" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="231" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C231" s="15"/>
       <c r="D231" s="15"/>
       <c r="E231" s="16"/>
       <c r="F231" s="15"/>
     </row>
-    <row r="232" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="232" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C232" s="15"/>
       <c r="D232" s="15"/>
       <c r="E232" s="16"/>
       <c r="F232" s="15"/>
     </row>
-    <row r="233" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="233" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C233" s="15"/>
       <c r="D233" s="15"/>
       <c r="E233" s="16"/>
       <c r="F233" s="15"/>
     </row>
-    <row r="234" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="234" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C234" s="15"/>
       <c r="D234" s="15"/>
       <c r="E234" s="16"/>
       <c r="F234" s="15"/>
     </row>
-    <row r="235" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="235" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C235" s="15"/>
       <c r="D235" s="15"/>
       <c r="E235" s="16"/>
       <c r="F235" s="15"/>
     </row>
-    <row r="236" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="236" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C236" s="15"/>
       <c r="D236" s="15"/>
       <c r="E236" s="16"/>
       <c r="F236" s="15"/>
     </row>
-    <row r="237" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="237" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C237" s="15"/>
       <c r="D237" s="15"/>
       <c r="E237" s="16"/>
       <c r="F237" s="15"/>
     </row>
-    <row r="238" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="238" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C238" s="15"/>
       <c r="D238" s="15"/>
       <c r="E238" s="16"/>
       <c r="F238" s="15"/>
     </row>
-    <row r="239" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="239" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C239" s="15"/>
       <c r="D239" s="15"/>
       <c r="E239" s="16"/>
       <c r="F239" s="15"/>
     </row>
-    <row r="240" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="240" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C240" s="15"/>
       <c r="D240" s="15"/>
       <c r="E240" s="16"/>
       <c r="F240" s="15"/>
     </row>
-    <row r="241" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="241" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C241" s="15"/>
       <c r="D241" s="15"/>
       <c r="E241" s="16"/>
       <c r="F241" s="15"/>
     </row>
-    <row r="242" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="242" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C242" s="15"/>
       <c r="D242" s="15"/>
       <c r="E242" s="16"/>
       <c r="F242" s="15"/>
     </row>
-    <row r="243" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="243" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C243" s="15"/>
       <c r="D243" s="15"/>
       <c r="E243" s="16"/>
       <c r="F243" s="15"/>
     </row>
-    <row r="244" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="244" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C244" s="15"/>
       <c r="D244" s="15"/>
       <c r="E244" s="16"/>
       <c r="F244" s="15"/>
     </row>
-    <row r="245" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="245" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C245" s="15"/>
       <c r="D245" s="15"/>
       <c r="E245" s="16"/>
       <c r="F245" s="15"/>
     </row>
-    <row r="246" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="246" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C246" s="15"/>
       <c r="D246" s="15"/>
       <c r="E246" s="16"/>
       <c r="F246" s="15"/>
     </row>
-    <row r="247" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="247" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C247" s="15"/>
       <c r="D247" s="15"/>
       <c r="E247" s="16"/>
       <c r="F247" s="15"/>
     </row>
-    <row r="248" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="248" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C248" s="15"/>
       <c r="D248" s="15"/>
       <c r="E248" s="16"/>
       <c r="F248" s="15"/>
     </row>
-    <row r="249" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="249" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C249" s="15"/>
       <c r="D249" s="15"/>
       <c r="E249" s="16"/>
       <c r="F249" s="15"/>
     </row>
-    <row r="250" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="250" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C250" s="15"/>
       <c r="D250" s="15"/>
       <c r="E250" s="16"/>
       <c r="F250" s="15"/>
     </row>
-    <row r="251" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="251" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C251" s="15"/>
       <c r="D251" s="15"/>
       <c r="E251" s="16"/>
       <c r="F251" s="15"/>
     </row>
-    <row r="252" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="252" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C252" s="15"/>
       <c r="D252" s="15"/>
       <c r="E252" s="16"/>
       <c r="F252" s="15"/>
     </row>
-    <row r="253" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="253" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C253" s="15"/>
       <c r="D253" s="15"/>
       <c r="E253" s="16"/>
       <c r="F253" s="15"/>
     </row>
-    <row r="254" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="254" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C254" s="15"/>
       <c r="D254" s="15"/>
       <c r="E254" s="16"/>
       <c r="F254" s="15"/>
     </row>
-    <row r="255" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="255" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C255" s="15"/>
       <c r="D255" s="15"/>
       <c r="E255" s="16"/>
       <c r="F255" s="15"/>
     </row>
-    <row r="256" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="256" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C256" s="15"/>
       <c r="D256" s="15"/>
       <c r="E256" s="16"/>
       <c r="F256" s="15"/>
     </row>
-    <row r="257" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="257" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C257" s="15"/>
       <c r="D257" s="15"/>
       <c r="E257" s="16"/>
       <c r="F257" s="15"/>
     </row>
-    <row r="258" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="258" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C258" s="15"/>
       <c r="D258" s="15"/>
       <c r="E258" s="16"/>
       <c r="F258" s="15"/>
     </row>
-    <row r="259" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="259" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C259" s="15"/>
       <c r="D259" s="15"/>
       <c r="E259" s="16"/>
       <c r="F259" s="15"/>
     </row>
-    <row r="260" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="260" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C260" s="15"/>
       <c r="D260" s="15"/>
       <c r="E260" s="16"/>
       <c r="F260" s="15"/>
     </row>
-    <row r="261" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="261" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C261" s="15"/>
       <c r="D261" s="15"/>
       <c r="E261" s="16"/>
       <c r="F261" s="15"/>
     </row>
-    <row r="262" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="262" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C262" s="15"/>
       <c r="D262" s="15"/>
       <c r="E262" s="16"/>
       <c r="F262" s="15"/>
     </row>
-    <row r="263" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="263" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C263" s="15"/>
       <c r="D263" s="15"/>
       <c r="E263" s="16"/>
       <c r="F263" s="15"/>
     </row>
-    <row r="264" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="264" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C264" s="15"/>
       <c r="D264" s="15"/>
       <c r="E264" s="16"/>
       <c r="F264" s="15"/>
     </row>
-    <row r="265" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="265" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C265" s="15"/>
       <c r="D265" s="15"/>
       <c r="E265" s="16"/>
       <c r="F265" s="15"/>
     </row>
-    <row r="266" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="266" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C266" s="15"/>
       <c r="D266" s="15"/>
       <c r="E266" s="16"/>
       <c r="F266" s="15"/>
     </row>
-    <row r="267" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="267" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C267" s="15"/>
       <c r="D267" s="15"/>
       <c r="E267" s="16"/>
       <c r="F267" s="15"/>
     </row>
-    <row r="268" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="268" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C268" s="15"/>
       <c r="D268" s="15"/>
       <c r="E268" s="16"/>
       <c r="F268" s="15"/>
     </row>
-    <row r="269" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="269" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C269" s="15"/>
       <c r="D269" s="15"/>
       <c r="E269" s="16"/>
       <c r="F269" s="15"/>
     </row>
-    <row r="270" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="270" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C270" s="15"/>
       <c r="D270" s="15"/>
       <c r="E270" s="16"/>
       <c r="F270" s="15"/>
     </row>
-    <row r="271" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="271" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C271" s="15"/>
       <c r="D271" s="15"/>
       <c r="E271" s="16"/>
       <c r="F271" s="15"/>
     </row>
-    <row r="272" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="272" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C272" s="15"/>
       <c r="D272" s="15"/>
       <c r="E272" s="16"/>
       <c r="F272" s="15"/>
     </row>
-    <row r="273" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="273" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C273" s="15"/>
       <c r="D273" s="15"/>
       <c r="E273" s="16"/>
       <c r="F273" s="15"/>
     </row>
-    <row r="274" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="274" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C274" s="15"/>
       <c r="D274" s="15"/>
       <c r="E274" s="16"/>
       <c r="F274" s="15"/>
     </row>
-    <row r="275" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="275" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C275" s="15"/>
       <c r="D275" s="15"/>
       <c r="E275" s="16"/>
       <c r="F275" s="15"/>
     </row>
-    <row r="276" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="276" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C276" s="15"/>
       <c r="D276" s="15"/>
       <c r="E276" s="16"/>
       <c r="F276" s="15"/>
     </row>
-    <row r="277" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="277" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C277" s="15"/>
       <c r="D277" s="15"/>
       <c r="E277" s="16"/>
       <c r="F277" s="15"/>
     </row>
-    <row r="278" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="278" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C278" s="15"/>
       <c r="D278" s="15"/>
       <c r="E278" s="16"/>
       <c r="F278" s="15"/>
     </row>
-    <row r="279" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="279" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C279" s="15"/>
       <c r="D279" s="15"/>
       <c r="E279" s="16"/>
       <c r="F279" s="15"/>
     </row>
-    <row r="280" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="280" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C280" s="15"/>
       <c r="D280" s="15"/>
       <c r="E280" s="16"/>
       <c r="F280" s="15"/>
     </row>
-    <row r="281" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="281" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C281" s="15"/>
       <c r="D281" s="15"/>
       <c r="E281" s="16"/>
       <c r="F281" s="15"/>
     </row>
-    <row r="282" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="282" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C282" s="15"/>
       <c r="D282" s="15"/>
       <c r="E282" s="16"/>
       <c r="F282" s="15"/>
     </row>
-    <row r="283" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="283" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C283" s="15"/>
       <c r="D283" s="15"/>
       <c r="E283" s="16"/>
       <c r="F283" s="15"/>
     </row>
-    <row r="284" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="284" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C284" s="15"/>
       <c r="D284" s="15"/>
       <c r="E284" s="16"/>
       <c r="F284" s="15"/>
     </row>
-    <row r="285" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="285" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C285" s="15"/>
       <c r="D285" s="15"/>
       <c r="E285" s="16"/>
       <c r="F285" s="15"/>
     </row>
-    <row r="286" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="286" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C286" s="15"/>
       <c r="D286" s="15"/>
       <c r="E286" s="16"/>
       <c r="F286" s="15"/>
     </row>
-    <row r="287" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="287" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C287" s="15"/>
       <c r="D287" s="15"/>
       <c r="E287" s="16"/>
       <c r="F287" s="15"/>
     </row>
-    <row r="288" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="288" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C288" s="15"/>
       <c r="D288" s="15"/>
       <c r="E288" s="16"/>
       <c r="F288" s="15"/>
     </row>
-    <row r="289" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="289" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C289" s="15"/>
       <c r="D289" s="15"/>
       <c r="E289" s="16"/>
       <c r="F289" s="15"/>
     </row>
-    <row r="290" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="290" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C290" s="15"/>
       <c r="D290" s="15"/>
       <c r="E290" s="16"/>
       <c r="F290" s="15"/>
     </row>
-    <row r="291" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="291" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C291" s="15"/>
       <c r="D291" s="15"/>
       <c r="E291" s="16"/>
       <c r="F291" s="15"/>
     </row>
-    <row r="292" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="292" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C292" s="15"/>
       <c r="D292" s="15"/>
       <c r="E292" s="16"/>
       <c r="F292" s="15"/>
     </row>
-    <row r="293" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="293" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C293" s="15"/>
       <c r="D293" s="15"/>
       <c r="E293" s="16"/>
       <c r="F293" s="15"/>
     </row>
-    <row r="294" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="294" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C294" s="15"/>
       <c r="D294" s="15"/>
       <c r="E294" s="16"/>
       <c r="F294" s="15"/>
     </row>
-    <row r="295" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="295" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C295" s="15"/>
       <c r="D295" s="15"/>
       <c r="E295" s="16"/>
       <c r="F295" s="15"/>
     </row>
-    <row r="296" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="296" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C296" s="15"/>
       <c r="D296" s="15"/>
       <c r="E296" s="16"/>
       <c r="F296" s="15"/>
     </row>
-    <row r="297" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="297" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C297" s="15"/>
       <c r="D297" s="15"/>
       <c r="E297" s="16"/>
       <c r="F297" s="15"/>
     </row>
-    <row r="298" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="298" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C298" s="15"/>
       <c r="D298" s="15"/>
       <c r="E298" s="16"/>
       <c r="F298" s="15"/>
     </row>
-    <row r="299" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="299" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C299" s="15"/>
       <c r="D299" s="15"/>
       <c r="E299" s="16"/>
       <c r="F299" s="15"/>
     </row>
-    <row r="300" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="300" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C300" s="15"/>
       <c r="D300" s="15"/>
       <c r="E300" s="16"/>
       <c r="F300" s="15"/>
     </row>
-    <row r="301" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="301" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C301" s="15"/>
       <c r="D301" s="15"/>
       <c r="E301" s="16"/>
       <c r="F301" s="15"/>
     </row>
-    <row r="302" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="302" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C302" s="15"/>
       <c r="D302" s="15"/>
       <c r="E302" s="16"/>
       <c r="F302" s="15"/>
     </row>
-    <row r="303" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="303" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C303" s="15"/>
       <c r="D303" s="15"/>
       <c r="E303" s="16"/>
       <c r="F303" s="15"/>
     </row>
-    <row r="304" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="304" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C304" s="15"/>
       <c r="D304" s="15"/>
       <c r="E304" s="16"/>
       <c r="F304" s="15"/>
     </row>
-    <row r="305" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="305" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C305" s="15"/>
       <c r="D305" s="15"/>
       <c r="E305" s="16"/>
       <c r="F305" s="15"/>
     </row>
-    <row r="306" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="306" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C306" s="15"/>
       <c r="D306" s="15"/>
       <c r="E306" s="16"/>
       <c r="F306" s="15"/>
     </row>
-    <row r="307" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="307" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C307" s="15"/>
       <c r="D307" s="15"/>
       <c r="E307" s="16"/>
       <c r="F307" s="15"/>
     </row>
-    <row r="308" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="308" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C308" s="15"/>
       <c r="D308" s="15"/>
       <c r="E308" s="16"/>
       <c r="F308" s="15"/>
     </row>
-    <row r="309" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="309" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C309" s="15"/>
       <c r="D309" s="15"/>
       <c r="E309" s="16"/>
       <c r="F309" s="15"/>
     </row>
-    <row r="310" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="310" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C310" s="15"/>
       <c r="D310" s="15"/>
       <c r="E310" s="16"/>
       <c r="F310" s="15"/>
     </row>
-    <row r="311" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="311" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C311" s="15"/>
       <c r="D311" s="15"/>
       <c r="E311" s="16"/>
       <c r="F311" s="15"/>
     </row>
-    <row r="312" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="312" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C312" s="15"/>
       <c r="D312" s="15"/>
       <c r="E312" s="16"/>
       <c r="F312" s="15"/>
     </row>
-    <row r="313" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="313" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C313" s="15"/>
       <c r="D313" s="15"/>
       <c r="E313" s="16"/>
       <c r="F313" s="15"/>
     </row>
-    <row r="314" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="314" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C314" s="15"/>
       <c r="D314" s="15"/>
       <c r="E314" s="16"/>
       <c r="F314" s="15"/>
     </row>
-    <row r="315" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="315" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C315" s="15"/>
       <c r="D315" s="15"/>
       <c r="E315" s="16"/>
       <c r="F315" s="15"/>
     </row>
-    <row r="316" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="316" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C316" s="15"/>
       <c r="D316" s="15"/>
       <c r="E316" s="16"/>
       <c r="F316" s="15"/>
     </row>
-    <row r="317" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="317" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C317" s="15"/>
       <c r="D317" s="15"/>
       <c r="E317" s="16"/>
       <c r="F317" s="15"/>
     </row>
-    <row r="318" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="318" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C318" s="15"/>
       <c r="D318" s="15"/>
       <c r="E318" s="16"/>
       <c r="F318" s="15"/>
     </row>
-    <row r="319" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="319" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C319" s="15"/>
       <c r="D319" s="15"/>
       <c r="E319" s="16"/>
       <c r="F319" s="15"/>
     </row>
-    <row r="320" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="320" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C320" s="15"/>
       <c r="D320" s="15"/>
       <c r="E320" s="16"/>
       <c r="F320" s="15"/>
     </row>
-    <row r="321" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="321" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C321" s="15"/>
       <c r="D321" s="15"/>
       <c r="E321" s="16"/>
       <c r="F321" s="15"/>
     </row>
-    <row r="322" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="322" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C322" s="15"/>
       <c r="D322" s="15"/>
       <c r="E322" s="16"/>
       <c r="F322" s="15"/>
     </row>
-    <row r="323" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="323" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C323" s="15"/>
       <c r="D323" s="15"/>
       <c r="E323" s="16"/>
       <c r="F323" s="15"/>
     </row>
-    <row r="324" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="324" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C324" s="15"/>
       <c r="D324" s="15"/>
       <c r="E324" s="16"/>
       <c r="F324" s="15"/>
     </row>
-    <row r="325" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="325" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C325" s="15"/>
       <c r="D325" s="15"/>
       <c r="E325" s="16"/>
       <c r="F325" s="15"/>
     </row>
-    <row r="326" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="326" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C326" s="15"/>
       <c r="D326" s="15"/>
       <c r="E326" s="16"/>
       <c r="F326" s="15"/>
     </row>
-    <row r="327" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="327" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C327" s="15"/>
       <c r="D327" s="15"/>
       <c r="E327" s="16"/>
       <c r="F327" s="15"/>
     </row>
-    <row r="328" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="328" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C328" s="15"/>
       <c r="D328" s="15"/>
       <c r="E328" s="16"/>
       <c r="F328" s="15"/>
     </row>
-    <row r="329" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="329" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C329" s="15"/>
       <c r="D329" s="15"/>
       <c r="E329" s="16"/>
       <c r="F329" s="15"/>
     </row>
-    <row r="330" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="330" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C330" s="15"/>
       <c r="D330" s="15"/>
       <c r="E330" s="16"/>
       <c r="F330" s="15"/>
     </row>
-    <row r="331" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="331" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C331" s="15"/>
       <c r="D331" s="15"/>
       <c r="E331" s="16"/>
       <c r="F331" s="15"/>
     </row>
-    <row r="332" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="332" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C332" s="15"/>
       <c r="D332" s="15"/>
       <c r="E332" s="16"/>
       <c r="F332" s="15"/>
     </row>
-    <row r="333" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="333" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C333" s="15"/>
       <c r="D333" s="15"/>
       <c r="E333" s="16"/>
       <c r="F333" s="15"/>
     </row>
-    <row r="334" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="334" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C334" s="15"/>
       <c r="D334" s="15"/>
       <c r="E334" s="16"/>
       <c r="F334" s="15"/>
     </row>
-    <row r="335" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="335" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C335" s="15"/>
       <c r="D335" s="15"/>
       <c r="E335" s="16"/>
       <c r="F335" s="15"/>
     </row>
-    <row r="336" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="336" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C336" s="15"/>
       <c r="D336" s="15"/>
       <c r="E336" s="16"/>
       <c r="F336" s="15"/>
     </row>
-    <row r="337" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="337" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C337" s="15"/>
       <c r="D337" s="15"/>
       <c r="E337" s="16"/>
       <c r="F337" s="15"/>
     </row>
-    <row r="338" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="338" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C338" s="15"/>
       <c r="D338" s="15"/>
       <c r="E338" s="16"/>
       <c r="F338" s="15"/>
     </row>
-    <row r="339" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="339" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C339" s="15"/>
       <c r="D339" s="15"/>
       <c r="E339" s="16"/>
       <c r="F339" s="15"/>
     </row>
-    <row r="340" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="340" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C340" s="15"/>
       <c r="D340" s="15"/>
       <c r="E340" s="16"/>
       <c r="F340" s="15"/>
     </row>
-    <row r="341" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="341" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C341" s="15"/>
       <c r="D341" s="15"/>
       <c r="E341" s="16"/>
       <c r="F341" s="15"/>
     </row>
-    <row r="342" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="342" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C342" s="15"/>
       <c r="D342" s="15"/>
       <c r="E342" s="16"/>
       <c r="F342" s="15"/>
     </row>
-    <row r="343" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="343" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C343" s="15"/>
       <c r="D343" s="15"/>
       <c r="E343" s="16"/>
       <c r="F343" s="15"/>
     </row>
-    <row r="344" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="344" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C344" s="15"/>
       <c r="D344" s="15"/>
       <c r="E344" s="16"/>
       <c r="F344" s="15"/>
     </row>
-    <row r="345" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="345" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C345" s="15"/>
       <c r="D345" s="15"/>
       <c r="E345" s="16"/>
       <c r="F345" s="15"/>
     </row>
-    <row r="346" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="346" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C346" s="15"/>
       <c r="D346" s="15"/>
       <c r="E346" s="16"/>
       <c r="F346" s="15"/>
     </row>
-    <row r="347" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="347" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C347" s="15"/>
       <c r="D347" s="15"/>
       <c r="E347" s="16"/>
       <c r="F347" s="15"/>
     </row>
-    <row r="348" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="348" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C348" s="15"/>
       <c r="D348" s="15"/>
       <c r="E348" s="16"/>
       <c r="F348" s="15"/>
     </row>
-    <row r="349" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="349" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C349" s="15"/>
       <c r="D349" s="15"/>
       <c r="E349" s="16"/>
       <c r="F349" s="15"/>
     </row>
-    <row r="350" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="350" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C350" s="15"/>
       <c r="D350" s="15"/>
       <c r="E350" s="16"/>
       <c r="F350" s="15"/>
     </row>
-    <row r="351" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="351" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C351" s="15"/>
       <c r="D351" s="15"/>
       <c r="E351" s="16"/>
       <c r="F351" s="15"/>
     </row>
-    <row r="352" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="352" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C352" s="15"/>
       <c r="D352" s="15"/>
       <c r="E352" s="16"/>
       <c r="F352" s="15"/>
     </row>
-    <row r="353" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="353" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C353" s="15"/>
       <c r="D353" s="15"/>
       <c r="E353" s="16"/>
       <c r="F353" s="15"/>
     </row>
-    <row r="354" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="354" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C354" s="15"/>
       <c r="D354" s="15"/>
       <c r="E354" s="16"/>
       <c r="F354" s="15"/>
     </row>
-    <row r="355" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="355" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C355" s="15"/>
       <c r="D355" s="15"/>
       <c r="E355" s="16"/>
       <c r="F355" s="15"/>
     </row>
-    <row r="356" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="356" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C356" s="15"/>
       <c r="D356" s="15"/>
       <c r="E356" s="16"/>
       <c r="F356" s="15"/>
     </row>
-    <row r="357" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="357" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C357" s="15"/>
       <c r="D357" s="15"/>
       <c r="E357" s="16"/>
       <c r="F357" s="15"/>
     </row>
-    <row r="358" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="358" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C358" s="15"/>
       <c r="D358" s="15"/>
       <c r="E358" s="16"/>
       <c r="F358" s="15"/>
     </row>
-    <row r="359" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="359" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C359" s="15"/>
       <c r="D359" s="15"/>
       <c r="E359" s="16"/>
       <c r="F359" s="15"/>
     </row>
-    <row r="360" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="360" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C360" s="15"/>
       <c r="D360" s="15"/>
       <c r="E360" s="16"/>
       <c r="F360" s="15"/>
     </row>
-    <row r="361" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="361" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C361" s="15"/>
       <c r="D361" s="15"/>
       <c r="E361" s="16"/>
       <c r="F361" s="15"/>
     </row>
-    <row r="362" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="362" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C362" s="15"/>
       <c r="D362" s="15"/>
       <c r="E362" s="16"/>
       <c r="F362" s="15"/>
     </row>
-    <row r="363" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="363" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C363" s="15"/>
       <c r="D363" s="15"/>
       <c r="E363" s="16"/>
       <c r="F363" s="15"/>
     </row>
-    <row r="364" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="364" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C364" s="15"/>
       <c r="D364" s="15"/>
       <c r="E364" s="16"/>
       <c r="F364" s="15"/>
     </row>
-    <row r="365" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="365" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C365" s="15"/>
       <c r="D365" s="15"/>
       <c r="E365" s="16"/>
       <c r="F365" s="15"/>
     </row>
-    <row r="366" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="366" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C366" s="15"/>
       <c r="D366" s="15"/>
       <c r="E366" s="16"/>
       <c r="F366" s="15"/>
     </row>
-    <row r="367" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="367" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C367" s="15"/>
       <c r="D367" s="15"/>
       <c r="E367" s="16"/>
       <c r="F367" s="15"/>
     </row>
-    <row r="368" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="368" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C368" s="15"/>
       <c r="D368" s="15"/>
       <c r="E368" s="16"/>
       <c r="F368" s="15"/>
     </row>
-    <row r="369" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="369" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C369" s="15"/>
       <c r="D369" s="15"/>
       <c r="E369" s="16"/>
       <c r="F369" s="15"/>
     </row>
-    <row r="370" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="370" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C370" s="15"/>
       <c r="D370" s="15"/>
       <c r="E370" s="16"/>
       <c r="F370" s="15"/>
     </row>
-    <row r="371" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="371" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C371" s="15"/>
       <c r="D371" s="15"/>
       <c r="E371" s="16"/>
       <c r="F371" s="15"/>
     </row>
-    <row r="372" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="372" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C372" s="15"/>
       <c r="D372" s="15"/>
       <c r="E372" s="16"/>
       <c r="F372" s="15"/>
     </row>
-    <row r="373" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="373" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C373" s="15"/>
       <c r="D373" s="15"/>
       <c r="E373" s="16"/>
       <c r="F373" s="15"/>
     </row>
-    <row r="374" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="374" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C374" s="15"/>
       <c r="D374" s="15"/>
       <c r="E374" s="16"/>
       <c r="F374" s="15"/>
     </row>
-    <row r="375" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="375" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C375" s="15"/>
       <c r="D375" s="15"/>
       <c r="E375" s="16"/>
       <c r="F375" s="15"/>
     </row>
-    <row r="376" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="376" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C376" s="15"/>
       <c r="D376" s="15"/>
       <c r="E376" s="16"/>
       <c r="F376" s="15"/>
     </row>
-    <row r="377" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="377" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C377" s="15"/>
       <c r="D377" s="15"/>
       <c r="E377" s="16"/>
       <c r="F377" s="15"/>
     </row>
-    <row r="378" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="378" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C378" s="15"/>
       <c r="D378" s="15"/>
       <c r="E378" s="16"/>
       <c r="F378" s="15"/>
     </row>
-    <row r="379" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="379" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C379" s="15"/>
       <c r="D379" s="15"/>
       <c r="E379" s="16"/>
       <c r="F379" s="15"/>
     </row>
-    <row r="380" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="380" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C380" s="15"/>
       <c r="D380" s="15"/>
       <c r="E380" s="16"/>
       <c r="F380" s="15"/>
     </row>
-    <row r="381" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="381" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C381" s="15"/>
       <c r="D381" s="15"/>
       <c r="E381" s="16"/>
       <c r="F381" s="15"/>
     </row>
-    <row r="382" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="382" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C382" s="15"/>
       <c r="D382" s="15"/>
       <c r="E382" s="16"/>
       <c r="F382" s="15"/>
     </row>
-    <row r="383" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="383" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C383" s="15"/>
       <c r="D383" s="15"/>
       <c r="E383" s="16"/>
       <c r="F383" s="15"/>
     </row>
-    <row r="384" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="384" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C384" s="15"/>
       <c r="D384" s="15"/>
       <c r="E384" s="16"/>
       <c r="F384" s="15"/>
     </row>
-    <row r="385" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="385" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C385" s="15"/>
       <c r="D385" s="15"/>
       <c r="E385" s="16"/>
       <c r="F385" s="15"/>
     </row>
-    <row r="386" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="386" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C386" s="15"/>
       <c r="D386" s="15"/>
       <c r="E386" s="16"/>
       <c r="F386" s="15"/>
     </row>
-    <row r="387" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="387" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C387" s="15"/>
       <c r="D387" s="15"/>
       <c r="E387" s="16"/>
       <c r="F387" s="15"/>
     </row>
-    <row r="388" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="388" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C388" s="15"/>
       <c r="D388" s="15"/>
       <c r="E388" s="16"/>
       <c r="F388" s="15"/>
     </row>
-    <row r="389" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="389" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C389" s="15"/>
       <c r="D389" s="15"/>
       <c r="E389" s="16"/>
       <c r="F389" s="15"/>
     </row>
-    <row r="390" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="390" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C390" s="15"/>
       <c r="D390" s="15"/>
       <c r="E390" s="16"/>
       <c r="F390" s="15"/>
     </row>
-    <row r="391" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="391" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C391" s="15"/>
       <c r="D391" s="15"/>
       <c r="E391" s="16"/>
       <c r="F391" s="15"/>
     </row>
-    <row r="392" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="392" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C392" s="15"/>
       <c r="D392" s="15"/>
       <c r="E392" s="16"/>
       <c r="F392" s="15"/>
     </row>
-    <row r="393" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="393" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C393" s="15"/>
       <c r="D393" s="15"/>
       <c r="E393" s="16"/>
       <c r="F393" s="15"/>
     </row>
-    <row r="394" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="394" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C394" s="15"/>
       <c r="D394" s="15"/>
       <c r="E394" s="16"/>
       <c r="F394" s="15"/>
     </row>
-    <row r="395" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="395" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C395" s="15"/>
       <c r="D395" s="15"/>
       <c r="E395" s="16"/>
       <c r="F395" s="15"/>
     </row>
-    <row r="396" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="396" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C396" s="15"/>
       <c r="D396" s="15"/>
       <c r="E396" s="16"/>
       <c r="F396" s="15"/>
     </row>
-    <row r="397" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="397" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C397" s="15"/>
       <c r="D397" s="15"/>
       <c r="E397" s="16"/>
       <c r="F397" s="15"/>
     </row>
-    <row r="398" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="398" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C398" s="15"/>
       <c r="D398" s="15"/>
       <c r="E398" s="16"/>
       <c r="F398" s="15"/>
     </row>
-    <row r="399" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="399" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C399" s="15"/>
       <c r="D399" s="15"/>
       <c r="E399" s="16"/>
       <c r="F399" s="15"/>
     </row>
-    <row r="400" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="400" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C400" s="15"/>
       <c r="D400" s="15"/>
       <c r="E400" s="16"/>
       <c r="F400" s="15"/>
     </row>
-    <row r="401" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="401" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C401" s="15"/>
       <c r="D401" s="15"/>
       <c r="E401" s="16"/>
       <c r="F401" s="15"/>
     </row>
-    <row r="402" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="402" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C402" s="15"/>
       <c r="D402" s="15"/>
       <c r="E402" s="16"/>
       <c r="F402" s="15"/>
     </row>
-    <row r="403" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="403" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C403" s="15"/>
       <c r="D403" s="15"/>
       <c r="E403" s="16"/>
       <c r="F403" s="15"/>
     </row>
-    <row r="404" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="404" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C404" s="15"/>
       <c r="D404" s="15"/>
       <c r="E404" s="16"/>
       <c r="F404" s="15"/>
     </row>
-    <row r="405" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="405" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C405" s="15"/>
       <c r="D405" s="15"/>
       <c r="E405" s="16"/>
       <c r="F405" s="15"/>
     </row>
-    <row r="406" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="406" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C406" s="15"/>
       <c r="D406" s="15"/>
       <c r="E406" s="16"/>
       <c r="F406" s="15"/>
     </row>
-    <row r="407" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="407" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C407" s="15"/>
       <c r="D407" s="15"/>
       <c r="E407" s="16"/>
       <c r="F407" s="15"/>
     </row>
-    <row r="408" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="408" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C408" s="15"/>
       <c r="D408" s="15"/>
       <c r="E408" s="16"/>
       <c r="F408" s="15"/>
     </row>
-    <row r="409" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="409" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C409" s="15"/>
       <c r="D409" s="15"/>
       <c r="E409" s="16"/>
       <c r="F409" s="15"/>
     </row>
-    <row r="410" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="410" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C410" s="15"/>
       <c r="D410" s="15"/>
       <c r="E410" s="16"/>
       <c r="F410" s="15"/>
     </row>
-    <row r="411" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="411" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C411" s="15"/>
       <c r="D411" s="15"/>
       <c r="E411" s="16"/>
       <c r="F411" s="15"/>
     </row>
-    <row r="412" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="412" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C412" s="15"/>
       <c r="D412" s="15"/>
       <c r="E412" s="16"/>
       <c r="F412" s="15"/>
     </row>
-    <row r="413" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="413" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C413" s="15"/>
       <c r="D413" s="15"/>
       <c r="E413" s="16"/>
       <c r="F413" s="15"/>
     </row>
-    <row r="414" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="414" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C414" s="15"/>
       <c r="D414" s="15"/>
       <c r="E414" s="16"/>
       <c r="F414" s="15"/>
     </row>
-    <row r="415" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="415" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C415" s="15"/>
       <c r="D415" s="15"/>
       <c r="E415" s="16"/>
       <c r="F415" s="15"/>
     </row>
-    <row r="416" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="416" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C416" s="15"/>
       <c r="D416" s="15"/>
       <c r="E416" s="16"/>
       <c r="F416" s="15"/>
     </row>
-    <row r="417" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="417" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C417" s="15"/>
       <c r="D417" s="15"/>
       <c r="E417" s="16"/>
       <c r="F417" s="15"/>
     </row>
-    <row r="418" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="418" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C418" s="15"/>
       <c r="D418" s="15"/>
       <c r="E418" s="16"/>
       <c r="F418" s="15"/>
     </row>
-    <row r="419" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="419" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C419" s="15"/>
       <c r="D419" s="15"/>
       <c r="E419" s="16"/>
       <c r="F419" s="15"/>
     </row>
-    <row r="420" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="420" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C420" s="15"/>
       <c r="D420" s="15"/>
       <c r="E420" s="16"/>
       <c r="F420" s="15"/>
     </row>
-    <row r="421" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="421" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C421" s="15"/>
       <c r="D421" s="15"/>
       <c r="E421" s="16"/>
       <c r="F421" s="15"/>
     </row>
-    <row r="422" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="422" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C422" s="15"/>
       <c r="D422" s="15"/>
       <c r="E422" s="16"/>
       <c r="F422" s="15"/>
     </row>
-    <row r="423" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="423" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C423" s="15"/>
       <c r="D423" s="15"/>
       <c r="E423" s="16"/>
       <c r="F423" s="15"/>
     </row>
-    <row r="424" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="424" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C424" s="15"/>
       <c r="D424" s="15"/>
       <c r="E424" s="16"/>
       <c r="F424" s="15"/>
     </row>
-    <row r="425" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="425" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C425" s="15"/>
       <c r="D425" s="15"/>
       <c r="E425" s="16"/>
       <c r="F425" s="15"/>
     </row>
-    <row r="426" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="426" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C426" s="15"/>
       <c r="D426" s="15"/>
       <c r="E426" s="16"/>
       <c r="F426" s="15"/>
     </row>
-    <row r="427" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="427" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C427" s="15"/>
       <c r="D427" s="15"/>
       <c r="E427" s="16"/>
       <c r="F427" s="15"/>
     </row>
-    <row r="428" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="428" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C428" s="15"/>
       <c r="D428" s="15"/>
       <c r="E428" s="16"/>
       <c r="F428" s="15"/>
     </row>
-    <row r="429" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="429" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C429" s="15"/>
       <c r="D429" s="15"/>
       <c r="E429" s="16"/>
       <c r="F429" s="15"/>
     </row>
-    <row r="430" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="430" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C430" s="15"/>
       <c r="D430" s="15"/>
       <c r="E430" s="16"/>
       <c r="F430" s="15"/>
     </row>
-    <row r="431" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="431" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C431" s="15"/>
       <c r="D431" s="15"/>
       <c r="E431" s="16"/>
       <c r="F431" s="15"/>
     </row>
-    <row r="432" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="432" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C432" s="15"/>
       <c r="D432" s="15"/>
       <c r="E432" s="16"/>
       <c r="F432" s="15"/>
     </row>
-    <row r="433" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="433" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C433" s="15"/>
       <c r="D433" s="15"/>
       <c r="E433" s="16"/>
       <c r="F433" s="15"/>
     </row>
-    <row r="434" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="434" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C434" s="15"/>
       <c r="D434" s="15"/>
       <c r="E434" s="16"/>
       <c r="F434" s="15"/>
     </row>
-    <row r="435" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="435" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C435" s="15"/>
       <c r="D435" s="15"/>
       <c r="E435" s="16"/>
       <c r="F435" s="15"/>
     </row>
-    <row r="436" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="436" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C436" s="15"/>
       <c r="D436" s="15"/>
       <c r="E436" s="16"/>
       <c r="F436" s="15"/>
     </row>
-    <row r="437" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="437" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C437" s="15"/>
       <c r="D437" s="15"/>
       <c r="E437" s="16"/>
       <c r="F437" s="15"/>
     </row>
-    <row r="438" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="438" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C438" s="15"/>
       <c r="D438" s="15"/>
       <c r="E438" s="16"/>
       <c r="F438" s="15"/>
     </row>
-    <row r="439" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="439" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C439" s="15"/>
       <c r="D439" s="15"/>
       <c r="E439" s="16"/>
       <c r="F439" s="15"/>
     </row>
-    <row r="440" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="440" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C440" s="15"/>
       <c r="D440" s="15"/>
       <c r="E440" s="16"/>
       <c r="F440" s="15"/>
     </row>
-    <row r="441" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="441" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C441" s="15"/>
       <c r="D441" s="15"/>
       <c r="E441" s="16"/>
       <c r="F441" s="15"/>
     </row>
-    <row r="442" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="442" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C442" s="15"/>
       <c r="D442" s="15"/>
       <c r="E442" s="16"/>
       <c r="F442" s="15"/>
     </row>
-    <row r="443" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="443" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C443" s="15"/>
       <c r="D443" s="15"/>
       <c r="E443" s="16"/>
       <c r="F443" s="15"/>
     </row>
-    <row r="444" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="444" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C444" s="15"/>
       <c r="D444" s="15"/>
       <c r="E444" s="16"/>
       <c r="F444" s="15"/>
     </row>
-    <row r="445" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="445" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C445" s="15"/>
       <c r="D445" s="15"/>
       <c r="E445" s="16"/>
       <c r="F445" s="15"/>
     </row>
-    <row r="446" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="446" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C446" s="15"/>
       <c r="D446" s="15"/>
       <c r="E446" s="16"/>
       <c r="F446" s="15"/>
     </row>
-    <row r="447" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="447" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C447" s="15"/>
       <c r="D447" s="15"/>
       <c r="E447" s="16"/>
       <c r="F447" s="15"/>
     </row>
-    <row r="448" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="448" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C448" s="15"/>
       <c r="D448" s="15"/>
       <c r="E448" s="16"/>
       <c r="F448" s="15"/>
     </row>
-    <row r="449" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="449" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C449" s="15"/>
       <c r="D449" s="15"/>
       <c r="E449" s="16"/>
       <c r="F449" s="15"/>
     </row>
-    <row r="450" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="450" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C450" s="15"/>
       <c r="D450" s="15"/>
       <c r="E450" s="16"/>
       <c r="F450" s="15"/>
     </row>
-    <row r="451" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="451" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C451" s="15"/>
       <c r="D451" s="15"/>
       <c r="E451" s="16"/>
       <c r="F451" s="15"/>
     </row>
-    <row r="452" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="452" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C452" s="15"/>
       <c r="D452" s="15"/>
       <c r="E452" s="16"/>
       <c r="F452" s="15"/>
     </row>
-    <row r="453" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="453" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C453" s="15"/>
       <c r="D453" s="15"/>
       <c r="E453" s="16"/>
       <c r="F453" s="15"/>
     </row>
-    <row r="454" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="454" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C454" s="15"/>
       <c r="D454" s="15"/>
       <c r="E454" s="16"/>
       <c r="F454" s="15"/>
     </row>
-    <row r="455" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="455" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C455" s="15"/>
       <c r="D455" s="15"/>
       <c r="E455" s="16"/>
       <c r="F455" s="15"/>
     </row>
-    <row r="456" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="456" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C456" s="15"/>
       <c r="D456" s="15"/>
       <c r="E456" s="16"/>
       <c r="F456" s="15"/>
     </row>
-    <row r="457" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="457" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C457" s="15"/>
       <c r="D457" s="15"/>
       <c r="E457" s="16"/>
       <c r="F457" s="15"/>
     </row>
-    <row r="458" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="458" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C458" s="15"/>
       <c r="D458" s="15"/>
       <c r="E458" s="16"/>
       <c r="F458" s="15"/>
     </row>
-    <row r="459" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="459" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C459" s="15"/>
       <c r="D459" s="15"/>
       <c r="E459" s="16"/>
       <c r="F459" s="15"/>
     </row>
-    <row r="460" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="460" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C460" s="15"/>
       <c r="D460" s="15"/>
       <c r="E460" s="16"/>
       <c r="F460" s="15"/>
     </row>
-    <row r="461" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="461" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C461" s="15"/>
       <c r="D461" s="15"/>
       <c r="E461" s="16"/>
       <c r="F461" s="15"/>
     </row>
-    <row r="462" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="462" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C462" s="15"/>
       <c r="D462" s="15"/>
       <c r="E462" s="16"/>
       <c r="F462" s="15"/>
     </row>
-    <row r="463" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="463" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C463" s="15"/>
       <c r="D463" s="15"/>
       <c r="E463" s="16"/>
       <c r="F463" s="15"/>
     </row>
-    <row r="464" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="464" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C464" s="15"/>
       <c r="D464" s="15"/>
       <c r="E464" s="16"/>
       <c r="F464" s="15"/>
     </row>
-    <row r="465" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="465" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C465" s="15"/>
       <c r="D465" s="15"/>
       <c r="E465" s="16"/>
       <c r="F465" s="15"/>
     </row>
-    <row r="466" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="466" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C466" s="15"/>
       <c r="D466" s="15"/>
       <c r="E466" s="16"/>
       <c r="F466" s="15"/>
     </row>
-    <row r="467" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="467" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C467" s="15"/>
       <c r="D467" s="15"/>
       <c r="E467" s="16"/>
       <c r="F467" s="15"/>
     </row>
-    <row r="468" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="468" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C468" s="15"/>
       <c r="D468" s="15"/>
       <c r="E468" s="16"/>
       <c r="F468" s="15"/>
     </row>
-    <row r="469" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="469" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C469" s="15"/>
       <c r="D469" s="15"/>
       <c r="E469" s="16"/>
       <c r="F469" s="15"/>
     </row>
-    <row r="470" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="470" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C470" s="15"/>
       <c r="D470" s="15"/>
       <c r="E470" s="16"/>
       <c r="F470" s="15"/>
     </row>
-    <row r="471" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="471" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C471" s="15"/>
       <c r="D471" s="15"/>
       <c r="E471" s="16"/>
       <c r="F471" s="15"/>
     </row>
-    <row r="472" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="472" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C472" s="15"/>
       <c r="D472" s="15"/>
       <c r="E472" s="16"/>
       <c r="F472" s="15"/>
     </row>
-    <row r="473" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="473" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C473" s="15"/>
       <c r="D473" s="15"/>
       <c r="E473" s="16"/>
       <c r="F473" s="15"/>
     </row>
-    <row r="474" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="474" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C474" s="15"/>
       <c r="D474" s="15"/>
       <c r="E474" s="16"/>
       <c r="F474" s="15"/>
     </row>
-    <row r="475" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="475" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C475" s="15"/>
       <c r="D475" s="15"/>
       <c r="E475" s="16"/>
       <c r="F475" s="15"/>
     </row>
-    <row r="476" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="476" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C476" s="15"/>
       <c r="D476" s="15"/>
       <c r="E476" s="16"/>
       <c r="F476" s="15"/>
     </row>
-    <row r="477" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="477" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C477" s="15"/>
       <c r="D477" s="15"/>
       <c r="E477" s="16"/>
       <c r="F477" s="15"/>
     </row>
-    <row r="478" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="478" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C478" s="15"/>
       <c r="D478" s="15"/>
       <c r="E478" s="16"/>
       <c r="F478" s="15"/>
     </row>
-    <row r="479" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="479" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C479" s="15"/>
       <c r="D479" s="15"/>
       <c r="E479" s="16"/>
       <c r="F479" s="15"/>
     </row>
-    <row r="480" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="480" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C480" s="15"/>
       <c r="D480" s="15"/>
       <c r="E480" s="16"/>
       <c r="F480" s="15"/>
     </row>
-    <row r="481" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="481" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C481" s="15"/>
       <c r="D481" s="15"/>
       <c r="E481" s="16"/>
       <c r="F481" s="15"/>
     </row>
-    <row r="482" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="482" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C482" s="15"/>
       <c r="D482" s="15"/>
       <c r="E482" s="16"/>
       <c r="F482" s="15"/>
     </row>
-    <row r="483" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="483" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C483" s="15"/>
       <c r="D483" s="15"/>
       <c r="E483" s="16"/>
       <c r="F483" s="15"/>
     </row>
-    <row r="484" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="484" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C484" s="15"/>
       <c r="D484" s="15"/>
       <c r="E484" s="16"/>
       <c r="F484" s="15"/>
     </row>
-    <row r="485" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="485" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C485" s="15"/>
       <c r="D485" s="15"/>
       <c r="E485" s="16"/>
       <c r="F485" s="15"/>
     </row>
-    <row r="486" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="486" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C486" s="15"/>
       <c r="D486" s="15"/>
       <c r="E486" s="16"/>
       <c r="F486" s="15"/>
     </row>
-    <row r="487" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="487" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C487" s="15"/>
       <c r="D487" s="15"/>
       <c r="E487" s="16"/>
       <c r="F487" s="15"/>
     </row>
-    <row r="488" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="488" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C488" s="15"/>
       <c r="D488" s="15"/>
       <c r="E488" s="16"/>
       <c r="F488" s="15"/>
     </row>
-    <row r="489" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="489" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C489" s="15"/>
       <c r="D489" s="15"/>
       <c r="E489" s="16"/>
       <c r="F489" s="15"/>
     </row>
-    <row r="490" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="490" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C490" s="15"/>
       <c r="D490" s="15"/>
       <c r="E490" s="16"/>
       <c r="F490" s="15"/>
     </row>
-    <row r="491" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="491" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C491" s="15"/>
       <c r="D491" s="15"/>
       <c r="E491" s="16"/>
       <c r="F491" s="15"/>
     </row>
-    <row r="492" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="492" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C492" s="15"/>
       <c r="D492" s="15"/>
       <c r="E492" s="16"/>
       <c r="F492" s="15"/>
     </row>
-    <row r="493" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="493" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C493" s="15"/>
       <c r="D493" s="15"/>
       <c r="E493" s="16"/>
       <c r="F493" s="15"/>
     </row>
-    <row r="494" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="494" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C494" s="15"/>
       <c r="D494" s="15"/>
       <c r="E494" s="16"/>
       <c r="F494" s="15"/>
     </row>
-    <row r="495" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="495" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C495" s="15"/>
       <c r="D495" s="15"/>
       <c r="E495" s="16"/>
       <c r="F495" s="15"/>
     </row>
-    <row r="496" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="496" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C496" s="15"/>
       <c r="D496" s="15"/>
       <c r="E496" s="16"/>
       <c r="F496" s="15"/>
     </row>
-    <row r="497" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="497" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C497" s="15"/>
       <c r="D497" s="15"/>
       <c r="E497" s="16"/>
       <c r="F497" s="15"/>
     </row>
-    <row r="498" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="498" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C498" s="15"/>
       <c r="D498" s="15"/>
       <c r="E498" s="16"/>
       <c r="F498" s="15"/>
     </row>
-    <row r="499" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="499" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C499" s="15"/>
       <c r="D499" s="15"/>
       <c r="E499" s="16"/>
       <c r="F499" s="15"/>
     </row>
-    <row r="500" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="500" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C500" s="15"/>
       <c r="D500" s="15"/>
       <c r="E500" s="16"/>
       <c r="F500" s="15"/>
     </row>
-    <row r="501" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="501" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C501" s="15"/>
       <c r="D501" s="15"/>
       <c r="E501" s="16"/>
       <c r="F501" s="15"/>
     </row>
-    <row r="502" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="502" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C502" s="15"/>
       <c r="D502" s="15"/>
       <c r="E502" s="16"/>
       <c r="F502" s="15"/>
     </row>
-    <row r="503" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="503" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C503" s="15"/>
       <c r="D503" s="15"/>
       <c r="E503" s="16"/>
       <c r="F503" s="15"/>
     </row>
-    <row r="504" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="504" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C504" s="15"/>
       <c r="D504" s="15"/>
       <c r="E504" s="16"/>
       <c r="F504" s="15"/>
     </row>
-    <row r="505" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="505" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C505" s="15"/>
       <c r="D505" s="15"/>
       <c r="E505" s="16"/>
       <c r="F505" s="15"/>
     </row>
-    <row r="506" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="506" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C506" s="15"/>
       <c r="D506" s="15"/>
       <c r="E506" s="16"/>
       <c r="F506" s="15"/>
     </row>
-    <row r="507" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="507" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C507" s="15"/>
       <c r="D507" s="15"/>
       <c r="E507" s="16"/>
       <c r="F507" s="15"/>
     </row>
-    <row r="508" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="508" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C508" s="15"/>
       <c r="D508" s="15"/>
       <c r="E508" s="16"/>
       <c r="F508" s="15"/>
     </row>
-    <row r="509" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="509" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C509" s="15"/>
       <c r="D509" s="15"/>
       <c r="E509" s="16"/>
       <c r="F509" s="15"/>
     </row>
-    <row r="510" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="510" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C510" s="15"/>
       <c r="D510" s="15"/>
       <c r="E510" s="16"/>
       <c r="F510" s="15"/>
     </row>
-    <row r="511" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="511" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C511" s="15"/>
       <c r="D511" s="15"/>
       <c r="E511" s="16"/>
       <c r="F511" s="15"/>
     </row>
-    <row r="512" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="512" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C512" s="15"/>
       <c r="D512" s="15"/>
       <c r="E512" s="16"/>
       <c r="F512" s="15"/>
     </row>
-    <row r="513" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="513" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C513" s="15"/>
       <c r="D513" s="15"/>
       <c r="E513" s="16"/>
       <c r="F513" s="15"/>
     </row>
-    <row r="514" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="514" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C514" s="15"/>
       <c r="D514" s="15"/>
       <c r="E514" s="16"/>
       <c r="F514" s="15"/>
     </row>
-    <row r="515" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="515" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C515" s="15"/>
       <c r="D515" s="15"/>
       <c r="E515" s="16"/>
       <c r="F515" s="15"/>
     </row>
-    <row r="516" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="516" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C516" s="15"/>
       <c r="D516" s="15"/>
       <c r="E516" s="16"/>
       <c r="F516" s="15"/>
     </row>
-    <row r="517" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="517" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C517" s="15"/>
       <c r="D517" s="15"/>
       <c r="E517" s="16"/>
       <c r="F517" s="15"/>
     </row>
-    <row r="518" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="518" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C518" s="15"/>
       <c r="D518" s="15"/>
       <c r="E518" s="16"/>
       <c r="F518" s="15"/>
     </row>
-    <row r="519" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="519" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C519" s="15"/>
       <c r="D519" s="15"/>
       <c r="E519" s="16"/>
       <c r="F519" s="15"/>
     </row>
-    <row r="520" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="520" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C520" s="15"/>
       <c r="D520" s="15"/>
       <c r="E520" s="16"/>
       <c r="F520" s="15"/>
     </row>
-    <row r="521" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="521" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C521" s="15"/>
       <c r="D521" s="15"/>
       <c r="E521" s="16"/>
       <c r="F521" s="15"/>
     </row>
-    <row r="522" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="522" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C522" s="15"/>
       <c r="D522" s="15"/>
       <c r="E522" s="16"/>
       <c r="F522" s="15"/>
     </row>
-    <row r="523" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="523" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C523" s="15"/>
       <c r="D523" s="15"/>
       <c r="E523" s="16"/>
       <c r="F523" s="15"/>
     </row>
-    <row r="524" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="524" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C524" s="15"/>
       <c r="D524" s="15"/>
       <c r="E524" s="16"/>
       <c r="F524" s="15"/>
     </row>
-    <row r="525" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="525" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C525" s="15"/>
       <c r="D525" s="15"/>
       <c r="E525" s="16"/>
       <c r="F525" s="15"/>
     </row>
-    <row r="526" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="526" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C526" s="15"/>
       <c r="D526" s="15"/>
       <c r="E526" s="16"/>
       <c r="F526" s="15"/>
     </row>
-    <row r="527" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="527" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C527" s="15"/>
       <c r="D527" s="15"/>
       <c r="E527" s="16"/>
       <c r="F527" s="15"/>
     </row>
-    <row r="528" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="528" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C528" s="15"/>
       <c r="D528" s="15"/>
       <c r="E528" s="16"/>
       <c r="F528" s="15"/>
     </row>
-    <row r="529" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="529" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C529" s="15"/>
       <c r="D529" s="15"/>
       <c r="E529" s="16"/>
       <c r="F529" s="15"/>
     </row>
-    <row r="530" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="530" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C530" s="15"/>
       <c r="D530" s="15"/>
       <c r="E530" s="16"/>
       <c r="F530" s="15"/>
     </row>
-    <row r="531" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="531" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C531" s="15"/>
       <c r="D531" s="15"/>
       <c r="E531" s="16"/>
       <c r="F531" s="15"/>
     </row>
-    <row r="532" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="532" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C532" s="15"/>
       <c r="D532" s="15"/>
       <c r="E532" s="16"/>
       <c r="F532" s="15"/>
     </row>
-    <row r="533" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="533" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C533" s="15"/>
       <c r="D533" s="15"/>
       <c r="E533" s="16"/>
       <c r="F533" s="15"/>
     </row>
-    <row r="534" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="534" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C534" s="15"/>
       <c r="D534" s="15"/>
       <c r="E534" s="16"/>
       <c r="F534" s="15"/>
     </row>
-    <row r="535" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="535" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C535" s="15"/>
       <c r="D535" s="15"/>
       <c r="E535" s="16"/>
       <c r="F535" s="15"/>
     </row>
-    <row r="536" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="536" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C536" s="15"/>
       <c r="D536" s="15"/>
       <c r="E536" s="16"/>
       <c r="F536" s="15"/>
     </row>
-    <row r="537" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="537" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C537" s="15"/>
       <c r="D537" s="15"/>
       <c r="E537" s="16"/>
       <c r="F537" s="15"/>
     </row>
-    <row r="538" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="538" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C538" s="15"/>
       <c r="D538" s="15"/>
       <c r="E538" s="16"/>
       <c r="F538" s="15"/>
     </row>
-    <row r="539" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="539" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C539" s="15"/>
       <c r="D539" s="15"/>
       <c r="E539" s="16"/>
       <c r="F539" s="15"/>
     </row>
-    <row r="540" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="540" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C540" s="15"/>
       <c r="D540" s="15"/>
       <c r="E540" s="16"/>
       <c r="F540" s="15"/>
     </row>
-    <row r="541" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="541" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C541" s="15"/>
       <c r="D541" s="15"/>
       <c r="E541" s="16"/>
       <c r="F541" s="15"/>
     </row>
-    <row r="542" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="542" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C542" s="15"/>
       <c r="D542" s="15"/>
       <c r="E542" s="16"/>
       <c r="F542" s="15"/>
     </row>
-    <row r="543" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="543" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C543" s="15"/>
       <c r="D543" s="15"/>
       <c r="E543" s="16"/>
       <c r="F543" s="15"/>
     </row>
-    <row r="544" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="544" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C544" s="15"/>
       <c r="D544" s="15"/>
       <c r="E544" s="16"/>
       <c r="F544" s="15"/>
     </row>
-    <row r="545" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="545" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C545" s="15"/>
       <c r="D545" s="15"/>
       <c r="E545" s="16"/>
       <c r="F545" s="15"/>
     </row>
-    <row r="546" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="546" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C546" s="15"/>
       <c r="D546" s="15"/>
       <c r="E546" s="16"/>
       <c r="F546" s="15"/>
     </row>
-    <row r="547" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="547" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C547" s="15"/>
       <c r="D547" s="15"/>
       <c r="E547" s="16"/>
       <c r="F547" s="15"/>
     </row>
-    <row r="548" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="548" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C548" s="15"/>
       <c r="D548" s="15"/>
       <c r="E548" s="16"/>
       <c r="F548" s="15"/>
     </row>
-    <row r="549" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="549" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C549" s="15"/>
       <c r="D549" s="15"/>
       <c r="E549" s="16"/>
       <c r="F549" s="15"/>
     </row>
-    <row r="550" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="550" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C550" s="15"/>
       <c r="D550" s="15"/>
       <c r="E550" s="16"/>
       <c r="F550" s="15"/>
     </row>
-    <row r="551" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="551" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C551" s="15"/>
       <c r="D551" s="15"/>
       <c r="E551" s="16"/>
       <c r="F551" s="15"/>
     </row>
-    <row r="552" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="552" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C552" s="15"/>
       <c r="D552" s="15"/>
       <c r="E552" s="16"/>
       <c r="F552" s="15"/>
     </row>
-    <row r="553" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="553" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C553" s="15"/>
       <c r="D553" s="15"/>
       <c r="E553" s="16"/>
       <c r="F553" s="15"/>
     </row>
-    <row r="554" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="554" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C554" s="15"/>
       <c r="D554" s="15"/>
       <c r="E554" s="16"/>
       <c r="F554" s="15"/>
     </row>
-    <row r="555" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="555" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C555" s="15"/>
       <c r="D555" s="15"/>
       <c r="E555" s="16"/>
       <c r="F555" s="15"/>
     </row>
-    <row r="556" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="556" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C556" s="15"/>
       <c r="D556" s="15"/>
       <c r="E556" s="16"/>
       <c r="F556" s="15"/>
     </row>
-    <row r="557" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="557" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C557" s="15"/>
       <c r="D557" s="15"/>
       <c r="E557" s="16"/>
       <c r="F557" s="15"/>
     </row>
-    <row r="558" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="558" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C558" s="15"/>
       <c r="D558" s="15"/>
       <c r="E558" s="16"/>
       <c r="F558" s="15"/>
     </row>
-    <row r="559" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="559" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C559" s="15"/>
       <c r="D559" s="15"/>
       <c r="E559" s="16"/>
       <c r="F559" s="15"/>
     </row>
-    <row r="560" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="560" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C560" s="15"/>
       <c r="D560" s="15"/>
       <c r="E560" s="16"/>
       <c r="F560" s="15"/>
     </row>
-    <row r="561" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="561" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C561" s="15"/>
       <c r="D561" s="15"/>
       <c r="E561" s="16"/>
       <c r="F561" s="15"/>
     </row>
-    <row r="562" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="562" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C562" s="15"/>
       <c r="D562" s="15"/>
       <c r="E562" s="16"/>
       <c r="F562" s="15"/>
     </row>
-    <row r="563" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="563" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C563" s="15"/>
       <c r="D563" s="15"/>
       <c r="E563" s="16"/>
       <c r="F563" s="15"/>
     </row>
-    <row r="564" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="564" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C564" s="15"/>
       <c r="D564" s="15"/>
       <c r="E564" s="16"/>
       <c r="F564" s="15"/>
     </row>
-    <row r="565" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="565" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C565" s="15"/>
       <c r="D565" s="15"/>
       <c r="E565" s="16"/>
       <c r="F565" s="15"/>
     </row>
-    <row r="566" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="566" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C566" s="15"/>
       <c r="D566" s="15"/>
       <c r="E566" s="16"/>
       <c r="F566" s="15"/>
     </row>
-    <row r="567" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="567" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C567" s="15"/>
       <c r="D567" s="15"/>
       <c r="E567" s="16"/>
       <c r="F567" s="15"/>
     </row>
-    <row r="568" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="568" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C568" s="15"/>
       <c r="D568" s="15"/>
       <c r="E568" s="16"/>
       <c r="F568" s="15"/>
     </row>
-    <row r="569" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="569" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C569" s="15"/>
       <c r="D569" s="15"/>
       <c r="E569" s="16"/>
       <c r="F569" s="15"/>
     </row>
-    <row r="570" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="570" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C570" s="15"/>
       <c r="D570" s="15"/>
       <c r="E570" s="16"/>
       <c r="F570" s="15"/>
     </row>
-    <row r="571" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="571" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C571" s="15"/>
       <c r="D571" s="15"/>
       <c r="E571" s="16"/>
       <c r="F571" s="15"/>
     </row>
-    <row r="572" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="572" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C572" s="15"/>
       <c r="D572" s="15"/>
       <c r="E572" s="16"/>
       <c r="F572" s="15"/>
     </row>
-    <row r="573" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="573" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C573" s="15"/>
       <c r="D573" s="15"/>
       <c r="E573" s="16"/>
       <c r="F573" s="15"/>
     </row>
-    <row r="574" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="574" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C574" s="15"/>
       <c r="D574" s="15"/>
       <c r="E574" s="16"/>
       <c r="F574" s="15"/>
     </row>
-    <row r="575" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="575" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C575" s="15"/>
       <c r="D575" s="15"/>
       <c r="E575" s="16"/>
       <c r="F575" s="15"/>
     </row>
-    <row r="576" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="576" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C576" s="15"/>
       <c r="D576" s="15"/>
       <c r="E576" s="16"/>
       <c r="F576" s="15"/>
     </row>
-    <row r="577" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="577" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C577" s="15"/>
       <c r="D577" s="15"/>
       <c r="E577" s="16"/>
       <c r="F577" s="15"/>
     </row>
-    <row r="578" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="578" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C578" s="15"/>
       <c r="D578" s="15"/>
       <c r="E578" s="16"/>
       <c r="F578" s="15"/>
     </row>
-    <row r="579" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="579" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C579" s="15"/>
       <c r="D579" s="15"/>
       <c r="E579" s="16"/>
       <c r="F579" s="15"/>
     </row>
-    <row r="580" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="580" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C580" s="15"/>
       <c r="D580" s="15"/>
       <c r="E580" s="16"/>
       <c r="F580" s="15"/>
     </row>
-    <row r="581" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="581" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C581" s="15"/>
       <c r="D581" s="15"/>
       <c r="E581" s="16"/>
       <c r="F581" s="15"/>
     </row>
-    <row r="582" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="582" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C582" s="15"/>
       <c r="D582" s="15"/>
       <c r="E582" s="16"/>
       <c r="F582" s="15"/>
     </row>
-    <row r="583" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="583" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C583" s="15"/>
       <c r="D583" s="15"/>
       <c r="E583" s="16"/>
       <c r="F583" s="15"/>
     </row>
-    <row r="584" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="584" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C584" s="15"/>
       <c r="D584" s="15"/>
       <c r="E584" s="16"/>
       <c r="F584" s="15"/>
     </row>
-    <row r="585" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="585" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C585" s="15"/>
       <c r="D585" s="15"/>
       <c r="E585" s="16"/>
       <c r="F585" s="15"/>
     </row>
-    <row r="586" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="586" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C586" s="15"/>
       <c r="D586" s="15"/>
       <c r="E586" s="16"/>
       <c r="F586" s="15"/>
     </row>
-    <row r="587" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="587" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C587" s="15"/>
       <c r="D587" s="15"/>
       <c r="E587" s="16"/>
       <c r="F587" s="15"/>
     </row>
-    <row r="588" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="588" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C588" s="15"/>
       <c r="D588" s="15"/>
       <c r="E588" s="16"/>
       <c r="F588" s="15"/>
     </row>
-    <row r="589" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="589" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C589" s="15"/>
       <c r="D589" s="15"/>
       <c r="E589" s="16"/>
       <c r="F589" s="15"/>
     </row>
-    <row r="590" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="590" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C590" s="15"/>
       <c r="D590" s="15"/>
       <c r="E590" s="16"/>
       <c r="F590" s="15"/>
     </row>
-    <row r="591" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="591" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C591" s="15"/>
       <c r="D591" s="15"/>
       <c r="E591" s="16"/>
       <c r="F591" s="15"/>
     </row>
-    <row r="592" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="592" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C592" s="15"/>
       <c r="D592" s="15"/>
       <c r="E592" s="16"/>
       <c r="F592" s="15"/>
     </row>
-    <row r="593" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="593" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C593" s="15"/>
       <c r="D593" s="15"/>
       <c r="E593" s="16"/>
       <c r="F593" s="15"/>
     </row>
-    <row r="594" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="594" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C594" s="15"/>
       <c r="D594" s="15"/>
       <c r="E594" s="16"/>
       <c r="F594" s="15"/>
     </row>
-    <row r="595" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="595" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C595" s="15"/>
       <c r="D595" s="15"/>
       <c r="E595" s="16"/>
       <c r="F595" s="15"/>
     </row>
-    <row r="596" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="596" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C596" s="15"/>
       <c r="D596" s="15"/>
       <c r="E596" s="16"/>
       <c r="F596" s="15"/>
     </row>
-    <row r="597" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="597" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C597" s="15"/>
       <c r="D597" s="15"/>
       <c r="E597" s="16"/>
       <c r="F597" s="15"/>
     </row>
-    <row r="598" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="598" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C598" s="15"/>
       <c r="D598" s="15"/>
       <c r="E598" s="16"/>
       <c r="F598" s="15"/>
     </row>
-    <row r="599" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="599" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C599" s="15"/>
       <c r="D599" s="15"/>
       <c r="E599" s="16"/>
       <c r="F599" s="15"/>
     </row>
-    <row r="600" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="600" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C600" s="15"/>
       <c r="D600" s="15"/>
       <c r="E600" s="16"/>
       <c r="F600" s="15"/>
     </row>
-    <row r="601" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="601" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C601" s="15"/>
       <c r="D601" s="15"/>
       <c r="E601" s="16"/>
       <c r="F601" s="15"/>
     </row>
-    <row r="602" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="602" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C602" s="15"/>
       <c r="D602" s="15"/>
       <c r="E602" s="16"/>
       <c r="F602" s="15"/>
     </row>
-    <row r="603" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="603" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C603" s="15"/>
       <c r="D603" s="15"/>
       <c r="E603" s="16"/>
       <c r="F603" s="15"/>
     </row>
-    <row r="604" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="604" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C604" s="15"/>
       <c r="D604" s="15"/>
       <c r="E604" s="16"/>
       <c r="F604" s="15"/>
     </row>
-    <row r="605" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="605" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C605" s="15"/>
       <c r="D605" s="15"/>
       <c r="E605" s="16"/>
       <c r="F605" s="15"/>
     </row>
-    <row r="606" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="606" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C606" s="15"/>
       <c r="D606" s="15"/>
       <c r="E606" s="16"/>
       <c r="F606" s="15"/>
     </row>
-    <row r="607" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="607" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C607" s="15"/>
       <c r="D607" s="15"/>
       <c r="E607" s="16"/>
       <c r="F607" s="15"/>
     </row>
-    <row r="608" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="608" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C608" s="15"/>
       <c r="D608" s="15"/>
       <c r="E608" s="16"/>
       <c r="F608" s="15"/>
     </row>
-    <row r="609" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="609" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C609" s="15"/>
       <c r="D609" s="15"/>
       <c r="E609" s="16"/>
       <c r="F609" s="15"/>
     </row>
-    <row r="610" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="610" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C610" s="15"/>
       <c r="D610" s="15"/>
       <c r="E610" s="16"/>
       <c r="F610" s="15"/>
     </row>
-    <row r="611" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="611" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C611" s="15"/>
       <c r="D611" s="15"/>
       <c r="E611" s="16"/>
       <c r="F611" s="15"/>
     </row>
-    <row r="612" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="612" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C612" s="15"/>
       <c r="D612" s="15"/>
       <c r="E612" s="16"/>
       <c r="F612" s="15"/>
     </row>
-    <row r="613" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="613" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C613" s="15"/>
       <c r="D613" s="15"/>
       <c r="E613" s="16"/>
       <c r="F613" s="15"/>
     </row>
-    <row r="614" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="614" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C614" s="15"/>
       <c r="D614" s="15"/>
       <c r="E614" s="16"/>
       <c r="F614" s="15"/>
     </row>
-    <row r="615" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="615" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C615" s="15"/>
       <c r="D615" s="15"/>
       <c r="E615" s="16"/>
       <c r="F615" s="15"/>
     </row>
-    <row r="616" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="616" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C616" s="15"/>
       <c r="D616" s="15"/>
       <c r="E616" s="16"/>
       <c r="F616" s="15"/>
     </row>
-    <row r="617" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="617" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C617" s="15"/>
       <c r="D617" s="15"/>
       <c r="E617" s="16"/>
       <c r="F617" s="15"/>
     </row>
-    <row r="618" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="618" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C618" s="15"/>
       <c r="D618" s="15"/>
       <c r="E618" s="16"/>
       <c r="F618" s="15"/>
     </row>
-    <row r="619" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="619" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C619" s="15"/>
       <c r="D619" s="15"/>
       <c r="E619" s="16"/>
       <c r="F619" s="15"/>
     </row>
-    <row r="620" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="620" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C620" s="15"/>
       <c r="D620" s="15"/>
       <c r="E620" s="16"/>
       <c r="F620" s="15"/>
     </row>
-    <row r="621" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="621" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C621" s="15"/>
       <c r="D621" s="15"/>
       <c r="E621" s="16"/>
       <c r="F621" s="15"/>
     </row>
-    <row r="622" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="622" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C622" s="15"/>
       <c r="D622" s="15"/>
       <c r="E622" s="16"/>
       <c r="F622" s="15"/>
     </row>
-    <row r="623" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="623" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C623" s="15"/>
       <c r="D623" s="15"/>
       <c r="E623" s="16"/>
       <c r="F623" s="15"/>
     </row>
-    <row r="624" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="624" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C624" s="15"/>
       <c r="D624" s="15"/>
       <c r="E624" s="16"/>
       <c r="F624" s="15"/>
     </row>
-    <row r="625" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="625" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C625" s="15"/>
       <c r="D625" s="15"/>
       <c r="E625" s="16"/>
       <c r="F625" s="15"/>
     </row>
-    <row r="626" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="626" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C626" s="15"/>
       <c r="D626" s="15"/>
       <c r="E626" s="16"/>
       <c r="F626" s="15"/>
     </row>
-    <row r="627" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="627" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C627" s="15"/>
       <c r="D627" s="15"/>
       <c r="E627" s="16"/>
       <c r="F627" s="15"/>
     </row>
-    <row r="628" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="628" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C628" s="15"/>
       <c r="D628" s="15"/>
       <c r="E628" s="16"/>
       <c r="F628" s="15"/>
     </row>
-    <row r="629" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="629" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C629" s="15"/>
       <c r="D629" s="15"/>
       <c r="E629" s="16"/>
       <c r="F629" s="15"/>
     </row>
-    <row r="630" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="630" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C630" s="15"/>
       <c r="D630" s="15"/>
       <c r="E630" s="16"/>
       <c r="F630" s="15"/>
     </row>
-    <row r="631" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="631" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C631" s="15"/>
       <c r="D631" s="15"/>
       <c r="E631" s="16"/>
       <c r="F631" s="15"/>
     </row>
-    <row r="632" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="632" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C632" s="15"/>
       <c r="D632" s="15"/>
       <c r="E632" s="16"/>
       <c r="F632" s="15"/>
     </row>
-    <row r="633" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="633" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C633" s="15"/>
       <c r="D633" s="15"/>
       <c r="E633" s="16"/>
       <c r="F633" s="15"/>
     </row>
-    <row r="634" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="634" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C634" s="15"/>
       <c r="D634" s="15"/>
       <c r="E634" s="16"/>
       <c r="F634" s="15"/>
     </row>
-    <row r="635" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="635" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C635" s="15"/>
       <c r="D635" s="15"/>
       <c r="E635" s="16"/>
       <c r="F635" s="15"/>
     </row>
-    <row r="636" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="636" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C636" s="15"/>
       <c r="D636" s="15"/>
       <c r="E636" s="16"/>
       <c r="F636" s="15"/>
     </row>
-    <row r="637" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="637" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C637" s="15"/>
       <c r="D637" s="15"/>
       <c r="E637" s="16"/>
       <c r="F637" s="15"/>
     </row>
-    <row r="638" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="638" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C638" s="15"/>
       <c r="D638" s="15"/>
       <c r="E638" s="16"/>
       <c r="F638" s="15"/>
     </row>
-    <row r="639" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="639" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C639" s="15"/>
       <c r="D639" s="15"/>
       <c r="E639" s="16"/>
       <c r="F639" s="15"/>
     </row>
-    <row r="640" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="640" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C640" s="15"/>
       <c r="D640" s="15"/>
       <c r="E640" s="16"/>
       <c r="F640" s="15"/>
     </row>
-    <row r="641" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="641" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C641" s="15"/>
       <c r="D641" s="15"/>
       <c r="E641" s="16"/>
       <c r="F641" s="15"/>
     </row>
-    <row r="642" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="642" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C642" s="15"/>
       <c r="D642" s="15"/>
       <c r="E642" s="16"/>
       <c r="F642" s="15"/>
     </row>
-    <row r="643" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="643" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C643" s="15"/>
       <c r="D643" s="15"/>
       <c r="E643" s="16"/>
       <c r="F643" s="15"/>
     </row>
-    <row r="644" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="644" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C644" s="15"/>
       <c r="D644" s="15"/>
       <c r="E644" s="16"/>
       <c r="F644" s="15"/>
     </row>
-    <row r="645" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="645" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C645" s="15"/>
       <c r="D645" s="15"/>
       <c r="E645" s="16"/>
       <c r="F645" s="15"/>
     </row>
-    <row r="646" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="646" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C646" s="15"/>
       <c r="D646" s="15"/>
       <c r="E646" s="16"/>
       <c r="F646" s="15"/>
     </row>
-    <row r="647" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="647" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C647" s="15"/>
       <c r="D647" s="15"/>
       <c r="E647" s="16"/>
       <c r="F647" s="15"/>
     </row>
-    <row r="648" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="648" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C648" s="15"/>
       <c r="D648" s="15"/>
       <c r="E648" s="16"/>
       <c r="F648" s="15"/>
     </row>
-    <row r="649" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="649" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C649" s="15"/>
       <c r="D649" s="15"/>
       <c r="E649" s="16"/>
       <c r="F649" s="15"/>
     </row>
-    <row r="650" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="650" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C650" s="15"/>
       <c r="D650" s="15"/>
       <c r="E650" s="16"/>
       <c r="F650" s="15"/>
     </row>
-    <row r="651" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="651" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C651" s="15"/>
       <c r="D651" s="15"/>
       <c r="E651" s="16"/>
       <c r="F651" s="15"/>
     </row>
-    <row r="652" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="652" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C652" s="15"/>
       <c r="D652" s="15"/>
       <c r="E652" s="16"/>
       <c r="F652" s="15"/>
     </row>
-    <row r="653" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="653" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C653" s="15"/>
       <c r="D653" s="15"/>
       <c r="E653" s="16"/>
       <c r="F653" s="15"/>
     </row>
-    <row r="654" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="654" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C654" s="15"/>
       <c r="D654" s="15"/>
       <c r="E654" s="16"/>
       <c r="F654" s="15"/>
     </row>
-    <row r="655" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="655" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C655" s="15"/>
       <c r="D655" s="15"/>
       <c r="E655" s="16"/>
       <c r="F655" s="15"/>
     </row>
-    <row r="656" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="656" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C656" s="15"/>
       <c r="D656" s="15"/>
       <c r="E656" s="16"/>
       <c r="F656" s="15"/>
     </row>
-    <row r="657" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="657" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C657" s="15"/>
       <c r="D657" s="15"/>
       <c r="E657" s="16"/>
       <c r="F657" s="15"/>
     </row>
-    <row r="658" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="658" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C658" s="15"/>
       <c r="D658" s="15"/>
       <c r="E658" s="16"/>
       <c r="F658" s="15"/>
     </row>
-    <row r="659" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="659" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C659" s="15"/>
       <c r="D659" s="15"/>
       <c r="E659" s="16"/>
       <c r="F659" s="15"/>
     </row>
-    <row r="660" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="660" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C660" s="15"/>
       <c r="D660" s="15"/>
       <c r="E660" s="16"/>
       <c r="F660" s="15"/>
     </row>
-    <row r="661" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="661" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C661" s="15"/>
       <c r="D661" s="15"/>
       <c r="E661" s="16"/>
       <c r="F661" s="15"/>
     </row>
-    <row r="662" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="662" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C662" s="15"/>
       <c r="D662" s="15"/>
       <c r="E662" s="16"/>
       <c r="F662" s="15"/>
     </row>
-    <row r="663" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="663" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C663" s="15"/>
       <c r="D663" s="15"/>
       <c r="E663" s="16"/>
       <c r="F663" s="15"/>
     </row>
-    <row r="664" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="664" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C664" s="15"/>
       <c r="D664" s="15"/>
       <c r="E664" s="16"/>
       <c r="F664" s="15"/>
     </row>
-    <row r="665" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="665" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C665" s="15"/>
       <c r="D665" s="15"/>
       <c r="E665" s="16"/>
       <c r="F665" s="15"/>
     </row>
-    <row r="666" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="666" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C666" s="15"/>
       <c r="D666" s="15"/>
       <c r="E666" s="16"/>
       <c r="F666" s="15"/>
     </row>
-    <row r="667" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="667" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C667" s="15"/>
       <c r="D667" s="15"/>
       <c r="E667" s="16"/>
       <c r="F667" s="15"/>
     </row>
-    <row r="668" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="668" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C668" s="15"/>
       <c r="D668" s="15"/>
       <c r="E668" s="16"/>
       <c r="F668" s="15"/>
     </row>
-    <row r="669" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="669" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C669" s="15"/>
       <c r="D669" s="15"/>
       <c r="E669" s="16"/>
       <c r="F669" s="15"/>
     </row>
-    <row r="670" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="670" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C670" s="15"/>
       <c r="D670" s="15"/>
       <c r="E670" s="16"/>
       <c r="F670" s="15"/>
     </row>
-    <row r="671" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="671" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C671" s="15"/>
       <c r="D671" s="15"/>
       <c r="E671" s="16"/>
       <c r="F671" s="15"/>
     </row>
-    <row r="672" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="672" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C672" s="15"/>
       <c r="D672" s="15"/>
       <c r="E672" s="16"/>
       <c r="F672" s="15"/>
     </row>
-    <row r="673" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="673" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C673" s="15"/>
       <c r="D673" s="15"/>
       <c r="E673" s="16"/>
       <c r="F673" s="15"/>
     </row>
-    <row r="674" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="674" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C674" s="15"/>
       <c r="D674" s="15"/>
       <c r="E674" s="16"/>
       <c r="F674" s="15"/>
     </row>
-    <row r="675" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="675" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C675" s="15"/>
       <c r="D675" s="15"/>
       <c r="E675" s="16"/>
       <c r="F675" s="15"/>
     </row>
-    <row r="676" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="676" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C676" s="15"/>
       <c r="D676" s="15"/>
       <c r="E676" s="16"/>
       <c r="F676" s="15"/>
     </row>
-    <row r="677" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="677" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C677" s="15"/>
       <c r="D677" s="15"/>
       <c r="E677" s="16"/>
       <c r="F677" s="15"/>
     </row>
-    <row r="678" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="678" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C678" s="15"/>
       <c r="D678" s="15"/>
       <c r="E678" s="16"/>
       <c r="F678" s="15"/>
     </row>
-    <row r="679" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="679" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C679" s="15"/>
       <c r="D679" s="15"/>
       <c r="E679" s="16"/>
       <c r="F679" s="15"/>
     </row>
-    <row r="680" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="680" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C680" s="15"/>
       <c r="D680" s="15"/>
       <c r="E680" s="16"/>
       <c r="F680" s="15"/>
     </row>
-    <row r="681" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="681" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C681" s="15"/>
       <c r="D681" s="15"/>
       <c r="E681" s="16"/>
       <c r="F681" s="15"/>
     </row>
-    <row r="682" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="682" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C682" s="15"/>
       <c r="D682" s="15"/>
       <c r="E682" s="16"/>
       <c r="F682" s="15"/>
     </row>
-    <row r="683" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="683" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C683" s="15"/>
       <c r="D683" s="15"/>
       <c r="E683" s="16"/>
       <c r="F683" s="15"/>
     </row>
-    <row r="684" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="684" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C684" s="15"/>
       <c r="D684" s="15"/>
       <c r="E684" s="16"/>
       <c r="F684" s="15"/>
     </row>
-    <row r="685" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="685" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C685" s="15"/>
       <c r="D685" s="15"/>
       <c r="E685" s="16"/>
       <c r="F685" s="15"/>
     </row>
-    <row r="686" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="686" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C686" s="15"/>
       <c r="D686" s="15"/>
       <c r="E686" s="16"/>
       <c r="F686" s="15"/>
     </row>
-    <row r="687" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="687" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C687" s="15"/>
       <c r="D687" s="15"/>
       <c r="E687" s="16"/>
       <c r="F687" s="15"/>
     </row>
-    <row r="688" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="688" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C688" s="15"/>
       <c r="D688" s="15"/>
       <c r="E688" s="16"/>
       <c r="F688" s="15"/>
     </row>
-    <row r="689" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="689" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C689" s="15"/>
       <c r="D689" s="15"/>
       <c r="E689" s="16"/>
       <c r="F689" s="15"/>
     </row>
-    <row r="690" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="690" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C690" s="15"/>
       <c r="D690" s="15"/>
       <c r="E690" s="16"/>
       <c r="F690" s="15"/>
     </row>
-    <row r="691" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="691" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C691" s="15"/>
       <c r="D691" s="15"/>
       <c r="E691" s="16"/>
       <c r="F691" s="15"/>
     </row>
-    <row r="692" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="692" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C692" s="15"/>
       <c r="D692" s="15"/>
       <c r="E692" s="16"/>
       <c r="F692" s="15"/>
     </row>
-    <row r="693" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="693" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C693" s="15"/>
       <c r="D693" s="15"/>
       <c r="E693" s="16"/>
       <c r="F693" s="15"/>
     </row>
-    <row r="694" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="694" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C694" s="15"/>
       <c r="D694" s="15"/>
       <c r="E694" s="16"/>
       <c r="F694" s="15"/>
     </row>
-    <row r="695" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="695" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C695" s="15"/>
       <c r="D695" s="15"/>
       <c r="E695" s="16"/>
       <c r="F695" s="15"/>
     </row>
-    <row r="696" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="696" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C696" s="15"/>
       <c r="D696" s="15"/>
       <c r="E696" s="16"/>
       <c r="F696" s="15"/>
     </row>
-    <row r="697" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="697" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C697" s="15"/>
       <c r="D697" s="15"/>
       <c r="E697" s="16"/>
       <c r="F697" s="15"/>
     </row>
-    <row r="698" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="698" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C698" s="15"/>
       <c r="D698" s="15"/>
       <c r="E698" s="16"/>
       <c r="F698" s="15"/>
     </row>
-    <row r="699" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="699" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C699" s="15"/>
       <c r="D699" s="15"/>
       <c r="E699" s="16"/>
       <c r="F699" s="15"/>
     </row>
-    <row r="700" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="700" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C700" s="15"/>
       <c r="D700" s="15"/>
       <c r="E700" s="16"/>
       <c r="F700" s="15"/>
     </row>
-    <row r="701" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="701" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C701" s="15"/>
       <c r="D701" s="15"/>
       <c r="E701" s="16"/>
       <c r="F701" s="15"/>
     </row>
-    <row r="702" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="702" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C702" s="15"/>
       <c r="D702" s="15"/>
       <c r="E702" s="16"/>
       <c r="F702" s="15"/>
     </row>
-    <row r="703" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="703" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C703" s="15"/>
       <c r="D703" s="15"/>
       <c r="E703" s="16"/>
       <c r="F703" s="15"/>
     </row>
-    <row r="704" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="704" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C704" s="15"/>
       <c r="D704" s="15"/>
       <c r="E704" s="16"/>
       <c r="F704" s="15"/>
     </row>
-    <row r="705" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="705" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C705" s="15"/>
       <c r="D705" s="15"/>
       <c r="E705" s="16"/>
       <c r="F705" s="15"/>
     </row>
-    <row r="706" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="706" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C706" s="15"/>
       <c r="D706" s="15"/>
       <c r="E706" s="16"/>
       <c r="F706" s="15"/>
     </row>
-    <row r="707" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="707" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C707" s="15"/>
       <c r="D707" s="15"/>
       <c r="E707" s="16"/>
       <c r="F707" s="15"/>
     </row>
-    <row r="708" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="708" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C708" s="15"/>
       <c r="D708" s="15"/>
       <c r="E708" s="16"/>
       <c r="F708" s="15"/>
     </row>
-    <row r="709" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="709" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C709" s="15"/>
       <c r="D709" s="15"/>
       <c r="E709" s="16"/>
       <c r="F709" s="15"/>
     </row>
-    <row r="710" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="710" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C710" s="15"/>
       <c r="D710" s="15"/>
       <c r="E710" s="16"/>
       <c r="F710" s="15"/>
     </row>
-    <row r="711" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="711" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C711" s="15"/>
       <c r="D711" s="15"/>
       <c r="E711" s="16"/>
       <c r="F711" s="15"/>
     </row>
-    <row r="712" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="712" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C712" s="15"/>
       <c r="D712" s="15"/>
       <c r="E712" s="16"/>
       <c r="F712" s="15"/>
     </row>
-    <row r="713" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="713" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C713" s="15"/>
       <c r="D713" s="15"/>
       <c r="E713" s="16"/>
       <c r="F713" s="15"/>
     </row>
-    <row r="714" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="714" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C714" s="15"/>
       <c r="D714" s="15"/>
       <c r="E714" s="16"/>
       <c r="F714" s="15"/>
     </row>
-    <row r="715" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="715" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C715" s="15"/>
       <c r="D715" s="15"/>
       <c r="E715" s="16"/>
       <c r="F715" s="15"/>
     </row>
-    <row r="716" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="716" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C716" s="15"/>
       <c r="D716" s="15"/>
       <c r="E716" s="16"/>
       <c r="F716" s="15"/>
     </row>
-    <row r="717" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="717" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C717" s="15"/>
       <c r="D717" s="15"/>
       <c r="E717" s="16"/>
       <c r="F717" s="15"/>
     </row>
-    <row r="718" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="718" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C718" s="15"/>
       <c r="D718" s="15"/>
       <c r="E718" s="16"/>
       <c r="F718" s="15"/>
     </row>
-    <row r="719" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="719" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C719" s="15"/>
       <c r="D719" s="15"/>
       <c r="E719" s="16"/>
       <c r="F719" s="15"/>
     </row>
-    <row r="720" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="720" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C720" s="15"/>
       <c r="D720" s="15"/>
       <c r="E720" s="16"/>
       <c r="F720" s="15"/>
     </row>
-    <row r="721" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="721" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C721" s="15"/>
       <c r="D721" s="15"/>
       <c r="E721" s="16"/>
       <c r="F721" s="15"/>
     </row>
-    <row r="722" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="722" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C722" s="15"/>
       <c r="D722" s="15"/>
       <c r="E722" s="16"/>
       <c r="F722" s="15"/>
     </row>
-    <row r="723" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="723" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C723" s="15"/>
       <c r="D723" s="15"/>
       <c r="E723" s="16"/>
       <c r="F723" s="15"/>
     </row>
-    <row r="724" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="724" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C724" s="15"/>
       <c r="D724" s="15"/>
       <c r="E724" s="16"/>
       <c r="F724" s="15"/>
     </row>
-    <row r="725" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="725" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C725" s="15"/>
       <c r="D725" s="15"/>
       <c r="E725" s="16"/>
       <c r="F725" s="15"/>
     </row>
-    <row r="726" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="726" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C726" s="15"/>
       <c r="D726" s="15"/>
       <c r="E726" s="16"/>
       <c r="F726" s="15"/>
     </row>
-    <row r="727" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="727" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C727" s="15"/>
       <c r="D727" s="15"/>
       <c r="E727" s="16"/>
       <c r="F727" s="15"/>
     </row>
-    <row r="728" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="728" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C728" s="15"/>
       <c r="D728" s="15"/>
       <c r="E728" s="16"/>
       <c r="F728" s="15"/>
     </row>
-    <row r="729" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="729" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C729" s="15"/>
       <c r="D729" s="15"/>
       <c r="E729" s="16"/>
       <c r="F729" s="15"/>
     </row>
-    <row r="730" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="730" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C730" s="15"/>
       <c r="D730" s="15"/>
       <c r="E730" s="16"/>
       <c r="F730" s="15"/>
     </row>
-    <row r="731" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="731" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C731" s="15"/>
       <c r="D731" s="15"/>
       <c r="E731" s="16"/>
       <c r="F731" s="15"/>
     </row>
-    <row r="732" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="732" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C732" s="15"/>
       <c r="D732" s="15"/>
       <c r="E732" s="16"/>
       <c r="F732" s="15"/>
     </row>
-    <row r="733" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="733" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C733" s="15"/>
       <c r="D733" s="15"/>
       <c r="E733" s="16"/>
       <c r="F733" s="15"/>
     </row>
-    <row r="734" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="734" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C734" s="15"/>
       <c r="D734" s="15"/>
       <c r="E734" s="16"/>
       <c r="F734" s="15"/>
     </row>
-    <row r="735" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="735" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C735" s="15"/>
       <c r="D735" s="15"/>
       <c r="E735" s="16"/>
       <c r="F735" s="15"/>
     </row>
-    <row r="736" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="736" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C736" s="15"/>
       <c r="D736" s="15"/>
       <c r="E736" s="16"/>
       <c r="F736" s="15"/>
     </row>
-    <row r="737" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="737" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C737" s="15"/>
       <c r="D737" s="15"/>
       <c r="E737" s="16"/>
       <c r="F737" s="15"/>
     </row>
-    <row r="738" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="738" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C738" s="15"/>
       <c r="D738" s="15"/>
       <c r="E738" s="16"/>
       <c r="F738" s="15"/>
     </row>
-    <row r="739" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="739" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C739" s="15"/>
       <c r="D739" s="15"/>
       <c r="E739" s="16"/>
       <c r="F739" s="15"/>
     </row>
-    <row r="740" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="740" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C740" s="15"/>
       <c r="D740" s="15"/>
       <c r="E740" s="16"/>
       <c r="F740" s="15"/>
     </row>
-    <row r="741" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="741" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C741" s="15"/>
       <c r="D741" s="15"/>
       <c r="E741" s="16"/>
       <c r="F741" s="15"/>
     </row>
-    <row r="742" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="742" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C742" s="15"/>
       <c r="D742" s="15"/>
       <c r="E742" s="16"/>
       <c r="F742" s="15"/>
     </row>
-    <row r="743" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="743" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C743" s="15"/>
       <c r="D743" s="15"/>
       <c r="E743" s="16"/>
       <c r="F743" s="15"/>
     </row>
-    <row r="744" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="744" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C744" s="15"/>
       <c r="D744" s="15"/>
       <c r="E744" s="16"/>
       <c r="F744" s="15"/>
     </row>
-    <row r="745" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="745" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C745" s="15"/>
       <c r="D745" s="15"/>
       <c r="E745" s="16"/>
       <c r="F745" s="15"/>
     </row>
-    <row r="746" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="746" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C746" s="15"/>
       <c r="D746" s="15"/>
       <c r="E746" s="16"/>
       <c r="F746" s="15"/>
     </row>
-    <row r="747" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="747" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C747" s="15"/>
       <c r="D747" s="15"/>
       <c r="E747" s="16"/>
       <c r="F747" s="15"/>
     </row>
-    <row r="748" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="748" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C748" s="15"/>
       <c r="D748" s="15"/>
       <c r="E748" s="16"/>
       <c r="F748" s="15"/>
     </row>
-    <row r="749" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="749" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C749" s="15"/>
       <c r="D749" s="15"/>
       <c r="E749" s="16"/>
       <c r="F749" s="15"/>
     </row>
-    <row r="750" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="750" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C750" s="15"/>
       <c r="D750" s="15"/>
       <c r="E750" s="16"/>
       <c r="F750" s="15"/>
     </row>
-    <row r="751" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="751" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C751" s="15"/>
       <c r="D751" s="15"/>
       <c r="E751" s="16"/>
       <c r="F751" s="15"/>
     </row>
-    <row r="752" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="752" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C752" s="15"/>
       <c r="D752" s="15"/>
       <c r="E752" s="16"/>
       <c r="F752" s="15"/>
     </row>
-    <row r="753" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="753" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C753" s="15"/>
       <c r="D753" s="15"/>
       <c r="E753" s="16"/>
       <c r="F753" s="15"/>
     </row>
-    <row r="754" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="754" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C754" s="15"/>
       <c r="D754" s="15"/>
       <c r="E754" s="16"/>
       <c r="F754" s="15"/>
     </row>
-    <row r="755" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="755" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C755" s="15"/>
       <c r="D755" s="15"/>
       <c r="E755" s="16"/>
       <c r="F755" s="15"/>
     </row>
-    <row r="756" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="756" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C756" s="15"/>
       <c r="D756" s="15"/>
       <c r="E756" s="16"/>
       <c r="F756" s="15"/>
     </row>
-    <row r="757" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="757" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C757" s="15"/>
       <c r="D757" s="15"/>
       <c r="E757" s="16"/>
       <c r="F757" s="15"/>
     </row>
-    <row r="758" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="758" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C758" s="15"/>
       <c r="D758" s="15"/>
       <c r="E758" s="16"/>
       <c r="F758" s="15"/>
     </row>
-    <row r="759" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="759" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C759" s="15"/>
       <c r="D759" s="15"/>
       <c r="E759" s="16"/>
       <c r="F759" s="15"/>
     </row>
-    <row r="760" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="760" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C760" s="15"/>
       <c r="D760" s="15"/>
       <c r="E760" s="16"/>
       <c r="F760" s="15"/>
     </row>
-    <row r="761" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="761" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C761" s="15"/>
       <c r="D761" s="15"/>
       <c r="E761" s="16"/>
       <c r="F761" s="15"/>
     </row>
-    <row r="762" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="762" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C762" s="15"/>
       <c r="D762" s="15"/>
       <c r="E762" s="16"/>
       <c r="F762" s="15"/>
     </row>
-    <row r="763" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="763" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C763" s="15"/>
       <c r="D763" s="15"/>
       <c r="E763" s="16"/>
       <c r="F763" s="15"/>
     </row>
-    <row r="764" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="764" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C764" s="15"/>
       <c r="D764" s="15"/>
       <c r="E764" s="16"/>
       <c r="F764" s="15"/>
     </row>
-    <row r="765" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="765" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C765" s="15"/>
       <c r="D765" s="15"/>
       <c r="E765" s="16"/>
       <c r="F765" s="15"/>
     </row>
-    <row r="766" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="766" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C766" s="15"/>
       <c r="D766" s="15"/>
       <c r="E766" s="16"/>
       <c r="F766" s="15"/>
     </row>
-    <row r="767" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="767" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C767" s="15"/>
       <c r="D767" s="15"/>
       <c r="E767" s="16"/>
       <c r="F767" s="15"/>
     </row>
-    <row r="768" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="768" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C768" s="15"/>
       <c r="D768" s="15"/>
       <c r="E768" s="16"/>
       <c r="F768" s="15"/>
     </row>
-    <row r="769" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="769" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C769" s="15"/>
       <c r="D769" s="15"/>
       <c r="E769" s="16"/>
       <c r="F769" s="15"/>
     </row>
-    <row r="770" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="770" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C770" s="15"/>
       <c r="D770" s="15"/>
       <c r="E770" s="16"/>
       <c r="F770" s="15"/>
     </row>
-    <row r="771" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="771" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C771" s="15"/>
       <c r="D771" s="15"/>
       <c r="E771" s="16"/>
       <c r="F771" s="15"/>
     </row>
-    <row r="772" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="772" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C772" s="15"/>
       <c r="D772" s="15"/>
       <c r="E772" s="16"/>
       <c r="F772" s="15"/>
     </row>
-    <row r="773" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="773" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C773" s="15"/>
       <c r="D773" s="15"/>
       <c r="E773" s="16"/>
       <c r="F773" s="15"/>
     </row>
-    <row r="774" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="774" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C774" s="15"/>
       <c r="D774" s="15"/>
       <c r="E774" s="16"/>
       <c r="F774" s="15"/>
     </row>
-    <row r="775" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="775" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C775" s="15"/>
       <c r="D775" s="15"/>
       <c r="E775" s="16"/>
       <c r="F775" s="15"/>
     </row>
-    <row r="776" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="776" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C776" s="15"/>
       <c r="D776" s="15"/>
       <c r="E776" s="16"/>
       <c r="F776" s="15"/>
     </row>
-    <row r="777" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="777" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C777" s="15"/>
       <c r="D777" s="15"/>
       <c r="E777" s="16"/>
       <c r="F777" s="15"/>
     </row>
-    <row r="778" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="778" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C778" s="15"/>
       <c r="D778" s="15"/>
       <c r="E778" s="16"/>
       <c r="F778" s="15"/>
     </row>
-    <row r="779" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="779" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C779" s="15"/>
       <c r="D779" s="15"/>
       <c r="E779" s="16"/>
       <c r="F779" s="15"/>
     </row>
-    <row r="780" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="780" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C780" s="15"/>
       <c r="D780" s="15"/>
       <c r="E780" s="16"/>
       <c r="F780" s="15"/>
     </row>
-    <row r="781" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="781" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C781" s="15"/>
       <c r="D781" s="15"/>
       <c r="E781" s="16"/>
       <c r="F781" s="15"/>
     </row>
-    <row r="782" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="782" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C782" s="15"/>
       <c r="D782" s="15"/>
       <c r="E782" s="16"/>
       <c r="F782" s="15"/>
     </row>
-    <row r="783" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="783" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C783" s="15"/>
       <c r="D783" s="15"/>
       <c r="E783" s="16"/>
       <c r="F783" s="15"/>
     </row>
-    <row r="784" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="784" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C784" s="15"/>
       <c r="D784" s="15"/>
       <c r="E784" s="16"/>
       <c r="F784" s="15"/>
     </row>
-    <row r="785" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="785" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C785" s="15"/>
       <c r="D785" s="15"/>
       <c r="E785" s="16"/>
       <c r="F785" s="15"/>
     </row>
-    <row r="786" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="786" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C786" s="15"/>
       <c r="D786" s="15"/>
       <c r="E786" s="16"/>
       <c r="F786" s="15"/>
     </row>
-    <row r="787" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="787" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C787" s="15"/>
       <c r="D787" s="15"/>
       <c r="E787" s="16"/>
       <c r="F787" s="15"/>
     </row>
-    <row r="788" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="788" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C788" s="15"/>
       <c r="D788" s="15"/>
       <c r="E788" s="16"/>
       <c r="F788" s="15"/>
     </row>
-    <row r="789" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="789" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C789" s="15"/>
       <c r="D789" s="15"/>
       <c r="E789" s="16"/>
       <c r="F789" s="15"/>
     </row>
-    <row r="790" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="790" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C790" s="15"/>
       <c r="D790" s="15"/>
       <c r="E790" s="16"/>
       <c r="F790" s="15"/>
     </row>
-    <row r="791" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="791" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C791" s="15"/>
       <c r="D791" s="15"/>
       <c r="E791" s="16"/>
       <c r="F791" s="15"/>
     </row>
-    <row r="792" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="792" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C792" s="15"/>
       <c r="D792" s="15"/>
       <c r="E792" s="16"/>
       <c r="F792" s="15"/>
     </row>
-    <row r="793" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="793" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C793" s="15"/>
       <c r="D793" s="15"/>
       <c r="E793" s="16"/>
       <c r="F793" s="15"/>
     </row>
-    <row r="794" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="794" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C794" s="15"/>
       <c r="D794" s="15"/>
       <c r="E794" s="16"/>
       <c r="F794" s="15"/>
     </row>
-    <row r="795" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="795" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C795" s="15"/>
       <c r="D795" s="15"/>
       <c r="E795" s="16"/>
       <c r="F795" s="15"/>
     </row>
-    <row r="796" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="796" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C796" s="15"/>
       <c r="D796" s="15"/>
       <c r="E796" s="16"/>
       <c r="F796" s="15"/>
     </row>
-    <row r="797" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="797" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C797" s="15"/>
       <c r="D797" s="15"/>
       <c r="E797" s="16"/>
       <c r="F797" s="15"/>
     </row>
-    <row r="798" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="798" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C798" s="15"/>
       <c r="D798" s="15"/>
       <c r="E798" s="16"/>
       <c r="F798" s="15"/>
     </row>
-    <row r="799" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="799" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C799" s="15"/>
       <c r="D799" s="15"/>
       <c r="E799" s="16"/>
       <c r="F799" s="15"/>
     </row>
-    <row r="800" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="800" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C800" s="15"/>
       <c r="D800" s="15"/>
       <c r="E800" s="16"/>
       <c r="F800" s="15"/>
     </row>
-    <row r="801" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="801" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C801" s="15"/>
       <c r="D801" s="15"/>
       <c r="E801" s="16"/>
       <c r="F801" s="15"/>
     </row>
-    <row r="802" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="802" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C802" s="15"/>
       <c r="D802" s="15"/>
       <c r="E802" s="16"/>
       <c r="F802" s="15"/>
     </row>
-    <row r="803" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="803" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C803" s="15"/>
       <c r="D803" s="15"/>
       <c r="E803" s="16"/>
       <c r="F803" s="15"/>
     </row>
-    <row r="804" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="804" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C804" s="15"/>
       <c r="D804" s="15"/>
       <c r="E804" s="16"/>
       <c r="F804" s="15"/>
     </row>
-    <row r="805" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="805" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C805" s="15"/>
       <c r="D805" s="15"/>
       <c r="E805" s="16"/>
       <c r="F805" s="15"/>
     </row>
-    <row r="806" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="806" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C806" s="15"/>
       <c r="D806" s="15"/>
       <c r="E806" s="16"/>
       <c r="F806" s="15"/>
     </row>
-    <row r="807" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="807" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C807" s="15"/>
       <c r="D807" s="15"/>
       <c r="E807" s="16"/>
       <c r="F807" s="15"/>
     </row>
-    <row r="808" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="808" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C808" s="15"/>
       <c r="D808" s="15"/>
       <c r="E808" s="16"/>
       <c r="F808" s="15"/>
     </row>
-    <row r="809" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="809" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C809" s="15"/>
       <c r="D809" s="15"/>
       <c r="E809" s="16"/>
       <c r="F809" s="15"/>
     </row>
-    <row r="810" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="810" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C810" s="15"/>
       <c r="D810" s="15"/>
       <c r="E810" s="16"/>
       <c r="F810" s="15"/>
     </row>
-    <row r="811" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="811" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C811" s="15"/>
       <c r="D811" s="15"/>
       <c r="E811" s="16"/>
       <c r="F811" s="15"/>
     </row>
-    <row r="812" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="812" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C812" s="15"/>
       <c r="D812" s="15"/>
       <c r="E812" s="16"/>
       <c r="F812" s="15"/>
     </row>
-    <row r="813" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="813" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C813" s="15"/>
       <c r="D813" s="15"/>
       <c r="E813" s="16"/>
       <c r="F813" s="15"/>
     </row>
-    <row r="814" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="814" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C814" s="15"/>
       <c r="D814" s="15"/>
       <c r="E814" s="16"/>
       <c r="F814" s="15"/>
     </row>
-    <row r="815" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="815" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C815" s="15"/>
       <c r="D815" s="15"/>
       <c r="E815" s="16"/>
       <c r="F815" s="15"/>
     </row>
-    <row r="816" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="816" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C816" s="15"/>
       <c r="D816" s="15"/>
       <c r="E816" s="16"/>
       <c r="F816" s="15"/>
     </row>
-    <row r="817" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="817" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C817" s="15"/>
       <c r="D817" s="15"/>
       <c r="E817" s="16"/>
       <c r="F817" s="15"/>
     </row>
-    <row r="818" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="818" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C818" s="15"/>
       <c r="D818" s="15"/>
       <c r="E818" s="16"/>
       <c r="F818" s="15"/>
     </row>
-    <row r="819" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="819" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C819" s="15"/>
       <c r="D819" s="15"/>
       <c r="E819" s="16"/>
       <c r="F819" s="15"/>
     </row>
-    <row r="820" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="820" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C820" s="15"/>
       <c r="D820" s="15"/>
       <c r="E820" s="16"/>
       <c r="F820" s="15"/>
     </row>
-    <row r="821" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="821" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C821" s="15"/>
       <c r="D821" s="15"/>
       <c r="E821" s="16"/>
       <c r="F821" s="15"/>
     </row>
-    <row r="822" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="822" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C822" s="15"/>
       <c r="D822" s="15"/>
       <c r="E822" s="16"/>
       <c r="F822" s="15"/>
     </row>
-    <row r="823" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="823" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C823" s="15"/>
       <c r="D823" s="15"/>
       <c r="E823" s="16"/>
       <c r="F823" s="15"/>
     </row>
-    <row r="824" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="824" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C824" s="15"/>
       <c r="D824" s="15"/>
       <c r="E824" s="16"/>
       <c r="F824" s="15"/>
     </row>
-    <row r="825" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="825" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C825" s="15"/>
       <c r="D825" s="15"/>
       <c r="E825" s="16"/>
       <c r="F825" s="15"/>
     </row>
-    <row r="826" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="826" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C826" s="15"/>
       <c r="D826" s="15"/>
       <c r="E826" s="16"/>
       <c r="F826" s="15"/>
     </row>
-    <row r="827" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="827" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C827" s="15"/>
       <c r="D827" s="15"/>
       <c r="E827" s="16"/>
       <c r="F827" s="15"/>
     </row>
-    <row r="828" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="828" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C828" s="15"/>
       <c r="D828" s="15"/>
       <c r="E828" s="16"/>
       <c r="F828" s="15"/>
     </row>
-    <row r="829" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="829" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C829" s="15"/>
       <c r="D829" s="15"/>
       <c r="E829" s="16"/>
       <c r="F829" s="15"/>
     </row>
-    <row r="830" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="830" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C830" s="15"/>
       <c r="D830" s="15"/>
       <c r="E830" s="16"/>
       <c r="F830" s="15"/>
     </row>
-    <row r="831" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="831" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C831" s="15"/>
       <c r="D831" s="15"/>
       <c r="E831" s="16"/>
       <c r="F831" s="15"/>
     </row>
-    <row r="832" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="832" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C832" s="15"/>
       <c r="D832" s="15"/>
       <c r="E832" s="16"/>
       <c r="F832" s="15"/>
     </row>
-    <row r="833" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="833" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C833" s="15"/>
       <c r="D833" s="15"/>
       <c r="E833" s="16"/>
       <c r="F833" s="15"/>
     </row>
-    <row r="834" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="834" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C834" s="15"/>
       <c r="D834" s="15"/>
       <c r="E834" s="16"/>
       <c r="F834" s="15"/>
     </row>
-    <row r="835" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="835" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C835" s="15"/>
       <c r="D835" s="15"/>
       <c r="E835" s="16"/>
       <c r="F835" s="15"/>
     </row>
-    <row r="836" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="836" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C836" s="15"/>
       <c r="D836" s="15"/>
       <c r="E836" s="16"/>
       <c r="F836" s="15"/>
     </row>
-    <row r="837" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="837" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C837" s="15"/>
       <c r="D837" s="15"/>
       <c r="E837" s="16"/>
       <c r="F837" s="15"/>
     </row>
-    <row r="838" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="838" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C838" s="15"/>
       <c r="D838" s="15"/>
       <c r="E838" s="16"/>
       <c r="F838" s="15"/>
     </row>
-    <row r="839" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="839" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C839" s="15"/>
       <c r="D839" s="15"/>
       <c r="E839" s="16"/>
       <c r="F839" s="15"/>
     </row>
-    <row r="840" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="840" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C840" s="15"/>
       <c r="D840" s="15"/>
       <c r="E840" s="16"/>
       <c r="F840" s="15"/>
     </row>
-    <row r="841" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="841" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C841" s="15"/>
       <c r="D841" s="15"/>
       <c r="E841" s="16"/>
       <c r="F841" s="15"/>
     </row>
-    <row r="842" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="842" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C842" s="15"/>
       <c r="D842" s="15"/>
       <c r="E842" s="16"/>
       <c r="F842" s="15"/>
     </row>
-    <row r="843" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="843" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C843" s="15"/>
       <c r="D843" s="15"/>
       <c r="E843" s="16"/>
       <c r="F843" s="15"/>
     </row>
-    <row r="844" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="844" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C844" s="15"/>
       <c r="D844" s="15"/>
       <c r="E844" s="16"/>
       <c r="F844" s="15"/>
     </row>
-    <row r="845" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="845" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C845" s="15"/>
       <c r="D845" s="15"/>
       <c r="E845" s="16"/>
       <c r="F845" s="15"/>
     </row>
-    <row r="846" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="846" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C846" s="15"/>
       <c r="D846" s="15"/>
       <c r="E846" s="16"/>
       <c r="F846" s="15"/>
     </row>
-    <row r="847" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="847" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C847" s="15"/>
       <c r="D847" s="15"/>
       <c r="E847" s="16"/>
       <c r="F847" s="15"/>
     </row>
-    <row r="848" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="848" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C848" s="15"/>
       <c r="D848" s="15"/>
       <c r="E848" s="16"/>
       <c r="F848" s="15"/>
     </row>
-    <row r="849" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="849" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C849" s="15"/>
       <c r="D849" s="15"/>
       <c r="E849" s="16"/>
       <c r="F849" s="15"/>
     </row>
-    <row r="850" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="850" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C850" s="15"/>
       <c r="D850" s="15"/>
       <c r="E850" s="16"/>
       <c r="F850" s="15"/>
     </row>
-    <row r="851" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="851" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C851" s="15"/>
       <c r="D851" s="15"/>
       <c r="E851" s="16"/>
       <c r="F851" s="15"/>
     </row>
-    <row r="852" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="852" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C852" s="15"/>
       <c r="D852" s="15"/>
       <c r="E852" s="16"/>
       <c r="F852" s="15"/>
     </row>
-    <row r="853" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="853" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C853" s="15"/>
       <c r="D853" s="15"/>
       <c r="E853" s="16"/>
       <c r="F853" s="15"/>
     </row>
-    <row r="854" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="854" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C854" s="15"/>
       <c r="D854" s="15"/>
       <c r="E854" s="16"/>
       <c r="F854" s="15"/>
     </row>
-    <row r="855" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="855" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C855" s="15"/>
       <c r="D855" s="15"/>
       <c r="E855" s="16"/>
       <c r="F855" s="15"/>
     </row>
-    <row r="856" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="856" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C856" s="15"/>
       <c r="D856" s="15"/>
       <c r="E856" s="16"/>
       <c r="F856" s="15"/>
     </row>
-    <row r="857" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="857" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C857" s="15"/>
       <c r="D857" s="15"/>
       <c r="E857" s="16"/>
       <c r="F857" s="15"/>
     </row>
-    <row r="858" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="858" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C858" s="15"/>
       <c r="D858" s="15"/>
       <c r="E858" s="16"/>
       <c r="F858" s="15"/>
     </row>
-    <row r="859" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="859" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C859" s="15"/>
       <c r="D859" s="15"/>
       <c r="E859" s="16"/>
       <c r="F859" s="15"/>
     </row>
-    <row r="860" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="860" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C860" s="15"/>
       <c r="D860" s="15"/>
       <c r="E860" s="16"/>
       <c r="F860" s="15"/>
     </row>
-    <row r="861" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="861" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C861" s="15"/>
       <c r="D861" s="15"/>
       <c r="E861" s="16"/>
       <c r="F861" s="15"/>
     </row>
-    <row r="862" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="862" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C862" s="15"/>
       <c r="D862" s="15"/>
       <c r="E862" s="16"/>
       <c r="F862" s="15"/>
     </row>
-    <row r="863" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="863" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C863" s="15"/>
       <c r="D863" s="15"/>
       <c r="E863" s="16"/>
       <c r="F863" s="15"/>
     </row>
-    <row r="864" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="864" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C864" s="15"/>
       <c r="D864" s="15"/>
       <c r="E864" s="16"/>
       <c r="F864" s="15"/>
     </row>
-    <row r="865" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="865" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C865" s="15"/>
       <c r="D865" s="15"/>
       <c r="E865" s="16"/>
       <c r="F865" s="15"/>
     </row>
-    <row r="866" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="866" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C866" s="15"/>
       <c r="D866" s="15"/>
       <c r="E866" s="16"/>
       <c r="F866" s="15"/>
     </row>
-    <row r="867" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="867" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C867" s="15"/>
       <c r="D867" s="15"/>
       <c r="E867" s="16"/>
       <c r="F867" s="15"/>
     </row>
-    <row r="868" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="868" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C868" s="15"/>
       <c r="D868" s="15"/>
       <c r="E868" s="16"/>
       <c r="F868" s="15"/>
     </row>
-    <row r="869" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="869" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C869" s="15"/>
       <c r="D869" s="15"/>
       <c r="E869" s="16"/>
       <c r="F869" s="15"/>
     </row>
-    <row r="870" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="870" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C870" s="15"/>
       <c r="D870" s="15"/>
       <c r="E870" s="16"/>
       <c r="F870" s="15"/>
     </row>
-    <row r="871" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="871" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C871" s="15"/>
       <c r="D871" s="15"/>
       <c r="E871" s="16"/>
       <c r="F871" s="15"/>
     </row>
-    <row r="872" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="872" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C872" s="15"/>
       <c r="D872" s="15"/>
       <c r="E872" s="16"/>
       <c r="F872" s="15"/>
     </row>
-    <row r="873" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="873" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C873" s="15"/>
       <c r="D873" s="15"/>
       <c r="E873" s="16"/>
       <c r="F873" s="15"/>
     </row>
-    <row r="874" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="874" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C874" s="15"/>
       <c r="D874" s="15"/>
       <c r="E874" s="16"/>
       <c r="F874" s="15"/>
     </row>
-    <row r="875" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="875" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C875" s="15"/>
       <c r="D875" s="15"/>
       <c r="E875" s="16"/>
       <c r="F875" s="15"/>
     </row>
-    <row r="876" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="876" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C876" s="15"/>
       <c r="D876" s="15"/>
       <c r="E876" s="16"/>
       <c r="F876" s="15"/>
     </row>
-    <row r="877" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="877" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C877" s="15"/>
       <c r="D877" s="15"/>
       <c r="E877" s="16"/>
       <c r="F877" s="15"/>
     </row>
-    <row r="878" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="878" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C878" s="15"/>
       <c r="D878" s="15"/>
       <c r="E878" s="16"/>
       <c r="F878" s="15"/>
     </row>
-    <row r="879" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="879" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C879" s="15"/>
       <c r="D879" s="15"/>
       <c r="E879" s="16"/>
       <c r="F879" s="15"/>
     </row>
-    <row r="880" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="880" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C880" s="15"/>
       <c r="D880" s="15"/>
       <c r="E880" s="16"/>
       <c r="F880" s="15"/>
     </row>
-    <row r="881" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="881" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C881" s="15"/>
       <c r="D881" s="15"/>
       <c r="E881" s="16"/>
       <c r="F881" s="15"/>
     </row>
-    <row r="882" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="882" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C882" s="15"/>
       <c r="D882" s="15"/>
       <c r="E882" s="16"/>
       <c r="F882" s="15"/>
     </row>
-    <row r="883" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="883" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C883" s="15"/>
       <c r="D883" s="15"/>
       <c r="E883" s="16"/>
       <c r="F883" s="15"/>
     </row>
-    <row r="884" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="884" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C884" s="15"/>
       <c r="D884" s="15"/>
       <c r="E884" s="16"/>
       <c r="F884" s="15"/>
     </row>
-    <row r="885" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="885" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C885" s="15"/>
       <c r="D885" s="15"/>
       <c r="E885" s="16"/>
       <c r="F885" s="15"/>
     </row>
-    <row r="886" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="886" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C886" s="15"/>
       <c r="D886" s="15"/>
       <c r="E886" s="16"/>
       <c r="F886" s="15"/>
     </row>
-    <row r="887" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="887" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C887" s="15"/>
       <c r="D887" s="15"/>
       <c r="E887" s="16"/>
       <c r="F887" s="15"/>
     </row>
-    <row r="888" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="888" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C888" s="15"/>
       <c r="D888" s="15"/>
       <c r="E888" s="16"/>
       <c r="F888" s="15"/>
     </row>
-    <row r="889" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="889" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C889" s="15"/>
       <c r="D889" s="15"/>
       <c r="E889" s="16"/>
       <c r="F889" s="15"/>
     </row>
-    <row r="890" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="890" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C890" s="15"/>
       <c r="D890" s="15"/>
       <c r="E890" s="16"/>
       <c r="F890" s="15"/>
     </row>
-    <row r="891" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="891" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C891" s="15"/>
       <c r="D891" s="15"/>
       <c r="E891" s="16"/>
       <c r="F891" s="15"/>
     </row>
-    <row r="892" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="892" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C892" s="15"/>
       <c r="D892" s="15"/>
       <c r="E892" s="16"/>
       <c r="F892" s="15"/>
     </row>
-    <row r="893" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="893" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C893" s="15"/>
       <c r="D893" s="15"/>
       <c r="E893" s="16"/>
       <c r="F893" s="15"/>
     </row>
-    <row r="894" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="894" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C894" s="15"/>
       <c r="D894" s="15"/>
       <c r="E894" s="16"/>
       <c r="F894" s="15"/>
     </row>
-    <row r="895" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="895" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C895" s="15"/>
       <c r="D895" s="15"/>
       <c r="E895" s="16"/>
       <c r="F895" s="15"/>
     </row>
-    <row r="896" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="896" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C896" s="15"/>
       <c r="D896" s="15"/>
       <c r="E896" s="16"/>
       <c r="F896" s="15"/>
     </row>
-    <row r="897" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="897" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C897" s="15"/>
       <c r="D897" s="15"/>
       <c r="E897" s="16"/>
       <c r="F897" s="15"/>
     </row>
-    <row r="898" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="898" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C898" s="15"/>
       <c r="D898" s="15"/>
       <c r="E898" s="16"/>
       <c r="F898" s="15"/>
     </row>
-    <row r="899" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="899" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C899" s="15"/>
       <c r="D899" s="15"/>
       <c r="E899" s="16"/>
       <c r="F899" s="15"/>
     </row>
-    <row r="900" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="900" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C900" s="15"/>
       <c r="D900" s="15"/>
       <c r="E900" s="16"/>
       <c r="F900" s="15"/>
     </row>
-    <row r="901" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="901" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C901" s="15"/>
       <c r="D901" s="15"/>
       <c r="E901" s="16"/>
       <c r="F901" s="15"/>
     </row>
-    <row r="902" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="902" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C902" s="15"/>
       <c r="D902" s="15"/>
       <c r="E902" s="16"/>
       <c r="F902" s="15"/>
     </row>
-    <row r="903" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="903" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C903" s="15"/>
       <c r="D903" s="15"/>
       <c r="E903" s="16"/>
       <c r="F903" s="15"/>
     </row>
-    <row r="904" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="904" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C904" s="15"/>
       <c r="D904" s="15"/>
       <c r="E904" s="16"/>
       <c r="F904" s="15"/>
     </row>
-    <row r="905" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="905" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C905" s="15"/>
       <c r="D905" s="15"/>
       <c r="E905" s="16"/>
       <c r="F905" s="15"/>
     </row>
-    <row r="906" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="906" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C906" s="15"/>
       <c r="D906" s="15"/>
       <c r="E906" s="16"/>
       <c r="F906" s="15"/>
     </row>
-    <row r="907" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="907" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C907" s="15"/>
       <c r="D907" s="15"/>
       <c r="E907" s="16"/>
       <c r="F907" s="15"/>
     </row>
-    <row r="908" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="908" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C908" s="15"/>
       <c r="D908" s="15"/>
       <c r="E908" s="16"/>
       <c r="F908" s="15"/>
     </row>
-    <row r="909" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="909" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C909" s="15"/>
       <c r="D909" s="15"/>
       <c r="E909" s="16"/>
       <c r="F909" s="15"/>
     </row>
-    <row r="910" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="910" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C910" s="15"/>
       <c r="D910" s="15"/>
       <c r="E910" s="16"/>
       <c r="F910" s="15"/>
     </row>
-    <row r="911" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="911" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C911" s="15"/>
       <c r="D911" s="15"/>
       <c r="E911" s="16"/>
       <c r="F911" s="15"/>
     </row>
-    <row r="912" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="912" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C912" s="15"/>
       <c r="D912" s="15"/>
       <c r="E912" s="16"/>
       <c r="F912" s="15"/>
     </row>
-    <row r="913" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="913" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C913" s="15"/>
       <c r="D913" s="15"/>
       <c r="E913" s="16"/>
       <c r="F913" s="15"/>
     </row>
-    <row r="914" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="914" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C914" s="15"/>
       <c r="D914" s="15"/>
       <c r="E914" s="16"/>
       <c r="F914" s="15"/>
     </row>
-    <row r="915" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="915" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C915" s="15"/>
       <c r="D915" s="15"/>
       <c r="E915" s="16"/>
       <c r="F915" s="15"/>
     </row>
-    <row r="916" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="916" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C916" s="15"/>
       <c r="D916" s="15"/>
       <c r="E916" s="16"/>
       <c r="F916" s="15"/>
     </row>
-    <row r="917" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="917" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C917" s="15"/>
       <c r="D917" s="15"/>
       <c r="E917" s="16"/>
       <c r="F917" s="15"/>
     </row>
-    <row r="918" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="918" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C918" s="15"/>
       <c r="D918" s="15"/>
       <c r="E918" s="16"/>
       <c r="F918" s="15"/>
     </row>
-    <row r="919" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="919" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C919" s="15"/>
       <c r="D919" s="15"/>
       <c r="E919" s="16"/>
       <c r="F919" s="15"/>
     </row>
-    <row r="920" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="920" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C920" s="15"/>
       <c r="D920" s="15"/>
       <c r="E920" s="16"/>
       <c r="F920" s="15"/>
     </row>
-    <row r="921" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="921" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C921" s="15"/>
       <c r="D921" s="15"/>
       <c r="E921" s="16"/>
       <c r="F921" s="15"/>
     </row>
-    <row r="922" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="922" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C922" s="15"/>
       <c r="D922" s="15"/>
       <c r="E922" s="16"/>
       <c r="F922" s="15"/>
     </row>
-    <row r="923" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="923" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C923" s="15"/>
       <c r="D923" s="15"/>
       <c r="E923" s="16"/>
       <c r="F923" s="15"/>
     </row>
-    <row r="924" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="924" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C924" s="15"/>
       <c r="D924" s="15"/>
       <c r="E924" s="16"/>
       <c r="F924" s="15"/>
     </row>
-    <row r="925" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="925" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C925" s="15"/>
       <c r="D925" s="15"/>
       <c r="E925" s="16"/>
       <c r="F925" s="15"/>
     </row>
-    <row r="926" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="926" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C926" s="15"/>
       <c r="D926" s="15"/>
       <c r="E926" s="16"/>
       <c r="F926" s="15"/>
     </row>
-    <row r="927" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="927" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C927" s="15"/>
       <c r="D927" s="15"/>
       <c r="E927" s="16"/>
       <c r="F927" s="15"/>
     </row>
-    <row r="928" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="928" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C928" s="15"/>
       <c r="D928" s="15"/>
       <c r="E928" s="16"/>
       <c r="F928" s="15"/>
     </row>
-    <row r="929" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="929" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C929" s="15"/>
       <c r="D929" s="15"/>
       <c r="E929" s="16"/>
       <c r="F929" s="15"/>
     </row>
-    <row r="930" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="930" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C930" s="15"/>
       <c r="D930" s="15"/>
       <c r="E930" s="16"/>
       <c r="F930" s="15"/>
     </row>
-    <row r="931" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="931" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C931" s="15"/>
       <c r="D931" s="15"/>
       <c r="E931" s="16"/>
       <c r="F931" s="15"/>
     </row>
-    <row r="932" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="932" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C932" s="15"/>
       <c r="D932" s="15"/>
       <c r="E932" s="16"/>
       <c r="F932" s="15"/>
     </row>
-    <row r="933" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="933" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C933" s="15"/>
       <c r="D933" s="15"/>
       <c r="E933" s="16"/>
       <c r="F933" s="15"/>
     </row>
-    <row r="934" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="934" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C934" s="15"/>
       <c r="D934" s="15"/>
       <c r="E934" s="16"/>
       <c r="F934" s="15"/>
     </row>
-    <row r="935" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="935" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C935" s="15"/>
       <c r="D935" s="15"/>
       <c r="E935" s="16"/>
       <c r="F935" s="15"/>
     </row>
-    <row r="936" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="936" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C936" s="15"/>
       <c r="D936" s="15"/>
       <c r="E936" s="16"/>
       <c r="F936" s="15"/>
     </row>
-    <row r="937" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="937" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C937" s="15"/>
       <c r="D937" s="15"/>
       <c r="E937" s="16"/>
       <c r="F937" s="15"/>
     </row>
-    <row r="938" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="938" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C938" s="15"/>
       <c r="D938" s="15"/>
       <c r="E938" s="16"/>
       <c r="F938" s="15"/>
     </row>
-    <row r="939" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="939" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C939" s="15"/>
       <c r="D939" s="15"/>
       <c r="E939" s="16"/>
       <c r="F939" s="15"/>
     </row>
-    <row r="940" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="940" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C940" s="15"/>
       <c r="D940" s="15"/>
       <c r="E940" s="16"/>
       <c r="F940" s="15"/>
     </row>
-    <row r="941" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="941" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C941" s="15"/>
       <c r="D941" s="15"/>
       <c r="E941" s="16"/>
       <c r="F941" s="15"/>
     </row>
-    <row r="942" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="942" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C942" s="15"/>
       <c r="D942" s="15"/>
       <c r="E942" s="16"/>
       <c r="F942" s="15"/>
     </row>
-    <row r="943" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="943" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C943" s="15"/>
       <c r="D943" s="15"/>
       <c r="E943" s="16"/>
       <c r="F943" s="15"/>
     </row>
-    <row r="944" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="944" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C944" s="15"/>
       <c r="D944" s="15"/>
       <c r="E944" s="16"/>
       <c r="F944" s="15"/>
     </row>
-    <row r="945" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="945" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C945" s="15"/>
       <c r="D945" s="15"/>
       <c r="E945" s="16"/>
       <c r="F945" s="15"/>
     </row>
-    <row r="946" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="946" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C946" s="15"/>
       <c r="D946" s="15"/>
       <c r="E946" s="16"/>
       <c r="F946" s="15"/>
     </row>
-    <row r="947" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="947" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C947" s="15"/>
       <c r="D947" s="15"/>
       <c r="E947" s="16"/>
       <c r="F947" s="15"/>
     </row>
-    <row r="948" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="948" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C948" s="15"/>
       <c r="D948" s="15"/>
       <c r="E948" s="16"/>
       <c r="F948" s="15"/>
     </row>
-    <row r="949" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="949" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C949" s="15"/>
       <c r="D949" s="15"/>
       <c r="E949" s="16"/>
       <c r="F949" s="15"/>
     </row>
-    <row r="950" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="950" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C950" s="15"/>
       <c r="D950" s="15"/>
       <c r="E950" s="16"/>
       <c r="F950" s="15"/>
     </row>
-    <row r="951" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="951" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C951" s="15"/>
       <c r="D951" s="15"/>
       <c r="E951" s="16"/>
       <c r="F951" s="15"/>
     </row>
-    <row r="952" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="952" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C952" s="15"/>
       <c r="D952" s="15"/>
       <c r="E952" s="16"/>
       <c r="F952" s="15"/>
     </row>
-    <row r="953" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="953" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C953" s="15"/>
       <c r="D953" s="15"/>
       <c r="E953" s="16"/>
       <c r="F953" s="15"/>
     </row>
-    <row r="954" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="954" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C954" s="15"/>
       <c r="D954" s="15"/>
       <c r="E954" s="16"/>
       <c r="F954" s="15"/>
     </row>
-    <row r="955" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="955" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C955" s="15"/>
       <c r="D955" s="15"/>
       <c r="E955" s="16"/>
       <c r="F955" s="15"/>
     </row>
-    <row r="956" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="956" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C956" s="15"/>
       <c r="D956" s="15"/>
       <c r="E956" s="16"/>
       <c r="F956" s="15"/>
     </row>
-    <row r="957" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="957" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C957" s="15"/>
       <c r="D957" s="15"/>
       <c r="E957" s="16"/>
       <c r="F957" s="15"/>
     </row>
-    <row r="958" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="958" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C958" s="15"/>
       <c r="D958" s="15"/>
       <c r="E958" s="16"/>
       <c r="F958" s="15"/>
     </row>
-    <row r="959" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="959" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C959" s="15"/>
       <c r="D959" s="15"/>
       <c r="E959" s="16"/>
       <c r="F959" s="15"/>
     </row>
-    <row r="960" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="960" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C960" s="15"/>
       <c r="D960" s="15"/>
       <c r="E960" s="16"/>
       <c r="F960" s="15"/>
     </row>
-    <row r="961" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="961" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C961" s="15"/>
       <c r="D961" s="15"/>
       <c r="E961" s="16"/>
       <c r="F961" s="15"/>
     </row>
-    <row r="962" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="962" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C962" s="15"/>
       <c r="D962" s="15"/>
       <c r="E962" s="16"/>
       <c r="F962" s="15"/>
     </row>
-    <row r="963" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="963" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C963" s="15"/>
       <c r="D963" s="15"/>
       <c r="E963" s="16"/>
       <c r="F963" s="15"/>
     </row>
-    <row r="964" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="964" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C964" s="15"/>
       <c r="D964" s="15"/>
       <c r="E964" s="16"/>
       <c r="F964" s="15"/>
     </row>
-    <row r="965" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="965" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C965" s="15"/>
       <c r="D965" s="15"/>
       <c r="E965" s="16"/>
       <c r="F965" s="15"/>
     </row>
-    <row r="966" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="966" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C966" s="15"/>
       <c r="D966" s="15"/>
       <c r="E966" s="16"/>
       <c r="F966" s="15"/>
     </row>
-    <row r="967" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="967" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C967" s="15"/>
       <c r="D967" s="15"/>
       <c r="E967" s="16"/>
       <c r="F967" s="15"/>
     </row>
-    <row r="968" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="968" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C968" s="15"/>
       <c r="D968" s="15"/>
       <c r="E968" s="16"/>
       <c r="F968" s="15"/>
     </row>
-    <row r="969" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="969" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C969" s="15"/>
       <c r="D969" s="15"/>
       <c r="E969" s="16"/>
       <c r="F969" s="15"/>
     </row>
-    <row r="970" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="970" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C970" s="15"/>
       <c r="D970" s="15"/>
       <c r="E970" s="16"/>
       <c r="F970" s="15"/>
     </row>
-    <row r="971" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="971" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C971" s="15"/>
       <c r="D971" s="15"/>
       <c r="E971" s="16"/>
       <c r="F971" s="15"/>
     </row>
-    <row r="972" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="972" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C972" s="15"/>
       <c r="D972" s="15"/>
       <c r="E972" s="16"/>
       <c r="F972" s="15"/>
     </row>
-    <row r="973" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="973" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C973" s="15"/>
       <c r="D973" s="15"/>
       <c r="E973" s="16"/>
       <c r="F973" s="15"/>
     </row>
-    <row r="974" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="974" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C974" s="15"/>
       <c r="D974" s="15"/>
       <c r="E974" s="16"/>
       <c r="F974" s="15"/>
     </row>
-    <row r="975" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="975" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C975" s="15"/>
       <c r="D975" s="15"/>
       <c r="E975" s="16"/>
       <c r="F975" s="15"/>
     </row>
-    <row r="976" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="976" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C976" s="15"/>
       <c r="D976" s="15"/>
       <c r="E976" s="16"/>
       <c r="F976" s="15"/>
     </row>
-    <row r="977" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="977" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C977" s="15"/>
       <c r="D977" s="15"/>
       <c r="E977" s="16"/>
       <c r="F977" s="15"/>
     </row>
-    <row r="978" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="978" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C978" s="15"/>
       <c r="D978" s="15"/>
       <c r="E978" s="16"/>
       <c r="F978" s="15"/>
     </row>
-    <row r="979" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="979" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C979" s="15"/>
       <c r="D979" s="15"/>
       <c r="E979" s="16"/>
       <c r="F979" s="15"/>
     </row>
-    <row r="980" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="980" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C980" s="15"/>
       <c r="D980" s="15"/>
       <c r="E980" s="16"/>
       <c r="F980" s="15"/>
     </row>
-    <row r="981" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="981" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C981" s="15"/>
       <c r="D981" s="15"/>
       <c r="E981" s="16"/>
       <c r="F981" s="15"/>
     </row>
-    <row r="982" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="982" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C982" s="15"/>
       <c r="D982" s="15"/>
       <c r="E982" s="16"/>
       <c r="F982" s="15"/>
     </row>
-    <row r="983" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="983" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C983" s="15"/>
       <c r="D983" s="15"/>
       <c r="E983" s="16"/>
       <c r="F983" s="15"/>
     </row>
-    <row r="984" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="984" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C984" s="15"/>
       <c r="D984" s="15"/>
       <c r="E984" s="16"/>
       <c r="F984" s="15"/>
     </row>
-    <row r="985" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="985" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C985" s="15"/>
       <c r="D985" s="15"/>
       <c r="E985" s="16"/>
       <c r="F985" s="15"/>
     </row>
-    <row r="986" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="986" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C986" s="15"/>
       <c r="D986" s="15"/>
       <c r="E986" s="16"/>
       <c r="F986" s="15"/>
     </row>
-    <row r="987" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="987" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C987" s="15"/>
       <c r="D987" s="15"/>
       <c r="E987" s="16"/>
       <c r="F987" s="15"/>
     </row>
-    <row r="988" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="988" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C988" s="15"/>
       <c r="D988" s="15"/>
       <c r="E988" s="16"/>
       <c r="F988" s="15"/>
     </row>
-    <row r="989" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="989" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C989" s="15"/>
       <c r="D989" s="15"/>
       <c r="E989" s="16"/>
       <c r="F989" s="15"/>
     </row>
-    <row r="990" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="990" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C990" s="15"/>
       <c r="D990" s="15"/>
       <c r="E990" s="16"/>
       <c r="F990" s="15"/>
     </row>
-    <row r="991" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="991" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C991" s="15"/>
       <c r="D991" s="15"/>
       <c r="E991" s="16"/>
       <c r="F991" s="15"/>
     </row>
-    <row r="992" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="992" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C992" s="15"/>
       <c r="D992" s="15"/>
       <c r="E992" s="16"/>
       <c r="F992" s="15"/>
     </row>
-    <row r="993" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="993" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C993" s="15"/>
       <c r="D993" s="15"/>
       <c r="E993" s="16"/>
       <c r="F993" s="15"/>
     </row>
-    <row r="994" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="994" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C994" s="15"/>
       <c r="D994" s="15"/>
       <c r="E994" s="16"/>
       <c r="F994" s="15"/>
     </row>
-    <row r="995" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="995" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C995" s="15"/>
       <c r="D995" s="15"/>
       <c r="E995" s="16"/>
       <c r="F995" s="15"/>
     </row>
-    <row r="996" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="996" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C996" s="15"/>
       <c r="D996" s="15"/>
       <c r="E996" s="16"/>
       <c r="F996" s="15"/>
     </row>
-    <row r="997" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="997" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C997" s="15"/>
       <c r="D997" s="15"/>
       <c r="E997" s="16"/>
       <c r="F997" s="15"/>
     </row>
-    <row r="998" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="998" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C998" s="15"/>
       <c r="D998" s="15"/>
       <c r="E998" s="16"/>
       <c r="F998" s="15"/>
     </row>
-    <row r="999" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="999" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C999" s="15"/>
       <c r="D999" s="15"/>
       <c r="E999" s="16"/>
       <c r="F999" s="15"/>
     </row>
-    <row r="1000" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="1000" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C1000" s="15"/>
       <c r="D1000" s="15"/>
       <c r="E1000" s="16"/>
@@ -9582,51 +9582,51 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AQ70"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="31.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="31.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.453125" style="1" customWidth="1"/>
     <col min="3" max="3" width="38" style="1" customWidth="1"/>
-    <col min="4" max="4" width="38.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="38.1796875" style="1" customWidth="1"/>
     <col min="5" max="5" width="15" style="1" customWidth="1"/>
-    <col min="6" max="6" width="31.42578125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="31.453125" style="1" customWidth="1"/>
     <col min="7" max="7" width="38" style="1" customWidth="1"/>
-    <col min="8" max="8" width="9.5703125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="26.42578125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="31.5703125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="32.42578125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="29.42578125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="19.42578125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="106.85546875" style="1" customWidth="1"/>
-    <col min="16" max="16" width="21.140625" style="1" customWidth="1"/>
-    <col min="17" max="17" width="26.140625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="10.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9.54296875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="26.453125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="31.54296875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="32.453125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="14.54296875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="29.453125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="19.453125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="106.81640625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="21.1796875" style="1" customWidth="1"/>
+    <col min="17" max="17" width="26.1796875" style="1" customWidth="1"/>
+    <col min="18" max="18" width="10.54296875" style="1" customWidth="1"/>
     <col min="19" max="20" width="23" style="1" customWidth="1"/>
-    <col min="21" max="21" width="12.42578125" style="1" customWidth="1"/>
-    <col min="22" max="22" width="29.85546875" style="1" customWidth="1"/>
-    <col min="23" max="23" width="15.140625" style="1" customWidth="1"/>
-    <col min="24" max="24" width="16.5703125" style="1" customWidth="1"/>
-    <col min="25" max="25" width="35.42578125" style="1" customWidth="1"/>
+    <col min="21" max="21" width="12.453125" style="1" customWidth="1"/>
+    <col min="22" max="22" width="29.81640625" style="1" customWidth="1"/>
+    <col min="23" max="23" width="15.1796875" style="1" customWidth="1"/>
+    <col min="24" max="24" width="16.54296875" style="1" customWidth="1"/>
+    <col min="25" max="25" width="35.453125" style="1" customWidth="1"/>
     <col min="26" max="27" width="23" style="1" customWidth="1"/>
-    <col min="28" max="28" width="33.85546875" style="1" customWidth="1"/>
-    <col min="29" max="29" width="16.5703125" style="1" customWidth="1"/>
+    <col min="28" max="28" width="33.81640625" style="1" customWidth="1"/>
+    <col min="29" max="29" width="16.54296875" style="1" customWidth="1"/>
     <col min="30" max="30" width="23" style="1" customWidth="1"/>
-    <col min="31" max="31" width="28.42578125" style="1" customWidth="1"/>
-    <col min="32" max="32" width="8.5703125" style="1" customWidth="1"/>
-    <col min="33" max="33" width="20.85546875" style="1" customWidth="1"/>
-    <col min="34" max="34" width="16.5703125" style="1" customWidth="1"/>
-    <col min="35" max="35" width="26.140625" style="1" customWidth="1"/>
-    <col min="36" max="36" width="27.5703125" style="1" customWidth="1"/>
-    <col min="37" max="37" width="22.85546875" style="1" customWidth="1"/>
-    <col min="38" max="38" width="38.140625" style="1" customWidth="1"/>
-    <col min="39" max="39" width="38.140625" style="5" customWidth="1"/>
-    <col min="40" max="40" width="18.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="17.28515625" style="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="31" max="31" width="28.453125" style="1" customWidth="1"/>
+    <col min="32" max="32" width="8.54296875" style="1" customWidth="1"/>
+    <col min="33" max="33" width="20.81640625" style="1" customWidth="1"/>
+    <col min="34" max="34" width="16.54296875" style="1" customWidth="1"/>
+    <col min="35" max="35" width="26.1796875" style="1" customWidth="1"/>
+    <col min="36" max="36" width="27.54296875" style="1" customWidth="1"/>
+    <col min="37" max="37" width="22.81640625" style="1" customWidth="1"/>
+    <col min="38" max="38" width="38.1796875" style="1" customWidth="1"/>
+    <col min="39" max="39" width="38.1796875" style="5" customWidth="1"/>
+    <col min="40" max="40" width="18.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="17.26953125" style="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:43" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -9755,7 +9755,7 @@
       </c>
       <c r="AQ1" s="2"/>
     </row>
-    <row r="2" spans="1:43" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:43" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="12" t="s">
         <v>39</v>
       </c>
@@ -9884,7 +9884,7 @@
       </c>
       <c r="AQ2" s="2"/>
     </row>
-    <row r="3" spans="1:43" ht="105" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:43" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>78</v>
       </c>
@@ -9984,7 +9984,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:43" ht="60" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:43" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>92</v>
       </c>
@@ -10084,7 +10084,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:43" ht="105" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:43" ht="87" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>100</v>
       </c>
@@ -10183,7 +10183,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:43" ht="75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:43" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>857</v>
       </c>
@@ -10283,7 +10283,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:43" ht="90" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:43" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>856</v>
       </c>
@@ -10380,7 +10380,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:43" ht="90" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:43" ht="87" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>114</v>
       </c>
@@ -10477,7 +10477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:43" ht="135" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:43" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>124</v>
       </c>
@@ -10556,7 +10556,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:43" ht="90" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:43" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>130</v>
       </c>
@@ -10644,7 +10644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:43" ht="60" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:43" ht="58" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>137</v>
       </c>
@@ -10693,7 +10693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:43" ht="60" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:43" ht="58" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>145</v>
       </c>
@@ -10760,7 +10760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:43" ht="60" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:43" ht="58" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>153</v>
       </c>
@@ -10833,7 +10833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:43" ht="90" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:43" ht="87" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>162</v>
       </c>
@@ -10945,7 +10945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:43" ht="120" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:43" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>174</v>
       </c>
@@ -11045,7 +11045,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:43" ht="60" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:43" ht="58" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>185</v>
       </c>
@@ -11130,7 +11130,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:42" ht="45" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:42" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>193</v>
       </c>
@@ -11215,7 +11215,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:42" ht="60" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:42" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
         <v>201</v>
       </c>
@@ -11282,7 +11282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:42" ht="60" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:42" ht="58" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>208</v>
       </c>
@@ -11361,7 +11361,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:42" ht="60" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:42" ht="58" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
         <v>216</v>
       </c>
@@ -11440,7 +11440,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:42" ht="60" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:42" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
         <v>221</v>
       </c>
@@ -11513,7 +11513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:42" ht="45" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:42" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
         <v>226</v>
       </c>
@@ -11553,7 +11553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:42" ht="45" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:42" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>232</v>
       </c>
@@ -11626,7 +11626,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:42" ht="75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:42" ht="58" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>238</v>
       </c>
@@ -11693,7 +11693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:42" ht="45" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:42" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>247</v>
       </c>
@@ -11757,7 +11757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:42" ht="45" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:42" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>255</v>
       </c>
@@ -11815,7 +11815,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:42" ht="45" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:42" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
         <v>264</v>
       </c>
@@ -11885,7 +11885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:42" ht="45" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:42" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
         <v>273</v>
       </c>
@@ -11961,7 +11961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:42" ht="60" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:42" ht="58" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
         <v>281</v>
       </c>
@@ -12034,7 +12034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:42" ht="45" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:42" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
         <v>291</v>
       </c>
@@ -12113,7 +12113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:42" ht="45" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:42" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
         <v>301</v>
       </c>
@@ -12186,7 +12186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:42" ht="45" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:42" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
         <v>312</v>
       </c>
@@ -12206,7 +12206,7 @@
         <v>855</v>
       </c>
       <c r="H32" s="1">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>112</v>
@@ -12259,7 +12259,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:42" ht="60" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:42" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
         <v>318</v>
       </c>
@@ -12326,7 +12326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:42" ht="45" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:42" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
         <v>327</v>
       </c>
@@ -12393,7 +12393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:42" ht="45" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:42" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
         <v>336</v>
       </c>
@@ -12439,7 +12439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:42" ht="45" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:42" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="s">
         <v>341</v>
       </c>
@@ -12500,7 +12500,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:42" ht="60" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:42" ht="58" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
         <v>347</v>
       </c>
@@ -12570,7 +12570,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:42" ht="60" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:42" ht="58" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
         <v>359</v>
       </c>
@@ -12643,7 +12643,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:42" ht="60" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:42" ht="58" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
         <v>363</v>
       </c>
@@ -12713,7 +12713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:42" ht="60" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:42" ht="58" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
         <v>371</v>
       </c>
@@ -12783,7 +12783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:42" ht="45" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:42" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
         <v>376</v>
       </c>
@@ -12853,7 +12853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:42" ht="45" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:42" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
         <v>383</v>
       </c>
@@ -12920,7 +12920,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:42" ht="45" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:42" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
         <v>388</v>
       </c>
@@ -12996,7 +12996,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:42" ht="45" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:42" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
         <v>396</v>
       </c>
@@ -13054,7 +13054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:42" ht="45" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:42" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
         <v>403</v>
       </c>
@@ -13127,7 +13127,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:42" ht="60" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:42" ht="58" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
         <v>408</v>
       </c>
@@ -13188,7 +13188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:42" ht="45" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:42" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
         <v>416</v>
       </c>
@@ -13237,7 +13237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:42" ht="90" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:42" ht="87" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
         <v>423</v>
       </c>
@@ -13322,7 +13322,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:42" ht="75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:42" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
         <v>435</v>
       </c>
@@ -13410,7 +13410,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:42" ht="60" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:42" ht="58" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
         <v>446</v>
       </c>
@@ -13507,7 +13507,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:42" ht="90" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:42" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
         <v>456</v>
       </c>
@@ -13598,7 +13598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:42" ht="75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:42" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
         <v>469</v>
       </c>
@@ -13686,7 +13686,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:42" ht="135" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:42" ht="116" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
         <v>482</v>
       </c>
@@ -13767,7 +13767,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:42" ht="60" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:42" ht="58" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
         <v>493</v>
       </c>
@@ -13846,7 +13846,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:42" ht="45" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:42" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
         <v>507</v>
       </c>
@@ -13898,7 +13898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:42" ht="45" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:42" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
         <v>512</v>
       </c>
@@ -13950,7 +13950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:42" ht="105" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:42" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
         <v>517</v>
       </c>
@@ -14038,7 +14038,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:42" ht="60" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:42" ht="58" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
         <v>530</v>
       </c>
@@ -14114,7 +14114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:42" ht="45" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:42" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
         <v>540</v>
       </c>
@@ -14193,7 +14193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:42" ht="60" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:42" ht="58" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
         <v>547</v>
       </c>
@@ -14272,7 +14272,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:42" ht="45" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:42" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
         <v>553</v>
       </c>
@@ -14345,7 +14345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:42" ht="45" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:42" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="s">
         <v>559</v>
       </c>
@@ -14415,7 +14415,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:42" ht="45" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:42" ht="29" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="s">
         <v>568</v>
       </c>
@@ -14485,7 +14485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:42" ht="45" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:42" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A64" s="4" t="s">
         <v>576</v>
       </c>
@@ -14540,7 +14540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:42" ht="45" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:42" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
         <v>581</v>
       </c>
@@ -14589,7 +14589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:42" ht="60" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:42" ht="58" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
         <v>586</v>
       </c>
@@ -14647,7 +14647,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:42" ht="45" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:42" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
         <v>594</v>
       </c>
@@ -14717,7 +14717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:42" ht="30" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:42" ht="29" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="s">
         <v>599</v>
       </c>
@@ -14793,7 +14793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:42" ht="45" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:42" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A69" s="4" t="s">
         <v>603</v>
       </c>
@@ -14866,7 +14866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A70"/>
       <c r="B70"/>
       <c r="C70"/>
@@ -15094,18 +15094,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D9BDE37-5F7B-4201-93B0-778CBF578919}">
   <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="48.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="76.140625" customWidth="1"/>
+    <col min="1" max="1" width="48.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="76.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="20" t="s">
         <v>618</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="21" t="s">
         <v>619</v>
       </c>
@@ -15113,7 +15113,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
         <v>621</v>
       </c>
@@ -15121,7 +15121,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
         <v>623</v>
       </c>
@@ -15129,7 +15129,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
         <v>625</v>
       </c>
@@ -15137,7 +15137,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
         <v>627</v>
       </c>
@@ -15145,7 +15145,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>842</v>
       </c>
@@ -15171,7 +15171,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>853</v>
       </c>
@@ -15190,26 +15190,26 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0493E6C7-5A74-4B2C-B0DD-75AC2A3DE532}">
   <dimension ref="A1:E81"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="70.42578125" customWidth="1"/>
-    <col min="2" max="2" width="76.140625" customWidth="1"/>
-    <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="57.140625" customWidth="1"/>
+    <col min="1" max="1" width="70.453125" customWidth="1"/>
+    <col min="2" max="2" width="76.1796875" customWidth="1"/>
+    <col min="3" max="3" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="57.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="298.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="298.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A1" s="17" t="s">
         <v>629</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="17" x14ac:dyDescent="0.4">
       <c r="A3" s="18" t="s">
         <v>630</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="9" t="s">
         <v>631</v>
       </c>
@@ -15217,7 +15217,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
         <v>633</v>
       </c>
@@ -15225,7 +15225,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
         <v>635</v>
       </c>
@@ -15233,7 +15233,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
         <v>637</v>
       </c>
@@ -15241,12 +15241,12 @@
         <v>638</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="19" t="s">
         <v>639</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="13" t="s">
         <v>640</v>
       </c>
@@ -15263,7 +15263,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>39</v>
       </c>
@@ -15280,7 +15280,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>40</v>
       </c>
@@ -15297,7 +15297,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>41</v>
       </c>
@@ -15314,7 +15314,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>42</v>
       </c>
@@ -15331,7 +15331,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>43</v>
       </c>
@@ -15348,7 +15348,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>44</v>
       </c>
@@ -15365,7 +15365,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>45</v>
       </c>
@@ -15382,7 +15382,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>46</v>
       </c>
@@ -15399,7 +15399,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>47</v>
       </c>
@@ -15416,7 +15416,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>48</v>
       </c>
@@ -15433,7 +15433,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -15450,7 +15450,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>50</v>
       </c>
@@ -15467,7 +15467,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>51</v>
       </c>
@@ -15484,7 +15484,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>52</v>
       </c>
@@ -15501,7 +15501,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>53</v>
       </c>
@@ -15518,7 +15518,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>54</v>
       </c>
@@ -15535,7 +15535,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>55</v>
       </c>
@@ -15552,7 +15552,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>56</v>
       </c>
@@ -15569,7 +15569,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>57</v>
       </c>
@@ -15586,7 +15586,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>58</v>
       </c>
@@ -15603,7 +15603,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>59</v>
       </c>
@@ -15620,7 +15620,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>60</v>
       </c>
@@ -15637,7 +15637,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>61</v>
       </c>
@@ -15654,7 +15654,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>62</v>
       </c>
@@ -15671,7 +15671,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>63</v>
       </c>
@@ -15688,7 +15688,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>64</v>
       </c>
@@ -15705,7 +15705,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>65</v>
       </c>
@@ -15722,7 +15722,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>66</v>
       </c>
@@ -15739,7 +15739,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>67</v>
       </c>
@@ -15756,7 +15756,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>68</v>
       </c>
@@ -15773,7 +15773,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>69</v>
       </c>
@@ -15790,7 +15790,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>70</v>
       </c>
@@ -15807,7 +15807,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>71</v>
       </c>
@@ -15824,7 +15824,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>72</v>
       </c>
@@ -15841,7 +15841,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>73</v>
       </c>
@@ -15858,7 +15858,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>74</v>
       </c>
@@ -15875,7 +15875,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>75</v>
       </c>
@@ -15892,7 +15892,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>76</v>
       </c>
@@ -15909,7 +15909,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>77</v>
       </c>
@@ -15926,12 +15926,12 @@
         <v>692</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" ht="17" x14ac:dyDescent="0.4">
       <c r="A51" s="18" t="s">
         <v>693</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" s="9" t="s">
         <v>631</v>
       </c>
@@ -15939,7 +15939,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" s="9" t="s">
         <v>633</v>
       </c>
@@ -15947,7 +15947,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" s="9" t="s">
         <v>635</v>
       </c>
@@ -15955,7 +15955,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" s="9" t="s">
         <v>697</v>
       </c>
@@ -15963,12 +15963,12 @@
         <v>698</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" s="19" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" s="13" t="s">
         <v>640</v>
       </c>
@@ -15985,7 +15985,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>613</v>
       </c>
@@ -16002,7 +16002,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>39</v>
       </c>
@@ -16019,7 +16019,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>614</v>
       </c>
@@ -16036,7 +16036,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>615</v>
       </c>
@@ -16053,7 +16053,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>616</v>
       </c>
@@ -16070,7 +16070,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>617</v>
       </c>
@@ -16087,27 +16087,27 @@
         <v>706</v>
       </c>
     </row>
-    <row r="66" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:2" ht="17" x14ac:dyDescent="0.4">
       <c r="A66" s="18" t="s">
         <v>707</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>708</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>709</v>
       </c>
     </row>
-    <row r="70" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:2" ht="17" x14ac:dyDescent="0.4">
       <c r="A70" s="18" t="s">
         <v>710</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" s="9" t="s">
         <v>711</v>
       </c>
@@ -16115,7 +16115,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" s="9" t="s">
         <v>713</v>
       </c>
@@ -16123,7 +16123,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" s="9" t="s">
         <v>715</v>
       </c>
@@ -16131,7 +16131,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" s="9" t="s">
         <v>717</v>
       </c>
@@ -16139,12 +16139,12 @@
         <v>718</v>
       </c>
     </row>
-    <row r="76" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:2" ht="17" x14ac:dyDescent="0.4">
       <c r="A76" s="18" t="s">
         <v>719</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" s="9">
         <v>1</v>
       </c>
@@ -16152,7 +16152,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" s="9">
         <v>2</v>
       </c>
@@ -16160,7 +16160,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" s="9">
         <v>3</v>
       </c>
@@ -16168,7 +16168,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" s="9">
         <v>4</v>
       </c>
@@ -16176,7 +16176,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" s="9">
         <v>5</v>
       </c>
@@ -16190,27 +16190,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d56b9130-d22a-480d-bb83-f34040f04d96">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Notes xmlns="d56b9130-d22a-480d-bb83-f34040f04d96" xsi:nil="true"/>
-    <TaxCatchAll xmlns="dd8606a3-d959-45f7-996e-3c98d970357c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010026B67AE13FBD584ABEFCF026840CED6F" ma:contentTypeVersion="21" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="11ebdf7d5c906124ef40ef85c2b08d8b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d56b9130-d22a-480d-bb83-f34040f04d96" xmlns:ns3="dd8606a3-d959-45f7-996e-3c98d970357c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="395e369db30c2620103728840cc29626" ns2:_="" ns3:_="">
     <xsd:import namespace="d56b9130-d22a-480d-bb83-f34040f04d96"/>
@@ -16479,10 +16458,42 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d56b9130-d22a-480d-bb83-f34040f04d96">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Notes xmlns="d56b9130-d22a-480d-bb83-f34040f04d96" xsi:nil="true"/>
+    <TaxCatchAll xmlns="dd8606a3-d959-45f7-996e-3c98d970357c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D4B7956-BCA0-46CA-BF6B-C7215DA15D81}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E038410E-E6A9-42FC-B223-5F20C9C2E8EB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="d56b9130-d22a-480d-bb83-f34040f04d96"/>
+    <ds:schemaRef ds:uri="dd8606a3-d959-45f7-996e-3c98d970357c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -16505,20 +16516,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E038410E-E6A9-42FC-B223-5F20C9C2E8EB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D4B7956-BCA0-46CA-BF6B-C7215DA15D81}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="d56b9130-d22a-480d-bb83-f34040f04d96"/>
-    <ds:schemaRef ds:uri="dd8606a3-d959-45f7-996e-3c98d970357c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>